--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94DF9CDB-D5CC-44BE-AAEA-245C48D89D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD75E5A-AC9A-45EE-BDB4-60B7CFFAB520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="464">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -1154,18 +1154,12 @@
     <t>Abdellah azzedine</t>
   </si>
   <si>
-    <t>cite 720 aadl bt15 n35</t>
-  </si>
-  <si>
     <t>2025177212</t>
   </si>
   <si>
     <t>Haoua hicham</t>
   </si>
   <si>
-    <t>cite 720 aadl bt17 n37</t>
-  </si>
-  <si>
     <t>NB(064/2026)</t>
   </si>
   <si>
@@ -1175,9 +1169,6 @@
     <t>Logt fonction laissaoui houaria</t>
   </si>
   <si>
-    <t>lycee bousmaha med chorfa</t>
-  </si>
-  <si>
     <t>NB(067/2026)</t>
   </si>
   <si>
@@ -1190,18 +1181,12 @@
     <t>Medjadji antar</t>
   </si>
   <si>
-    <t>cite 500 aadl bt38 n02</t>
-  </si>
-  <si>
     <t>2025177214</t>
   </si>
   <si>
     <t>Saoudi hamid</t>
   </si>
   <si>
-    <t>cite 720 aadl bt14 n28</t>
-  </si>
-  <si>
     <t>B42060</t>
   </si>
   <si>
@@ -1223,12 +1208,6 @@
     <t>Boutaleb ouahiba</t>
   </si>
   <si>
-    <t>cite 720 aadl bt10 n37</t>
-  </si>
-  <si>
-    <t>cite 720 aadl bt10 n9</t>
-  </si>
-  <si>
     <t>NB(072/2026)</t>
   </si>
   <si>
@@ -1307,9 +1286,6 @@
     <t>Guesmi mahdjoub</t>
   </si>
   <si>
-    <t>cite 720 aadl bt6 n15</t>
-  </si>
-  <si>
     <t>B40226</t>
   </si>
   <si>
@@ -1428,13 +1404,103 @@
   </si>
   <si>
     <t>2025177508</t>
+  </si>
+  <si>
+    <t>B40473</t>
+  </si>
+  <si>
+    <t>2025177302</t>
+  </si>
+  <si>
+    <t>B40474</t>
+  </si>
+  <si>
+    <t>2025177310</t>
+  </si>
+  <si>
+    <t>B40482</t>
+  </si>
+  <si>
+    <t>2025177304</t>
+  </si>
+  <si>
+    <t>B21504</t>
+  </si>
+  <si>
+    <t>2025177307</t>
+  </si>
+  <si>
+    <t>B21503</t>
+  </si>
+  <si>
+    <t>2025177301</t>
+  </si>
+  <si>
+    <t>2025177306</t>
+  </si>
+  <si>
+    <t>NB(517/2025)</t>
+  </si>
+  <si>
+    <t>Baghdadi billel</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt6 n32</t>
+  </si>
+  <si>
+    <t>2025177303</t>
+  </si>
+  <si>
+    <t>Zemir samir</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt7 n15</t>
+  </si>
+  <si>
+    <t>NB(707/2025)</t>
+  </si>
+  <si>
+    <t>2025177309</t>
+  </si>
+  <si>
+    <t>Madani fateh</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt7 n5</t>
+  </si>
+  <si>
+    <t>NB(703/2025)</t>
+  </si>
+  <si>
+    <t>2025177305</t>
+  </si>
+  <si>
+    <t>Bouzidi bachir</t>
+  </si>
+  <si>
+    <t>NB(081/2026)</t>
+  </si>
+  <si>
+    <t>2025177308</t>
+  </si>
+  <si>
+    <t>Noui sihem</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt1 n10</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt15 n36</t>
+  </si>
+  <si>
+    <t>NB(535/2025)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1518,6 +1584,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1586,7 +1658,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1666,6 +1738,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6121,7 +6202,7 @@
       <c r="J2" s="24"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -6143,7 +6224,7 @@
       <c r="J3" s="24"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -6183,7 +6264,7 @@
       <c r="J5" s="24"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7524,23 +7605,21 @@
         <v>18</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E54" s="15">
         <v>46063</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G54" s="17">
         <v>1</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>365</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="I54" s="4"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="12">
@@ -7568,9 +7647,7 @@
       <c r="H55" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="I55" s="4" t="s">
-        <v>350</v>
-      </c>
+      <c r="I55" s="4"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="12">
@@ -7584,23 +7661,21 @@
         <v>18</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E56" s="15">
         <v>46064</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G56" s="17">
         <v>1</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="I56" s="4" t="s">
-        <v>353</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="I56" s="4"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="12">
@@ -7614,23 +7689,21 @@
         <v>18</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E57" s="15">
         <v>46065</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G57" s="17">
         <v>1</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="I57" s="20" t="s">
-        <v>357</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="I57" s="20"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="12">
@@ -7644,23 +7717,21 @@
         <v>18</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E58" s="15">
         <v>46065</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G58" s="17">
         <v>1</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="I58" s="4" t="s">
-        <v>362</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="I58" s="4"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="12">
@@ -7668,13 +7739,13 @@
         <v>53</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C59" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E59" s="15">
         <v>46068</v>
@@ -7700,23 +7771,21 @@
         <v>18</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E60" s="15">
         <v>46069</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="G60" s="17">
         <v>1</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="I60" s="4" t="s">
-        <v>374</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="I60" s="4"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="12">
@@ -7730,23 +7799,21 @@
         <v>18</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E61" s="15">
         <v>46069</v>
       </c>
       <c r="F61" s="16" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="G61" s="17">
         <v>1</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>373</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="I61" s="4"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="12">
@@ -7754,13 +7821,13 @@
         <v>56</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="C62" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="E62" s="15">
         <v>46069</v>
@@ -7779,13 +7846,13 @@
         <v>57</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="C63" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="E63" s="15">
         <v>46069</v>
@@ -7805,13 +7872,13 @@
         <v>58</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="C64" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="E64" s="15">
         <v>46069</v>
@@ -7831,13 +7898,13 @@
         <v>59</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="C65" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="E65" s="15">
         <v>46069</v>
@@ -7857,13 +7924,13 @@
         <v>60</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C66" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="E66" s="15">
         <v>46069</v>
@@ -7882,13 +7949,13 @@
         <v>61</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C67" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="E67" s="15">
         <v>46069</v>
@@ -7908,13 +7975,13 @@
         <v>62</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="C68" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="E68" s="15">
         <v>46069</v>
@@ -7933,13 +8000,13 @@
         <v>63</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="C69" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="E69" s="15">
         <v>46069</v>
@@ -7959,13 +8026,13 @@
         <v>64</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C70" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="E70" s="15">
         <v>46069</v>
@@ -7985,13 +8052,13 @@
         <v>65</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="C71" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="E71" s="15">
         <v>46069</v>
@@ -8010,13 +8077,13 @@
         <v>66</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C72" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E72" s="15">
         <v>46070</v>
@@ -8041,23 +8108,21 @@
         <v>18</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="E73" s="15">
         <v>46070</v>
       </c>
       <c r="F73" s="16" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="G73" s="17">
         <v>1</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="I73" s="4" t="s">
-        <v>401</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="I73" s="4"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="12">
@@ -8065,13 +8130,13 @@
         <v>68</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C74" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="E74" s="15">
         <v>46070</v>
@@ -8090,13 +8155,13 @@
         <v>69</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C75" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="E75" s="15">
         <v>46070</v>
@@ -8115,13 +8180,13 @@
         <v>70</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C76" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="E76" s="15">
         <v>46070</v>
@@ -8140,13 +8205,13 @@
         <v>71</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C77" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="E77" s="15">
         <v>46070</v>
@@ -8165,13 +8230,13 @@
         <v>72</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C78" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E78" s="15">
         <v>46070</v>
@@ -8190,13 +8255,13 @@
         <v>73</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C79" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="E79" s="15">
         <v>46070</v>
@@ -8215,13 +8280,13 @@
         <v>74</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="C80" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E80" s="15">
         <v>46070</v>
@@ -8240,13 +8305,13 @@
         <v>75</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C81" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="E81" s="15">
         <v>46070</v>
@@ -8265,13 +8330,13 @@
         <v>76</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="C82" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E82" s="15">
         <v>46070</v>
@@ -8290,13 +8355,13 @@
         <v>77</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C83" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="E83" s="15">
         <v>46070</v>
@@ -8315,13 +8380,13 @@
         <v>78</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C84" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="E84" s="15">
         <v>46071</v>
@@ -8340,13 +8405,13 @@
         <v>79</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="C85" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="E85" s="15">
         <v>46071</v>
@@ -8365,13 +8430,13 @@
         <v>80</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="C86" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="E86" s="15">
         <v>46071</v>
@@ -8390,13 +8455,13 @@
         <v>81</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="C87" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="E87" s="15">
         <v>46071</v>
@@ -8415,13 +8480,13 @@
         <v>82</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C88" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="E88" s="15">
         <v>46071</v>
@@ -8440,13 +8505,13 @@
         <v>83</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C89" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D89" s="14" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="E89" s="15">
         <v>46071</v>
@@ -8465,13 +8530,13 @@
         <v>84</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C90" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="E90" s="15">
         <v>46071</v>
@@ -8490,13 +8555,13 @@
         <v>85</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="C91" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E91" s="15">
         <v>46071</v>
@@ -8515,13 +8580,13 @@
         <v>86</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C92" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="E92" s="15">
         <v>46071</v>
@@ -8540,13 +8605,13 @@
         <v>87</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C93" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D93" s="14" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="E93" s="15">
         <v>46071</v>
@@ -8564,11 +8629,21 @@
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="B94" s="15"/>
-      <c r="C94" s="13"/>
-      <c r="D94" s="14"/>
-      <c r="E94" s="15"/>
-      <c r="F94" s="16"/>
+      <c r="B94" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D94" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="E94" s="15">
+        <v>46072</v>
+      </c>
+      <c r="F94" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G94" s="17">
         <v>1</v>
       </c>
@@ -8579,11 +8654,21 @@
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="B95" s="15"/>
-      <c r="C95" s="13"/>
-      <c r="D95" s="14"/>
-      <c r="E95" s="15"/>
-      <c r="F95" s="16"/>
+      <c r="B95" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D95" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="E95" s="15">
+        <v>46072</v>
+      </c>
+      <c r="F95" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G95" s="17">
         <v>1</v>
       </c>
@@ -8594,122 +8679,227 @@
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="B96" s="15"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
-      <c r="E96" s="15"/>
-      <c r="F96" s="16"/>
+      <c r="B96" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="E96" s="15">
+        <v>46072</v>
+      </c>
+      <c r="F96" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G96" s="17">
         <v>1</v>
       </c>
       <c r="H96" s="4"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="12">
         <f t="shared" si="1"/>
         <v>91</v>
       </c>
-      <c r="B97" s="15"/>
-      <c r="C97" s="13"/>
-      <c r="D97" s="14"/>
-      <c r="E97" s="15"/>
-      <c r="F97" s="16"/>
+      <c r="B97" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D97" s="14" t="s">
+        <v>437</v>
+      </c>
+      <c r="E97" s="15">
+        <v>46072</v>
+      </c>
+      <c r="F97" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G97" s="17">
         <v>1</v>
       </c>
       <c r="H97" s="4"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="12">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="B98" s="15"/>
-      <c r="C98" s="13"/>
-      <c r="D98" s="14"/>
-      <c r="E98" s="15"/>
-      <c r="F98" s="16"/>
+      <c r="B98" s="28" t="s">
+        <v>442</v>
+      </c>
+      <c r="C98" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="D98" s="30" t="s">
+        <v>443</v>
+      </c>
+      <c r="E98" s="28">
+        <v>46075</v>
+      </c>
+      <c r="F98" s="21" t="s">
+        <v>162</v>
+      </c>
       <c r="G98" s="17">
         <v>1</v>
       </c>
       <c r="H98" s="4"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="12">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
-      <c r="B99" s="15"/>
-      <c r="C99" s="13"/>
-      <c r="D99" s="14"/>
-      <c r="E99" s="15"/>
-      <c r="F99" s="16"/>
+      <c r="B99" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D99" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="E99" s="15">
+        <v>46075</v>
+      </c>
+      <c r="F99" s="16" t="s">
+        <v>451</v>
+      </c>
       <c r="G99" s="17">
         <v>1</v>
       </c>
-      <c r="H99" s="4"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H99" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="I99" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="12">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
-      <c r="B100" s="15"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
-      <c r="E100" s="15"/>
-      <c r="F100" s="16"/>
+      <c r="B100" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D100" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="E100" s="15">
+        <v>46075</v>
+      </c>
+      <c r="F100" s="16" t="s">
+        <v>458</v>
+      </c>
       <c r="G100" s="17">
         <v>1</v>
       </c>
-      <c r="H100" s="4"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H100" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="I100" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="12">
         <f t="shared" si="1"/>
         <v>95</v>
       </c>
-      <c r="B101" s="15"/>
-      <c r="C101" s="13"/>
-      <c r="D101" s="14"/>
-      <c r="E101" s="15"/>
-      <c r="F101" s="16"/>
+      <c r="B101" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D101" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="E101" s="15">
+        <v>46075</v>
+      </c>
+      <c r="F101" s="16" t="s">
+        <v>445</v>
+      </c>
       <c r="G101" s="17">
         <v>1</v>
       </c>
-      <c r="H101" s="4"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H101" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="I101" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="12">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-      <c r="B102" s="15"/>
-      <c r="C102" s="13"/>
-      <c r="D102" s="14"/>
-      <c r="E102" s="15"/>
-      <c r="F102" s="16"/>
+      <c r="B102" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D102" s="14" t="s">
+        <v>459</v>
+      </c>
+      <c r="E102" s="15">
+        <v>46075</v>
+      </c>
+      <c r="F102" s="16" t="s">
+        <v>463</v>
+      </c>
       <c r="G102" s="17">
         <v>1</v>
       </c>
-      <c r="H102" s="4"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H102" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="I102" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="12">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
-      <c r="B103" s="15"/>
-      <c r="C103" s="13"/>
-      <c r="D103" s="14"/>
-      <c r="E103" s="15"/>
-      <c r="F103" s="16"/>
+      <c r="B103" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C103" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D103" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="E103" s="15">
+        <v>46075</v>
+      </c>
+      <c r="F103" s="16" t="s">
+        <v>455</v>
+      </c>
       <c r="G103" s="17">
         <v>1</v>
       </c>
-      <c r="H103" s="4"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H103" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="I103" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="12">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -8724,7 +8914,7 @@
       </c>
       <c r="H104" s="4"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="12">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -8739,7 +8929,7 @@
       </c>
       <c r="H105" s="4"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="12">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -8754,7 +8944,7 @@
       </c>
       <c r="H106" s="4"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="12">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -8769,7 +8959,7 @@
       </c>
       <c r="H107" s="4"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="12">
         <f t="shared" si="1"/>
         <v>102</v>
@@ -8784,7 +8974,7 @@
       </c>
       <c r="H108" s="4"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="12">
         <f t="shared" si="1"/>
         <v>103</v>
@@ -8799,7 +8989,7 @@
       </c>
       <c r="H109" s="4"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="12">
         <f t="shared" si="1"/>
         <v>104</v>
@@ -8814,7 +9004,7 @@
       </c>
       <c r="H110" s="4"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="12">
         <f t="shared" si="1"/>
         <v>105</v>
@@ -8829,7 +9019,7 @@
       </c>
       <c r="H111" s="4"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="12">
         <f t="shared" si="1"/>
         <v>106</v>
@@ -8920,9 +9110,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I93">
-    <sortCondition ref="E7:E93"/>
-    <sortCondition ref="D7:D93"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I103">
+    <sortCondition ref="E7:E103"/>
+    <sortCondition ref="D7:D103"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD75E5A-AC9A-45EE-BDB4-60B7CFFAB520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEF2F58-0F47-4644-B7C7-4F88C66061E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Janvier 2026 (2)" sheetId="2" r:id="rId1"/>
+    <sheet name="Janvier 2026 " sheetId="2" r:id="rId1"/>
     <sheet name="Février 2026" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Février 2026'!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Janvier 2026 (2)'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Janvier 2026 '!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="486">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -1430,9 +1430,6 @@
     <t>2025177307</t>
   </si>
   <si>
-    <t>B21503</t>
-  </si>
-  <si>
     <t>2025177301</t>
   </si>
   <si>
@@ -1494,6 +1491,75 @@
   </si>
   <si>
     <t>NB(535/2025)</t>
+  </si>
+  <si>
+    <t>B251278</t>
+  </si>
+  <si>
+    <t>2025178090</t>
+  </si>
+  <si>
+    <t>NB(052/2026)</t>
+  </si>
+  <si>
+    <t>Logt fonction lamri el abbes</t>
+  </si>
+  <si>
+    <t>Lycee bousmaha Chorfa</t>
+  </si>
+  <si>
+    <t>2025177941</t>
+  </si>
+  <si>
+    <t>NB(190/2025)</t>
+  </si>
+  <si>
+    <t>Mamouni djamel</t>
+  </si>
+  <si>
+    <t>Ain omrane</t>
+  </si>
+  <si>
+    <t>2025177942</t>
+  </si>
+  <si>
+    <t>2025177943</t>
+  </si>
+  <si>
+    <t>NB(750/2025)</t>
+  </si>
+  <si>
+    <t>Naili boualem</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt7 n31</t>
+  </si>
+  <si>
+    <t>NB(526/2025)</t>
+  </si>
+  <si>
+    <t>Lahfair moussa</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt14 n4</t>
+  </si>
+  <si>
+    <t>2025177361</t>
+  </si>
+  <si>
+    <t>2025177364</t>
+  </si>
+  <si>
+    <t>2025177369</t>
+  </si>
+  <si>
+    <t>B15945</t>
+  </si>
+  <si>
+    <t>B16130</t>
+  </si>
+  <si>
+    <t>B15746</t>
   </si>
 </sst>
 </file>
@@ -1658,7 +1724,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1721,6 +1787,9 @@
     <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1738,15 +1807,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1827,15 +1887,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>38110</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:colOff>104785</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1850,7 +1910,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="628660" y="20431125"/>
+          <a:off x="695335" y="21678900"/>
           <a:ext cx="4476740" cy="238125"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -2153,11 +2213,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -2170,11 +2230,11 @@
       <c r="K1" s="4"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
       <c r="D2" s="2"/>
       <c r="E2" s="5" t="s">
         <v>3</v>
@@ -2182,21 +2242,21 @@
       <c r="F2" s="5"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="24"/>
+      <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
         <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
       <c r="D3" s="5"/>
       <c r="E3" s="3" t="s">
         <v>6</v>
@@ -2204,50 +2264,50 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="24"/>
+      <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
         <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="24"/>
+      <c r="J4" s="25"/>
       <c r="K4" s="6">
         <f>SUMIF(F7:F364,"Ve*",G7:G364)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="24"/>
+      <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
         <v>96</v>
@@ -6167,11 +6227,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -6184,11 +6244,11 @@
       <c r="K1" s="4"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
       <c r="D2" s="2"/>
       <c r="E2" s="5" t="s">
         <v>3</v>
@@ -6196,21 +6256,21 @@
       <c r="F2" s="5"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="24"/>
+      <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
         <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
       <c r="D3" s="5"/>
       <c r="E3" s="3" t="s">
         <v>6</v>
@@ -6218,53 +6278,53 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="24"/>
+      <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="24"/>
+      <c r="J4" s="25"/>
       <c r="K4" s="6">
         <f>SUMIF(F7:F364,"Ve*",G7:G364)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="23" t="s">
         <v>258</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="24"/>
+      <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -8729,19 +8789,19 @@
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="B98" s="28" t="s">
+      <c r="B98" s="15" t="s">
+        <v>463</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D98" s="15" t="s">
         <v>442</v>
       </c>
-      <c r="C98" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="D98" s="30" t="s">
-        <v>443</v>
-      </c>
-      <c r="E98" s="28">
+      <c r="E98" s="15">
         <v>46075</v>
       </c>
-      <c r="F98" s="21" t="s">
+      <c r="F98" s="15" t="s">
         <v>162</v>
       </c>
       <c r="G98" s="17">
@@ -8761,22 +8821,22 @@
         <v>18</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E99" s="15">
         <v>46075</v>
       </c>
       <c r="F99" s="16" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G99" s="17">
         <v>1</v>
       </c>
       <c r="H99" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="I99" t="s">
         <v>449</v>
-      </c>
-      <c r="I99" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
@@ -8791,22 +8851,22 @@
         <v>18</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E100" s="15">
         <v>46075</v>
       </c>
       <c r="F100" s="16" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G100" s="17">
         <v>1</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I100" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
@@ -8821,22 +8881,22 @@
         <v>18</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E101" s="15">
         <v>46075</v>
       </c>
       <c r="F101" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="G101" s="17">
+        <v>1</v>
+      </c>
+      <c r="H101" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="G101" s="17">
-        <v>1</v>
-      </c>
-      <c r="H101" s="4" t="s">
+      <c r="I101" t="s">
         <v>446</v>
-      </c>
-      <c r="I101" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
@@ -8851,22 +8911,22 @@
         <v>18</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E102" s="15">
         <v>46075</v>
       </c>
       <c r="F102" s="16" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G102" s="17">
         <v>1</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I102" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
@@ -8881,22 +8941,22 @@
         <v>18</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E103" s="15">
         <v>46075</v>
       </c>
       <c r="F103" s="16" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G103" s="17">
         <v>1</v>
       </c>
       <c r="H103" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="I103" t="s">
         <v>453</v>
-      </c>
-      <c r="I103" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
@@ -8904,69 +8964,135 @@
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
-      <c r="B104" s="15"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
-      <c r="E104" s="15"/>
-      <c r="F104" s="16"/>
+      <c r="B104" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D104" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="E104" s="15">
+        <v>46055</v>
+      </c>
+      <c r="F104" s="16" t="s">
+        <v>465</v>
+      </c>
       <c r="G104" s="17">
         <v>1</v>
       </c>
-      <c r="H104" s="4"/>
+      <c r="H104" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="I104" t="s">
+        <v>467</v>
+      </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="12">
         <f t="shared" si="1"/>
         <v>99</v>
       </c>
-      <c r="B105" s="15"/>
-      <c r="C105" s="13"/>
-      <c r="D105" s="14"/>
-      <c r="E105" s="15"/>
-      <c r="F105" s="16"/>
+      <c r="B105" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C105" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D105" s="14" t="s">
+        <v>468</v>
+      </c>
+      <c r="E105" s="15">
+        <v>46078</v>
+      </c>
+      <c r="F105" s="16" t="s">
+        <v>469</v>
+      </c>
       <c r="G105" s="17">
         <v>1</v>
       </c>
-      <c r="H105" s="4"/>
+      <c r="H105" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="I105" t="s">
+        <v>471</v>
+      </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="12">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="B106" s="15"/>
-      <c r="C106" s="13"/>
-      <c r="D106" s="14"/>
-      <c r="E106" s="15"/>
-      <c r="F106" s="16"/>
+      <c r="B106" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C106" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D106" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="E106" s="15">
+        <v>46079</v>
+      </c>
+      <c r="F106" s="16" t="s">
+        <v>474</v>
+      </c>
       <c r="G106" s="17">
         <v>1</v>
       </c>
-      <c r="H106" s="4"/>
+      <c r="H106" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="I106" t="s">
+        <v>476</v>
+      </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="12">
         <f t="shared" si="1"/>
         <v>101</v>
       </c>
-      <c r="B107" s="15"/>
-      <c r="C107" s="13"/>
-      <c r="D107" s="14"/>
-      <c r="E107" s="15"/>
-      <c r="F107" s="16"/>
+      <c r="B107" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C107" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D107" s="14" t="s">
+        <v>473</v>
+      </c>
+      <c r="E107" s="15">
+        <v>46079</v>
+      </c>
+      <c r="F107" s="16" t="s">
+        <v>477</v>
+      </c>
       <c r="G107" s="17">
         <v>1</v>
       </c>
-      <c r="H107" s="4"/>
+      <c r="H107" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="I107" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="12">
         <f t="shared" si="1"/>
         <v>102</v>
       </c>
-      <c r="B108" s="15"/>
-      <c r="C108" s="13"/>
-      <c r="D108" s="14"/>
+      <c r="B108" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="C108" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D108" s="14" t="s">
+        <v>480</v>
+      </c>
       <c r="E108" s="15"/>
       <c r="F108" s="16"/>
       <c r="G108" s="17">
@@ -8979,9 +9105,15 @@
         <f t="shared" si="1"/>
         <v>103</v>
       </c>
-      <c r="B109" s="15"/>
-      <c r="C109" s="13"/>
-      <c r="D109" s="14"/>
+      <c r="B109" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="C109" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D109" s="14" t="s">
+        <v>481</v>
+      </c>
       <c r="E109" s="15"/>
       <c r="F109" s="16"/>
       <c r="G109" s="17">
@@ -8994,9 +9126,15 @@
         <f t="shared" si="1"/>
         <v>104</v>
       </c>
-      <c r="B110" s="15"/>
-      <c r="C110" s="13"/>
-      <c r="D110" s="14"/>
+      <c r="B110" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="C110" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D110" s="14" t="s">
+        <v>482</v>
+      </c>
       <c r="E110" s="15"/>
       <c r="F110" s="16"/>
       <c r="G110" s="17">

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEF2F58-0F47-4644-B7C7-4F88C66061E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6D54C8-4643-48CF-B074-A2286A0FB18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Janvier 2026 " sheetId="2" r:id="rId1"/>
     <sheet name="Février 2026" sheetId="1" r:id="rId2"/>
+    <sheet name="Mars 2026" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Février 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Janvier 2026 '!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mars 2026'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="524">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -1560,6 +1562,141 @@
   </si>
   <si>
     <t>B15746</t>
+  </si>
+  <si>
+    <r>
+      <t>Mois de Mars</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <t>B30023</t>
+  </si>
+  <si>
+    <t>BC0475</t>
+  </si>
+  <si>
+    <t>B21071</t>
+  </si>
+  <si>
+    <t>B40259</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt1 n4</t>
+  </si>
+  <si>
+    <t>NB(074/2026)</t>
+  </si>
+  <si>
+    <t>Mahdad med</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt11 n17</t>
+  </si>
+  <si>
+    <t>NB(644/2025)</t>
+  </si>
+  <si>
+    <t>Gheribi fatima</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt6 n19</t>
+  </si>
+  <si>
+    <t>Benziane aek</t>
+  </si>
+  <si>
+    <t>cite 483 n4</t>
+  </si>
+  <si>
+    <t>NB(580/2025)</t>
+  </si>
+  <si>
+    <t>Aettahri habiba</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt4 n31</t>
+  </si>
+  <si>
+    <t>Badi ibrahim</t>
+  </si>
+  <si>
+    <t>cite 140 aadl bt B2 n13</t>
+  </si>
+  <si>
+    <t>NB(082/2026)</t>
+  </si>
+  <si>
+    <t>Yahmi ayache</t>
+  </si>
+  <si>
+    <t>djenane tebal n13</t>
+  </si>
+  <si>
+    <t>NB(080/2026)</t>
+  </si>
+  <si>
+    <t>Maadadi bachir</t>
+  </si>
+  <si>
+    <t>lotis 48 logts ain omrane</t>
+  </si>
+  <si>
+    <t>Lakhel belkacem</t>
+  </si>
+  <si>
+    <t>route si el mahdjoub</t>
+  </si>
+  <si>
+    <t>Zouabia mhamed</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt11 n11</t>
+  </si>
+  <si>
+    <t>NB(084/2026)</t>
+  </si>
+  <si>
+    <t>Saci sellami</t>
+  </si>
+  <si>
+    <t>cité 64 logts bloc C2 n2 -chorfa</t>
+  </si>
+  <si>
+    <t>NB(686/2025)</t>
+  </si>
+  <si>
+    <t>NB(745/2025)</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>hh</t>
+  </si>
+  <si>
+    <t>B40080</t>
+  </si>
+  <si>
+    <t>B40090</t>
   </si>
 </sst>
 </file>
@@ -1937,6 +2074,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>104785</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connecteur droit 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB1F9D24-F73A-439D-AF8C-610170735631}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="695335" y="21678900"/>
+          <a:ext cx="4476740" cy="238125"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -6284,7 +6476,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -6324,7 +6516,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -8801,7 +8993,7 @@
       <c r="E98" s="15">
         <v>46075</v>
       </c>
-      <c r="F98" s="15" t="s">
+      <c r="F98" s="16" t="s">
         <v>162</v>
       </c>
       <c r="G98" s="17">
@@ -9093,12 +9285,21 @@
       <c r="D108" s="14" t="s">
         <v>480</v>
       </c>
-      <c r="E108" s="15"/>
-      <c r="F108" s="16"/>
+      <c r="E108" s="15">
+        <v>46069</v>
+      </c>
+      <c r="F108" s="16" t="s">
+        <v>495</v>
+      </c>
       <c r="G108" s="17">
         <v>1</v>
       </c>
-      <c r="H108" s="4"/>
+      <c r="H108" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="I108" t="s">
+        <v>497</v>
+      </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="12">
@@ -9114,12 +9315,21 @@
       <c r="D109" s="14" t="s">
         <v>481</v>
       </c>
-      <c r="E109" s="15"/>
-      <c r="F109" s="16"/>
+      <c r="E109" s="15">
+        <v>46068</v>
+      </c>
+      <c r="F109" s="16" t="s">
+        <v>492</v>
+      </c>
       <c r="G109" s="17">
         <v>1</v>
       </c>
-      <c r="H109" s="4"/>
+      <c r="H109" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="I109" t="s">
+        <v>494</v>
+      </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="12">
@@ -9135,12 +9345,21 @@
       <c r="D110" s="14" t="s">
         <v>482</v>
       </c>
-      <c r="E110" s="15"/>
-      <c r="F110" s="16"/>
+      <c r="E110" s="15">
+        <v>46068</v>
+      </c>
+      <c r="F110" s="16" t="s">
+        <v>155</v>
+      </c>
       <c r="G110" s="17">
         <v>1</v>
       </c>
-      <c r="H110" s="4"/>
+      <c r="H110" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="I110" t="s">
+        <v>491</v>
+      </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="12">
@@ -9271,4 +9490,2120 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DD4AEBE-5A1B-459D-B0ED-7F40FC0068FB}">
+  <dimension ref="A1:K117"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+    <col min="9" max="9" width="32.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="25"/>
+      <c r="K2" s="6">
+        <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="25"/>
+      <c r="K3" s="6">
+        <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="25"/>
+      <c r="K4" s="6">
+        <f>SUMIF(F7:F364,"Ve*",G7:G364)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>486</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="8">
+        <f>SUM(K2:K4)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="11" t="s">
+        <v>520</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>1</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="13">
+        <v>2025177944</v>
+      </c>
+      <c r="E7" s="15">
+        <v>46082</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>518</v>
+      </c>
+      <c r="G7" s="17">
+        <v>1</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>511</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>512</v>
+      </c>
+      <c r="J7" s="19"/>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <f t="shared" ref="A8:A19" si="0">+A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="13">
+        <v>2025177945</v>
+      </c>
+      <c r="E8" s="15">
+        <v>46082</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G8" s="17">
+        <v>1</v>
+      </c>
+      <c r="H8" s="18"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="13">
+        <v>2025177947</v>
+      </c>
+      <c r="E9" s="15">
+        <v>46082</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G9" s="17">
+        <v>1</v>
+      </c>
+      <c r="H9" s="18"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="13">
+        <v>2025177949</v>
+      </c>
+      <c r="E10" s="15">
+        <v>46083</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>519</v>
+      </c>
+      <c r="G10" s="17">
+        <v>1</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>517</v>
+      </c>
+      <c r="J10" s="20"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="13">
+        <v>2025177950</v>
+      </c>
+      <c r="E11" s="15">
+        <v>46083</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G11" s="17">
+        <v>1</v>
+      </c>
+      <c r="H11" s="18"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="13">
+        <v>2025177592</v>
+      </c>
+      <c r="E12" s="15">
+        <v>46084</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>515</v>
+      </c>
+      <c r="G12" s="17">
+        <v>1</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>513</v>
+      </c>
+      <c r="I12" t="s">
+        <v>514</v>
+      </c>
+      <c r="J12" s="20"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="13">
+        <v>2025177593</v>
+      </c>
+      <c r="E13" s="15">
+        <v>46084</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="G13" s="17">
+        <v>1</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>501</v>
+      </c>
+      <c r="I13" t="s">
+        <v>502</v>
+      </c>
+      <c r="J13" s="20"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="13">
+        <v>2025177594</v>
+      </c>
+      <c r="E14" s="15">
+        <v>46084</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>505</v>
+      </c>
+      <c r="G14" s="17">
+        <v>1</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>503</v>
+      </c>
+      <c r="I14" t="s">
+        <v>504</v>
+      </c>
+      <c r="J14" s="20"/>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="13">
+        <v>2025177946</v>
+      </c>
+      <c r="E15" s="15">
+        <v>46084</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="G15" s="17">
+        <v>1</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>506</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>507</v>
+      </c>
+      <c r="J15" s="20"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="13">
+        <v>2025177948</v>
+      </c>
+      <c r="E16" s="15">
+        <v>46084</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="G16" s="17">
+        <v>1</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>509</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>510</v>
+      </c>
+      <c r="J16" s="20"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="13">
+        <v>2025177595</v>
+      </c>
+      <c r="E17" s="15">
+        <v>46085</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="G17" s="17">
+        <v>1</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>498</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>499</v>
+      </c>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="13">
+        <v>2025177598</v>
+      </c>
+      <c r="E18" s="15">
+        <v>46085</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G18" s="17">
+        <v>1</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>490</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="13">
+        <v>2025177599</v>
+      </c>
+      <c r="E19" s="15">
+        <v>46085</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G19" s="17">
+        <v>1</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
+        <f t="shared" ref="A20:A72" si="1">+A19+1</f>
+        <v>14</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="13">
+        <v>2025177596</v>
+      </c>
+      <c r="E20" s="15">
+        <v>46086</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G20" s="17">
+        <v>1</v>
+      </c>
+      <c r="H20" s="18"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="13">
+        <v>2025177597</v>
+      </c>
+      <c r="E21" s="15">
+        <v>46086</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G21" s="17">
+        <v>1</v>
+      </c>
+      <c r="H21" s="18"/>
+      <c r="J21" s="20"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17">
+        <v>1</v>
+      </c>
+      <c r="H22" s="18"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="17">
+        <v>1</v>
+      </c>
+      <c r="H23" s="18"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="17">
+        <v>1</v>
+      </c>
+      <c r="H24" s="18"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17">
+        <v>1</v>
+      </c>
+      <c r="H25" s="18"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="17">
+        <v>1</v>
+      </c>
+      <c r="H26" s="18"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17">
+        <v>1</v>
+      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17">
+        <v>1</v>
+      </c>
+      <c r="H28" s="18"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="12">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="15"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17">
+        <v>1</v>
+      </c>
+      <c r="H30" s="18"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="15"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="17">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="15"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="17">
+        <v>1</v>
+      </c>
+      <c r="H32" s="18"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="12">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="17">
+        <v>1</v>
+      </c>
+      <c r="H33" s="18"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="12">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="15"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="17">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="12">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="15"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="17">
+        <v>1</v>
+      </c>
+      <c r="H35" s="18"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="12">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="15"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="17">
+        <v>1</v>
+      </c>
+      <c r="H36" s="4"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="12">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="15"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="17">
+        <v>1</v>
+      </c>
+      <c r="H37" s="4"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="12">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="15"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="17">
+        <v>1</v>
+      </c>
+      <c r="H38" s="4"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="12">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B39" s="15"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="17">
+        <v>1</v>
+      </c>
+      <c r="H39" s="18"/>
+      <c r="I39" s="20"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="12">
+        <f>+A39+1</f>
+        <v>34</v>
+      </c>
+      <c r="B40" s="15"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="17">
+        <v>1</v>
+      </c>
+      <c r="H40" s="4"/>
+      <c r="I40" s="20"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="12">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="17">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="20"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="12">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="17">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4"/>
+      <c r="I42" s="20"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="12">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="17">
+        <v>1</v>
+      </c>
+      <c r="H43" s="4"/>
+      <c r="I43" s="20"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="12">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="15"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="17">
+        <v>1</v>
+      </c>
+      <c r="H44" s="4"/>
+      <c r="I44" s="20"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="12">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="17">
+        <v>1</v>
+      </c>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="12">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="17">
+        <v>1</v>
+      </c>
+      <c r="H46" s="4"/>
+      <c r="I46" s="20"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="12">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="17">
+        <v>1</v>
+      </c>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="12">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B48" s="15"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="17">
+        <v>1</v>
+      </c>
+      <c r="H48" s="4"/>
+      <c r="I48" s="20"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="12">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="17">
+        <v>1</v>
+      </c>
+      <c r="H49" s="4"/>
+      <c r="I49" s="20"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="12">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="17">
+        <v>1</v>
+      </c>
+      <c r="H50" s="4"/>
+      <c r="I50" s="20"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="12">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="17">
+        <v>1</v>
+      </c>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="12">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="17">
+        <v>1</v>
+      </c>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="12">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="17">
+        <v>1</v>
+      </c>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="12">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B54" s="15"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="17">
+        <v>1</v>
+      </c>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="12">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B55" s="15"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="17">
+        <v>1</v>
+      </c>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="12">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B56" s="15"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="17">
+        <v>1</v>
+      </c>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="12">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="17">
+        <v>1</v>
+      </c>
+      <c r="H57" s="4"/>
+      <c r="I57" s="20"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="12">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B58" s="15"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="17">
+        <v>1</v>
+      </c>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="12">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B59" s="15"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="17">
+        <v>1</v>
+      </c>
+      <c r="H59" s="4"/>
+      <c r="I59" s="20"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="12">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B60" s="15"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="17">
+        <v>1</v>
+      </c>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="12">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="B61" s="15"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="17">
+        <v>1</v>
+      </c>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="12">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="B62" s="15"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="17">
+        <v>1</v>
+      </c>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="12">
+        <f t="shared" si="1"/>
+        <v>57</v>
+      </c>
+      <c r="B63" s="15"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="17">
+        <v>1</v>
+      </c>
+      <c r="H63" s="4"/>
+      <c r="I63" s="20"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="12">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+      <c r="B64" s="15"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="15"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="17">
+        <v>1</v>
+      </c>
+      <c r="H64" s="4"/>
+      <c r="I64" s="20"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="12">
+        <f t="shared" si="1"/>
+        <v>59</v>
+      </c>
+      <c r="B65" s="15"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="17">
+        <v>1</v>
+      </c>
+      <c r="H65" s="4"/>
+      <c r="I65" s="20"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="12">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="17">
+        <v>1</v>
+      </c>
+      <c r="H66" s="4"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="12">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
+      <c r="B67" s="15"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="15"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="17">
+        <v>1</v>
+      </c>
+      <c r="H67" s="4"/>
+      <c r="I67" s="20"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="12">
+        <f t="shared" si="1"/>
+        <v>62</v>
+      </c>
+      <c r="B68" s="15"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="17">
+        <v>1</v>
+      </c>
+      <c r="H68" s="4"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="12">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+      <c r="B69" s="15"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="17">
+        <v>1</v>
+      </c>
+      <c r="H69" s="4"/>
+      <c r="I69" s="20"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="12">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+      <c r="B70" s="15"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="17">
+        <v>1</v>
+      </c>
+      <c r="H70" s="4"/>
+      <c r="I70" s="20"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="12">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="B71" s="15"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="17">
+        <v>1</v>
+      </c>
+      <c r="H71" s="4"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="12">
+        <f t="shared" si="1"/>
+        <v>66</v>
+      </c>
+      <c r="B72" s="15"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="17">
+        <v>1</v>
+      </c>
+      <c r="H72" s="4"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="12">
+        <f t="shared" ref="A73:A117" si="2">+A72+1</f>
+        <v>67</v>
+      </c>
+      <c r="B73" s="15"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="17">
+        <v>1</v>
+      </c>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="12">
+        <f t="shared" si="2"/>
+        <v>68</v>
+      </c>
+      <c r="B74" s="15"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="17">
+        <v>1</v>
+      </c>
+      <c r="H74" s="4"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="12">
+        <f t="shared" si="2"/>
+        <v>69</v>
+      </c>
+      <c r="B75" s="15"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="17">
+        <v>1</v>
+      </c>
+      <c r="H75" s="4"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="12">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="B76" s="15"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="17">
+        <v>1</v>
+      </c>
+      <c r="H76" s="4"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="12">
+        <f t="shared" si="2"/>
+        <v>71</v>
+      </c>
+      <c r="B77" s="15"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="17">
+        <v>1</v>
+      </c>
+      <c r="H77" s="4"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="12">
+        <f t="shared" si="2"/>
+        <v>72</v>
+      </c>
+      <c r="B78" s="15"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="17">
+        <v>1</v>
+      </c>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="12">
+        <f t="shared" si="2"/>
+        <v>73</v>
+      </c>
+      <c r="B79" s="15"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="17">
+        <v>1</v>
+      </c>
+      <c r="H79" s="4"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="12">
+        <f t="shared" si="2"/>
+        <v>74</v>
+      </c>
+      <c r="B80" s="15"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="17">
+        <v>1</v>
+      </c>
+      <c r="H80" s="4"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="12">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+      <c r="B81" s="15"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="17">
+        <v>1</v>
+      </c>
+      <c r="H81" s="4"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="12">
+        <f t="shared" si="2"/>
+        <v>76</v>
+      </c>
+      <c r="B82" s="15"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="17">
+        <v>1</v>
+      </c>
+      <c r="H82" s="4"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="12">
+        <f t="shared" si="2"/>
+        <v>77</v>
+      </c>
+      <c r="B83" s="15"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="17">
+        <v>1</v>
+      </c>
+      <c r="H83" s="4"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="12">
+        <f t="shared" si="2"/>
+        <v>78</v>
+      </c>
+      <c r="B84" s="15"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="15"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="17">
+        <v>1</v>
+      </c>
+      <c r="H84" s="4"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="12">
+        <f t="shared" si="2"/>
+        <v>79</v>
+      </c>
+      <c r="B85" s="15"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="16"/>
+      <c r="G85" s="17">
+        <v>1</v>
+      </c>
+      <c r="H85" s="4"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="12">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="B86" s="15"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="16"/>
+      <c r="G86" s="17">
+        <v>1</v>
+      </c>
+      <c r="H86" s="4"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="12">
+        <f t="shared" si="2"/>
+        <v>81</v>
+      </c>
+      <c r="B87" s="15"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="17">
+        <v>1</v>
+      </c>
+      <c r="H87" s="4"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="12">
+        <f t="shared" si="2"/>
+        <v>82</v>
+      </c>
+      <c r="B88" s="15"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="17">
+        <v>1</v>
+      </c>
+      <c r="H88" s="4"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="12">
+        <f t="shared" si="2"/>
+        <v>83</v>
+      </c>
+      <c r="B89" s="15"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="17">
+        <v>1</v>
+      </c>
+      <c r="H89" s="4"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="12">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+      <c r="B90" s="15"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="16"/>
+      <c r="G90" s="17">
+        <v>1</v>
+      </c>
+      <c r="H90" s="4"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="12">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="B91" s="15"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="17">
+        <v>1</v>
+      </c>
+      <c r="H91" s="4"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="12">
+        <f t="shared" si="2"/>
+        <v>86</v>
+      </c>
+      <c r="B92" s="15"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="17">
+        <v>1</v>
+      </c>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="12">
+        <f t="shared" si="2"/>
+        <v>87</v>
+      </c>
+      <c r="B93" s="15"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="17">
+        <v>1</v>
+      </c>
+      <c r="H93" s="4"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="12">
+        <f t="shared" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="B94" s="15"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="15"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="17">
+        <v>1</v>
+      </c>
+      <c r="H94" s="4"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="12">
+        <f t="shared" si="2"/>
+        <v>89</v>
+      </c>
+      <c r="B95" s="15"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="15"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="17">
+        <v>1</v>
+      </c>
+      <c r="H95" s="4"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="12">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="B96" s="15"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="16"/>
+      <c r="G96" s="17">
+        <v>1</v>
+      </c>
+      <c r="H96" s="4"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="12">
+        <f t="shared" si="2"/>
+        <v>91</v>
+      </c>
+      <c r="B97" s="15"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="16"/>
+      <c r="G97" s="17">
+        <v>1</v>
+      </c>
+      <c r="H97" s="4"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="12">
+        <f t="shared" si="2"/>
+        <v>92</v>
+      </c>
+      <c r="B98" s="15"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="16"/>
+      <c r="G98" s="17">
+        <v>1</v>
+      </c>
+      <c r="H98" s="4"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="12">
+        <f t="shared" si="2"/>
+        <v>93</v>
+      </c>
+      <c r="B99" s="15"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="15"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="17">
+        <v>1</v>
+      </c>
+      <c r="H99" s="4"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="12">
+        <f t="shared" si="2"/>
+        <v>94</v>
+      </c>
+      <c r="B100" s="15"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="15"/>
+      <c r="F100" s="16"/>
+      <c r="G100" s="17">
+        <v>1</v>
+      </c>
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="12">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="B101" s="15"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="16"/>
+      <c r="G101" s="17">
+        <v>1</v>
+      </c>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="12">
+        <f t="shared" si="2"/>
+        <v>96</v>
+      </c>
+      <c r="B102" s="15"/>
+      <c r="C102" s="13"/>
+      <c r="D102" s="14"/>
+      <c r="E102" s="15"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="17">
+        <v>1</v>
+      </c>
+      <c r="H102" s="4"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="12">
+        <f t="shared" si="2"/>
+        <v>97</v>
+      </c>
+      <c r="B103" s="15"/>
+      <c r="C103" s="13"/>
+      <c r="D103" s="14"/>
+      <c r="E103" s="15"/>
+      <c r="F103" s="16"/>
+      <c r="G103" s="17">
+        <v>1</v>
+      </c>
+      <c r="H103" s="4"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="12">
+        <f t="shared" si="2"/>
+        <v>98</v>
+      </c>
+      <c r="B104" s="15"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="22"/>
+      <c r="E104" s="15"/>
+      <c r="F104" s="16"/>
+      <c r="G104" s="17">
+        <v>1</v>
+      </c>
+      <c r="H104" s="4"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="12">
+        <f t="shared" si="2"/>
+        <v>99</v>
+      </c>
+      <c r="B105" s="15"/>
+      <c r="C105" s="13"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="15"/>
+      <c r="F105" s="16"/>
+      <c r="G105" s="17">
+        <v>1</v>
+      </c>
+      <c r="H105" s="4"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="12">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="B106" s="15"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="15"/>
+      <c r="F106" s="16"/>
+      <c r="G106" s="17">
+        <v>1</v>
+      </c>
+      <c r="H106" s="4"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="12">
+        <f t="shared" si="2"/>
+        <v>101</v>
+      </c>
+      <c r="B107" s="15"/>
+      <c r="C107" s="13"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="15"/>
+      <c r="F107" s="16"/>
+      <c r="G107" s="17">
+        <v>1</v>
+      </c>
+      <c r="H107" s="4"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="12">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="B108" s="15"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="14"/>
+      <c r="E108" s="15"/>
+      <c r="F108" s="16"/>
+      <c r="G108" s="17">
+        <v>1</v>
+      </c>
+      <c r="H108" s="4"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="12">
+        <f t="shared" si="2"/>
+        <v>103</v>
+      </c>
+      <c r="B109" s="15"/>
+      <c r="C109" s="13"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="15"/>
+      <c r="F109" s="16"/>
+      <c r="G109" s="17">
+        <v>1</v>
+      </c>
+      <c r="H109" s="4"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="12">
+        <f t="shared" si="2"/>
+        <v>104</v>
+      </c>
+      <c r="B110" s="15"/>
+      <c r="C110" s="13"/>
+      <c r="D110" s="14"/>
+      <c r="E110" s="15"/>
+      <c r="F110" s="16"/>
+      <c r="G110" s="17">
+        <v>1</v>
+      </c>
+      <c r="H110" s="4"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="12">
+        <f t="shared" si="2"/>
+        <v>105</v>
+      </c>
+      <c r="B111" s="15"/>
+      <c r="C111" s="13"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="15"/>
+      <c r="F111" s="16"/>
+      <c r="G111" s="17">
+        <v>1</v>
+      </c>
+      <c r="H111" s="4"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="12">
+        <f t="shared" si="2"/>
+        <v>106</v>
+      </c>
+      <c r="B112" s="15"/>
+      <c r="C112" s="13"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="15"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="17">
+        <v>1</v>
+      </c>
+      <c r="H112" s="4"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="12">
+        <f t="shared" si="2"/>
+        <v>107</v>
+      </c>
+      <c r="B113" s="15"/>
+      <c r="C113" s="13"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="15"/>
+      <c r="F113" s="16"/>
+      <c r="G113" s="17">
+        <v>1</v>
+      </c>
+      <c r="H113" s="4"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="12">
+        <f t="shared" si="2"/>
+        <v>108</v>
+      </c>
+      <c r="B114" s="15"/>
+      <c r="C114" s="13"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="15"/>
+      <c r="F114" s="16"/>
+      <c r="G114" s="17">
+        <v>1</v>
+      </c>
+      <c r="H114" s="4"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="12">
+        <f t="shared" si="2"/>
+        <v>109</v>
+      </c>
+      <c r="B115" s="15"/>
+      <c r="C115" s="13"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="15"/>
+      <c r="F115" s="16"/>
+      <c r="G115" s="17">
+        <v>1</v>
+      </c>
+      <c r="H115" s="4"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="12">
+        <f t="shared" si="2"/>
+        <v>110</v>
+      </c>
+      <c r="B116" s="15"/>
+      <c r="C116" s="13"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="15"/>
+      <c r="F116" s="16"/>
+      <c r="G116" s="17">
+        <v>1</v>
+      </c>
+      <c r="H116" s="4"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="12">
+        <f t="shared" si="2"/>
+        <v>111</v>
+      </c>
+      <c r="B117" s="15"/>
+      <c r="C117" s="13"/>
+      <c r="D117" s="14"/>
+      <c r="E117" s="15"/>
+      <c r="F117" s="16"/>
+      <c r="G117" s="17">
+        <v>1</v>
+      </c>
+      <c r="H117" s="4"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I21">
+    <sortCondition ref="E7:E21"/>
+    <sortCondition ref="D7:D21"/>
+  </sortState>
+  <mergeCells count="9">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="I4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283472" right="0.45" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6D54C8-4643-48CF-B074-A2286A0FB18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26609908-579F-429B-B849-D0DCCAA6C2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Janvier 2026 " sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="512">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -1444,18 +1444,12 @@
     <t>Baghdadi billel</t>
   </si>
   <si>
-    <t>cite 720 aadl bt6 n32</t>
-  </si>
-  <si>
     <t>2025177303</t>
   </si>
   <si>
     <t>Zemir samir</t>
   </si>
   <si>
-    <t>cite 720 aadl bt7 n15</t>
-  </si>
-  <si>
     <t>NB(707/2025)</t>
   </si>
   <si>
@@ -1465,9 +1459,6 @@
     <t>Madani fateh</t>
   </si>
   <si>
-    <t>cite 720 aadl bt7 n5</t>
-  </si>
-  <si>
     <t>NB(703/2025)</t>
   </si>
   <si>
@@ -1486,18 +1477,9 @@
     <t>Noui sihem</t>
   </si>
   <si>
-    <t>cite 720 aadl bt1 n10</t>
-  </si>
-  <si>
-    <t>cite 720 aadl bt15 n36</t>
-  </si>
-  <si>
     <t>NB(535/2025)</t>
   </si>
   <si>
-    <t>B251278</t>
-  </si>
-  <si>
     <t>2025178090</t>
   </si>
   <si>
@@ -1507,9 +1489,6 @@
     <t>Logt fonction lamri el abbes</t>
   </si>
   <si>
-    <t>Lycee bousmaha Chorfa</t>
-  </si>
-  <si>
     <t>2025177941</t>
   </si>
   <si>
@@ -1519,9 +1498,6 @@
     <t>Mamouni djamel</t>
   </si>
   <si>
-    <t>Ain omrane</t>
-  </si>
-  <si>
     <t>2025177942</t>
   </si>
   <si>
@@ -1534,16 +1510,10 @@
     <t>Naili boualem</t>
   </si>
   <si>
-    <t>cite 720 aadl bt7 n31</t>
-  </si>
-  <si>
     <t>NB(526/2025)</t>
   </si>
   <si>
     <t>Lahfair moussa</t>
-  </si>
-  <si>
-    <t>cite 720 aadl bt14 n4</t>
   </si>
   <si>
     <t>2025177361</t>
@@ -1600,27 +1570,18 @@
     <t>B40259</t>
   </si>
   <si>
-    <t>cite 720 aadl bt1 n4</t>
-  </si>
-  <si>
     <t>NB(074/2026)</t>
   </si>
   <si>
     <t>Mahdad med</t>
   </si>
   <si>
-    <t>cite 720 aadl bt11 n17</t>
-  </si>
-  <si>
     <t>NB(644/2025)</t>
   </si>
   <si>
     <t>Gheribi fatima</t>
   </si>
   <si>
-    <t>cite 720 aadl bt6 n19</t>
-  </si>
-  <si>
     <t>Benziane aek</t>
   </si>
   <si>
@@ -1697,6 +1658,9 @@
   </si>
   <si>
     <t>B40090</t>
+  </si>
+  <si>
+    <t>B21278</t>
   </si>
 </sst>
 </file>
@@ -2024,15 +1988,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>104785</xdr:colOff>
-      <xdr:row>112</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>114</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1133475</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2047,8 +2011,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="695335" y="21678900"/>
-          <a:ext cx="4476740" cy="238125"/>
+          <a:off x="600075" y="21116925"/>
+          <a:ext cx="4371975" cy="1295400"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -7310,25 +7274,26 @@
         <v>28</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>321</v>
+        <v>19</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>322</v>
+        <v>458</v>
       </c>
       <c r="E34" s="15">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>162</v>
+        <v>459</v>
       </c>
       <c r="G34" s="17">
         <v>1</v>
       </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="20"/>
+      <c r="H34" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7337,13 +7302,13 @@
         <v>29</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="E35" s="15">
         <v>46056</v>
@@ -7354,7 +7319,7 @@
       <c r="G35" s="17">
         <v>1</v>
       </c>
-      <c r="H35" s="18"/>
+      <c r="H35" s="4"/>
       <c r="I35" s="20"/>
       <c r="J35" s="4"/>
     </row>
@@ -7364,13 +7329,13 @@
         <v>30</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C36" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="E36" s="15">
         <v>46056</v>
@@ -7381,7 +7346,7 @@
       <c r="G36" s="17">
         <v>1</v>
       </c>
-      <c r="H36" s="4"/>
+      <c r="H36" s="18"/>
       <c r="I36" s="20"/>
       <c r="J36" s="4"/>
     </row>
@@ -7391,13 +7356,13 @@
         <v>31</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E37" s="15">
         <v>46056</v>
@@ -7418,13 +7383,13 @@
         <v>32</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C38" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E38" s="15">
         <v>46056</v>
@@ -7445,13 +7410,13 @@
         <v>33</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E39" s="15">
         <v>46056</v>
@@ -7462,22 +7427,22 @@
       <c r="G39" s="17">
         <v>1</v>
       </c>
-      <c r="H39" s="18"/>
+      <c r="H39" s="4"/>
       <c r="I39" s="20"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
-        <f>+A39+1</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C40" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="E40" s="15">
         <v>46056</v>
@@ -7488,7 +7453,7 @@
       <c r="G40" s="17">
         <v>1</v>
       </c>
-      <c r="H40" s="4"/>
+      <c r="H40" s="18"/>
       <c r="I40" s="20"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -7496,14 +7461,14 @@
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B41" s="13" t="s">
-        <v>319</v>
+      <c r="B41" s="15" t="s">
+        <v>301</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="E41" s="15">
         <v>46056</v>
@@ -7523,13 +7488,13 @@
         <v>36</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E42" s="15">
         <v>46056</v>
@@ -7549,13 +7514,13 @@
         <v>37</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E43" s="15">
         <v>46056</v>
@@ -7574,14 +7539,14 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B44" s="15" t="s">
-        <v>313</v>
+      <c r="B44" s="13" t="s">
+        <v>318</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E44" s="15">
         <v>46056</v>
@@ -7600,28 +7565,26 @@
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B45" s="13" t="s">
-        <v>19</v>
+      <c r="B45" s="15" t="s">
+        <v>313</v>
       </c>
       <c r="C45" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="E45" s="15">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>328</v>
+        <v>162</v>
       </c>
       <c r="G45" s="17">
         <v>1</v>
       </c>
-      <c r="H45" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="I45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="20"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="12">
@@ -7635,21 +7598,21 @@
         <v>18</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E46" s="15">
         <v>46057</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G46" s="17">
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="I46" s="20"/>
+        <v>327</v>
+      </c>
+      <c r="I46" s="4"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
@@ -7663,74 +7626,74 @@
         <v>18</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="E47" s="15">
         <v>46057</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="G47" s="17">
         <v>1</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="I47" s="4"/>
+        <v>330</v>
+      </c>
+      <c r="I47" s="20"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="12">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B48" s="15" t="s">
-        <v>332</v>
+      <c r="B48" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="C48" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="E48" s="15">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>162</v>
+        <v>324</v>
       </c>
       <c r="G48" s="17">
         <v>1</v>
       </c>
-      <c r="H48" s="4"/>
-      <c r="I48" s="20"/>
+      <c r="H48" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="I48" s="4"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="12">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B49" s="13" t="s">
-        <v>19</v>
+      <c r="B49" s="15" t="s">
+        <v>332</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="E49" s="15">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>343</v>
+        <v>162</v>
       </c>
       <c r="G49" s="17">
         <v>1</v>
       </c>
-      <c r="H49" s="4" t="s">
-        <v>330</v>
-      </c>
+      <c r="H49" s="4"/>
       <c r="I49" s="20"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -7745,13 +7708,13 @@
         <v>18</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E50" s="15">
         <v>46062</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G50" s="17">
         <v>1</v>
@@ -7773,21 +7736,21 @@
         <v>18</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="E51" s="15">
         <v>46062</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="G51" s="17">
         <v>1</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="I51" s="4"/>
+        <v>330</v>
+      </c>
+      <c r="I51" s="20"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="12">
@@ -7801,19 +7764,19 @@
         <v>18</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="E52" s="15">
         <v>46062</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="G52" s="17">
         <v>1</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="I52" s="4"/>
     </row>
@@ -7829,19 +7792,19 @@
         <v>18</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="E53" s="15">
         <v>46062</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="G53" s="17">
         <v>1</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="I53" s="4"/>
     </row>
@@ -7850,26 +7813,26 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>359</v>
+        <v>337</v>
       </c>
       <c r="E54" s="15">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="G54" s="17">
         <v>1</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="I54" s="4"/>
     </row>
@@ -7885,19 +7848,19 @@
         <v>18</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="E55" s="15">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="G55" s="17">
         <v>1</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="I55" s="4"/>
     </row>
@@ -7913,19 +7876,19 @@
         <v>18</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E56" s="15">
         <v>46064</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G56" s="17">
         <v>1</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I56" s="4"/>
     </row>
@@ -7941,21 +7904,21 @@
         <v>18</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E57" s="15">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G57" s="17">
         <v>1</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="I57" s="20"/>
+        <v>351</v>
+      </c>
+      <c r="I57" s="4"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="12">
@@ -7969,21 +7932,21 @@
         <v>18</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E58" s="15">
         <v>46065</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G58" s="17">
         <v>1</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="I58" s="4"/>
+        <v>354</v>
+      </c>
+      <c r="I58" s="20"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="12">
@@ -7991,25 +7954,27 @@
         <v>53</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="C59" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="E59" s="15">
-        <v>46068</v>
+        <v>46065</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>162</v>
+        <v>357</v>
       </c>
       <c r="G59" s="17">
         <v>1</v>
       </c>
-      <c r="H59" s="4"/>
-      <c r="I59" s="20"/>
+      <c r="H59" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I59" s="4"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="12">
@@ -8017,27 +7982,26 @@
         <v>54</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>19</v>
+        <v>474</v>
       </c>
       <c r="C60" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>366</v>
+        <v>471</v>
       </c>
       <c r="E60" s="15">
-        <v>46069</v>
+        <v>46068</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>368</v>
+        <v>481</v>
       </c>
       <c r="G60" s="17">
         <v>1</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="I60" s="4"/>
+        <v>482</v>
+      </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="12">
@@ -8045,27 +8009,25 @@
         <v>55</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="C61" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E61" s="15">
-        <v>46069</v>
+        <v>46068</v>
       </c>
       <c r="F61" s="16" t="s">
-        <v>364</v>
+        <v>162</v>
       </c>
       <c r="G61" s="17">
         <v>1</v>
       </c>
-      <c r="H61" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="I61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="20"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="12">
@@ -8073,24 +8035,26 @@
         <v>56</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>383</v>
+        <v>475</v>
       </c>
       <c r="C62" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>384</v>
+        <v>472</v>
       </c>
       <c r="E62" s="15">
-        <v>46069</v>
+        <v>46068</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="G62" s="17">
         <v>1</v>
       </c>
-      <c r="H62" s="4"/>
+      <c r="H62" s="4" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="12">
@@ -8098,25 +8062,26 @@
         <v>57</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>377</v>
+        <v>473</v>
       </c>
       <c r="C63" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>378</v>
+        <v>470</v>
       </c>
       <c r="E63" s="15">
         <v>46069</v>
       </c>
       <c r="F63" s="16" t="s">
-        <v>162</v>
+        <v>483</v>
       </c>
       <c r="G63" s="17">
         <v>1</v>
       </c>
-      <c r="H63" s="4"/>
-      <c r="I63" s="20"/>
+      <c r="H63" s="4" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="12">
@@ -8124,25 +8089,27 @@
         <v>58</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>375</v>
+        <v>19</v>
       </c>
       <c r="C64" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="E64" s="15">
         <v>46069</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>162</v>
+        <v>368</v>
       </c>
       <c r="G64" s="17">
         <v>1</v>
       </c>
-      <c r="H64" s="4"/>
-      <c r="I64" s="20"/>
+      <c r="H64" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="I64" s="4"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="12">
@@ -8150,25 +8117,27 @@
         <v>59</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>373</v>
+        <v>19</v>
       </c>
       <c r="C65" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="E65" s="15">
         <v>46069</v>
       </c>
       <c r="F65" s="16" t="s">
-        <v>162</v>
+        <v>364</v>
       </c>
       <c r="G65" s="17">
         <v>1</v>
       </c>
-      <c r="H65" s="4"/>
-      <c r="I65" s="20"/>
+      <c r="H65" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="I65" s="4"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="12">
@@ -8176,13 +8145,13 @@
         <v>60</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C66" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E66" s="15">
         <v>46069</v>
@@ -8201,13 +8170,13 @@
         <v>61</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C67" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="E67" s="15">
         <v>46069</v>
@@ -8227,13 +8196,13 @@
         <v>62</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="C68" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="E68" s="15">
         <v>46069</v>
@@ -8245,6 +8214,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="4"/>
+      <c r="I68" s="20"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="12">
@@ -8252,13 +8222,13 @@
         <v>63</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C69" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="E69" s="15">
         <v>46069</v>
@@ -8278,13 +8248,13 @@
         <v>64</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="C70" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="E70" s="15">
         <v>46069</v>
@@ -8296,7 +8266,6 @@
         <v>1</v>
       </c>
       <c r="H70" s="4"/>
-      <c r="I70" s="20"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="12">
@@ -8304,13 +8273,13 @@
         <v>65</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="C71" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="E71" s="15">
         <v>46069</v>
@@ -8322,6 +8291,7 @@
         <v>1</v>
       </c>
       <c r="H71" s="4"/>
+      <c r="I71" s="20"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="12">
@@ -8329,16 +8299,16 @@
         <v>66</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C72" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E72" s="15">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="F72" s="16" t="s">
         <v>162</v>
@@ -8350,31 +8320,29 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="12">
-        <f t="shared" ref="A73:A117" si="1">+A72+1</f>
+        <f t="shared" ref="A73:A87" si="1">+A72+1</f>
         <v>67</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>19</v>
+        <v>379</v>
       </c>
       <c r="C73" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="E73" s="15">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="F73" s="16" t="s">
-        <v>392</v>
+        <v>162</v>
       </c>
       <c r="G73" s="17">
         <v>1</v>
       </c>
-      <c r="H73" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="I73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="20"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="12">
@@ -8382,16 +8350,16 @@
         <v>68</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="C74" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>403</v>
+        <v>372</v>
       </c>
       <c r="E74" s="15">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="F74" s="16" t="s">
         <v>162</v>
@@ -8400,6 +8368,7 @@
         <v>1</v>
       </c>
       <c r="H74" s="4"/>
+      <c r="I74" s="20"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="12">
@@ -8407,16 +8376,16 @@
         <v>69</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="C75" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="E75" s="15">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="F75" s="16" t="s">
         <v>162</v>
@@ -8432,13 +8401,13 @@
         <v>70</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="C76" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="E76" s="15">
         <v>46070</v>
@@ -8457,24 +8426,27 @@
         <v>71</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>406</v>
+        <v>19</v>
       </c>
       <c r="C77" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="E77" s="15">
         <v>46070</v>
       </c>
       <c r="F77" s="16" t="s">
-        <v>162</v>
+        <v>392</v>
       </c>
       <c r="G77" s="17">
         <v>1</v>
       </c>
-      <c r="H77" s="4"/>
+      <c r="H77" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="I77" s="4"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="12">
@@ -8482,13 +8454,13 @@
         <v>72</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C78" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E78" s="15">
         <v>46070</v>
@@ -8507,13 +8479,13 @@
         <v>73</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C79" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="E79" s="15">
         <v>46070</v>
@@ -8532,13 +8504,13 @@
         <v>74</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="C80" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="E80" s="15">
         <v>46070</v>
@@ -8557,13 +8529,13 @@
         <v>75</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="C81" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="E81" s="15">
         <v>46070</v>
@@ -8582,13 +8554,13 @@
         <v>76</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C82" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E82" s="15">
         <v>46070</v>
@@ -8607,13 +8579,13 @@
         <v>77</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="C83" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="E83" s="15">
         <v>46070</v>
@@ -8632,16 +8604,16 @@
         <v>78</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="C84" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="E84" s="15">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="F84" s="16" t="s">
         <v>162</v>
@@ -8657,16 +8629,16 @@
         <v>79</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>424</v>
+        <v>396</v>
       </c>
       <c r="C85" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>425</v>
+        <v>397</v>
       </c>
       <c r="E85" s="15">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="F85" s="16" t="s">
         <v>162</v>
@@ -8682,16 +8654,16 @@
         <v>80</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="C86" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="E86" s="15">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="F86" s="16" t="s">
         <v>162</v>
@@ -8707,16 +8679,16 @@
         <v>81</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>421</v>
+        <v>394</v>
       </c>
       <c r="C87" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>420</v>
+        <v>395</v>
       </c>
       <c r="E87" s="15">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="F87" s="16" t="s">
         <v>162</v>
@@ -8728,17 +8700,17 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="12">
-        <f t="shared" si="1"/>
+        <f>+A87+1</f>
         <v>82</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C88" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E88" s="15">
         <v>46071</v>
@@ -8753,17 +8725,17 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A89:A115" si="2">+A88+1</f>
         <v>83</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C89" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D89" s="14" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E89" s="15">
         <v>46071</v>
@@ -8778,17 +8750,17 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="C90" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="E90" s="15">
         <v>46071</v>
@@ -8803,17 +8775,17 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>85</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="C91" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="E91" s="15">
         <v>46071</v>
@@ -8828,17 +8800,17 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>86</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="C92" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="E92" s="15">
         <v>46071</v>
@@ -8853,17 +8825,17 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>87</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C93" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D93" s="14" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="E93" s="15">
         <v>46071</v>
@@ -8878,20 +8850,20 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>88</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="C94" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="E94" s="15">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="F94" s="16" t="s">
         <v>162</v>
@@ -8903,20 +8875,20 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>89</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="C95" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="E95" s="15">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="F95" s="16" t="s">
         <v>162</v>
@@ -8928,20 +8900,20 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="C96" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D96" s="14" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="E96" s="15">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="F96" s="16" t="s">
         <v>162</v>
@@ -8951,22 +8923,22 @@
       </c>
       <c r="H96" s="4"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>91</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="C97" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="E97" s="15">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="F97" s="16" t="s">
         <v>162</v>
@@ -8976,22 +8948,22 @@
       </c>
       <c r="H97" s="4"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>92</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>463</v>
-      </c>
-      <c r="C98" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D98" s="15" t="s">
-        <v>442</v>
+        <v>434</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>435</v>
       </c>
       <c r="E98" s="15">
-        <v>46075</v>
+        <v>46072</v>
       </c>
       <c r="F98" s="16" t="s">
         <v>162</v>
@@ -9001,129 +8973,109 @@
       </c>
       <c r="H98" s="4"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>93</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>19</v>
+        <v>438</v>
       </c>
       <c r="C99" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="E99" s="15">
-        <v>46075</v>
+        <v>46072</v>
       </c>
       <c r="F99" s="16" t="s">
-        <v>450</v>
+        <v>162</v>
       </c>
       <c r="G99" s="17">
         <v>1</v>
       </c>
-      <c r="H99" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="I99" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H99" s="4"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>94</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>19</v>
+        <v>440</v>
       </c>
       <c r="C100" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="E100" s="15">
-        <v>46075</v>
+        <v>46072</v>
       </c>
       <c r="F100" s="16" t="s">
-        <v>457</v>
+        <v>162</v>
       </c>
       <c r="G100" s="17">
         <v>1</v>
       </c>
-      <c r="H100" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="I100" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>19</v>
+        <v>436</v>
       </c>
       <c r="C101" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E101" s="15">
-        <v>46075</v>
+        <v>46072</v>
       </c>
       <c r="F101" s="16" t="s">
-        <v>444</v>
+        <v>162</v>
       </c>
       <c r="G101" s="17">
         <v>1</v>
       </c>
-      <c r="H101" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="I101" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C102" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D102" s="14" t="s">
-        <v>458</v>
+        <v>511</v>
+      </c>
+      <c r="C102" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D102" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="E102" s="15">
         <v>46075</v>
       </c>
       <c r="F102" s="16" t="s">
-        <v>462</v>
+        <v>162</v>
       </c>
       <c r="G102" s="17">
         <v>1</v>
       </c>
-      <c r="H102" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="I102" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H102" s="4"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97</v>
       </c>
       <c r="B103" s="15" t="s">
@@ -9133,27 +9085,24 @@
         <v>18</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="E103" s="15">
         <v>46075</v>
       </c>
       <c r="F103" s="16" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="G103" s="17">
         <v>1</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="I103" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>98</v>
       </c>
       <c r="B104" s="15" t="s">
@@ -9162,58 +9111,52 @@
       <c r="C104" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D104" s="22" t="s">
-        <v>464</v>
+      <c r="D104" s="14" t="s">
+        <v>452</v>
       </c>
       <c r="E104" s="15">
-        <v>46055</v>
+        <v>46075</v>
       </c>
       <c r="F104" s="16" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="G104" s="17">
         <v>1</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="I104" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>99</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C105" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D105" s="14" t="s">
-        <v>468</v>
+        <v>443</v>
       </c>
       <c r="E105" s="15">
-        <v>46078</v>
+        <v>46075</v>
       </c>
       <c r="F105" s="16" t="s">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="G105" s="17">
         <v>1</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="I105" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="B106" s="15" t="s">
@@ -9223,27 +9166,24 @@
         <v>18</v>
       </c>
       <c r="D106" s="14" t="s">
-        <v>472</v>
+        <v>455</v>
       </c>
       <c r="E106" s="15">
-        <v>46079</v>
+        <v>46075</v>
       </c>
       <c r="F106" s="16" t="s">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="G106" s="17">
         <v>1</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="I106" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>101</v>
       </c>
       <c r="B107" s="15" t="s">
@@ -9253,117 +9193,105 @@
         <v>18</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="E107" s="15">
+        <v>46075</v>
+      </c>
+      <c r="F107" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="G107" s="17">
+        <v>1</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="12">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="B108" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C108" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D108" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="E108" s="15">
+        <v>46078</v>
+      </c>
+      <c r="F108" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="G108" s="17">
+        <v>1</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="12">
+        <f t="shared" si="2"/>
+        <v>103</v>
+      </c>
+      <c r="B109" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C109" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D109" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="E109" s="15">
         <v>46079</v>
       </c>
-      <c r="F107" s="16" t="s">
-        <v>477</v>
-      </c>
-      <c r="G107" s="17">
-        <v>1</v>
-      </c>
-      <c r="H107" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="I107" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="12">
-        <f t="shared" si="1"/>
-        <v>102</v>
-      </c>
-      <c r="B108" s="15" t="s">
-        <v>483</v>
-      </c>
-      <c r="C108" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D108" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E108" s="15">
-        <v>46069</v>
-      </c>
-      <c r="F108" s="16" t="s">
-        <v>495</v>
-      </c>
-      <c r="G108" s="17">
-        <v>1</v>
-      </c>
-      <c r="H108" s="4" t="s">
-        <v>496</v>
-      </c>
-      <c r="I108" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="12">
-        <f t="shared" si="1"/>
-        <v>103</v>
-      </c>
-      <c r="B109" s="15" t="s">
-        <v>484</v>
-      </c>
-      <c r="C109" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D109" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="E109" s="15">
-        <v>46068</v>
-      </c>
       <c r="F109" s="16" t="s">
-        <v>492</v>
+        <v>466</v>
       </c>
       <c r="G109" s="17">
         <v>1</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="I109" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>104</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>485</v>
+        <v>19</v>
       </c>
       <c r="C110" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="E110" s="15">
-        <v>46068</v>
+        <v>46079</v>
       </c>
       <c r="F110" s="16" t="s">
-        <v>155</v>
+        <v>468</v>
       </c>
       <c r="G110" s="17">
         <v>1</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="I110" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>105</v>
       </c>
       <c r="B111" s="15"/>
@@ -9376,9 +9304,9 @@
       </c>
       <c r="H111" s="4"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>106</v>
       </c>
       <c r="B112" s="15"/>
@@ -9393,7 +9321,7 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>107</v>
       </c>
       <c r="B113" s="15"/>
@@ -9408,7 +9336,7 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>108</v>
       </c>
       <c r="B114" s="15"/>
@@ -9423,7 +9351,7 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>109</v>
       </c>
       <c r="B115" s="15"/>
@@ -9438,7 +9366,7 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A116:A117" si="3">+A115+1</f>
         <v>110</v>
       </c>
       <c r="B116" s="15"/>
@@ -9453,7 +9381,7 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>111</v>
       </c>
       <c r="B117" s="15"/>
@@ -9467,9 +9395,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I103">
-    <sortCondition ref="E7:E103"/>
-    <sortCondition ref="D7:D103"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I110">
+    <sortCondition ref="E7:E110"/>
+    <sortCondition ref="D7:D110"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>
@@ -9589,7 +9517,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="23"/>
@@ -9628,10 +9556,10 @@
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="11" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="4"/>
@@ -9653,16 +9581,16 @@
         <v>46082</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="G7" s="17">
         <v>1</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="J7" s="19"/>
       <c r="K7" s="4"/>
@@ -9673,7 +9601,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>18</v>
@@ -9701,7 +9629,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>18</v>
@@ -9741,16 +9669,16 @@
         <v>46083</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="G10" s="17">
         <v>1</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="I10" s="20" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="J10" s="20"/>
       <c r="K10" s="4"/>
@@ -9761,7 +9689,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>18</v>
@@ -9801,16 +9729,16 @@
         <v>46084</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="G12" s="17">
         <v>1</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="I12" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="J12" s="20"/>
       <c r="K12" s="4"/>
@@ -9833,16 +9761,16 @@
         <v>46084</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="G13" s="17">
         <v>1</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="I13" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="J13" s="20"/>
       <c r="K13" s="4"/>
@@ -9865,16 +9793,16 @@
         <v>46084</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="G14" s="17">
         <v>1</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="I14" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="J14" s="20"/>
       <c r="K14" s="4"/>
@@ -9897,16 +9825,16 @@
         <v>46084</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="G15" s="17">
         <v>1</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="I15" s="20" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="J15" s="20"/>
     </row>
@@ -9934,10 +9862,10 @@
         <v>1</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="J16" s="20"/>
     </row>
@@ -9965,10 +9893,10 @@
         <v>1</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="I17" s="20" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="J17" s="20"/>
     </row>
@@ -10005,7 +9933,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>18</v>
@@ -10032,7 +9960,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>18</v>
@@ -10059,7 +9987,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>18</v>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26609908-579F-429B-B849-D0DCCAA6C2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC228ECE-02DB-465B-9D40-A15EB39868B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Janvier 2026 " sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="542">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -1661,6 +1661,96 @@
   </si>
   <si>
     <t>B21278</t>
+  </si>
+  <si>
+    <t>B40210</t>
+  </si>
+  <si>
+    <t>NB(090/2026)</t>
+  </si>
+  <si>
+    <t>Reboud med</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt7 n18</t>
+  </si>
+  <si>
+    <t>NB(094/2026)</t>
+  </si>
+  <si>
+    <t>Goumaz ammar</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt2 n14</t>
+  </si>
+  <si>
+    <t>NB(077/2026)</t>
+  </si>
+  <si>
+    <t>Benzerga benyoucef</t>
+  </si>
+  <si>
+    <t>djenane tebal bloc01 n8</t>
+  </si>
+  <si>
+    <t>djenane tebal bloc01 n7</t>
+  </si>
+  <si>
+    <t>NB(076/2026)</t>
+  </si>
+  <si>
+    <t>Sahraoui fatma</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt5 n10</t>
+  </si>
+  <si>
+    <t>NB(632/2025)</t>
+  </si>
+  <si>
+    <t>NB(738/2025)</t>
+  </si>
+  <si>
+    <t>Daoudi saifeddine</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt7 n24</t>
+  </si>
+  <si>
+    <t>Fergani fethi</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt15 n33</t>
+  </si>
+  <si>
+    <t>NB(583/2025)</t>
+  </si>
+  <si>
+    <t>Serihi med</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt4 n25</t>
+  </si>
+  <si>
+    <t>NB(014/2026)</t>
+  </si>
+  <si>
+    <t>Mag ould zmirli nasreddine</t>
+  </si>
+  <si>
+    <t>rue amir aek</t>
+  </si>
+  <si>
+    <t>NB(023/2026)</t>
+  </si>
+  <si>
+    <t>Guessmia mahfoud</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt3 n10</t>
+  </si>
+  <si>
+    <t>NB(088/2026)</t>
   </si>
 </sst>
 </file>
@@ -9492,7 +9582,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -9532,7 +9622,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -9906,7 +9996,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>375</v>
+        <v>512</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>18</v>
@@ -10012,16 +10102,30 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="16"/>
+      <c r="B22" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="13">
+        <v>2025177591</v>
+      </c>
+      <c r="E22" s="15">
+        <v>46091</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>513</v>
+      </c>
       <c r="G22" s="17">
         <v>1</v>
       </c>
-      <c r="H22" s="18"/>
-      <c r="I22" s="20"/>
+      <c r="H22" s="18" t="s">
+        <v>514</v>
+      </c>
+      <c r="I22" t="s">
+        <v>515</v>
+      </c>
       <c r="J22" s="20"/>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10029,16 +10133,30 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="16"/>
+      <c r="B23" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="13">
+        <v>2025177600</v>
+      </c>
+      <c r="E23" s="15">
+        <v>46091</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>538</v>
+      </c>
       <c r="G23" s="17">
         <v>1</v>
       </c>
-      <c r="H23" s="18"/>
-      <c r="I23" s="20"/>
+      <c r="H23" s="18" t="s">
+        <v>536</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>537</v>
+      </c>
       <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10046,16 +10164,30 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="16"/>
+      <c r="B24" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="13">
+        <v>2025177851</v>
+      </c>
+      <c r="E24" s="15">
+        <v>46091</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>535</v>
+      </c>
       <c r="G24" s="17">
         <v>1</v>
       </c>
-      <c r="H24" s="18"/>
-      <c r="I24" s="20"/>
+      <c r="H24" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="I24" t="s">
+        <v>534</v>
+      </c>
       <c r="J24" s="20"/>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10063,16 +10195,30 @@
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="16"/>
+      <c r="B25" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="13">
+        <v>2025177852</v>
+      </c>
+      <c r="E25" s="15">
+        <v>46091</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>527</v>
+      </c>
       <c r="G25" s="17">
         <v>1</v>
       </c>
-      <c r="H25" s="18"/>
-      <c r="I25" s="20"/>
+      <c r="H25" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="I25" t="s">
+        <v>529</v>
+      </c>
       <c r="J25" s="20"/>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10080,16 +10226,30 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="16"/>
+      <c r="B26" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="13">
+        <v>2025177853</v>
+      </c>
+      <c r="E26" s="15">
+        <v>46091</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>526</v>
+      </c>
       <c r="G26" s="17">
         <v>1</v>
       </c>
-      <c r="H26" s="18"/>
-      <c r="I26" s="20"/>
+      <c r="H26" s="18" t="s">
+        <v>524</v>
+      </c>
+      <c r="I26" t="s">
+        <v>525</v>
+      </c>
       <c r="J26" s="20"/>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10097,16 +10257,30 @@
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="16"/>
+      <c r="B27" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="13">
+        <v>2025177854</v>
+      </c>
+      <c r="E27" s="15">
+        <v>46091</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>532</v>
+      </c>
       <c r="G27" s="17">
         <v>1</v>
       </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="20"/>
+      <c r="H27" s="18" t="s">
+        <v>530</v>
+      </c>
+      <c r="I27" t="s">
+        <v>531</v>
+      </c>
       <c r="J27" s="20"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10114,16 +10288,30 @@
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="16"/>
+      <c r="B28" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="13">
+        <v>2025177856</v>
+      </c>
+      <c r="E28" s="15">
+        <v>46091</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>516</v>
+      </c>
       <c r="G28" s="17">
         <v>1</v>
       </c>
-      <c r="H28" s="18"/>
-      <c r="I28" s="20"/>
+      <c r="H28" s="18" t="s">
+        <v>517</v>
+      </c>
+      <c r="I28" t="s">
+        <v>518</v>
+      </c>
       <c r="J28" s="20"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10131,16 +10319,30 @@
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="16"/>
+      <c r="B29" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="13">
+        <v>2025177857</v>
+      </c>
+      <c r="E29" s="15">
+        <v>46091</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>519</v>
+      </c>
       <c r="G29" s="17">
         <v>1</v>
       </c>
-      <c r="H29" s="4"/>
-      <c r="I29" s="20"/>
+      <c r="H29" s="18" t="s">
+        <v>520</v>
+      </c>
+      <c r="I29" t="s">
+        <v>521</v>
+      </c>
       <c r="J29" s="20"/>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10148,16 +10350,30 @@
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="16"/>
+      <c r="B30" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="13">
+        <v>2025177858</v>
+      </c>
+      <c r="E30" s="15">
+        <v>46091</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>523</v>
+      </c>
       <c r="G30" s="17">
         <v>1</v>
       </c>
-      <c r="H30" s="18"/>
-      <c r="I30" s="20"/>
+      <c r="H30" s="18" t="s">
+        <v>520</v>
+      </c>
+      <c r="I30" t="s">
+        <v>522</v>
+      </c>
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10165,16 +10381,30 @@
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="16"/>
+      <c r="B31" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="13">
+        <v>2025177859</v>
+      </c>
+      <c r="E31" s="15">
+        <v>46091</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>541</v>
+      </c>
       <c r="G31" s="17">
         <v>1</v>
       </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
+      <c r="H31" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="I31" t="s">
+        <v>540</v>
+      </c>
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11512,9 +11742,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I21">
-    <sortCondition ref="E7:E21"/>
-    <sortCondition ref="D7:D21"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I31">
+    <sortCondition ref="E7:E31"/>
+    <sortCondition ref="D7:D31"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC228ECE-02DB-465B-9D40-A15EB39868B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AA05A4-554F-40D3-B3E1-037A02984D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="548">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -1751,6 +1751,24 @@
   </si>
   <si>
     <t>NB(088/2026)</t>
+  </si>
+  <si>
+    <t>B21903</t>
+  </si>
+  <si>
+    <t>BC0330</t>
+  </si>
+  <si>
+    <t>2025178021</t>
+  </si>
+  <si>
+    <t>2025177932</t>
+  </si>
+  <si>
+    <t>Mag rahmi azzedine</t>
+  </si>
+  <si>
+    <t>NB(720/2025)</t>
   </si>
 </sst>
 </file>
@@ -9560,7 +9578,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -9582,7 +9600,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -9622,7 +9640,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -10412,11 +10430,21 @@
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="16"/>
+      <c r="B32" s="15" t="s">
+        <v>542</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="13">
+        <v>2025177855</v>
+      </c>
+      <c r="E32" s="15">
+        <v>46097</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G32" s="17">
         <v>1</v>
       </c>
@@ -10429,11 +10457,21 @@
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="16"/>
+      <c r="B33" s="13" t="s">
+        <v>543</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="E33" s="15">
+        <v>46107</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G33" s="17">
         <v>1</v>
       </c>
@@ -10446,16 +10484,30 @@
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="16"/>
+      <c r="B34" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>545</v>
+      </c>
+      <c r="E34" s="15">
+        <v>46110</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>547</v>
+      </c>
       <c r="G34" s="17">
         <v>1</v>
       </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="20"/>
+      <c r="H34" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="I34" s="20" t="s">
+        <v>537</v>
+      </c>
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AA05A4-554F-40D3-B3E1-037A02984D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62327D8-05C4-4B4B-8DEA-F632D2FECE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="586">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -1759,16 +1759,130 @@
     <t>BC0330</t>
   </si>
   <si>
-    <t>2025178021</t>
-  </si>
-  <si>
-    <t>2025177932</t>
-  </si>
-  <si>
-    <t>Mag rahmi azzedine</t>
-  </si>
-  <si>
     <t>NB(720/2025)</t>
+  </si>
+  <si>
+    <t>NB(638/2025)</t>
+  </si>
+  <si>
+    <t>Khelfi mourad</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt11 n04</t>
+  </si>
+  <si>
+    <t>Benzerga abderahmane</t>
+  </si>
+  <si>
+    <t>djenane tebbal n30</t>
+  </si>
+  <si>
+    <t>NB(746/2025)</t>
+  </si>
+  <si>
+    <t>NB(391/2025)</t>
+  </si>
+  <si>
+    <t>Benaicha aicha</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt16 n10</t>
+  </si>
+  <si>
+    <t>NB(004/2026)</t>
+  </si>
+  <si>
+    <t>Lakhel ezzine med</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt01 n31</t>
+  </si>
+  <si>
+    <t>Belkhir ziane &amp; ferrache fiala</t>
+  </si>
+  <si>
+    <t>residence chorfi A n22</t>
+  </si>
+  <si>
+    <t>NB(101/2026)</t>
+  </si>
+  <si>
+    <t>Bouziane ali</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt19 n21</t>
+  </si>
+  <si>
+    <t>NB(105/2026)</t>
+  </si>
+  <si>
+    <t>Hacene med</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt01 n17</t>
+  </si>
+  <si>
+    <t>NB(099/2026)</t>
+  </si>
+  <si>
+    <t>Mag rahmani azzedine</t>
+  </si>
+  <si>
+    <t>2025177737</t>
+  </si>
+  <si>
+    <t>NB(083/2026)</t>
+  </si>
+  <si>
+    <t>Pharmacie maasmi zineb</t>
+  </si>
+  <si>
+    <t>cite 40 logts bt29 n5</t>
+  </si>
+  <si>
+    <t>NB(096/2026)</t>
+  </si>
+  <si>
+    <t>Mag hasnaoui ramdane</t>
+  </si>
+  <si>
+    <t>cite 44 logts lsp b n16</t>
+  </si>
+  <si>
+    <t>2025177736</t>
+  </si>
+  <si>
+    <t>NB(010/2024)</t>
+  </si>
+  <si>
+    <t>Mag sebti billel</t>
+  </si>
+  <si>
+    <t>cite 40 logts auxibat bt n4</t>
+  </si>
+  <si>
+    <t>Masnouri med</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt 12 n33</t>
+  </si>
+  <si>
+    <t>B15888</t>
+  </si>
+  <si>
+    <t>NB(103/2026)</t>
+  </si>
+  <si>
+    <t>Korichi soufiane</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt 4 n38</t>
+  </si>
+  <si>
+    <t>BC0236</t>
+  </si>
+  <si>
+    <t>18041007795</t>
   </si>
 </sst>
 </file>
@@ -2048,8 +2162,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1200150</xdr:colOff>
-      <xdr:row>126</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2065,7 +2179,7 @@
       <xdr:spPr>
         <a:xfrm flipH="1">
           <a:off x="590550" y="19659600"/>
-          <a:ext cx="4448175" cy="4562475"/>
+          <a:ext cx="4448175" cy="2609850"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2464,7 +2578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A10B43B6-0248-48FC-B214-98DE0DBC6EF4}">
-  <dimension ref="A1:K208"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
@@ -2511,7 +2625,7 @@
       </c>
       <c r="J2" s="25"/>
       <c r="K2" s="6">
-        <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
+        <f>SUMIF(F7:F252,"Elimination*",G7:G252)</f>
         <v>35</v>
       </c>
     </row>
@@ -2533,7 +2647,7 @@
       </c>
       <c r="J3" s="25"/>
       <c r="K3" s="6">
-        <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
+        <f>SUMIF(F7:F252,"NB*",G7:G252)</f>
         <v>61</v>
       </c>
     </row>
@@ -2553,7 +2667,7 @@
       </c>
       <c r="J4" s="25"/>
       <c r="K4" s="6">
-        <f>SUMIF(F7:F364,"Ve*",G7:G364)</f>
+        <f>SUMIF(F7:F252,"Ve*",G7:G252)</f>
         <v>0</v>
       </c>
     </row>
@@ -4480,7 +4594,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="12">
-        <f t="shared" ref="A73:A136" si="1">+A72+1</f>
+        <f t="shared" ref="A73:A116" si="1">+A72+1</f>
         <v>67</v>
       </c>
       <c r="B73" s="15" t="s">
@@ -5437,1022 +5551,6 @@
         <v>1</v>
       </c>
       <c r="H116" s="4"/>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="12">
-        <f t="shared" si="1"/>
-        <v>111</v>
-      </c>
-      <c r="B117" s="15"/>
-      <c r="C117" s="13"/>
-      <c r="D117" s="14"/>
-      <c r="E117" s="15"/>
-      <c r="F117" s="16"/>
-      <c r="G117" s="17">
-        <v>1</v>
-      </c>
-      <c r="H117" s="4"/>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="12">
-        <f t="shared" si="1"/>
-        <v>112</v>
-      </c>
-      <c r="B118" s="15"/>
-      <c r="C118" s="13"/>
-      <c r="D118" s="14"/>
-      <c r="E118" s="15"/>
-      <c r="F118" s="16"/>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="12">
-        <f t="shared" si="1"/>
-        <v>113</v>
-      </c>
-      <c r="B119" s="15"/>
-      <c r="C119" s="13"/>
-      <c r="D119" s="14"/>
-      <c r="E119" s="15"/>
-      <c r="F119" s="16"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="12">
-        <f t="shared" si="1"/>
-        <v>114</v>
-      </c>
-      <c r="B120" s="15"/>
-      <c r="C120" s="13"/>
-      <c r="D120" s="14"/>
-      <c r="E120" s="15"/>
-      <c r="F120" s="16"/>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="12">
-        <f t="shared" si="1"/>
-        <v>115</v>
-      </c>
-      <c r="B121" s="15"/>
-      <c r="C121" s="13"/>
-      <c r="D121" s="14"/>
-      <c r="E121" s="15"/>
-      <c r="F121" s="16"/>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="12">
-        <f t="shared" si="1"/>
-        <v>116</v>
-      </c>
-      <c r="B122" s="15"/>
-      <c r="C122" s="13"/>
-      <c r="D122" s="14"/>
-      <c r="E122" s="15"/>
-      <c r="F122" s="16"/>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="12">
-        <f t="shared" si="1"/>
-        <v>117</v>
-      </c>
-      <c r="B123" s="15"/>
-      <c r="C123" s="13"/>
-      <c r="D123" s="14"/>
-      <c r="E123" s="15"/>
-      <c r="F123" s="16"/>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="12">
-        <f t="shared" si="1"/>
-        <v>118</v>
-      </c>
-      <c r="B124" s="15"/>
-      <c r="C124" s="13"/>
-      <c r="D124" s="14"/>
-      <c r="E124" s="15"/>
-      <c r="F124" s="16"/>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="12">
-        <f t="shared" si="1"/>
-        <v>119</v>
-      </c>
-      <c r="B125" s="15"/>
-      <c r="C125" s="13"/>
-      <c r="D125" s="14"/>
-      <c r="E125" s="15"/>
-      <c r="F125" s="16"/>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="12">
-        <f t="shared" si="1"/>
-        <v>120</v>
-      </c>
-      <c r="B126" s="15"/>
-      <c r="C126" s="13"/>
-      <c r="D126" s="14"/>
-      <c r="E126" s="15"/>
-      <c r="F126" s="16"/>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="12">
-        <f t="shared" si="1"/>
-        <v>121</v>
-      </c>
-      <c r="B127" s="15"/>
-      <c r="C127" s="13"/>
-      <c r="D127" s="14"/>
-      <c r="E127" s="15"/>
-      <c r="F127" s="16"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="12">
-        <f t="shared" si="1"/>
-        <v>122</v>
-      </c>
-      <c r="B128" s="15"/>
-      <c r="C128" s="13"/>
-      <c r="D128" s="14"/>
-      <c r="E128" s="15"/>
-      <c r="F128" s="16"/>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="12">
-        <f t="shared" si="1"/>
-        <v>123</v>
-      </c>
-      <c r="B129" s="15"/>
-      <c r="C129" s="13"/>
-      <c r="D129" s="14"/>
-      <c r="E129" s="15"/>
-      <c r="F129" s="16"/>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="12">
-        <f t="shared" si="1"/>
-        <v>124</v>
-      </c>
-      <c r="B130" s="15"/>
-      <c r="C130" s="13"/>
-      <c r="D130" s="14"/>
-      <c r="E130" s="15"/>
-      <c r="F130" s="16"/>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="12">
-        <f t="shared" si="1"/>
-        <v>125</v>
-      </c>
-      <c r="B131" s="15"/>
-      <c r="C131" s="13"/>
-      <c r="D131" s="14"/>
-      <c r="E131" s="15"/>
-      <c r="F131" s="16"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="12">
-        <f t="shared" si="1"/>
-        <v>126</v>
-      </c>
-      <c r="B132" s="15"/>
-      <c r="C132" s="13"/>
-      <c r="D132" s="14"/>
-      <c r="E132" s="15"/>
-      <c r="F132" s="16"/>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="12">
-        <f t="shared" si="1"/>
-        <v>127</v>
-      </c>
-      <c r="B133" s="15"/>
-      <c r="C133" s="13"/>
-      <c r="D133" s="14"/>
-      <c r="E133" s="15"/>
-      <c r="F133" s="16"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="12">
-        <f t="shared" si="1"/>
-        <v>128</v>
-      </c>
-      <c r="B134" s="15"/>
-      <c r="C134" s="13"/>
-      <c r="D134" s="14"/>
-      <c r="E134" s="15"/>
-      <c r="F134" s="16"/>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="12">
-        <f t="shared" si="1"/>
-        <v>129</v>
-      </c>
-      <c r="B135" s="15"/>
-      <c r="C135" s="13"/>
-      <c r="D135" s="14"/>
-      <c r="E135" s="15"/>
-      <c r="F135" s="16"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="12">
-        <f t="shared" si="1"/>
-        <v>130</v>
-      </c>
-      <c r="B136" s="15"/>
-      <c r="C136" s="13"/>
-      <c r="D136" s="14"/>
-      <c r="E136" s="15"/>
-      <c r="F136" s="16"/>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="12">
-        <f t="shared" ref="A137:A200" si="2">+A136+1</f>
-        <v>131</v>
-      </c>
-      <c r="B137" s="15"/>
-      <c r="C137" s="13"/>
-      <c r="D137" s="14"/>
-      <c r="E137" s="15"/>
-      <c r="F137" s="16"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="12">
-        <f t="shared" si="2"/>
-        <v>132</v>
-      </c>
-      <c r="B138" s="15"/>
-      <c r="C138" s="13"/>
-      <c r="D138" s="14"/>
-      <c r="E138" s="15"/>
-      <c r="F138" s="16"/>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="12">
-        <f t="shared" si="2"/>
-        <v>133</v>
-      </c>
-      <c r="B139" s="15"/>
-      <c r="C139" s="13"/>
-      <c r="D139" s="14"/>
-      <c r="E139" s="15"/>
-      <c r="F139" s="16"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="12">
-        <f t="shared" si="2"/>
-        <v>134</v>
-      </c>
-      <c r="B140" s="15"/>
-      <c r="C140" s="13"/>
-      <c r="D140" s="14"/>
-      <c r="E140" s="15"/>
-      <c r="F140" s="16"/>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="12">
-        <f t="shared" si="2"/>
-        <v>135</v>
-      </c>
-      <c r="B141" s="15"/>
-      <c r="C141" s="13"/>
-      <c r="D141" s="14"/>
-      <c r="E141" s="15"/>
-      <c r="F141" s="16"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="12">
-        <f t="shared" si="2"/>
-        <v>136</v>
-      </c>
-      <c r="B142" s="15"/>
-      <c r="C142" s="13"/>
-      <c r="D142" s="14"/>
-      <c r="E142" s="15"/>
-      <c r="F142" s="16"/>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="12">
-        <f t="shared" si="2"/>
-        <v>137</v>
-      </c>
-      <c r="B143" s="15"/>
-      <c r="C143" s="13"/>
-      <c r="D143" s="14"/>
-      <c r="E143" s="15"/>
-      <c r="F143" s="16"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="12">
-        <f t="shared" si="2"/>
-        <v>138</v>
-      </c>
-      <c r="B144" s="15"/>
-      <c r="C144" s="13"/>
-      <c r="D144" s="14"/>
-      <c r="E144" s="15"/>
-      <c r="F144" s="16"/>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="12">
-        <f t="shared" si="2"/>
-        <v>139</v>
-      </c>
-      <c r="B145" s="15"/>
-      <c r="C145" s="13"/>
-      <c r="D145" s="14"/>
-      <c r="E145" s="15"/>
-      <c r="F145" s="16"/>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" s="12">
-        <f t="shared" si="2"/>
-        <v>140</v>
-      </c>
-      <c r="B146" s="15"/>
-      <c r="C146" s="13"/>
-      <c r="D146" s="14"/>
-      <c r="E146" s="15"/>
-      <c r="F146" s="16"/>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" s="12">
-        <f t="shared" si="2"/>
-        <v>141</v>
-      </c>
-      <c r="B147" s="15"/>
-      <c r="C147" s="13"/>
-      <c r="D147" s="14"/>
-      <c r="E147" s="15"/>
-      <c r="F147" s="16"/>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" s="12">
-        <f t="shared" si="2"/>
-        <v>142</v>
-      </c>
-      <c r="B148" s="15"/>
-      <c r="C148" s="13"/>
-      <c r="D148" s="14"/>
-      <c r="E148" s="15"/>
-      <c r="F148" s="16"/>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" s="12">
-        <f t="shared" si="2"/>
-        <v>143</v>
-      </c>
-      <c r="B149" s="15"/>
-      <c r="C149" s="13"/>
-      <c r="D149" s="14"/>
-      <c r="E149" s="15"/>
-      <c r="F149" s="16"/>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" s="12">
-        <f t="shared" si="2"/>
-        <v>144</v>
-      </c>
-      <c r="B150" s="15"/>
-      <c r="C150" s="13"/>
-      <c r="D150" s="14"/>
-      <c r="E150" s="15"/>
-      <c r="F150" s="16"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" s="12">
-        <f t="shared" si="2"/>
-        <v>145</v>
-      </c>
-      <c r="B151" s="15"/>
-      <c r="C151" s="13"/>
-      <c r="D151" s="14"/>
-      <c r="E151" s="15"/>
-      <c r="F151" s="16"/>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="12">
-        <f t="shared" si="2"/>
-        <v>146</v>
-      </c>
-      <c r="B152" s="15"/>
-      <c r="C152" s="13"/>
-      <c r="D152" s="14"/>
-      <c r="E152" s="15"/>
-      <c r="F152" s="16"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" s="12">
-        <f t="shared" si="2"/>
-        <v>147</v>
-      </c>
-      <c r="B153" s="15"/>
-      <c r="C153" s="13"/>
-      <c r="D153" s="14"/>
-      <c r="E153" s="15"/>
-      <c r="F153" s="16"/>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A154" s="12">
-        <f t="shared" si="2"/>
-        <v>148</v>
-      </c>
-      <c r="B154" s="15"/>
-      <c r="C154" s="13"/>
-      <c r="D154" s="14"/>
-      <c r="E154" s="15"/>
-      <c r="F154" s="16"/>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" s="12">
-        <f t="shared" si="2"/>
-        <v>149</v>
-      </c>
-      <c r="B155" s="15"/>
-      <c r="C155" s="13"/>
-      <c r="D155" s="14"/>
-      <c r="E155" s="15"/>
-      <c r="F155" s="16"/>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A156" s="12">
-        <f t="shared" si="2"/>
-        <v>150</v>
-      </c>
-      <c r="B156" s="15"/>
-      <c r="C156" s="13"/>
-      <c r="D156" s="14"/>
-      <c r="E156" s="15"/>
-      <c r="F156" s="16"/>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157" s="12">
-        <f t="shared" si="2"/>
-        <v>151</v>
-      </c>
-      <c r="B157" s="15"/>
-      <c r="C157" s="13"/>
-      <c r="D157" s="14"/>
-      <c r="E157" s="15"/>
-      <c r="F157" s="16"/>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" s="12">
-        <f t="shared" si="2"/>
-        <v>152</v>
-      </c>
-      <c r="B158" s="15"/>
-      <c r="C158" s="13"/>
-      <c r="D158" s="14"/>
-      <c r="E158" s="15"/>
-      <c r="F158" s="16"/>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" s="12">
-        <f t="shared" si="2"/>
-        <v>153</v>
-      </c>
-      <c r="B159" s="15"/>
-      <c r="C159" s="13"/>
-      <c r="D159" s="14"/>
-      <c r="E159" s="15"/>
-      <c r="F159" s="16"/>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="12">
-        <f t="shared" si="2"/>
-        <v>154</v>
-      </c>
-      <c r="B160" s="15"/>
-      <c r="C160" s="13"/>
-      <c r="D160" s="14"/>
-      <c r="E160" s="15"/>
-      <c r="F160" s="16"/>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="12">
-        <f t="shared" si="2"/>
-        <v>155</v>
-      </c>
-      <c r="B161" s="15"/>
-      <c r="C161" s="13"/>
-      <c r="D161" s="14"/>
-      <c r="E161" s="15"/>
-      <c r="F161" s="16"/>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" s="12">
-        <f t="shared" si="2"/>
-        <v>156</v>
-      </c>
-      <c r="B162" s="15"/>
-      <c r="C162" s="13"/>
-      <c r="D162" s="14"/>
-      <c r="E162" s="15"/>
-      <c r="F162" s="16"/>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" s="12">
-        <f t="shared" si="2"/>
-        <v>157</v>
-      </c>
-      <c r="B163" s="15"/>
-      <c r="C163" s="13"/>
-      <c r="D163" s="14"/>
-      <c r="E163" s="15"/>
-      <c r="F163" s="16"/>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" s="12">
-        <f t="shared" si="2"/>
-        <v>158</v>
-      </c>
-      <c r="B164" s="15"/>
-      <c r="C164" s="13"/>
-      <c r="D164" s="14"/>
-      <c r="E164" s="15"/>
-      <c r="F164" s="16"/>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165" s="12">
-        <f t="shared" si="2"/>
-        <v>159</v>
-      </c>
-      <c r="B165" s="15"/>
-      <c r="C165" s="13"/>
-      <c r="D165" s="14"/>
-      <c r="E165" s="15"/>
-      <c r="F165" s="16"/>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" s="12">
-        <f t="shared" si="2"/>
-        <v>160</v>
-      </c>
-      <c r="B166" s="15"/>
-      <c r="C166" s="13"/>
-      <c r="D166" s="14"/>
-      <c r="E166" s="15"/>
-      <c r="F166" s="16"/>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" s="12">
-        <f t="shared" si="2"/>
-        <v>161</v>
-      </c>
-      <c r="B167" s="15"/>
-      <c r="C167" s="13"/>
-      <c r="D167" s="14"/>
-      <c r="E167" s="15"/>
-      <c r="F167" s="16"/>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" s="12">
-        <f t="shared" si="2"/>
-        <v>162</v>
-      </c>
-      <c r="B168" s="15"/>
-      <c r="C168" s="13"/>
-      <c r="D168" s="14"/>
-      <c r="E168" s="15"/>
-      <c r="F168" s="16"/>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" s="12">
-        <f t="shared" si="2"/>
-        <v>163</v>
-      </c>
-      <c r="B169" s="15"/>
-      <c r="C169" s="13"/>
-      <c r="D169" s="14"/>
-      <c r="E169" s="15"/>
-      <c r="F169" s="16"/>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" s="12">
-        <f t="shared" si="2"/>
-        <v>164</v>
-      </c>
-      <c r="B170" s="15"/>
-      <c r="C170" s="13"/>
-      <c r="D170" s="14"/>
-      <c r="E170" s="15"/>
-      <c r="F170" s="16"/>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171" s="12">
-        <f t="shared" si="2"/>
-        <v>165</v>
-      </c>
-      <c r="B171" s="15"/>
-      <c r="C171" s="13"/>
-      <c r="D171" s="14"/>
-      <c r="E171" s="15"/>
-      <c r="F171" s="16"/>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A172" s="12">
-        <f t="shared" si="2"/>
-        <v>166</v>
-      </c>
-      <c r="B172" s="15"/>
-      <c r="C172" s="13"/>
-      <c r="D172" s="14"/>
-      <c r="E172" s="15"/>
-      <c r="F172" s="16"/>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A173" s="12">
-        <f t="shared" si="2"/>
-        <v>167</v>
-      </c>
-      <c r="B173" s="15"/>
-      <c r="C173" s="13"/>
-      <c r="D173" s="14"/>
-      <c r="E173" s="15"/>
-      <c r="F173" s="16"/>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A174" s="12">
-        <f t="shared" si="2"/>
-        <v>168</v>
-      </c>
-      <c r="B174" s="15"/>
-      <c r="C174" s="13"/>
-      <c r="D174" s="14"/>
-      <c r="E174" s="15"/>
-      <c r="F174" s="16"/>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A175" s="12">
-        <f t="shared" si="2"/>
-        <v>169</v>
-      </c>
-      <c r="B175" s="15"/>
-      <c r="C175" s="13"/>
-      <c r="D175" s="14"/>
-      <c r="E175" s="15"/>
-      <c r="F175" s="16"/>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A176" s="12">
-        <f t="shared" si="2"/>
-        <v>170</v>
-      </c>
-      <c r="B176" s="15"/>
-      <c r="C176" s="13"/>
-      <c r="D176" s="14"/>
-      <c r="E176" s="15"/>
-      <c r="F176" s="16"/>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A177" s="12">
-        <f t="shared" si="2"/>
-        <v>171</v>
-      </c>
-      <c r="B177" s="15"/>
-      <c r="C177" s="13"/>
-      <c r="D177" s="14"/>
-      <c r="E177" s="15"/>
-      <c r="F177" s="16"/>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A178" s="12">
-        <f t="shared" si="2"/>
-        <v>172</v>
-      </c>
-      <c r="B178" s="15"/>
-      <c r="C178" s="13"/>
-      <c r="D178" s="14"/>
-      <c r="E178" s="15"/>
-      <c r="F178" s="16"/>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A179" s="12">
-        <f t="shared" si="2"/>
-        <v>173</v>
-      </c>
-      <c r="B179" s="15"/>
-      <c r="C179" s="13"/>
-      <c r="D179" s="14"/>
-      <c r="E179" s="15"/>
-      <c r="F179" s="16"/>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A180" s="12">
-        <f t="shared" si="2"/>
-        <v>174</v>
-      </c>
-      <c r="B180" s="15"/>
-      <c r="C180" s="13"/>
-      <c r="D180" s="14"/>
-      <c r="E180" s="15"/>
-      <c r="F180" s="16"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181" s="12">
-        <f t="shared" si="2"/>
-        <v>175</v>
-      </c>
-      <c r="B181" s="15"/>
-      <c r="C181" s="13"/>
-      <c r="D181" s="14"/>
-      <c r="E181" s="15"/>
-      <c r="F181" s="16"/>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A182" s="12">
-        <f t="shared" si="2"/>
-        <v>176</v>
-      </c>
-      <c r="B182" s="15"/>
-      <c r="C182" s="13"/>
-      <c r="D182" s="14"/>
-      <c r="E182" s="15"/>
-      <c r="F182" s="16"/>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183" s="12">
-        <f t="shared" si="2"/>
-        <v>177</v>
-      </c>
-      <c r="B183" s="15"/>
-      <c r="C183" s="13"/>
-      <c r="D183" s="14"/>
-      <c r="E183" s="15"/>
-      <c r="F183" s="16"/>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" s="12">
-        <f t="shared" si="2"/>
-        <v>178</v>
-      </c>
-      <c r="B184" s="15"/>
-      <c r="C184" s="13"/>
-      <c r="D184" s="14"/>
-      <c r="E184" s="15"/>
-      <c r="F184" s="16"/>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185" s="12">
-        <f t="shared" si="2"/>
-        <v>179</v>
-      </c>
-      <c r="B185" s="15"/>
-      <c r="C185" s="13"/>
-      <c r="D185" s="14"/>
-      <c r="E185" s="15"/>
-      <c r="F185" s="16"/>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A186" s="12">
-        <f t="shared" si="2"/>
-        <v>180</v>
-      </c>
-      <c r="B186" s="15"/>
-      <c r="C186" s="13"/>
-      <c r="D186" s="14"/>
-      <c r="E186" s="15"/>
-      <c r="F186" s="16"/>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187" s="12">
-        <f t="shared" si="2"/>
-        <v>181</v>
-      </c>
-      <c r="B187" s="15"/>
-      <c r="C187" s="13"/>
-      <c r="D187" s="14"/>
-      <c r="E187" s="15"/>
-      <c r="F187" s="16"/>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188" s="12">
-        <f t="shared" si="2"/>
-        <v>182</v>
-      </c>
-      <c r="B188" s="15"/>
-      <c r="C188" s="13"/>
-      <c r="D188" s="14"/>
-      <c r="E188" s="15"/>
-      <c r="F188" s="16"/>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A189" s="12">
-        <f t="shared" si="2"/>
-        <v>183</v>
-      </c>
-      <c r="B189" s="15"/>
-      <c r="C189" s="13"/>
-      <c r="D189" s="14"/>
-      <c r="E189" s="15"/>
-      <c r="F189" s="16"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A190" s="12">
-        <f t="shared" si="2"/>
-        <v>184</v>
-      </c>
-      <c r="B190" s="15"/>
-      <c r="C190" s="13"/>
-      <c r="D190" s="14"/>
-      <c r="E190" s="15"/>
-      <c r="F190" s="16"/>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A191" s="12">
-        <f t="shared" si="2"/>
-        <v>185</v>
-      </c>
-      <c r="B191" s="15"/>
-      <c r="C191" s="13"/>
-      <c r="D191" s="14"/>
-      <c r="E191" s="15"/>
-      <c r="F191" s="16"/>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A192" s="12">
-        <f t="shared" si="2"/>
-        <v>186</v>
-      </c>
-      <c r="B192" s="15"/>
-      <c r="C192" s="13"/>
-      <c r="D192" s="14"/>
-      <c r="E192" s="15"/>
-      <c r="F192" s="16"/>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A193" s="12">
-        <f t="shared" si="2"/>
-        <v>187</v>
-      </c>
-      <c r="B193" s="15"/>
-      <c r="C193" s="13"/>
-      <c r="D193" s="14"/>
-      <c r="E193" s="15"/>
-      <c r="F193" s="16"/>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A194" s="12">
-        <f t="shared" si="2"/>
-        <v>188</v>
-      </c>
-      <c r="B194" s="15"/>
-      <c r="C194" s="13"/>
-      <c r="D194" s="14"/>
-      <c r="E194" s="15"/>
-      <c r="F194" s="16"/>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A195" s="12">
-        <f t="shared" si="2"/>
-        <v>189</v>
-      </c>
-      <c r="B195" s="15"/>
-      <c r="C195" s="13"/>
-      <c r="D195" s="14"/>
-      <c r="E195" s="15"/>
-      <c r="F195" s="16"/>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A196" s="12">
-        <f t="shared" si="2"/>
-        <v>190</v>
-      </c>
-      <c r="B196" s="15"/>
-      <c r="C196" s="13"/>
-      <c r="D196" s="14"/>
-      <c r="E196" s="15"/>
-      <c r="F196" s="16"/>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A197" s="12">
-        <f t="shared" si="2"/>
-        <v>191</v>
-      </c>
-      <c r="B197" s="15"/>
-      <c r="C197" s="13"/>
-      <c r="D197" s="14"/>
-      <c r="E197" s="15"/>
-      <c r="F197" s="16"/>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A198" s="12">
-        <f t="shared" si="2"/>
-        <v>192</v>
-      </c>
-      <c r="B198" s="15"/>
-      <c r="C198" s="13"/>
-      <c r="D198" s="14"/>
-      <c r="E198" s="15"/>
-      <c r="F198" s="16"/>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A199" s="12">
-        <f t="shared" si="2"/>
-        <v>193</v>
-      </c>
-      <c r="B199" s="15"/>
-      <c r="C199" s="13"/>
-      <c r="D199" s="14"/>
-      <c r="E199" s="15"/>
-      <c r="F199" s="16"/>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200" s="12">
-        <f t="shared" si="2"/>
-        <v>194</v>
-      </c>
-      <c r="B200" s="15"/>
-      <c r="C200" s="13"/>
-      <c r="D200" s="14"/>
-      <c r="E200" s="15"/>
-      <c r="F200" s="16"/>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A201" s="12">
-        <f t="shared" ref="A201:A208" si="3">+A200+1</f>
-        <v>195</v>
-      </c>
-      <c r="B201" s="15"/>
-      <c r="C201" s="13"/>
-      <c r="D201" s="14"/>
-      <c r="E201" s="15"/>
-      <c r="F201" s="16"/>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202" s="12">
-        <f t="shared" si="3"/>
-        <v>196</v>
-      </c>
-      <c r="B202" s="15"/>
-      <c r="C202" s="13"/>
-      <c r="D202" s="14"/>
-      <c r="E202" s="15"/>
-      <c r="F202" s="16"/>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A203" s="12">
-        <f t="shared" si="3"/>
-        <v>197</v>
-      </c>
-      <c r="B203" s="15"/>
-      <c r="C203" s="13"/>
-      <c r="D203" s="14"/>
-      <c r="E203" s="15"/>
-      <c r="F203" s="16"/>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A204" s="12">
-        <f t="shared" si="3"/>
-        <v>198</v>
-      </c>
-      <c r="B204" s="15"/>
-      <c r="C204" s="13"/>
-      <c r="D204" s="14"/>
-      <c r="E204" s="15"/>
-      <c r="F204" s="16"/>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A205" s="12">
-        <f t="shared" si="3"/>
-        <v>199</v>
-      </c>
-      <c r="B205" s="15"/>
-      <c r="C205" s="13"/>
-      <c r="D205" s="14"/>
-      <c r="E205" s="15"/>
-      <c r="F205" s="16"/>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" s="12">
-        <f t="shared" si="3"/>
-        <v>200</v>
-      </c>
-      <c r="B206" s="15"/>
-      <c r="C206" s="13"/>
-      <c r="D206" s="14"/>
-      <c r="E206" s="15"/>
-      <c r="F206" s="16"/>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A207" s="12">
-        <f t="shared" si="3"/>
-        <v>201</v>
-      </c>
-      <c r="B207" s="15"/>
-      <c r="C207" s="13"/>
-      <c r="D207" s="14"/>
-      <c r="E207" s="15"/>
-      <c r="F207" s="16"/>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A208" s="12">
-        <f t="shared" si="3"/>
-        <v>202</v>
-      </c>
-      <c r="B208" s="15"/>
-      <c r="C208" s="13"/>
-      <c r="D208" s="14"/>
-      <c r="E208" s="15"/>
-      <c r="F208" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -9535,6 +8633,7 @@
   <cols>
     <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" customWidth="1"/>
     <col min="6" max="6" width="18.28515625" customWidth="1"/>
     <col min="7" max="7" width="4.7109375" hidden="1" customWidth="1"/>
@@ -9578,7 +8677,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -9600,7 +8699,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -9640,7 +8739,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -10457,26 +9556,30 @@
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>543</v>
+      <c r="B33" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="14" t="s">
-        <v>544</v>
+      <c r="D33" s="13">
+        <v>2025178026</v>
       </c>
       <c r="E33" s="15">
-        <v>46107</v>
+        <v>46097</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>162</v>
+        <v>550</v>
       </c>
       <c r="G33" s="17">
         <v>1</v>
       </c>
-      <c r="H33" s="18"/>
-      <c r="I33" s="20"/>
+      <c r="H33" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="I33" s="20" t="s">
+        <v>549</v>
+      </c>
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10485,28 +9588,28 @@
         <v>28</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="13">
+        <v>2025178029</v>
+      </c>
+      <c r="E34" s="15">
+        <v>46097</v>
+      </c>
+      <c r="F34" s="16" t="s">
         <v>545</v>
       </c>
-      <c r="E34" s="15">
-        <v>46110</v>
-      </c>
-      <c r="F34" s="16" t="s">
+      <c r="G34" s="17">
+        <v>1</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>546</v>
+      </c>
+      <c r="I34" t="s">
         <v>547</v>
-      </c>
-      <c r="G34" s="17">
-        <v>1</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="I34" s="20" t="s">
-        <v>537</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -10515,16 +9618,30 @@
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="16"/>
+      <c r="B35" s="13" t="s">
+        <v>580</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="13">
+        <v>2025178030</v>
+      </c>
+      <c r="E35" s="15">
+        <v>46097</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>581</v>
+      </c>
       <c r="G35" s="17">
         <v>1</v>
       </c>
-      <c r="H35" s="18"/>
-      <c r="I35" s="20"/>
+      <c r="H35" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="I35" t="s">
+        <v>583</v>
+      </c>
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10532,16 +9649,30 @@
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="16"/>
+      <c r="B36" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="13">
+        <v>2025178028</v>
+      </c>
+      <c r="E36" s="15">
+        <v>46100</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>554</v>
+      </c>
       <c r="G36" s="17">
         <v>1</v>
       </c>
-      <c r="H36" s="4"/>
-      <c r="I36" s="20"/>
+      <c r="H36" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="I36" t="s">
+        <v>556</v>
+      </c>
       <c r="J36" s="4"/>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10549,16 +9680,30 @@
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="16"/>
+      <c r="B37" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="13">
+        <v>2025178022</v>
+      </c>
+      <c r="E37" s="15">
+        <v>46104</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>551</v>
+      </c>
       <c r="G37" s="17">
         <v>1</v>
       </c>
-      <c r="H37" s="4"/>
-      <c r="I37" s="20"/>
+      <c r="H37" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="I37" t="s">
+        <v>553</v>
+      </c>
       <c r="J37" s="4"/>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10566,16 +9711,30 @@
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="16"/>
+      <c r="B38" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="13">
+        <v>2025178023</v>
+      </c>
+      <c r="E38" s="15">
+        <v>46104</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>562</v>
+      </c>
       <c r="G38" s="17">
         <v>1</v>
       </c>
-      <c r="H38" s="4"/>
-      <c r="I38" s="20"/>
+      <c r="H38" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="I38" t="s">
+        <v>561</v>
+      </c>
       <c r="J38" s="4"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -10583,79 +9742,145 @@
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="16"/>
+      <c r="B39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="13">
+        <v>2025178027</v>
+      </c>
+      <c r="E39" s="15">
+        <v>46104</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>559</v>
+      </c>
       <c r="G39" s="17">
         <v>1</v>
       </c>
-      <c r="H39" s="18"/>
-      <c r="I39" s="20"/>
+      <c r="H39" s="18" t="s">
+        <v>557</v>
+      </c>
+      <c r="I39" s="20" t="s">
+        <v>558</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
         <f>+A39+1</f>
         <v>34</v>
       </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="16"/>
+      <c r="B40" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="13">
+        <v>2025178024</v>
+      </c>
+      <c r="E40" s="15">
+        <v>46106</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>565</v>
+      </c>
       <c r="G40" s="17">
         <v>1</v>
       </c>
-      <c r="H40" s="4"/>
-      <c r="I40" s="20"/>
+      <c r="H40" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="I40" t="s">
+        <v>564</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="16"/>
+      <c r="B41" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="13">
+        <v>2025178025</v>
+      </c>
+      <c r="E41" s="15">
+        <v>46106</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>571</v>
+      </c>
       <c r="G41" s="17">
         <v>1</v>
       </c>
-      <c r="H41" s="4"/>
-      <c r="I41" s="20"/>
+      <c r="H41" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="I41" t="s">
+        <v>573</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="16"/>
+      <c r="B42" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="13">
+        <v>2025177931</v>
+      </c>
+      <c r="E42" s="15">
+        <v>46107</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>544</v>
+      </c>
       <c r="G42" s="17">
         <v>1</v>
       </c>
-      <c r="H42" s="4"/>
-      <c r="I42" s="20"/>
+      <c r="H42" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="I42" t="s">
+        <v>579</v>
+      </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="16"/>
+      <c r="B43" s="13" t="s">
+        <v>543</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="13">
+        <v>2025178021</v>
+      </c>
+      <c r="E43" s="15">
+        <v>46107</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G43" s="17">
         <v>1</v>
       </c>
-      <c r="H43" s="4"/>
+      <c r="H43" s="18"/>
       <c r="I43" s="20"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -10663,59 +9888,111 @@
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="B44" s="15"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="16"/>
+      <c r="B44" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>574</v>
+      </c>
+      <c r="E44" s="15">
+        <v>46107</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>575</v>
+      </c>
       <c r="G44" s="17">
         <v>1</v>
       </c>
-      <c r="H44" s="4"/>
-      <c r="I44" s="20"/>
+      <c r="H44" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="I44" t="s">
+        <v>577</v>
+      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="12">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="16"/>
+      <c r="B45" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="E45" s="15">
+        <v>46107</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>568</v>
+      </c>
       <c r="G45" s="17">
         <v>1</v>
       </c>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
+      <c r="H45" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="I45" t="s">
+        <v>570</v>
+      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="12">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="16"/>
+      <c r="B46" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="13">
+        <v>2025177932</v>
+      </c>
+      <c r="E46" s="15">
+        <v>46110</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>544</v>
+      </c>
       <c r="G46" s="17">
         <v>1</v>
       </c>
-      <c r="H46" s="4"/>
-      <c r="I46" s="20"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H46" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="I46" s="20" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="16"/>
+      <c r="B47" s="13" t="s">
+        <v>584</v>
+      </c>
+      <c r="C47" s="13">
+        <v>30</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>585</v>
+      </c>
+      <c r="E47" s="15">
+        <v>46112</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G47" s="17">
         <v>1</v>
       </c>
@@ -11794,9 +11071,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I31">
-    <sortCondition ref="E7:E31"/>
-    <sortCondition ref="D7:D31"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I46">
+    <sortCondition ref="E7:E46"/>
+    <sortCondition ref="D7:D46"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62327D8-05C4-4B4B-8DEA-F632D2FECE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045D4F3A-D2BB-4CD7-BC6E-B2E8342637D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Janvier 2026 " sheetId="2" r:id="rId1"/>
     <sheet name="Février 2026" sheetId="1" r:id="rId2"/>
     <sheet name="Mars 2026" sheetId="3" r:id="rId3"/>
+    <sheet name="Avril 2026" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Avril 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Février 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Janvier 2026 '!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mars 2026'!$1:$6</definedName>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="603">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -1883,6 +1885,78 @@
   </si>
   <si>
     <t>18041007795</t>
+  </si>
+  <si>
+    <t>NB(115/2026)</t>
+  </si>
+  <si>
+    <t>Benaddad djamel</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt 13 n25</t>
+  </si>
+  <si>
+    <t>Kouadri abdelrahim</t>
+  </si>
+  <si>
+    <t>cite 720 aadl bt 8 n36</t>
+  </si>
+  <si>
+    <t>NB(106/2026)</t>
+  </si>
+  <si>
+    <t>Talbi safia</t>
+  </si>
+  <si>
+    <t>NB(120/2026)</t>
+  </si>
+  <si>
+    <r>
+      <t>Mois de Avril</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <t>Aid med</t>
+  </si>
+  <si>
+    <t>Rebhi ayman</t>
+  </si>
+  <si>
+    <t>720 aadl bloc 4 n26</t>
+  </si>
+  <si>
+    <t>720 aadl bloc 17 n31</t>
+  </si>
+  <si>
+    <t>NB(112/2026)</t>
+  </si>
+  <si>
+    <t>Benaissane hacen</t>
+  </si>
+  <si>
+    <t>720 aadl bloc 15 n37</t>
+  </si>
+  <si>
+    <t>NB(111/2026)</t>
   </si>
 </sst>
 </file>
@@ -2315,6 +2389,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>104785</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connecteur droit 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24C23E79-7F7F-417E-9E58-9A20FC4299A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="695335" y="21678900"/>
+          <a:ext cx="4743440" cy="238125"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -8699,7 +8828,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -8739,7 +8868,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -10004,48 +10133,90 @@
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="16"/>
+      <c r="B48" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="13">
+        <v>2025177935</v>
+      </c>
+      <c r="E48" s="15">
+        <v>46112</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>586</v>
+      </c>
       <c r="G48" s="17">
         <v>1</v>
       </c>
-      <c r="H48" s="4"/>
-      <c r="I48" s="20"/>
+      <c r="H48" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="I48" t="s">
+        <v>588</v>
+      </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="12">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="16"/>
+      <c r="B49" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="13">
+        <v>2025177934</v>
+      </c>
+      <c r="E49" s="15">
+        <v>46112</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>591</v>
+      </c>
       <c r="G49" s="17">
         <v>1</v>
       </c>
-      <c r="H49" s="4"/>
-      <c r="I49" s="20"/>
+      <c r="H49" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="I49" t="s">
+        <v>590</v>
+      </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="12">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="16"/>
+      <c r="B50" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="13">
+        <v>2025177933</v>
+      </c>
+      <c r="E50" s="15">
+        <v>46112</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>593</v>
+      </c>
       <c r="G50" s="17">
         <v>1</v>
       </c>
-      <c r="H50" s="4"/>
-      <c r="I50" s="20"/>
+      <c r="H50" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="I50" t="s">
+        <v>558</v>
+      </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="12">
@@ -11093,4 +11264,1952 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95F13438-98C9-4F81-B39D-4B0DEC2DB426}">
+  <dimension ref="A1:K117"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+    <col min="9" max="9" width="32.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="25"/>
+      <c r="K2" s="6">
+        <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="25"/>
+      <c r="K3" s="6">
+        <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="25"/>
+      <c r="K4" s="6">
+        <f>SUMIF(F7:F364,"Ve*",G7:G364)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>594</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="8">
+        <f>SUM(K2:K4)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>1</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="13">
+        <v>2025177938</v>
+      </c>
+      <c r="E7" s="15">
+        <v>46113</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="G7" s="17">
+        <v>1</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>595</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>597</v>
+      </c>
+      <c r="J7" s="19"/>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <f t="shared" ref="A8:A71" si="0">+A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="13">
+        <v>2025177937</v>
+      </c>
+      <c r="E8" s="15">
+        <v>46113</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>599</v>
+      </c>
+      <c r="G8" s="17">
+        <v>1</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>596</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="J8" s="20"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="13">
+        <v>2025177936</v>
+      </c>
+      <c r="E9" s="15">
+        <v>46113</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="G9" s="17">
+        <v>1</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>600</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>601</v>
+      </c>
+      <c r="J9" s="20"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="17">
+        <v>1</v>
+      </c>
+      <c r="H10" s="18"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="17">
+        <v>1</v>
+      </c>
+      <c r="H11" s="18"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="17">
+        <v>1</v>
+      </c>
+      <c r="H12" s="18"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17">
+        <v>1</v>
+      </c>
+      <c r="H13" s="18"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="17">
+        <v>1</v>
+      </c>
+      <c r="H14" s="18"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17">
+        <v>1</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="17">
+        <v>1</v>
+      </c>
+      <c r="H16" s="18"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17">
+        <v>1</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="17">
+        <v>1</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="17">
+        <v>1</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="17">
+        <v>1</v>
+      </c>
+      <c r="H20" s="18"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="17">
+        <v>1</v>
+      </c>
+      <c r="H21" s="18"/>
+      <c r="J21" s="20"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17">
+        <v>1</v>
+      </c>
+      <c r="H22" s="18"/>
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="17">
+        <v>1</v>
+      </c>
+      <c r="H23" s="18"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="17">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4"/>
+      <c r="J24" s="20"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="J25" s="20"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="17">
+        <v>1</v>
+      </c>
+      <c r="H26" s="18"/>
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17">
+        <v>1</v>
+      </c>
+      <c r="H27" s="18"/>
+      <c r="J27" s="20"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17">
+        <v>1</v>
+      </c>
+      <c r="H28" s="18"/>
+      <c r="J28" s="20"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="12">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17">
+        <v>1</v>
+      </c>
+      <c r="H29" s="18"/>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17">
+        <v>1</v>
+      </c>
+      <c r="H30" s="18"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="17">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="15"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="17">
+        <v>1</v>
+      </c>
+      <c r="H32" s="18"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="12">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="15"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="17">
+        <v>1</v>
+      </c>
+      <c r="H33" s="4"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="12">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="15"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="17">
+        <v>1</v>
+      </c>
+      <c r="H34" s="18"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="12">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="17">
+        <v>1</v>
+      </c>
+      <c r="H35" s="4"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="12">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="15"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="17">
+        <v>1</v>
+      </c>
+      <c r="H36" s="4"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="12">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="15"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="17">
+        <v>1</v>
+      </c>
+      <c r="H37" s="4"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="12">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="15"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="17">
+        <v>1</v>
+      </c>
+      <c r="H38" s="4"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="12">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B39" s="15"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="17">
+        <v>1</v>
+      </c>
+      <c r="H39" s="18"/>
+      <c r="I39" s="20"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="12">
+        <f>+A39+1</f>
+        <v>34</v>
+      </c>
+      <c r="B40" s="15"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="17">
+        <v>1</v>
+      </c>
+      <c r="H40" s="4"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="12">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="17">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="12">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="17">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="12">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="17">
+        <v>1</v>
+      </c>
+      <c r="H43" s="18"/>
+      <c r="I43" s="20"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="12">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="17">
+        <v>1</v>
+      </c>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="12">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="17">
+        <v>1</v>
+      </c>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="12">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="15"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="17">
+        <v>1</v>
+      </c>
+      <c r="H46" s="4"/>
+      <c r="I46" s="20"/>
+    </row>
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="12">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="17">
+        <v>1</v>
+      </c>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="12">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B48" s="15"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="17">
+        <v>1</v>
+      </c>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="12">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B49" s="15"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="17">
+        <v>1</v>
+      </c>
+      <c r="H49" s="4"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="12">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B50" s="15"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="17">
+        <v>1</v>
+      </c>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="12">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="17">
+        <v>1</v>
+      </c>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="12">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="17">
+        <v>1</v>
+      </c>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="12">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="17">
+        <v>1</v>
+      </c>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="12">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B54" s="15"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="17">
+        <v>1</v>
+      </c>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="12">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B55" s="15"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="17">
+        <v>1</v>
+      </c>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="12">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B56" s="15"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="17">
+        <v>1</v>
+      </c>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="12">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="17">
+        <v>1</v>
+      </c>
+      <c r="H57" s="4"/>
+      <c r="I57" s="20"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="12">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B58" s="15"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="17">
+        <v>1</v>
+      </c>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="12">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B59" s="15"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="17">
+        <v>1</v>
+      </c>
+      <c r="H59" s="4"/>
+      <c r="I59" s="20"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="12">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B60" s="15"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="17">
+        <v>1</v>
+      </c>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="12">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B61" s="15"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="17">
+        <v>1</v>
+      </c>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="12">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B62" s="15"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="17">
+        <v>1</v>
+      </c>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="12">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B63" s="15"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="17">
+        <v>1</v>
+      </c>
+      <c r="H63" s="4"/>
+      <c r="I63" s="20"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="12">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B64" s="15"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="15"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="17">
+        <v>1</v>
+      </c>
+      <c r="H64" s="4"/>
+      <c r="I64" s="20"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="12">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B65" s="15"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="17">
+        <v>1</v>
+      </c>
+      <c r="H65" s="4"/>
+      <c r="I65" s="20"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="12">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="17">
+        <v>1</v>
+      </c>
+      <c r="H66" s="4"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="12">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B67" s="15"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="15"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="17">
+        <v>1</v>
+      </c>
+      <c r="H67" s="4"/>
+      <c r="I67" s="20"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="12">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B68" s="15"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="17">
+        <v>1</v>
+      </c>
+      <c r="H68" s="4"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="12">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B69" s="15"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="17">
+        <v>1</v>
+      </c>
+      <c r="H69" s="4"/>
+      <c r="I69" s="20"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="12">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B70" s="15"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="17">
+        <v>1</v>
+      </c>
+      <c r="H70" s="4"/>
+      <c r="I70" s="20"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="12">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B71" s="15"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="17">
+        <v>1</v>
+      </c>
+      <c r="H71" s="4"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="12">
+        <f t="shared" ref="A72:A117" si="1">+A71+1</f>
+        <v>66</v>
+      </c>
+      <c r="B72" s="15"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="17">
+        <v>1</v>
+      </c>
+      <c r="H72" s="4"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="12">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="B73" s="15"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="17">
+        <v>1</v>
+      </c>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="12">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="B74" s="15"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="17">
+        <v>1</v>
+      </c>
+      <c r="H74" s="4"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="12">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B75" s="15"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="17">
+        <v>1</v>
+      </c>
+      <c r="H75" s="4"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="12">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="B76" s="15"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="17">
+        <v>1</v>
+      </c>
+      <c r="H76" s="4"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="12">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="B77" s="15"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="17">
+        <v>1</v>
+      </c>
+      <c r="H77" s="4"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="12">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="B78" s="15"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="17">
+        <v>1</v>
+      </c>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="12">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="B79" s="15"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="17">
+        <v>1</v>
+      </c>
+      <c r="H79" s="4"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="12">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="B80" s="15"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="17">
+        <v>1</v>
+      </c>
+      <c r="H80" s="4"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="12">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="B81" s="15"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="17">
+        <v>1</v>
+      </c>
+      <c r="H81" s="4"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="12">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="B82" s="15"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="17">
+        <v>1</v>
+      </c>
+      <c r="H82" s="4"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="12">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="B83" s="15"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="17">
+        <v>1</v>
+      </c>
+      <c r="H83" s="4"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="12">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="B84" s="15"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="15"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="17">
+        <v>1</v>
+      </c>
+      <c r="H84" s="4"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="12">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="B85" s="15"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="16"/>
+      <c r="G85" s="17">
+        <v>1</v>
+      </c>
+      <c r="H85" s="4"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="12">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="B86" s="15"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="16"/>
+      <c r="G86" s="17">
+        <v>1</v>
+      </c>
+      <c r="H86" s="4"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="12">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="B87" s="15"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="17">
+        <v>1</v>
+      </c>
+      <c r="H87" s="4"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="12">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="B88" s="15"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="17">
+        <v>1</v>
+      </c>
+      <c r="H88" s="4"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="12">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="B89" s="15"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="17">
+        <v>1</v>
+      </c>
+      <c r="H89" s="4"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="12">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="B90" s="15"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="16"/>
+      <c r="G90" s="17">
+        <v>1</v>
+      </c>
+      <c r="H90" s="4"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="12">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="B91" s="15"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="17">
+        <v>1</v>
+      </c>
+      <c r="H91" s="4"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="12">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="B92" s="15"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="17">
+        <v>1</v>
+      </c>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="12">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="B93" s="15"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="17">
+        <v>1</v>
+      </c>
+      <c r="H93" s="4"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="12">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="B94" s="15"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="15"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="17">
+        <v>1</v>
+      </c>
+      <c r="H94" s="4"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="12">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="B95" s="15"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="15"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="17">
+        <v>1</v>
+      </c>
+      <c r="H95" s="4"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="12">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="B96" s="15"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="16"/>
+      <c r="G96" s="17">
+        <v>1</v>
+      </c>
+      <c r="H96" s="4"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="12">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="B97" s="15"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="16"/>
+      <c r="G97" s="17">
+        <v>1</v>
+      </c>
+      <c r="H97" s="4"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="12">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="B98" s="15"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="16"/>
+      <c r="G98" s="17">
+        <v>1</v>
+      </c>
+      <c r="H98" s="4"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="12">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="B99" s="15"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="15"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="17">
+        <v>1</v>
+      </c>
+      <c r="H99" s="4"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="12">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="B100" s="15"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="15"/>
+      <c r="F100" s="16"/>
+      <c r="G100" s="17">
+        <v>1</v>
+      </c>
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="12">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="B101" s="15"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="16"/>
+      <c r="G101" s="17">
+        <v>1</v>
+      </c>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="12">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="B102" s="15"/>
+      <c r="C102" s="13"/>
+      <c r="D102" s="14"/>
+      <c r="E102" s="15"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="17">
+        <v>1</v>
+      </c>
+      <c r="H102" s="4"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="12">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="B103" s="15"/>
+      <c r="C103" s="13"/>
+      <c r="D103" s="14"/>
+      <c r="E103" s="15"/>
+      <c r="F103" s="16"/>
+      <c r="G103" s="17">
+        <v>1</v>
+      </c>
+      <c r="H103" s="4"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="12">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="B104" s="15"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="22"/>
+      <c r="E104" s="15"/>
+      <c r="F104" s="16"/>
+      <c r="G104" s="17">
+        <v>1</v>
+      </c>
+      <c r="H104" s="4"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="12">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="B105" s="15"/>
+      <c r="C105" s="13"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="15"/>
+      <c r="F105" s="16"/>
+      <c r="G105" s="17">
+        <v>1</v>
+      </c>
+      <c r="H105" s="4"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="12">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="B106" s="15"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="15"/>
+      <c r="F106" s="16"/>
+      <c r="G106" s="17">
+        <v>1</v>
+      </c>
+      <c r="H106" s="4"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="12">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="B107" s="15"/>
+      <c r="C107" s="13"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="15"/>
+      <c r="F107" s="16"/>
+      <c r="G107" s="17">
+        <v>1</v>
+      </c>
+      <c r="H107" s="4"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="12">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="B108" s="15"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="14"/>
+      <c r="E108" s="15"/>
+      <c r="F108" s="16"/>
+      <c r="G108" s="17">
+        <v>1</v>
+      </c>
+      <c r="H108" s="4"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="12">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="B109" s="15"/>
+      <c r="C109" s="13"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="15"/>
+      <c r="F109" s="16"/>
+      <c r="G109" s="17">
+        <v>1</v>
+      </c>
+      <c r="H109" s="4"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="12">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="B110" s="15"/>
+      <c r="C110" s="13"/>
+      <c r="D110" s="14"/>
+      <c r="E110" s="15"/>
+      <c r="F110" s="16"/>
+      <c r="G110" s="17">
+        <v>1</v>
+      </c>
+      <c r="H110" s="4"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="12">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="B111" s="15"/>
+      <c r="C111" s="13"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="15"/>
+      <c r="F111" s="16"/>
+      <c r="G111" s="17">
+        <v>1</v>
+      </c>
+      <c r="H111" s="4"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="12">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="B112" s="15"/>
+      <c r="C112" s="13"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="15"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="17">
+        <v>1</v>
+      </c>
+      <c r="H112" s="4"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="12">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="B113" s="15"/>
+      <c r="C113" s="13"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="15"/>
+      <c r="F113" s="16"/>
+      <c r="G113" s="17">
+        <v>1</v>
+      </c>
+      <c r="H113" s="4"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="12">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="B114" s="15"/>
+      <c r="C114" s="13"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="15"/>
+      <c r="F114" s="16"/>
+      <c r="G114" s="17">
+        <v>1</v>
+      </c>
+      <c r="H114" s="4"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="12">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="B115" s="15"/>
+      <c r="C115" s="13"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="15"/>
+      <c r="F115" s="16"/>
+      <c r="G115" s="17">
+        <v>1</v>
+      </c>
+      <c r="H115" s="4"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="12">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="B116" s="15"/>
+      <c r="C116" s="13"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="15"/>
+      <c r="F116" s="16"/>
+      <c r="G116" s="17">
+        <v>1</v>
+      </c>
+      <c r="H116" s="4"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="12">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="B117" s="15"/>
+      <c r="C117" s="13"/>
+      <c r="D117" s="14"/>
+      <c r="E117" s="15"/>
+      <c r="F117" s="16"/>
+      <c r="G117" s="17">
+        <v>1</v>
+      </c>
+      <c r="H117" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="I4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283472" right="0.45" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045D4F3A-D2BB-4CD7-BC6E-B2E8342637D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52822236-4690-4D66-A908-C49607DAF8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="588">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -1674,39 +1674,24 @@
     <t>Reboud med</t>
   </si>
   <si>
-    <t>cite 720 aadl bt7 n18</t>
-  </si>
-  <si>
     <t>NB(094/2026)</t>
   </si>
   <si>
     <t>Goumaz ammar</t>
   </si>
   <si>
-    <t>cite 720 aadl bt2 n14</t>
-  </si>
-  <si>
     <t>NB(077/2026)</t>
   </si>
   <si>
     <t>Benzerga benyoucef</t>
   </si>
   <si>
-    <t>djenane tebal bloc01 n8</t>
-  </si>
-  <si>
-    <t>djenane tebal bloc01 n7</t>
-  </si>
-  <si>
     <t>NB(076/2026)</t>
   </si>
   <si>
     <t>Sahraoui fatma</t>
   </si>
   <si>
-    <t>cite 720 aadl bt5 n10</t>
-  </si>
-  <si>
     <t>NB(632/2025)</t>
   </si>
   <si>
@@ -1716,42 +1701,27 @@
     <t>Daoudi saifeddine</t>
   </si>
   <si>
-    <t>cite 720 aadl bt7 n24</t>
-  </si>
-  <si>
     <t>Fergani fethi</t>
   </si>
   <si>
-    <t>cite 720 aadl bt15 n33</t>
-  </si>
-  <si>
     <t>NB(583/2025)</t>
   </si>
   <si>
     <t>Serihi med</t>
   </si>
   <si>
-    <t>cite 720 aadl bt4 n25</t>
-  </si>
-  <si>
     <t>NB(014/2026)</t>
   </si>
   <si>
     <t>Mag ould zmirli nasreddine</t>
   </si>
   <si>
-    <t>rue amir aek</t>
-  </si>
-  <si>
     <t>NB(023/2026)</t>
   </si>
   <si>
     <t>Guessmia mahfoud</t>
   </si>
   <si>
-    <t>cite 720 aadl bt3 n10</t>
-  </si>
-  <si>
     <t>NB(088/2026)</t>
   </si>
   <si>
@@ -1770,15 +1740,9 @@
     <t>Khelfi mourad</t>
   </si>
   <si>
-    <t>cite 720 aadl bt11 n04</t>
-  </si>
-  <si>
     <t>Benzerga abderahmane</t>
   </si>
   <si>
-    <t>djenane tebbal n30</t>
-  </si>
-  <si>
     <t>NB(746/2025)</t>
   </si>
   <si>
@@ -1788,42 +1752,27 @@
     <t>Benaicha aicha</t>
   </si>
   <si>
-    <t>cite 720 aadl bt16 n10</t>
-  </si>
-  <si>
     <t>NB(004/2026)</t>
   </si>
   <si>
     <t>Lakhel ezzine med</t>
   </si>
   <si>
-    <t>cite 720 aadl bt01 n31</t>
-  </si>
-  <si>
     <t>Belkhir ziane &amp; ferrache fiala</t>
   </si>
   <si>
-    <t>residence chorfi A n22</t>
-  </si>
-  <si>
     <t>NB(101/2026)</t>
   </si>
   <si>
     <t>Bouziane ali</t>
   </si>
   <si>
-    <t>cite 720 aadl bt19 n21</t>
-  </si>
-  <si>
     <t>NB(105/2026)</t>
   </si>
   <si>
     <t>Hacene med</t>
   </si>
   <si>
-    <t>cite 720 aadl bt01 n17</t>
-  </si>
-  <si>
     <t>NB(099/2026)</t>
   </si>
   <si>
@@ -1839,18 +1788,12 @@
     <t>Pharmacie maasmi zineb</t>
   </si>
   <si>
-    <t>cite 40 logts bt29 n5</t>
-  </si>
-  <si>
     <t>NB(096/2026)</t>
   </si>
   <si>
     <t>Mag hasnaoui ramdane</t>
   </si>
   <si>
-    <t>cite 44 logts lsp b n16</t>
-  </si>
-  <si>
     <t>2025177736</t>
   </si>
   <si>
@@ -1860,15 +1803,9 @@
     <t>Mag sebti billel</t>
   </si>
   <si>
-    <t>cite 40 logts auxibat bt n4</t>
-  </si>
-  <si>
     <t>Masnouri med</t>
   </si>
   <si>
-    <t>cite 720 aadl bt 12 n33</t>
-  </si>
-  <si>
     <t>B15888</t>
   </si>
   <si>
@@ -1878,9 +1815,6 @@
     <t>Korichi soufiane</t>
   </si>
   <si>
-    <t>cite 720 aadl bt 4 n38</t>
-  </si>
-  <si>
     <t>BC0236</t>
   </si>
   <si>
@@ -1893,13 +1827,7 @@
     <t>Benaddad djamel</t>
   </si>
   <si>
-    <t>cite 720 aadl bt 13 n25</t>
-  </si>
-  <si>
     <t>Kouadri abdelrahim</t>
-  </si>
-  <si>
-    <t>cite 720 aadl bt 8 n36</t>
   </si>
   <si>
     <t>NB(106/2026)</t>
@@ -1957,6 +1885,33 @@
   </si>
   <si>
     <t>NB(111/2026)</t>
+  </si>
+  <si>
+    <t>B14651</t>
+  </si>
+  <si>
+    <t>B33347</t>
+  </si>
+  <si>
+    <t>BC0073</t>
+  </si>
+  <si>
+    <t>B35639</t>
+  </si>
+  <si>
+    <t>NB(119/2026)</t>
+  </si>
+  <si>
+    <t>residence chrofi bt A n6</t>
+  </si>
+  <si>
+    <t>Amri salima</t>
+  </si>
+  <si>
+    <t>720 aadl bloc 11 n13</t>
+  </si>
+  <si>
+    <t>NB(114/2026)</t>
   </si>
 </sst>
 </file>
@@ -2386,6 +2341,56 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1209675</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Connecteur droit 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D29C794-A465-5DA6-4CF4-A77023659A90}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="581025" y="9705975"/>
+          <a:ext cx="4733925" cy="6877050"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -9369,9 +9374,6 @@
       <c r="H22" s="18" t="s">
         <v>514</v>
       </c>
-      <c r="I22" t="s">
-        <v>515</v>
-      </c>
       <c r="J22" s="20"/>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9392,17 +9394,15 @@
         <v>46091</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="G23" s="17">
         <v>1</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>536</v>
-      </c>
-      <c r="I23" s="20" t="s">
-        <v>537</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="I23" s="20"/>
       <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9423,16 +9423,13 @@
         <v>46091</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="G24" s="17">
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="I24" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="J24" s="20"/>
     </row>
@@ -9454,16 +9451,13 @@
         <v>46091</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="G25" s="17">
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="I25" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="J25" s="20"/>
     </row>
@@ -9485,16 +9479,13 @@
         <v>46091</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="G26" s="17">
         <v>1</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>524</v>
-      </c>
-      <c r="I26" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="J26" s="20"/>
     </row>
@@ -9516,16 +9507,13 @@
         <v>46091</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="G27" s="17">
         <v>1</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>530</v>
-      </c>
-      <c r="I27" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="J27" s="20"/>
     </row>
@@ -9547,16 +9535,13 @@
         <v>46091</v>
       </c>
       <c r="F28" s="16" t="s">
+        <v>515</v>
+      </c>
+      <c r="G28" s="17">
+        <v>1</v>
+      </c>
+      <c r="H28" s="18" t="s">
         <v>516</v>
-      </c>
-      <c r="G28" s="17">
-        <v>1</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>517</v>
-      </c>
-      <c r="I28" t="s">
-        <v>518</v>
       </c>
       <c r="J28" s="20"/>
     </row>
@@ -9578,16 +9563,13 @@
         <v>46091</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G29" s="17">
         <v>1</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>520</v>
-      </c>
-      <c r="I29" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="J29" s="20"/>
     </row>
@@ -9609,16 +9591,13 @@
         <v>46091</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="G30" s="17">
         <v>1</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>520</v>
-      </c>
-      <c r="I30" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="J30" s="4"/>
     </row>
@@ -9640,16 +9619,13 @@
         <v>46091</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="G31" s="17">
         <v>1</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="I31" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="J31" s="4"/>
     </row>
@@ -9659,7 +9635,7 @@
         <v>26</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>18</v>
@@ -9698,17 +9674,15 @@
         <v>46097</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="G33" s="17">
         <v>1</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="I33" s="20" t="s">
-        <v>549</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="I33" s="20"/>
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9729,16 +9703,13 @@
         <v>46097</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="G34" s="17">
         <v>1</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>546</v>
-      </c>
-      <c r="I34" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -9748,7 +9719,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>18</v>
@@ -9760,16 +9731,13 @@
         <v>46097</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>581</v>
+        <v>560</v>
       </c>
       <c r="G35" s="17">
         <v>1</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="I35" t="s">
-        <v>583</v>
+        <v>561</v>
       </c>
       <c r="J35" s="4"/>
     </row>
@@ -9791,16 +9759,13 @@
         <v>46100</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="G36" s="17">
         <v>1</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="I36" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="J36" s="4"/>
     </row>
@@ -9822,16 +9787,13 @@
         <v>46104</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="G37" s="17">
         <v>1</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="I37" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="J37" s="4"/>
     </row>
@@ -9853,16 +9815,13 @@
         <v>46104</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="G38" s="17">
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="I38" t="s">
-        <v>561</v>
+        <v>545</v>
       </c>
       <c r="J38" s="4"/>
     </row>
@@ -9884,17 +9843,15 @@
         <v>46104</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="G39" s="17">
         <v>1</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>557</v>
-      </c>
-      <c r="I39" s="20" t="s">
-        <v>558</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="I39" s="20"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
@@ -9914,16 +9871,13 @@
         <v>46106</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>565</v>
+        <v>548</v>
       </c>
       <c r="G40" s="17">
         <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="I40" t="s">
-        <v>564</v>
+        <v>547</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -9944,16 +9898,13 @@
         <v>46106</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>571</v>
+        <v>553</v>
       </c>
       <c r="G41" s="17">
         <v>1</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="I41" t="s">
-        <v>573</v>
+        <v>554</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -9974,16 +9925,13 @@
         <v>46107</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="G42" s="17">
         <v>1</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="I42" t="s">
-        <v>579</v>
+        <v>558</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -9992,7 +9940,7 @@
         <v>37</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>18</v>
@@ -10024,22 +9972,19 @@
         <v>18</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>574</v>
+        <v>555</v>
       </c>
       <c r="E44" s="15">
         <v>46107</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>575</v>
+        <v>556</v>
       </c>
       <c r="G44" s="17">
         <v>1</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="I44" t="s">
-        <v>577</v>
+        <v>557</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -10054,22 +9999,19 @@
         <v>18</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>567</v>
+        <v>550</v>
       </c>
       <c r="E45" s="15">
         <v>46107</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="G45" s="17">
         <v>1</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="I45" t="s">
-        <v>570</v>
+        <v>552</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -10090,17 +10032,15 @@
         <v>46110</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="G46" s="17">
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>566</v>
-      </c>
-      <c r="I46" s="20" t="s">
-        <v>537</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="I46" s="20"/>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
@@ -10108,13 +10048,13 @@
         <v>41</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>584</v>
+        <v>562</v>
       </c>
       <c r="C47" s="13">
         <v>30</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>585</v>
+        <v>563</v>
       </c>
       <c r="E47" s="15">
         <v>46112</v>
@@ -10146,16 +10086,13 @@
         <v>46112</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>586</v>
+        <v>564</v>
       </c>
       <c r="G48" s="17">
         <v>1</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="I48" t="s">
-        <v>588</v>
+        <v>565</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -10176,16 +10113,13 @@
         <v>46112</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>591</v>
+        <v>567</v>
       </c>
       <c r="G49" s="17">
         <v>1</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="I49" t="s">
-        <v>590</v>
+        <v>566</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -10206,16 +10140,13 @@
         <v>46112</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>593</v>
+        <v>569</v>
       </c>
       <c r="G50" s="17">
         <v>1</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="I50" t="s">
-        <v>558</v>
+        <v>568</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -11317,7 +11248,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -11339,7 +11270,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -11364,7 +11295,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>594</v>
+        <v>570</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="23"/>
@@ -11379,7 +11310,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -11422,22 +11353,22 @@
         <v>18</v>
       </c>
       <c r="D7" s="13">
-        <v>2025177938</v>
+        <v>2025177936</v>
       </c>
       <c r="E7" s="15">
         <v>46113</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="G7" s="17">
         <v>1</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>595</v>
+        <v>576</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>597</v>
+        <v>573</v>
       </c>
       <c r="J7" s="19"/>
       <c r="K7" s="4"/>
@@ -11460,16 +11391,16 @@
         <v>46113</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>599</v>
+        <v>575</v>
       </c>
       <c r="G8" s="17">
         <v>1</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>596</v>
+        <v>572</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>598</v>
+        <v>574</v>
       </c>
       <c r="J8" s="20"/>
       <c r="K8" s="4"/>
@@ -11486,22 +11417,22 @@
         <v>18</v>
       </c>
       <c r="D9" s="13">
-        <v>2025177936</v>
+        <v>2025177938</v>
       </c>
       <c r="E9" s="15">
         <v>46113</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>602</v>
+        <v>548</v>
       </c>
       <c r="G9" s="17">
         <v>1</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>600</v>
+        <v>571</v>
       </c>
       <c r="I9" s="20" t="s">
-        <v>601</v>
+        <v>577</v>
       </c>
       <c r="J9" s="20"/>
       <c r="K9" s="4"/>
@@ -11511,11 +11442,21 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="16"/>
+      <c r="B10" s="13" t="s">
+        <v>580</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="13">
+        <v>2025177939</v>
+      </c>
+      <c r="E10" s="15">
+        <v>46116</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G10" s="17">
         <v>1</v>
       </c>
@@ -11529,11 +11470,21 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="16"/>
+      <c r="B11" s="13" t="s">
+        <v>579</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="13">
+        <v>2025177940</v>
+      </c>
+      <c r="E11" s="15">
+        <v>46116</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G11" s="17">
         <v>1</v>
       </c>
@@ -11547,11 +11498,21 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="16"/>
+      <c r="B12" s="13" t="s">
+        <v>581</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="13">
+        <v>2025177731</v>
+      </c>
+      <c r="E12" s="15">
+        <v>46117</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G12" s="17">
         <v>1</v>
       </c>
@@ -11564,11 +11525,21 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="16"/>
+      <c r="B13" s="13" t="s">
+        <v>582</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="13">
+        <v>2025177732</v>
+      </c>
+      <c r="E13" s="15">
+        <v>46117</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G13" s="17">
         <v>1</v>
       </c>
@@ -11581,15 +11552,30 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="16"/>
+      <c r="B14" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="13">
+        <v>2025177734</v>
+      </c>
+      <c r="E14" s="15">
+        <v>46117</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>587</v>
+      </c>
       <c r="G14" s="17">
         <v>1</v>
       </c>
-      <c r="H14" s="18"/>
+      <c r="H14" s="18" t="s">
+        <v>585</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>586</v>
+      </c>
       <c r="J14" s="20"/>
       <c r="K14" s="4"/>
     </row>
@@ -11598,16 +11584,30 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="16"/>
+      <c r="B15" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="13">
+        <v>2025177739</v>
+      </c>
+      <c r="E15" s="15">
+        <v>46117</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>583</v>
+      </c>
       <c r="G15" s="17">
         <v>1</v>
       </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="20"/>
+      <c r="H15" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="I15" t="s">
+        <v>584</v>
+      </c>
       <c r="J15" s="20"/>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13194,6 +13194,10 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I15">
+    <sortCondition ref="E7:E15"/>
+    <sortCondition ref="D7:D15"/>
+  </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="I5:J5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52822236-4690-4D66-A908-C49607DAF8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56B512B-8EB5-491B-AB14-293BF698A161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="604">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -1912,6 +1912,54 @@
   </si>
   <si>
     <t>NB(114/2026)</t>
+  </si>
+  <si>
+    <t>NB(124/2026)</t>
+  </si>
+  <si>
+    <t>Mallah rachid</t>
+  </si>
+  <si>
+    <t>720 aadl bloc 19 n19</t>
+  </si>
+  <si>
+    <t>NB(655/2056)</t>
+  </si>
+  <si>
+    <t>Chouihi oussama</t>
+  </si>
+  <si>
+    <t>720 aadl bloc 11 n33</t>
+  </si>
+  <si>
+    <t>NB(674/2025)</t>
+  </si>
+  <si>
+    <t>Guezmir hamza</t>
+  </si>
+  <si>
+    <t>720 aadl bloc 11 n34</t>
+  </si>
+  <si>
+    <t>B40914</t>
+  </si>
+  <si>
+    <t>B41561</t>
+  </si>
+  <si>
+    <t>B41029</t>
+  </si>
+  <si>
+    <t>B41548</t>
+  </si>
+  <si>
+    <t>B41792</t>
+  </si>
+  <si>
+    <t>B41866</t>
+  </si>
+  <si>
+    <t>B41553</t>
   </si>
 </sst>
 </file>
@@ -11248,7 +11296,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -11270,7 +11318,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -11310,7 +11358,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -11449,7 +11497,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="13">
-        <v>2025177939</v>
+        <v>2025177738</v>
       </c>
       <c r="E10" s="15">
         <v>46116</v>
@@ -11559,22 +11607,22 @@
         <v>18</v>
       </c>
       <c r="D14" s="13">
-        <v>2025177734</v>
+        <v>2025177739</v>
       </c>
       <c r="E14" s="15">
         <v>46117</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="G14" s="17">
         <v>1</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>585</v>
-      </c>
-      <c r="I14" s="20" t="s">
-        <v>586</v>
+        <v>330</v>
+      </c>
+      <c r="I14" t="s">
+        <v>584</v>
       </c>
       <c r="J14" s="20"/>
       <c r="K14" s="4"/>
@@ -11591,22 +11639,22 @@
         <v>18</v>
       </c>
       <c r="D15" s="13">
-        <v>2025177739</v>
+        <v>2025177939</v>
       </c>
       <c r="E15" s="15">
         <v>46117</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="G15" s="17">
         <v>1</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="I15" t="s">
-        <v>584</v>
+        <v>585</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>586</v>
       </c>
       <c r="J15" s="20"/>
     </row>
@@ -11615,16 +11663,25 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="16"/>
+      <c r="B16" s="13" t="s">
+        <v>599</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="13">
+        <v>2025119571</v>
+      </c>
+      <c r="E16" s="15">
+        <v>46119</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G16" s="17">
         <v>1</v>
       </c>
       <c r="H16" s="18"/>
-      <c r="I16" s="20"/>
       <c r="J16" s="20"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11632,16 +11689,25 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="16"/>
+      <c r="B17" s="13" t="s">
+        <v>603</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="13">
+        <v>2025119572</v>
+      </c>
+      <c r="E17" s="15">
+        <v>46119</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G17" s="17">
         <v>1</v>
       </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="20"/>
+      <c r="H17" s="4"/>
       <c r="J17" s="20"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11649,16 +11715,25 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="16"/>
+      <c r="B18" s="13" t="s">
+        <v>602</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="13">
+        <v>2025119573</v>
+      </c>
+      <c r="E18" s="15">
+        <v>46119</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G18" s="17">
         <v>1</v>
       </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="20"/>
+      <c r="H18" s="4"/>
       <c r="J18" s="20"/>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11666,11 +11741,21 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
+      <c r="B19" s="13" t="s">
+        <v>601</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="13">
+        <v>2025119574</v>
+      </c>
+      <c r="E19" s="15">
+        <v>46119</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G19" s="17">
         <v>1</v>
       </c>
@@ -11683,11 +11768,21 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="16"/>
+      <c r="B20" s="13" t="s">
+        <v>597</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="13">
+        <v>2025119576</v>
+      </c>
+      <c r="E20" s="15">
+        <v>46119</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G20" s="17">
         <v>1</v>
       </c>
@@ -11700,15 +11795,26 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="16"/>
+      <c r="B21" s="13" t="s">
+        <v>598</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="13">
+        <v>2025119578</v>
+      </c>
+      <c r="E21" s="15">
+        <v>46119</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G21" s="17">
         <v>1</v>
       </c>
       <c r="H21" s="18"/>
+      <c r="I21" s="20"/>
       <c r="J21" s="20"/>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11716,11 +11822,21 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="16"/>
+      <c r="B22" s="13" t="s">
+        <v>600</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="13">
+        <v>2025119579</v>
+      </c>
+      <c r="E22" s="15">
+        <v>46119</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G22" s="17">
         <v>1</v>
       </c>
@@ -11732,16 +11848,30 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="16"/>
+      <c r="B23" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="13">
+        <v>2025177733</v>
+      </c>
+      <c r="E23" s="15">
+        <v>46119</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>594</v>
+      </c>
       <c r="G23" s="17">
         <v>1</v>
       </c>
-      <c r="H23" s="18"/>
-      <c r="I23" s="20"/>
+      <c r="H23" s="18" t="s">
+        <v>595</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>596</v>
+      </c>
       <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11749,15 +11879,30 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="16"/>
+      <c r="B24" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="13">
+        <v>2025177734</v>
+      </c>
+      <c r="E24" s="15">
+        <v>46119</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>591</v>
+      </c>
       <c r="G24" s="17">
         <v>1</v>
       </c>
-      <c r="H24" s="4"/>
+      <c r="H24" s="18" t="s">
+        <v>592</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>593</v>
+      </c>
       <c r="J24" s="20"/>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11765,15 +11910,30 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="16"/>
+      <c r="B25" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="13">
+        <v>2025177740</v>
+      </c>
+      <c r="E25" s="15">
+        <v>46119</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>588</v>
+      </c>
       <c r="G25" s="17">
         <v>1</v>
       </c>
-      <c r="H25" s="4"/>
+      <c r="H25" s="18" t="s">
+        <v>589</v>
+      </c>
+      <c r="I25" s="20" t="s">
+        <v>590</v>
+      </c>
       <c r="J25" s="20"/>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13194,9 +13354,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I15">
-    <sortCondition ref="E7:E15"/>
-    <sortCondition ref="D7:D15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I25">
+    <sortCondition ref="E7:E25"/>
+    <sortCondition ref="D7:D25"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56B512B-8EB5-491B-AB14-293BF698A161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12D8706-D2D5-4E45-BA65-84931302E200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="628">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -1960,6 +1960,78 @@
   </si>
   <si>
     <t>B41553</t>
+  </si>
+  <si>
+    <t>B41721</t>
+  </si>
+  <si>
+    <t>B41723</t>
+  </si>
+  <si>
+    <t>B41760</t>
+  </si>
+  <si>
+    <t>B41973</t>
+  </si>
+  <si>
+    <t>B40022</t>
+  </si>
+  <si>
+    <t>B40029</t>
+  </si>
+  <si>
+    <t>B42218</t>
+  </si>
+  <si>
+    <t>B42269</t>
+  </si>
+  <si>
+    <t>B42343</t>
+  </si>
+  <si>
+    <t>B41787</t>
+  </si>
+  <si>
+    <t>B10358</t>
+  </si>
+  <si>
+    <t>B10349</t>
+  </si>
+  <si>
+    <t>NB(095/2026)</t>
+  </si>
+  <si>
+    <t>Mag aliati adbelaziz</t>
+  </si>
+  <si>
+    <t>18 logts bt A</t>
+  </si>
+  <si>
+    <t>Benrached rachid</t>
+  </si>
+  <si>
+    <t>10 eme tranche n12</t>
+  </si>
+  <si>
+    <t>NB(063/2026)</t>
+  </si>
+  <si>
+    <t>NB(022/2026)</t>
+  </si>
+  <si>
+    <t>Azizane rabah</t>
+  </si>
+  <si>
+    <t>720 aadl bloc 18 n30</t>
+  </si>
+  <si>
+    <t>Mag arab boulares</t>
+  </si>
+  <si>
+    <t>cité djedi aek bt 28 n3</t>
+  </si>
+  <si>
+    <t>NB(210/2025)</t>
   </si>
 </sst>
 </file>
@@ -2124,7 +2196,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2207,6 +2279,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -11296,7 +11371,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -11318,7 +11393,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -11358,7 +11433,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -11941,11 +12016,21 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="16"/>
+      <c r="B26" s="13" t="s">
+        <v>604</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D26" s="13">
+        <v>2024004543</v>
+      </c>
+      <c r="E26" s="15">
+        <v>46120</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G26" s="17">
         <v>1</v>
       </c>
@@ -11957,11 +12042,21 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="16"/>
+      <c r="B27" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D27" s="13">
+        <v>2024004659</v>
+      </c>
+      <c r="E27" s="15">
+        <v>46120</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G27" s="17">
         <v>1</v>
       </c>
@@ -11973,15 +12068,25 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="16"/>
+      <c r="B28" s="13" t="s">
+        <v>613</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="13">
+        <v>2025177681</v>
+      </c>
+      <c r="E28" s="15">
+        <v>46120</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G28" s="17">
         <v>1</v>
       </c>
-      <c r="H28" s="18"/>
+      <c r="H28" s="4"/>
       <c r="J28" s="20"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11989,15 +12094,25 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="16"/>
+      <c r="B29" s="15" t="s">
+        <v>615</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="13">
+        <v>2025177682</v>
+      </c>
+      <c r="E29" s="15">
+        <v>46120</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G29" s="17">
         <v>1</v>
       </c>
-      <c r="H29" s="18"/>
+      <c r="H29" s="4"/>
       <c r="J29" s="20"/>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12005,11 +12120,21 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="16"/>
+      <c r="B30" s="15" t="s">
+        <v>612</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="13">
+        <v>2025177683</v>
+      </c>
+      <c r="E30" s="15">
+        <v>46120</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G30" s="17">
         <v>1</v>
       </c>
@@ -12021,15 +12146,26 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="16"/>
+      <c r="B31" s="15" t="s">
+        <v>611</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="13">
+        <v>2025177684</v>
+      </c>
+      <c r="E31" s="15">
+        <v>46120</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G31" s="17">
         <v>1</v>
       </c>
       <c r="H31" s="4"/>
+      <c r="I31" s="20"/>
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12037,16 +12173,25 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="16"/>
+      <c r="B32" s="15" t="s">
+        <v>614</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="13">
+        <v>2025177685</v>
+      </c>
+      <c r="E32" s="15">
+        <v>46120</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G32" s="17">
         <v>1</v>
       </c>
-      <c r="H32" s="18"/>
-      <c r="I32" s="20"/>
+      <c r="H32" s="4"/>
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12054,16 +12199,25 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="16"/>
+      <c r="B33" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="13">
+        <v>2025177686</v>
+      </c>
+      <c r="E33" s="15">
+        <v>46120</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G33" s="17">
         <v>1</v>
       </c>
       <c r="H33" s="4"/>
-      <c r="I33" s="20"/>
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12071,11 +12225,21 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="16"/>
+      <c r="B34" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="13">
+        <v>2025177687</v>
+      </c>
+      <c r="E34" s="15">
+        <v>46120</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G34" s="17">
         <v>1</v>
       </c>
@@ -12087,15 +12251,25 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="16"/>
+      <c r="B35" s="13" t="s">
+        <v>607</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="13">
+        <v>2025177688</v>
+      </c>
+      <c r="E35" s="15">
+        <v>46120</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G35" s="17">
         <v>1</v>
       </c>
-      <c r="H35" s="4"/>
+      <c r="H35" s="18"/>
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12103,15 +12277,25 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="16"/>
+      <c r="B36" s="13" t="s">
+        <v>605</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="13">
+        <v>2025177689</v>
+      </c>
+      <c r="E36" s="15">
+        <v>46120</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G36" s="17">
         <v>1</v>
       </c>
-      <c r="H36" s="4"/>
+      <c r="H36" s="18"/>
       <c r="J36" s="4"/>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12119,15 +12303,26 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="16"/>
+      <c r="B37" s="15" t="s">
+        <v>610</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="13">
+        <v>2025177690</v>
+      </c>
+      <c r="E37" s="15">
+        <v>46120</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G37" s="17">
         <v>1</v>
       </c>
-      <c r="H37" s="4"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="20"/>
       <c r="J37" s="4"/>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12135,15 +12330,30 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="16"/>
+      <c r="B38" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="13">
+        <v>2025119577</v>
+      </c>
+      <c r="E38" s="15">
+        <v>46124</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>616</v>
+      </c>
       <c r="G38" s="17">
         <v>1</v>
       </c>
-      <c r="H38" s="4"/>
+      <c r="H38" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="I38" t="s">
+        <v>618</v>
+      </c>
       <c r="J38" s="4"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -12151,46 +12361,90 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="16"/>
+      <c r="B39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="13">
+        <v>2025177348</v>
+      </c>
+      <c r="E39" s="15">
+        <v>46124</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>621</v>
+      </c>
       <c r="G39" s="17">
         <v>1</v>
       </c>
-      <c r="H39" s="18"/>
-      <c r="I39" s="20"/>
+      <c r="H39" s="18" t="s">
+        <v>619</v>
+      </c>
+      <c r="I39" s="20" t="s">
+        <v>620</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
         <f>+A39+1</f>
         <v>34</v>
       </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="16"/>
+      <c r="B40" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="13">
+        <v>2025177349</v>
+      </c>
+      <c r="E40" s="15">
+        <v>46124</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>622</v>
+      </c>
       <c r="G40" s="17">
         <v>1</v>
       </c>
-      <c r="H40" s="4"/>
+      <c r="H40" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="I40" s="20" t="s">
+        <v>624</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="16"/>
+      <c r="B41" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="13">
+        <v>2025177350</v>
+      </c>
+      <c r="E41" s="15">
+        <v>46124</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>627</v>
+      </c>
       <c r="G41" s="17">
         <v>1</v>
       </c>
-      <c r="H41" s="4"/>
+      <c r="H41" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="I41" s="29" t="s">
+        <v>626</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
@@ -13354,9 +13608,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I25">
-    <sortCondition ref="E7:E25"/>
-    <sortCondition ref="D7:D25"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I41">
+    <sortCondition ref="E7:E41"/>
+    <sortCondition ref="D7:D41"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12D8706-D2D5-4E45-BA65-84931302E200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57F7B3E-AFB6-43AB-B5AA-B378030DF864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="624">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -1869,21 +1869,12 @@
     <t>Rebhi ayman</t>
   </si>
   <si>
-    <t>720 aadl bloc 4 n26</t>
-  </si>
-  <si>
-    <t>720 aadl bloc 17 n31</t>
-  </si>
-  <si>
     <t>NB(112/2026)</t>
   </si>
   <si>
     <t>Benaissane hacen</t>
   </si>
   <si>
-    <t>720 aadl bloc 15 n37</t>
-  </si>
-  <si>
     <t>NB(111/2026)</t>
   </si>
   <si>
@@ -1896,21 +1887,12 @@
     <t>BC0073</t>
   </si>
   <si>
-    <t>B35639</t>
-  </si>
-  <si>
     <t>NB(119/2026)</t>
   </si>
   <si>
-    <t>residence chrofi bt A n6</t>
-  </si>
-  <si>
     <t>Amri salima</t>
   </si>
   <si>
-    <t>720 aadl bloc 11 n13</t>
-  </si>
-  <si>
     <t>NB(114/2026)</t>
   </si>
   <si>
@@ -1920,27 +1902,15 @@
     <t>Mallah rachid</t>
   </si>
   <si>
-    <t>720 aadl bloc 19 n19</t>
-  </si>
-  <si>
-    <t>NB(655/2056)</t>
-  </si>
-  <si>
     <t>Chouihi oussama</t>
   </si>
   <si>
-    <t>720 aadl bloc 11 n33</t>
-  </si>
-  <si>
     <t>NB(674/2025)</t>
   </si>
   <si>
     <t>Guezmir hamza</t>
   </si>
   <si>
-    <t>720 aadl bloc 11 n34</t>
-  </si>
-  <si>
     <t>B40914</t>
   </si>
   <si>
@@ -2004,15 +1974,9 @@
     <t>Mag aliati adbelaziz</t>
   </si>
   <si>
-    <t>18 logts bt A</t>
-  </si>
-  <si>
     <t>Benrached rachid</t>
   </si>
   <si>
-    <t>10 eme tranche n12</t>
-  </si>
-  <si>
     <t>NB(063/2026)</t>
   </si>
   <si>
@@ -2022,9 +1986,6 @@
     <t>Azizane rabah</t>
   </si>
   <si>
-    <t>720 aadl bloc 18 n30</t>
-  </si>
-  <si>
     <t>Mag arab boulares</t>
   </si>
   <si>
@@ -2032,6 +1993,33 @@
   </si>
   <si>
     <t>NB(210/2025)</t>
+  </si>
+  <si>
+    <t>B35629</t>
+  </si>
+  <si>
+    <t>NB(655/2025)</t>
+  </si>
+  <si>
+    <t>Benallal farida</t>
+  </si>
+  <si>
+    <t>720 aadl bloc 14 n18</t>
+  </si>
+  <si>
+    <t>NB(126/2026)</t>
+  </si>
+  <si>
+    <t>BC0819</t>
+  </si>
+  <si>
+    <t>NB(481/2025)</t>
+  </si>
+  <si>
+    <t>Belaissa azeddine</t>
+  </si>
+  <si>
+    <t>quartier z'mala</t>
   </si>
 </sst>
 </file>
@@ -2196,7 +2184,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2279,9 +2267,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -10009,7 +9994,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>257</v>
+        <v>620</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>18</v>
@@ -11393,7 +11378,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -11433,7 +11418,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -11482,17 +11467,15 @@
         <v>46113</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="G7" s="17">
         <v>1</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>576</v>
-      </c>
-      <c r="I7" s="20" t="s">
-        <v>573</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="I7" s="20"/>
       <c r="J7" s="19"/>
       <c r="K7" s="4"/>
     </row>
@@ -11514,7 +11497,7 @@
         <v>46113</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="G8" s="17">
         <v>1</v>
@@ -11522,9 +11505,7 @@
       <c r="H8" s="18" t="s">
         <v>572</v>
       </c>
-      <c r="I8" s="20" t="s">
-        <v>574</v>
-      </c>
+      <c r="I8" s="20"/>
       <c r="J8" s="20"/>
       <c r="K8" s="4"/>
     </row>
@@ -11554,9 +11535,7 @@
       <c r="H9" s="18" t="s">
         <v>571</v>
       </c>
-      <c r="I9" s="20" t="s">
-        <v>577</v>
-      </c>
+      <c r="I9" s="20"/>
       <c r="J9" s="20"/>
       <c r="K9" s="4"/>
     </row>
@@ -11566,16 +11545,16 @@
         <v>4</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="13">
-        <v>2025177738</v>
+        <v>2025177731</v>
       </c>
       <c r="E10" s="15">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="F10" s="16" t="s">
         <v>162</v>
@@ -11584,7 +11563,6 @@
         <v>1</v>
       </c>
       <c r="H10" s="18"/>
-      <c r="I10" s="20"/>
       <c r="J10" s="20"/>
       <c r="K10" s="4"/>
     </row>
@@ -11594,16 +11572,16 @@
         <v>5</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>579</v>
+        <v>615</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="13">
-        <v>2025177940</v>
+        <v>2025177732</v>
       </c>
       <c r="E11" s="15">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="F11" s="16" t="s">
         <v>162</v>
@@ -11612,7 +11590,6 @@
         <v>1</v>
       </c>
       <c r="H11" s="18"/>
-      <c r="I11" s="20"/>
       <c r="J11" s="20"/>
       <c r="K11" s="4"/>
     </row>
@@ -11622,13 +11599,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="13">
-        <v>2025177731</v>
+        <v>2025177738</v>
       </c>
       <c r="E12" s="15">
         <v>46117</v>
@@ -11640,6 +11617,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="18"/>
+      <c r="I12" s="20"/>
       <c r="J12" s="20"/>
       <c r="K12" s="4"/>
     </row>
@@ -11649,24 +11627,26 @@
         <v>7</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>582</v>
+        <v>19</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D13" s="13">
-        <v>2025177732</v>
+        <v>2025177739</v>
       </c>
       <c r="E13" s="15">
         <v>46117</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>162</v>
+        <v>579</v>
       </c>
       <c r="G13" s="17">
         <v>1</v>
       </c>
-      <c r="H13" s="18"/>
+      <c r="H13" s="18" t="s">
+        <v>330</v>
+      </c>
       <c r="J13" s="20"/>
       <c r="K13" s="4"/>
     </row>
@@ -11682,23 +11662,21 @@
         <v>18</v>
       </c>
       <c r="D14" s="13">
-        <v>2025177739</v>
+        <v>2025177939</v>
       </c>
       <c r="E14" s="15">
         <v>46117</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="G14" s="17">
         <v>1</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="I14" t="s">
-        <v>584</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="I14" s="20"/>
       <c r="J14" s="20"/>
       <c r="K14" s="4"/>
     </row>
@@ -11708,29 +11686,25 @@
         <v>9</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>19</v>
+        <v>576</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D15" s="13">
-        <v>2025177939</v>
+        <v>2025177940</v>
       </c>
       <c r="E15" s="15">
         <v>46117</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>587</v>
+        <v>162</v>
       </c>
       <c r="G15" s="17">
         <v>1</v>
       </c>
-      <c r="H15" s="18" t="s">
-        <v>585</v>
-      </c>
-      <c r="I15" s="20" t="s">
-        <v>586</v>
-      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="20"/>
       <c r="J15" s="20"/>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11739,7 +11713,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>18</v>
@@ -11765,7 +11739,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>18</v>
@@ -11791,7 +11765,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>18</v>
@@ -11817,7 +11791,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>18</v>
@@ -11844,7 +11818,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>18</v>
@@ -11871,7 +11845,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>18</v>
@@ -11898,7 +11872,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>18</v>
@@ -11936,17 +11910,15 @@
         <v>46119</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="G23" s="17">
         <v>1</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>595</v>
-      </c>
-      <c r="I23" s="20" t="s">
-        <v>596</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="I23" s="20"/>
       <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11967,17 +11939,15 @@
         <v>46119</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>591</v>
+        <v>616</v>
       </c>
       <c r="G24" s="17">
         <v>1</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>592</v>
-      </c>
-      <c r="I24" s="20" t="s">
-        <v>593</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="I24" s="20"/>
       <c r="J24" s="20"/>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11998,17 +11968,15 @@
         <v>46119</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="G25" s="17">
         <v>1</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>589</v>
-      </c>
-      <c r="I25" s="20" t="s">
-        <v>590</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="I25" s="20"/>
       <c r="J25" s="20"/>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12017,7 +11985,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>284</v>
@@ -12043,7 +12011,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>284</v>
@@ -12069,7 +12037,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>18</v>
@@ -12095,7 +12063,7 @@
         <v>23</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>18</v>
@@ -12121,7 +12089,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>18</v>
@@ -12147,7 +12115,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>18</v>
@@ -12174,7 +12142,7 @@
         <v>26</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>18</v>
@@ -12200,7 +12168,7 @@
         <v>27</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>18</v>
@@ -12226,7 +12194,7 @@
         <v>28</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>18</v>
@@ -12252,7 +12220,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>18</v>
@@ -12278,7 +12246,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="C36" s="13" t="s">
         <v>18</v>
@@ -12304,7 +12272,7 @@
         <v>31</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>18</v>
@@ -12343,16 +12311,13 @@
         <v>46124</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="G38" s="17">
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="I38" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="J38" s="4"/>
     </row>
@@ -12374,17 +12339,15 @@
         <v>46124</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="G39" s="17">
         <v>1</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>619</v>
-      </c>
-      <c r="I39" s="20" t="s">
-        <v>620</v>
-      </c>
+        <v>608</v>
+      </c>
+      <c r="I39" s="20"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
@@ -12404,17 +12367,15 @@
         <v>46124</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="G40" s="17">
         <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="I40" s="20" t="s">
-        <v>624</v>
-      </c>
+        <v>611</v>
+      </c>
+      <c r="I40" s="20"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
@@ -12434,16 +12395,16 @@
         <v>46124</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="G41" s="17">
         <v>1</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="I41" s="29" t="s">
-        <v>626</v>
+        <v>612</v>
+      </c>
+      <c r="I41" s="20" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -12451,31 +12412,60 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="16"/>
+      <c r="B42" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="13">
+        <v>2025177344</v>
+      </c>
+      <c r="E42" s="15">
+        <v>46126</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>619</v>
+      </c>
       <c r="G42" s="17">
         <v>1</v>
       </c>
-      <c r="H42" s="4"/>
+      <c r="H42" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="I42" s="20" t="s">
+        <v>618</v>
+      </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="16"/>
+      <c r="B43" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="13">
+        <v>2025177342</v>
+      </c>
+      <c r="E43" s="15">
+        <v>46127</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>621</v>
+      </c>
       <c r="G43" s="17">
         <v>1</v>
       </c>
-      <c r="H43" s="18"/>
-      <c r="I43" s="20"/>
+      <c r="H43" s="18" t="s">
+        <v>622</v>
+      </c>
+      <c r="I43" s="20" t="s">
+        <v>623</v>
+      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="12">

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57F7B3E-AFB6-43AB-B5AA-B378030DF864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40A68CB-3DA1-4026-B222-802D93D9EA2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="633">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -2020,6 +2020,33 @@
   </si>
   <si>
     <t>quartier z'mala</t>
+  </si>
+  <si>
+    <t>B21230</t>
+  </si>
+  <si>
+    <t>BB0038</t>
+  </si>
+  <si>
+    <t>23986205</t>
+  </si>
+  <si>
+    <t>NB(397/2025)</t>
+  </si>
+  <si>
+    <t>Ouatouat hadjira</t>
+  </si>
+  <si>
+    <t>720 aadl bloc 18 n6</t>
+  </si>
+  <si>
+    <t>NB(127/2026)</t>
+  </si>
+  <si>
+    <t>Djemmah tayeb</t>
+  </si>
+  <si>
+    <t>720 aadl bloc 18 n31</t>
   </si>
 </sst>
 </file>
@@ -11356,7 +11383,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -11378,7 +11405,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -11418,7 +11445,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -12472,11 +12499,21 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="16"/>
+      <c r="B44" s="13" t="s">
+        <v>624</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="13">
+        <v>2025177345</v>
+      </c>
+      <c r="E44" s="15">
+        <v>46127</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G44" s="17">
         <v>1</v>
       </c>
@@ -12487,11 +12524,21 @@
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="16"/>
+      <c r="B45" s="13" t="s">
+        <v>625</v>
+      </c>
+      <c r="C45" s="13">
+        <v>100</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>626</v>
+      </c>
+      <c r="E45" s="15">
+        <v>46127</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G45" s="17">
         <v>1</v>
       </c>
@@ -12502,32 +12549,60 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B46" s="15"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="16"/>
+      <c r="B46" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="13">
+        <v>2025177341</v>
+      </c>
+      <c r="E46" s="15">
+        <v>46128</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>627</v>
+      </c>
       <c r="G46" s="17">
         <v>1</v>
       </c>
-      <c r="H46" s="4"/>
-      <c r="I46" s="20"/>
+      <c r="H46" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="I46" s="20" t="s">
+        <v>629</v>
+      </c>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="16"/>
+      <c r="B47" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" s="13">
+        <v>2025177474</v>
+      </c>
+      <c r="E47" s="15">
+        <v>46128</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>630</v>
+      </c>
       <c r="G47" s="17">
         <v>1</v>
       </c>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
+      <c r="H47" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="I47" s="20" t="s">
+        <v>632</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="12">
@@ -13598,9 +13673,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I41">
-    <sortCondition ref="E7:E41"/>
-    <sortCondition ref="D7:D41"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I47">
+    <sortCondition ref="E7:E47"/>
+    <sortCondition ref="D7:D47"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40A68CB-3DA1-4026-B222-802D93D9EA2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5BEB20-22D7-4964-9098-9829FE3B6862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="707">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -1989,9 +1989,6 @@
     <t>Mag arab boulares</t>
   </si>
   <si>
-    <t>cité djedi aek bt 28 n3</t>
-  </si>
-  <si>
     <t>NB(210/2025)</t>
   </si>
   <si>
@@ -2004,9 +2001,6 @@
     <t>Benallal farida</t>
   </si>
   <si>
-    <t>720 aadl bloc 14 n18</t>
-  </si>
-  <si>
     <t>NB(126/2026)</t>
   </si>
   <si>
@@ -2019,9 +2013,6 @@
     <t>Belaissa azeddine</t>
   </si>
   <si>
-    <t>quartier z'mala</t>
-  </si>
-  <si>
     <t>B21230</t>
   </si>
   <si>
@@ -2037,16 +2028,247 @@
     <t>Ouatouat hadjira</t>
   </si>
   <si>
-    <t>720 aadl bloc 18 n6</t>
-  </si>
-  <si>
     <t>NB(127/2026)</t>
   </si>
   <si>
     <t>Djemmah tayeb</t>
   </si>
   <si>
-    <t>720 aadl bloc 18 n31</t>
+    <t>BC0510</t>
+  </si>
+  <si>
+    <t>Sabour mahmoud</t>
+  </si>
+  <si>
+    <t>720 bt 10 n18</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>Belmadoui med adlane</t>
+  </si>
+  <si>
+    <t>zmala</t>
+  </si>
+  <si>
+    <t>NB(089/2026)</t>
+  </si>
+  <si>
+    <t>Hatchane yacine</t>
+  </si>
+  <si>
+    <t>720 bt 11 n39</t>
+  </si>
+  <si>
+    <t>NB(137/2026)</t>
+  </si>
+  <si>
+    <t>NB(133/2026)</t>
+  </si>
+  <si>
+    <t>Bouksani lila</t>
+  </si>
+  <si>
+    <t>residence chorfi A n23</t>
+  </si>
+  <si>
+    <t>Laadjali aida</t>
+  </si>
+  <si>
+    <t>720 bt 12 n03</t>
+  </si>
+  <si>
+    <t>NB(134/2026)</t>
+  </si>
+  <si>
+    <t>Abdelouahab fatiha</t>
+  </si>
+  <si>
+    <t>720 bt 17 n11</t>
+  </si>
+  <si>
+    <t>NB(129/2026)</t>
+  </si>
+  <si>
+    <t>Khazaz djamila</t>
+  </si>
+  <si>
+    <t>720 bt 01 n21</t>
+  </si>
+  <si>
+    <t>NB(125/2026)</t>
+  </si>
+  <si>
+    <t>Maachou med</t>
+  </si>
+  <si>
+    <t>720 bt 12 n15</t>
+  </si>
+  <si>
+    <t>NB(629/2025)</t>
+  </si>
+  <si>
+    <t>Benhaoua zohir</t>
+  </si>
+  <si>
+    <t>720 bt 2 n21</t>
+  </si>
+  <si>
+    <t>NB(107/2026)</t>
+  </si>
+  <si>
+    <t>NB(150/2026)</t>
+  </si>
+  <si>
+    <t>Ayat mourad</t>
+  </si>
+  <si>
+    <t>720 bt 15 n16</t>
+  </si>
+  <si>
+    <t>Bechlagheme yacine</t>
+  </si>
+  <si>
+    <t>720 bt 06 n16</t>
+  </si>
+  <si>
+    <t>NB</t>
+  </si>
+  <si>
+    <t>Toubal samia</t>
+  </si>
+  <si>
+    <t>720 bt 12 n36</t>
+  </si>
+  <si>
+    <t>NB(140/2026)</t>
+  </si>
+  <si>
+    <t>Lachenani imad</t>
+  </si>
+  <si>
+    <t>720 bt 03 n06</t>
+  </si>
+  <si>
+    <t>NB(145/2026)</t>
+  </si>
+  <si>
+    <t>B10616</t>
+  </si>
+  <si>
+    <t>B10659</t>
+  </si>
+  <si>
+    <t>B10664</t>
+  </si>
+  <si>
+    <t>B11287</t>
+  </si>
+  <si>
+    <t>B11332</t>
+  </si>
+  <si>
+    <t>B11704</t>
+  </si>
+  <si>
+    <t>B12125</t>
+  </si>
+  <si>
+    <t>B12162</t>
+  </si>
+  <si>
+    <t>B12190</t>
+  </si>
+  <si>
+    <t>B13175</t>
+  </si>
+  <si>
+    <t>2025177185</t>
+  </si>
+  <si>
+    <t>2025177183</t>
+  </si>
+  <si>
+    <t>2025177184</t>
+  </si>
+  <si>
+    <t>2025177187</t>
+  </si>
+  <si>
+    <t>2025177188</t>
+  </si>
+  <si>
+    <t>2025177181</t>
+  </si>
+  <si>
+    <t>2025177182</t>
+  </si>
+  <si>
+    <t>2025177189</t>
+  </si>
+  <si>
+    <t>2025177190</t>
+  </si>
+  <si>
+    <t>2025177186</t>
+  </si>
+  <si>
+    <t>2025117922</t>
+  </si>
+  <si>
+    <t>Rabhallah aek</t>
+  </si>
+  <si>
+    <t>720 bt 08 n28</t>
+  </si>
+  <si>
+    <t>2025117925</t>
+  </si>
+  <si>
+    <t>NB(144/2026)</t>
+  </si>
+  <si>
+    <t>Sadok faiza</t>
+  </si>
+  <si>
+    <t>720 bt 15 n18</t>
+  </si>
+  <si>
+    <t>2025117921</t>
+  </si>
+  <si>
+    <t>Hadjadj kamel</t>
+  </si>
+  <si>
+    <t>720 bt 07 n21</t>
+  </si>
+  <si>
+    <t>NB(149/2026)</t>
+  </si>
+  <si>
+    <t>2025117924</t>
+  </si>
+  <si>
+    <t>NB(526/2023)</t>
+  </si>
+  <si>
+    <t>Hasnaoui ali</t>
+  </si>
+  <si>
+    <t>Hantabli n56</t>
+  </si>
+  <si>
+    <t>2025117923</t>
+  </si>
+  <si>
+    <t>NB(110/2026)</t>
+  </si>
+  <si>
+    <t>Djabri kheladi</t>
+  </si>
+  <si>
+    <t>djennane tebbal n132</t>
   </si>
 </sst>
 </file>
@@ -10021,7 +10243,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>18</v>
@@ -11383,7 +11605,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -11405,7 +11627,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -11445,7 +11667,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>41</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -11599,7 +11821,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>18</v>
@@ -11966,7 +12188,7 @@
         <v>46119</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G24" s="17">
         <v>1</v>
@@ -12410,7 +12632,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>18</v>
@@ -12422,7 +12644,7 @@
         <v>46124</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G41" s="17">
         <v>1</v>
@@ -12430,9 +12652,7 @@
       <c r="H41" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="I41" s="20" t="s">
-        <v>613</v>
-      </c>
+      <c r="I41" s="20"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
@@ -12452,17 +12672,15 @@
         <v>46126</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="G42" s="17">
         <v>1</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="I42" s="20" t="s">
-        <v>618</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="I42" s="20"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
@@ -12482,17 +12700,15 @@
         <v>46127</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G43" s="17">
         <v>1</v>
       </c>
       <c r="H43" s="18" t="s">
-        <v>622</v>
-      </c>
-      <c r="I43" s="20" t="s">
-        <v>623</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="I43" s="20"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="12">
@@ -12500,7 +12716,7 @@
         <v>38</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>18</v>
@@ -12525,13 +12741,13 @@
         <v>39</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C45" s="13">
         <v>100</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="E45" s="15">
         <v>46127</v>
@@ -12562,17 +12778,15 @@
         <v>46128</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="G46" s="17">
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="I46" s="20" t="s">
-        <v>629</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="I46" s="20"/>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
@@ -12592,28 +12806,36 @@
         <v>46128</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="G47" s="17">
         <v>1</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="I47" s="20" t="s">
-        <v>632</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="I47" s="20"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="12">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="16"/>
+      <c r="B48" s="15" t="s">
+        <v>628</v>
+      </c>
+      <c r="C48" s="13">
+        <v>40</v>
+      </c>
+      <c r="D48" s="13">
+        <v>14855527</v>
+      </c>
+      <c r="E48" s="15">
+        <v>46130</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G48" s="17">
         <v>1</v>
       </c>
@@ -12624,248 +12846,462 @@
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="16"/>
+      <c r="B49" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="13">
+        <v>2025177204</v>
+      </c>
+      <c r="E49" s="15">
+        <v>46133</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>655</v>
+      </c>
       <c r="G49" s="17">
         <v>1</v>
       </c>
-      <c r="H49" s="4"/>
+      <c r="H49" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="I49" t="s">
+        <v>654</v>
+      </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="12">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="16"/>
+      <c r="B50" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="13">
+        <v>2025177205</v>
+      </c>
+      <c r="E50" s="15">
+        <v>46133</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>652</v>
+      </c>
       <c r="G50" s="17">
         <v>1</v>
       </c>
-      <c r="H50" s="4"/>
+      <c r="H50" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="I50" t="s">
+        <v>651</v>
+      </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="12">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="16"/>
+      <c r="B51" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="13">
+        <v>2025177206</v>
+      </c>
+      <c r="E51" s="15">
+        <v>46133</v>
+      </c>
+      <c r="F51" s="16" t="s">
+        <v>646</v>
+      </c>
       <c r="G51" s="17">
         <v>1</v>
       </c>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
+      <c r="H51" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="I51" t="s">
+        <v>645</v>
+      </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="12">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="16"/>
+      <c r="B52" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="13">
+        <v>2025177207</v>
+      </c>
+      <c r="E52" s="15">
+        <v>46133</v>
+      </c>
+      <c r="F52" s="16" t="s">
+        <v>643</v>
+      </c>
       <c r="G52" s="17">
         <v>1</v>
       </c>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
+      <c r="H52" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="I52" t="s">
+        <v>642</v>
+      </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="12">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="16"/>
+      <c r="B53" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53" s="13">
+        <v>2025177208</v>
+      </c>
+      <c r="E53" s="15">
+        <v>46133</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>649</v>
+      </c>
       <c r="G53" s="17">
         <v>1</v>
       </c>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
+      <c r="H53" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="I53" t="s">
+        <v>648</v>
+      </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="12">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B54" s="15"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="16"/>
+      <c r="B54" s="15" t="s">
+        <v>631</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="13">
+        <v>2025177209</v>
+      </c>
+      <c r="E54" s="15">
+        <v>46133</v>
+      </c>
+      <c r="F54" s="16" t="s">
+        <v>634</v>
+      </c>
       <c r="G54" s="17">
         <v>1</v>
       </c>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
+      <c r="H54" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="I54" t="s">
+        <v>633</v>
+      </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="12">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B55" s="15"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="16"/>
+      <c r="B55" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D55" s="13">
+        <v>2025177210</v>
+      </c>
+      <c r="E55" s="15">
+        <v>46133</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>638</v>
+      </c>
       <c r="G55" s="17">
         <v>1</v>
       </c>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
+      <c r="H55" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="12">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B56" s="15"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="16"/>
+      <c r="B56" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" s="13">
+        <v>2025177471</v>
+      </c>
+      <c r="E56" s="15">
+        <v>46133</v>
+      </c>
+      <c r="F56" s="16" t="s">
+        <v>626</v>
+      </c>
       <c r="G56" s="17">
         <v>1</v>
       </c>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
+      <c r="H56" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="I56" t="s">
+        <v>630</v>
+      </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="12">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B57" s="15"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="16"/>
+      <c r="B57" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" s="13">
+        <v>2025177475</v>
+      </c>
+      <c r="E57" s="15">
+        <v>46133</v>
+      </c>
+      <c r="F57" s="16" t="s">
+        <v>637</v>
+      </c>
       <c r="G57" s="17">
         <v>1</v>
       </c>
-      <c r="H57" s="4"/>
-      <c r="I57" s="20"/>
+      <c r="H57" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="I57" t="s">
+        <v>636</v>
+      </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="12">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B58" s="15"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="16"/>
+      <c r="B58" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D58" s="13">
+        <v>2025177202</v>
+      </c>
+      <c r="E58" s="15">
+        <v>46134</v>
+      </c>
+      <c r="F58" s="16" t="s">
+        <v>661</v>
+      </c>
       <c r="G58" s="17">
         <v>1</v>
       </c>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
+      <c r="H58" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="I58" t="s">
+        <v>660</v>
+      </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="12">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B59" s="15"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="16"/>
+      <c r="B59" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" s="13">
+        <v>2025177203</v>
+      </c>
+      <c r="E59" s="15">
+        <v>46134</v>
+      </c>
+      <c r="F59" s="16" t="s">
+        <v>656</v>
+      </c>
       <c r="G59" s="17">
         <v>1</v>
       </c>
-      <c r="H59" s="4"/>
-      <c r="I59" s="20"/>
+      <c r="H59" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="I59" t="s">
+        <v>658</v>
+      </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="12">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B60" s="15"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="16"/>
+      <c r="B60" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" s="13">
+        <v>2025177478</v>
+      </c>
+      <c r="E60" s="15">
+        <v>46134</v>
+      </c>
+      <c r="F60" s="16" t="s">
+        <v>664</v>
+      </c>
       <c r="G60" s="17">
         <v>1</v>
       </c>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
+      <c r="H60" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="I60" t="s">
+        <v>663</v>
+      </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="12">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B61" s="15"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="16"/>
+      <c r="B61" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D61" s="13">
+        <v>2025177479</v>
+      </c>
+      <c r="E61" s="15">
+        <v>46134</v>
+      </c>
+      <c r="F61" s="16" t="s">
+        <v>667</v>
+      </c>
       <c r="G61" s="17">
         <v>1</v>
       </c>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
+      <c r="H61" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="I61" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="12">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B62" s="15"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="16"/>
+      <c r="B62" s="15" t="s">
+        <v>673</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" s="14" t="s">
+        <v>683</v>
+      </c>
+      <c r="E62" s="15">
+        <v>46137</v>
+      </c>
+      <c r="F62" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G62" s="17">
         <v>1</v>
       </c>
       <c r="H62" s="4"/>
+      <c r="I62" s="20"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="12">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B63" s="15"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="16"/>
+      <c r="B63" s="15" t="s">
+        <v>674</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" s="14" t="s">
+        <v>684</v>
+      </c>
+      <c r="E63" s="15">
+        <v>46137</v>
+      </c>
+      <c r="F63" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G63" s="17">
         <v>1</v>
       </c>
       <c r="H63" s="4"/>
-      <c r="I63" s="20"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="12">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B64" s="15"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="15"/>
-      <c r="F64" s="16"/>
+      <c r="B64" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>679</v>
+      </c>
+      <c r="E64" s="15">
+        <v>46137</v>
+      </c>
+      <c r="F64" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G64" s="17">
         <v>1</v>
       </c>
@@ -12877,11 +13313,21 @@
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B65" s="15"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="16"/>
+      <c r="B65" s="15" t="s">
+        <v>670</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" s="14" t="s">
+        <v>680</v>
+      </c>
+      <c r="E65" s="15">
+        <v>46137</v>
+      </c>
+      <c r="F65" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G65" s="17">
         <v>1</v>
       </c>
@@ -12893,11 +13339,21 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B66" s="15"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="16"/>
+      <c r="B66" s="15" t="s">
+        <v>668</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>678</v>
+      </c>
+      <c r="E66" s="15">
+        <v>46137</v>
+      </c>
+      <c r="F66" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G66" s="17">
         <v>1</v>
       </c>
@@ -12908,58 +13364,97 @@
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B67" s="15"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="16"/>
+      <c r="B67" s="15" t="s">
+        <v>677</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>687</v>
+      </c>
+      <c r="E67" s="15">
+        <v>46137</v>
+      </c>
+      <c r="F67" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G67" s="17">
         <v>1</v>
       </c>
       <c r="H67" s="4"/>
-      <c r="I67" s="20"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="12">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B68" s="15"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="15"/>
-      <c r="F68" s="16"/>
+      <c r="B68" s="15" t="s">
+        <v>671</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>681</v>
+      </c>
+      <c r="E68" s="15">
+        <v>46137</v>
+      </c>
+      <c r="F68" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G68" s="17">
         <v>1</v>
       </c>
       <c r="H68" s="4"/>
+      <c r="I68" s="20"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="12">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B69" s="15"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="15"/>
-      <c r="F69" s="16"/>
+      <c r="B69" s="15" t="s">
+        <v>672</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" s="14" t="s">
+        <v>682</v>
+      </c>
+      <c r="E69" s="15">
+        <v>46137</v>
+      </c>
+      <c r="F69" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G69" s="17">
         <v>1</v>
       </c>
       <c r="H69" s="4"/>
-      <c r="I69" s="20"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="12">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B70" s="15"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="16"/>
+      <c r="B70" s="15" t="s">
+        <v>675</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>685</v>
+      </c>
+      <c r="E70" s="15">
+        <v>46137</v>
+      </c>
+      <c r="F70" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G70" s="17">
         <v>1</v>
       </c>
@@ -12971,91 +13466,176 @@
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="13"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="16"/>
+      <c r="B71" s="15" t="s">
+        <v>676</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="E71" s="15">
+        <v>46137</v>
+      </c>
+      <c r="F71" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G71" s="17">
         <v>1</v>
       </c>
       <c r="H71" s="4"/>
+      <c r="I71" s="20"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="12">
         <f t="shared" ref="A72:A117" si="1">+A71+1</f>
         <v>66</v>
       </c>
-      <c r="B72" s="15"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="16"/>
+      <c r="B72" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>688</v>
+      </c>
+      <c r="E72" s="15">
+        <v>46135</v>
+      </c>
+      <c r="F72" s="16" t="s">
+        <v>664</v>
+      </c>
       <c r="G72" s="17">
         <v>1</v>
       </c>
-      <c r="H72" s="4"/>
+      <c r="H72" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="I72" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="12">
         <f t="shared" si="1"/>
         <v>67</v>
       </c>
-      <c r="B73" s="15"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="15"/>
-      <c r="F73" s="16"/>
+      <c r="B73" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D73" s="14" t="s">
+        <v>691</v>
+      </c>
+      <c r="E73" s="15">
+        <v>46138</v>
+      </c>
+      <c r="F73" s="16" t="s">
+        <v>692</v>
+      </c>
       <c r="G73" s="17">
         <v>1</v>
       </c>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
+      <c r="H73" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="I73" t="s">
+        <v>694</v>
+      </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="12">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
-      <c r="B74" s="15"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="15"/>
-      <c r="F74" s="16"/>
+      <c r="B74" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>695</v>
+      </c>
+      <c r="E74" s="15">
+        <v>46138</v>
+      </c>
+      <c r="F74" s="16" t="s">
+        <v>698</v>
+      </c>
       <c r="G74" s="17">
         <v>1</v>
       </c>
-      <c r="H74" s="4"/>
+      <c r="H74" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="I74" t="s">
+        <v>697</v>
+      </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="12">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
-      <c r="B75" s="15"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="15"/>
-      <c r="F75" s="16"/>
+      <c r="B75" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" s="14" t="s">
+        <v>699</v>
+      </c>
+      <c r="E75" s="15">
+        <v>46138</v>
+      </c>
+      <c r="F75" s="16" t="s">
+        <v>700</v>
+      </c>
       <c r="G75" s="17">
         <v>1</v>
       </c>
-      <c r="H75" s="4"/>
+      <c r="H75" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="I75" t="s">
+        <v>702</v>
+      </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="12">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="B76" s="15"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="15"/>
-      <c r="F76" s="16"/>
+      <c r="B76" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="E76" s="15">
+        <v>46138</v>
+      </c>
+      <c r="F76" s="16" t="s">
+        <v>704</v>
+      </c>
       <c r="G76" s="17">
         <v>1</v>
       </c>
-      <c r="H76" s="4"/>
+      <c r="H76" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="I76" t="s">
+        <v>706</v>
+      </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="12">
@@ -13673,9 +14253,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I47">
-    <sortCondition ref="E7:E47"/>
-    <sortCondition ref="D7:D47"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I71">
+    <sortCondition ref="E7:E71"/>
+    <sortCondition ref="D7:D71"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>
@@ -13688,6 +14268,7 @@
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="I4:J4"/>
   </mergeCells>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.45" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
   <headerFooter>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5BEB20-22D7-4964-9098-9829FE3B6862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE4F4C1-59D3-4C1B-BA5C-E563FC2D0F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Janvier 2026 " sheetId="2" r:id="rId1"/>
     <sheet name="Février 2026" sheetId="1" r:id="rId2"/>
     <sheet name="Mars 2026" sheetId="3" r:id="rId3"/>
     <sheet name="Avril 2026" sheetId="4" r:id="rId4"/>
+    <sheet name="Mai 2026" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Avril 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Février 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Janvier 2026 '!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Mai 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mars 2026'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="772">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -2040,27 +2042,18 @@
     <t>Sabour mahmoud</t>
   </si>
   <si>
-    <t>720 bt 10 n18</t>
-  </si>
-  <si>
     <t>B3</t>
   </si>
   <si>
     <t>Belmadoui med adlane</t>
   </si>
   <si>
-    <t>zmala</t>
-  </si>
-  <si>
     <t>NB(089/2026)</t>
   </si>
   <si>
     <t>Hatchane yacine</t>
   </si>
   <si>
-    <t>720 bt 11 n39</t>
-  </si>
-  <si>
     <t>NB(137/2026)</t>
   </si>
   <si>
@@ -2070,51 +2063,33 @@
     <t>Bouksani lila</t>
   </si>
   <si>
-    <t>residence chorfi A n23</t>
-  </si>
-  <si>
     <t>Laadjali aida</t>
   </si>
   <si>
-    <t>720 bt 12 n03</t>
-  </si>
-  <si>
     <t>NB(134/2026)</t>
   </si>
   <si>
     <t>Abdelouahab fatiha</t>
   </si>
   <si>
-    <t>720 bt 17 n11</t>
-  </si>
-  <si>
     <t>NB(129/2026)</t>
   </si>
   <si>
     <t>Khazaz djamila</t>
   </si>
   <si>
-    <t>720 bt 01 n21</t>
-  </si>
-  <si>
     <t>NB(125/2026)</t>
   </si>
   <si>
     <t>Maachou med</t>
   </si>
   <si>
-    <t>720 bt 12 n15</t>
-  </si>
-  <si>
     <t>NB(629/2025)</t>
   </si>
   <si>
     <t>Benhaoua zohir</t>
   </si>
   <si>
-    <t>720 bt 2 n21</t>
-  </si>
-  <si>
     <t>NB(107/2026)</t>
   </si>
   <si>
@@ -2124,33 +2099,18 @@
     <t>Ayat mourad</t>
   </si>
   <si>
-    <t>720 bt 15 n16</t>
-  </si>
-  <si>
     <t>Bechlagheme yacine</t>
   </si>
   <si>
-    <t>720 bt 06 n16</t>
-  </si>
-  <si>
-    <t>NB</t>
-  </si>
-  <si>
     <t>Toubal samia</t>
   </si>
   <si>
-    <t>720 bt 12 n36</t>
-  </si>
-  <si>
     <t>NB(140/2026)</t>
   </si>
   <si>
     <t>Lachenani imad</t>
   </si>
   <si>
-    <t>720 bt 03 n06</t>
-  </si>
-  <si>
     <t>NB(145/2026)</t>
   </si>
   <si>
@@ -2220,9 +2180,6 @@
     <t>Rabhallah aek</t>
   </si>
   <si>
-    <t>720 bt 08 n28</t>
-  </si>
-  <si>
     <t>2025117925</t>
   </si>
   <si>
@@ -2232,18 +2189,12 @@
     <t>Sadok faiza</t>
   </si>
   <si>
-    <t>720 bt 15 n18</t>
-  </si>
-  <si>
     <t>2025117921</t>
   </si>
   <si>
     <t>Hadjadj kamel</t>
   </si>
   <si>
-    <t>720 bt 07 n21</t>
-  </si>
-  <si>
     <t>NB(149/2026)</t>
   </si>
   <si>
@@ -2256,9 +2207,6 @@
     <t>Hasnaoui ali</t>
   </si>
   <si>
-    <t>Hantabli n56</t>
-  </si>
-  <si>
     <t>2025117923</t>
   </si>
   <si>
@@ -2268,7 +2216,277 @@
     <t>Djabri kheladi</t>
   </si>
   <si>
-    <t>djennane tebbal n132</t>
+    <t>2025117927</t>
+  </si>
+  <si>
+    <t>NB(136/2026)</t>
+  </si>
+  <si>
+    <t>Drim poste contrôle</t>
+  </si>
+  <si>
+    <t>BB0003</t>
+  </si>
+  <si>
+    <t>2025117928</t>
+  </si>
+  <si>
+    <t>2025177168</t>
+  </si>
+  <si>
+    <t>2025177929</t>
+  </si>
+  <si>
+    <t>2025177930</t>
+  </si>
+  <si>
+    <t>Berkane med amine</t>
+  </si>
+  <si>
+    <t>NB(679/2025)</t>
+  </si>
+  <si>
+    <t>Hacene menad</t>
+  </si>
+  <si>
+    <t>NB(575/2025)</t>
+  </si>
+  <si>
+    <t>Tlemcani zoheir</t>
+  </si>
+  <si>
+    <t>NB(130/2026)</t>
+  </si>
+  <si>
+    <t>B20306</t>
+  </si>
+  <si>
+    <t>2025177169</t>
+  </si>
+  <si>
+    <t>2025177170</t>
+  </si>
+  <si>
+    <t>NB(163/2026)</t>
+  </si>
+  <si>
+    <t>Benaoua kheira</t>
+  </si>
+  <si>
+    <t>2025177926</t>
+  </si>
+  <si>
+    <t>Mecene samiha</t>
+  </si>
+  <si>
+    <t>NB(156/2026)</t>
+  </si>
+  <si>
+    <t>B10542</t>
+  </si>
+  <si>
+    <t>2025177167</t>
+  </si>
+  <si>
+    <t>B11660</t>
+  </si>
+  <si>
+    <t>2025177166</t>
+  </si>
+  <si>
+    <t>NB(160/2026)</t>
+  </si>
+  <si>
+    <t>NB(155/2026)</t>
+  </si>
+  <si>
+    <t>Djedi med</t>
+  </si>
+  <si>
+    <t>rue emir aek</t>
+  </si>
+  <si>
+    <r>
+      <t>Mois de Mai</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <t>B5</t>
+  </si>
+  <si>
+    <t>NB(040/2026)</t>
+  </si>
+  <si>
+    <t>Ent bakhti dahmane</t>
+  </si>
+  <si>
+    <t>projet 80  logts lpa cité cheriet</t>
+  </si>
+  <si>
+    <t>B50020</t>
+  </si>
+  <si>
+    <t>B34007</t>
+  </si>
+  <si>
+    <t>202323987123</t>
+  </si>
+  <si>
+    <t>BB0235</t>
+  </si>
+  <si>
+    <t>B50086</t>
+  </si>
+  <si>
+    <t>NB(534/2022)</t>
+  </si>
+  <si>
+    <t>Fergani sahraoui</t>
+  </si>
+  <si>
+    <t>ouled fergane</t>
+  </si>
+  <si>
+    <t>Hannichi med</t>
+  </si>
+  <si>
+    <t>djenane tebbal</t>
+  </si>
+  <si>
+    <t>NB(150/2025)</t>
+  </si>
+  <si>
+    <t>NB(169/2026)</t>
+  </si>
+  <si>
+    <t>Hamzaoui bachir</t>
+  </si>
+  <si>
+    <t>cité 720 logts b30 n19</t>
+  </si>
+  <si>
+    <t>Bouamra brahim</t>
+  </si>
+  <si>
+    <t>residence chorfi A n12</t>
+  </si>
+  <si>
+    <t>NB(159/2026)</t>
+  </si>
+  <si>
+    <t>NB(619/2025)</t>
+  </si>
+  <si>
+    <t>Merah mourad</t>
+  </si>
+  <si>
+    <t>la remonte</t>
+  </si>
+  <si>
+    <t>Yahmi missoum</t>
+  </si>
+  <si>
+    <t>cité hantable n118</t>
+  </si>
+  <si>
+    <t>NB(135/2026)</t>
+  </si>
+  <si>
+    <t>Makhloufi med</t>
+  </si>
+  <si>
+    <t>cité 720 logts b6 n8</t>
+  </si>
+  <si>
+    <t>NB(168/2025)</t>
+  </si>
+  <si>
+    <t>Rezkallah salima</t>
+  </si>
+  <si>
+    <t>cité 720 logts b 11 n20</t>
+  </si>
+  <si>
+    <t>NB(167/2025)</t>
+  </si>
+  <si>
+    <t>Askri med</t>
+  </si>
+  <si>
+    <t>cité 720 logts b 2 n15</t>
+  </si>
+  <si>
+    <t>NB(025/2026)</t>
+  </si>
+  <si>
+    <t>Benzayed hamza</t>
+  </si>
+  <si>
+    <t>cité 720 logts b 5 n11</t>
+  </si>
+  <si>
+    <t>Bouchenafa ali</t>
+  </si>
+  <si>
+    <t>cité 720 logts b 7 n36</t>
+  </si>
+  <si>
+    <t>NB(166/2026)</t>
+  </si>
+  <si>
+    <t>Zerga benaissa</t>
+  </si>
+  <si>
+    <t>cité 720 logts b 10 n4</t>
+  </si>
+  <si>
+    <t>NB(123/2026)</t>
+  </si>
+  <si>
+    <t>Makhloufi med amine</t>
+  </si>
+  <si>
+    <t>cité 720 logts b 17 n32</t>
+  </si>
+  <si>
+    <t>NB(152/2026)</t>
+  </si>
+  <si>
+    <t>Benabderrahmane boulanouar</t>
+  </si>
+  <si>
+    <t>cité 720 logts b 19 n12</t>
+  </si>
+  <si>
+    <t>NB(069/2026)</t>
+  </si>
+  <si>
+    <t>Aneka hichem</t>
+  </si>
+  <si>
+    <t>cité 720 logts b 15 n34</t>
+  </si>
+  <si>
+    <t>NB(753/2025)</t>
   </si>
 </sst>
 </file>
@@ -2433,7 +2651,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2516,6 +2734,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2772,6 +2993,61 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24C23E79-7F7F-417E-9E58-9A20FC4299A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="695335" y="21678900"/>
+          <a:ext cx="4743440" cy="238125"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>104785</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connecteur droit 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C94C3202-AAC9-4927-B56F-454E0C55EA4D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3978,7 +4254,7 @@
         <v>27</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>19</v>
+        <v>630</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>18</v>
@@ -11605,7 +11881,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -11627,7 +11903,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -11667,7 +11943,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -12859,16 +13135,13 @@
         <v>46133</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="G49" s="17">
         <v>1</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="I49" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -12889,16 +13162,13 @@
         <v>46133</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="G50" s="17">
         <v>1</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>650</v>
-      </c>
-      <c r="I50" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -12919,16 +13189,13 @@
         <v>46133</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="G51" s="17">
         <v>1</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>644</v>
-      </c>
-      <c r="I51" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -12949,16 +13216,13 @@
         <v>46133</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="G52" s="17">
         <v>1</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="I52" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -12979,16 +13243,13 @@
         <v>46133</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="G53" s="17">
         <v>1</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>647</v>
-      </c>
-      <c r="I53" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -12997,7 +13258,7 @@
         <v>48</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>18</v>
@@ -13009,16 +13270,13 @@
         <v>46133</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G54" s="17">
         <v>1</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="I54" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -13039,17 +13297,15 @@
         <v>46133</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="G55" s="17">
         <v>1</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>639</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>640</v>
-      </c>
+        <v>636</v>
+      </c>
+      <c r="I55" s="4"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="12">
@@ -13077,9 +13333,6 @@
       <c r="H56" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="I56" t="s">
-        <v>630</v>
-      </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="12">
@@ -13099,16 +13352,13 @@
         <v>46133</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G57" s="17">
         <v>1</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="I57" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -13129,16 +13379,13 @@
         <v>46134</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>661</v>
+        <v>714</v>
       </c>
       <c r="G58" s="17">
         <v>1</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>659</v>
-      </c>
-      <c r="I58" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -13159,16 +13406,13 @@
         <v>46134</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="G59" s="17">
         <v>1</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="I59" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -13189,16 +13433,13 @@
         <v>46134</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="G60" s="17">
         <v>1</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>662</v>
-      </c>
-      <c r="I60" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -13219,16 +13460,13 @@
         <v>46134</v>
       </c>
       <c r="F61" s="16" t="s">
-        <v>667</v>
+        <v>653</v>
       </c>
       <c r="G61" s="17">
         <v>1</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>665</v>
-      </c>
-      <c r="I61" t="s">
-        <v>666</v>
+        <v>652</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -13237,25 +13475,26 @@
         <v>56</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>673</v>
+        <v>19</v>
       </c>
       <c r="C62" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="E62" s="15">
-        <v>46137</v>
+        <v>46135</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>162</v>
+        <v>651</v>
       </c>
       <c r="G62" s="17">
         <v>1</v>
       </c>
-      <c r="H62" s="4"/>
-      <c r="I62" s="20"/>
+      <c r="H62" s="4" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="12">
@@ -13263,13 +13502,13 @@
         <v>57</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>674</v>
+        <v>659</v>
       </c>
       <c r="C63" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="E63" s="15">
         <v>46137</v>
@@ -13281,6 +13520,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="4"/>
+      <c r="I63" s="20"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="12">
@@ -13288,13 +13528,13 @@
         <v>58</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="C64" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="E64" s="15">
         <v>46137</v>
@@ -13306,7 +13546,6 @@
         <v>1</v>
       </c>
       <c r="H64" s="4"/>
-      <c r="I64" s="20"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="12">
@@ -13314,13 +13553,13 @@
         <v>59</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>670</v>
+        <v>655</v>
       </c>
       <c r="C65" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>680</v>
+        <v>665</v>
       </c>
       <c r="E65" s="15">
         <v>46137</v>
@@ -13340,13 +13579,13 @@
         <v>60</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="C66" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="E66" s="15">
         <v>46137</v>
@@ -13358,6 +13597,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="4"/>
+      <c r="I66" s="20"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="12">
@@ -13365,13 +13605,13 @@
         <v>61</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>677</v>
+        <v>654</v>
       </c>
       <c r="C67" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>687</v>
+        <v>664</v>
       </c>
       <c r="E67" s="15">
         <v>46137</v>
@@ -13390,13 +13630,13 @@
         <v>62</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C68" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="E68" s="15">
         <v>46137</v>
@@ -13408,7 +13648,6 @@
         <v>1</v>
       </c>
       <c r="H68" s="4"/>
-      <c r="I68" s="20"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="12">
@@ -13416,13 +13655,13 @@
         <v>63</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>672</v>
+        <v>657</v>
       </c>
       <c r="C69" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>682</v>
+        <v>667</v>
       </c>
       <c r="E69" s="15">
         <v>46137</v>
@@ -13434,6 +13673,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="4"/>
+      <c r="I69" s="20"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="12">
@@ -13441,13 +13681,13 @@
         <v>64</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>675</v>
+        <v>658</v>
       </c>
       <c r="C70" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>685</v>
+        <v>668</v>
       </c>
       <c r="E70" s="15">
         <v>46137</v>
@@ -13459,7 +13699,6 @@
         <v>1</v>
       </c>
       <c r="H70" s="4"/>
-      <c r="I70" s="20"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="12">
@@ -13467,13 +13706,13 @@
         <v>65</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>676</v>
+        <v>661</v>
       </c>
       <c r="C71" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>686</v>
+        <v>671</v>
       </c>
       <c r="E71" s="15">
         <v>46137</v>
@@ -13493,29 +13732,25 @@
         <v>66</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>19</v>
+        <v>662</v>
       </c>
       <c r="C72" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>688</v>
+        <v>672</v>
       </c>
       <c r="E72" s="15">
-        <v>46135</v>
+        <v>46137</v>
       </c>
       <c r="F72" s="16" t="s">
-        <v>664</v>
+        <v>162</v>
       </c>
       <c r="G72" s="17">
         <v>1</v>
       </c>
-      <c r="H72" s="4" t="s">
-        <v>689</v>
-      </c>
-      <c r="I72" t="s">
-        <v>690</v>
-      </c>
+      <c r="H72" s="4"/>
+      <c r="I72" s="20"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="12">
@@ -13529,22 +13764,19 @@
         <v>18</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="E73" s="15">
         <v>46138</v>
       </c>
       <c r="F73" s="16" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="G73" s="17">
         <v>1</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="I73" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -13559,22 +13791,19 @@
         <v>18</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="E74" s="15">
         <v>46138</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="G74" s="17">
         <v>1</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="I74" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
@@ -13589,22 +13818,19 @@
         <v>18</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>699</v>
+        <v>682</v>
       </c>
       <c r="E75" s="15">
         <v>46138</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>700</v>
+        <v>683</v>
       </c>
       <c r="G75" s="17">
         <v>1</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>701</v>
-      </c>
-      <c r="I75" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -13619,22 +13845,19 @@
         <v>18</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>703</v>
+        <v>676</v>
       </c>
       <c r="E76" s="15">
         <v>46138</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>704</v>
+        <v>677</v>
       </c>
       <c r="G76" s="17">
         <v>1</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>705</v>
-      </c>
-      <c r="I76" t="s">
-        <v>706</v>
+        <v>678</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -13642,26 +13865,48 @@
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
-      <c r="B77" s="15"/>
-      <c r="C77" s="13"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="16"/>
+      <c r="B77" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D77" s="14" t="s">
+        <v>688</v>
+      </c>
+      <c r="E77" s="15">
+        <v>46139</v>
+      </c>
+      <c r="F77" s="16" t="s">
+        <v>689</v>
+      </c>
       <c r="G77" s="17">
         <v>1</v>
       </c>
-      <c r="H77" s="4"/>
+      <c r="H77" s="4" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="12">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
-      <c r="B78" s="15"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="15"/>
-      <c r="F78" s="16"/>
+      <c r="B78" s="15" t="s">
+        <v>691</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>692</v>
+      </c>
+      <c r="E78" s="15">
+        <v>46139</v>
+      </c>
+      <c r="F78" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G78" s="17">
         <v>1</v>
       </c>
@@ -13672,56 +13917,102 @@
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
-      <c r="B79" s="15"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="16"/>
+      <c r="B79" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D79" s="14" t="s">
+        <v>693</v>
+      </c>
+      <c r="E79" s="15">
+        <v>46140</v>
+      </c>
+      <c r="F79" s="16" t="s">
+        <v>697</v>
+      </c>
       <c r="G79" s="17">
         <v>1</v>
       </c>
-      <c r="H79" s="4"/>
+      <c r="H79" s="4" t="s">
+        <v>696</v>
+      </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="12">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
-      <c r="B80" s="15"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="15"/>
-      <c r="F80" s="16"/>
+      <c r="B80" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D80" s="14" t="s">
+        <v>694</v>
+      </c>
+      <c r="E80" s="15">
+        <v>46140</v>
+      </c>
+      <c r="F80" s="16" t="s">
+        <v>699</v>
+      </c>
       <c r="G80" s="17">
         <v>1</v>
       </c>
-      <c r="H80" s="4"/>
+      <c r="H80" s="4" t="s">
+        <v>698</v>
+      </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="12">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
-      <c r="B81" s="15"/>
-      <c r="C81" s="13"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="15"/>
-      <c r="F81" s="16"/>
+      <c r="B81" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>695</v>
+      </c>
+      <c r="E81" s="15">
+        <v>46140</v>
+      </c>
+      <c r="F81" s="16" t="s">
+        <v>701</v>
+      </c>
       <c r="G81" s="17">
         <v>1</v>
       </c>
-      <c r="H81" s="4"/>
+      <c r="H81" s="4" t="s">
+        <v>700</v>
+      </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="12">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
-      <c r="B82" s="15"/>
-      <c r="C82" s="13"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="15"/>
-      <c r="F82" s="16"/>
+      <c r="B82" s="15" t="s">
+        <v>712</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>713</v>
+      </c>
+      <c r="E82" s="15">
+        <v>46141</v>
+      </c>
+      <c r="F82" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G82" s="17">
         <v>1</v>
       </c>
@@ -13732,11 +14023,21 @@
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
-      <c r="B83" s="15"/>
-      <c r="C83" s="13"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="15"/>
-      <c r="F83" s="16"/>
+      <c r="B83" s="15" t="s">
+        <v>710</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>711</v>
+      </c>
+      <c r="E83" s="15">
+        <v>46141</v>
+      </c>
+      <c r="F83" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G83" s="17">
         <v>1</v>
       </c>
@@ -13747,11 +14048,21 @@
         <f t="shared" si="1"/>
         <v>78</v>
       </c>
-      <c r="B84" s="15"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="15"/>
-      <c r="F84" s="16"/>
+      <c r="B84" s="15" t="s">
+        <v>702</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D84" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="E84" s="15">
+        <v>46141</v>
+      </c>
+      <c r="F84" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G84" s="17">
         <v>1</v>
       </c>
@@ -13762,30 +14073,54 @@
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
-      <c r="B85" s="15"/>
-      <c r="C85" s="13"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="15"/>
-      <c r="F85" s="16"/>
+      <c r="B85" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D85" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="E85" s="15">
+        <v>46142</v>
+      </c>
+      <c r="F85" s="16" t="s">
+        <v>705</v>
+      </c>
       <c r="G85" s="17">
         <v>1</v>
       </c>
-      <c r="H85" s="4"/>
+      <c r="H85" s="4" t="s">
+        <v>706</v>
+      </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="12">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="B86" s="15"/>
-      <c r="C86" s="13"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="15"/>
-      <c r="F86" s="16"/>
+      <c r="B86" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D86" s="14" t="s">
+        <v>707</v>
+      </c>
+      <c r="E86" s="15">
+        <v>46142</v>
+      </c>
+      <c r="F86" s="16" t="s">
+        <v>709</v>
+      </c>
       <c r="G86" s="17">
         <v>1</v>
       </c>
-      <c r="H86" s="4"/>
+      <c r="H86" s="4" t="s">
+        <v>708</v>
+      </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="12">
@@ -14253,9 +14588,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I71">
-    <sortCondition ref="E7:E71"/>
-    <sortCondition ref="D7:D71"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I86">
+    <sortCondition ref="E7:E86"/>
+    <sortCondition ref="D7:D86"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>
@@ -14276,4 +14611,2191 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2D3AD9E-BB20-4389-9DF1-348806D42BC2}">
+  <dimension ref="A1:K117"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+    <col min="9" max="9" width="32.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="25"/>
+      <c r="K2" s="6">
+        <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="25"/>
+      <c r="K3" s="6">
+        <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="25"/>
+      <c r="K4" s="6">
+        <f>SUMIF(F7:F364,"Ve*",G7:G364)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="8">
+        <f>SUM(K2:K4)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>1</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="13">
+        <v>2025177162</v>
+      </c>
+      <c r="E7" s="15">
+        <v>46144</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>715</v>
+      </c>
+      <c r="G7" s="17">
+        <v>1</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>716</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>717</v>
+      </c>
+      <c r="J7" s="19"/>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <f t="shared" ref="A8:A71" si="0">+A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>723</v>
+      </c>
+      <c r="C8" s="13">
+        <v>40</v>
+      </c>
+      <c r="D8" s="13">
+        <v>14855502</v>
+      </c>
+      <c r="E8" s="15">
+        <v>46145</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G8" s="17">
+        <v>1</v>
+      </c>
+      <c r="H8" s="18"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>719</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="13">
+        <v>2025177161</v>
+      </c>
+      <c r="E9" s="15">
+        <v>46145</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>720</v>
+      </c>
+      <c r="G9" s="17">
+        <v>1</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>721</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>722</v>
+      </c>
+      <c r="J9" s="20"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>724</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="13">
+        <v>2025177476</v>
+      </c>
+      <c r="E10" s="15">
+        <v>46145</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G10" s="17">
+        <v>1</v>
+      </c>
+      <c r="H10" s="18"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="C11" s="13">
+        <v>30</v>
+      </c>
+      <c r="D11" s="13">
+        <v>18041007498</v>
+      </c>
+      <c r="E11" s="15">
+        <v>46146</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G11" s="17">
+        <v>1</v>
+      </c>
+      <c r="H11" s="18"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>726</v>
+      </c>
+      <c r="C12" s="13">
+        <v>100</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>725</v>
+      </c>
+      <c r="E12" s="15">
+        <v>46146</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G12" s="17">
+        <v>1</v>
+      </c>
+      <c r="H12" s="18"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="13">
+        <v>2025177163</v>
+      </c>
+      <c r="E13" s="15">
+        <v>46148</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>734</v>
+      </c>
+      <c r="G13" s="17">
+        <v>1</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>735</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>736</v>
+      </c>
+      <c r="J13" s="20"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="13">
+        <v>2025177165</v>
+      </c>
+      <c r="E14" s="15">
+        <v>46148</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>759</v>
+      </c>
+      <c r="G14" s="17">
+        <v>1</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>757</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>758</v>
+      </c>
+      <c r="J14" s="20"/>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="13">
+        <v>2025177178</v>
+      </c>
+      <c r="E15" s="15">
+        <v>46148</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>728</v>
+      </c>
+      <c r="G15" s="17">
+        <v>1</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>729</v>
+      </c>
+      <c r="I15" t="s">
+        <v>730</v>
+      </c>
+      <c r="J15" s="20"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="13">
+        <v>2025177179</v>
+      </c>
+      <c r="E16" s="15">
+        <v>46148</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>739</v>
+      </c>
+      <c r="G16" s="17">
+        <v>1</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>737</v>
+      </c>
+      <c r="I16" s="29" t="s">
+        <v>738</v>
+      </c>
+      <c r="J16" s="20"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="13">
+        <v>2025177180</v>
+      </c>
+      <c r="E17" s="15">
+        <v>46148</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>771</v>
+      </c>
+      <c r="G17" s="17">
+        <v>1</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>769</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>770</v>
+      </c>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="13">
+        <v>2025177871</v>
+      </c>
+      <c r="E18" s="15">
+        <v>46148</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>762</v>
+      </c>
+      <c r="G18" s="17">
+        <v>1</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>760</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>761</v>
+      </c>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="13">
+        <v>2025177872</v>
+      </c>
+      <c r="E19" s="15">
+        <v>46148</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>754</v>
+      </c>
+      <c r="G19" s="17">
+        <v>1</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>752</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>753</v>
+      </c>
+      <c r="J19" s="20"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="13">
+        <v>2025177873</v>
+      </c>
+      <c r="E20" s="15">
+        <v>46148</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>748</v>
+      </c>
+      <c r="G20" s="17">
+        <v>1</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>746</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>747</v>
+      </c>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="13">
+        <v>2025177874</v>
+      </c>
+      <c r="E21" s="15">
+        <v>46148</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>734</v>
+      </c>
+      <c r="G21" s="17">
+        <v>1</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>755</v>
+      </c>
+      <c r="I21" s="20" t="s">
+        <v>756</v>
+      </c>
+      <c r="J21" s="20"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="13">
+        <v>2025177875</v>
+      </c>
+      <c r="E22" s="15">
+        <v>46148</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>751</v>
+      </c>
+      <c r="G22" s="17">
+        <v>1</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>749</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>750</v>
+      </c>
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="13">
+        <v>2025177876</v>
+      </c>
+      <c r="E23" s="15">
+        <v>46148</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>768</v>
+      </c>
+      <c r="G23" s="17">
+        <v>1</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>766</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>767</v>
+      </c>
+      <c r="J23" s="20"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="13">
+        <v>2025177877</v>
+      </c>
+      <c r="E24" s="15">
+        <v>46148</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>740</v>
+      </c>
+      <c r="G24" s="17">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="I24" s="29" t="s">
+        <v>742</v>
+      </c>
+      <c r="J24" s="20"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="13">
+        <v>2025177878</v>
+      </c>
+      <c r="E25" s="15">
+        <v>46148</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>745</v>
+      </c>
+      <c r="G25" s="17">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="I25" s="29" t="s">
+        <v>744</v>
+      </c>
+      <c r="J25" s="20"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="13">
+        <v>2025177879</v>
+      </c>
+      <c r="E26" s="15">
+        <v>46148</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>765</v>
+      </c>
+      <c r="G26" s="17">
+        <v>1</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>763</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>764</v>
+      </c>
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="13">
+        <v>2025177880</v>
+      </c>
+      <c r="E27" s="15">
+        <v>46148</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>733</v>
+      </c>
+      <c r="G27" s="17">
+        <v>1</v>
+      </c>
+      <c r="H27" s="18" t="s">
+        <v>731</v>
+      </c>
+      <c r="I27" s="20" t="s">
+        <v>732</v>
+      </c>
+      <c r="J27" s="20"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4"/>
+      <c r="J28" s="20"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="12">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="15"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4"/>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="15"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17">
+        <v>1</v>
+      </c>
+      <c r="H30" s="18"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="15"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="17">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="15"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="17">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="12">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="17">
+        <v>1</v>
+      </c>
+      <c r="H33" s="4"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="12">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="17">
+        <v>1</v>
+      </c>
+      <c r="H34" s="18"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="12">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="17">
+        <v>1</v>
+      </c>
+      <c r="H35" s="18"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="12">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="17">
+        <v>1</v>
+      </c>
+      <c r="H36" s="18"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="12">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="15"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="17">
+        <v>1</v>
+      </c>
+      <c r="H37" s="18"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="12">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="15"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="17">
+        <v>1</v>
+      </c>
+      <c r="H38" s="4"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="12">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B39" s="15"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="17">
+        <v>1</v>
+      </c>
+      <c r="H39" s="18"/>
+      <c r="I39" s="20"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="12">
+        <f>+A39+1</f>
+        <v>34</v>
+      </c>
+      <c r="B40" s="15"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="17">
+        <v>1</v>
+      </c>
+      <c r="H40" s="4"/>
+      <c r="I40" s="20"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="12">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="15"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="17">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="20"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="12">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="17">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4"/>
+      <c r="I42" s="20"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="12">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="17">
+        <v>1</v>
+      </c>
+      <c r="H43" s="18"/>
+      <c r="I43" s="20"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="12">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="17">
+        <v>1</v>
+      </c>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="12">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="17">
+        <v>1</v>
+      </c>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="12">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="15"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="17">
+        <v>1</v>
+      </c>
+      <c r="H46" s="4"/>
+      <c r="I46" s="20"/>
+    </row>
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="12">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B47" s="15"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="17">
+        <v>1</v>
+      </c>
+      <c r="H47" s="4"/>
+      <c r="I47" s="20"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="12">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B48" s="15"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="17">
+        <v>1</v>
+      </c>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="12">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B49" s="15"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="17">
+        <v>1</v>
+      </c>
+      <c r="H49" s="4"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="12">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B50" s="15"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="17">
+        <v>1</v>
+      </c>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="12">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B51" s="15"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="17">
+        <v>1</v>
+      </c>
+      <c r="H51" s="4"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="12">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B52" s="15"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="17">
+        <v>1</v>
+      </c>
+      <c r="H52" s="4"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="12">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B53" s="15"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="17">
+        <v>1</v>
+      </c>
+      <c r="H53" s="4"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="12">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B54" s="15"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="17">
+        <v>1</v>
+      </c>
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="12">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B55" s="15"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="17">
+        <v>1</v>
+      </c>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="12">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B56" s="15"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="17">
+        <v>1</v>
+      </c>
+      <c r="H56" s="4"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="12">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="17">
+        <v>1</v>
+      </c>
+      <c r="H57" s="4"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="12">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B58" s="15"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="17">
+        <v>1</v>
+      </c>
+      <c r="H58" s="4"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="12">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B59" s="15"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="17">
+        <v>1</v>
+      </c>
+      <c r="H59" s="4"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="12">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B60" s="15"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="17">
+        <v>1</v>
+      </c>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="12">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B61" s="15"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="17">
+        <v>1</v>
+      </c>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="12">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B62" s="15"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="17">
+        <v>1</v>
+      </c>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="12">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B63" s="15"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="17">
+        <v>1</v>
+      </c>
+      <c r="H63" s="4"/>
+      <c r="I63" s="20"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="12">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B64" s="15"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="15"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="17">
+        <v>1</v>
+      </c>
+      <c r="H64" s="4"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="12">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B65" s="15"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="17">
+        <v>1</v>
+      </c>
+      <c r="H65" s="4"/>
+      <c r="I65" s="20"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="12">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="17">
+        <v>1</v>
+      </c>
+      <c r="H66" s="4"/>
+      <c r="I66" s="20"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="12">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B67" s="15"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="15"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="17">
+        <v>1</v>
+      </c>
+      <c r="H67" s="4"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="12">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B68" s="15"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="17">
+        <v>1</v>
+      </c>
+      <c r="H68" s="4"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="12">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B69" s="15"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="17">
+        <v>1</v>
+      </c>
+      <c r="H69" s="4"/>
+      <c r="I69" s="20"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="12">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B70" s="15"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="17">
+        <v>1</v>
+      </c>
+      <c r="H70" s="4"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="12">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B71" s="15"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="17">
+        <v>1</v>
+      </c>
+      <c r="H71" s="4"/>
+      <c r="I71" s="20"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="12">
+        <f t="shared" ref="A72:A117" si="1">+A71+1</f>
+        <v>66</v>
+      </c>
+      <c r="B72" s="15"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="17">
+        <v>1</v>
+      </c>
+      <c r="H72" s="4"/>
+      <c r="I72" s="20"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="12">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="B73" s="15"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="17">
+        <v>1</v>
+      </c>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="12">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="B74" s="15"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="17">
+        <v>1</v>
+      </c>
+      <c r="H74" s="4"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="12">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B75" s="15"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="17">
+        <v>1</v>
+      </c>
+      <c r="H75" s="4"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="12">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="B76" s="15"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="17">
+        <v>1</v>
+      </c>
+      <c r="H76" s="4"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="12">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="B77" s="15"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="17">
+        <v>1</v>
+      </c>
+      <c r="H77" s="4"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="12">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="B78" s="15"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="17">
+        <v>1</v>
+      </c>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="12">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="B79" s="15"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="17">
+        <v>1</v>
+      </c>
+      <c r="H79" s="4"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="12">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="B80" s="15"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="17">
+        <v>1</v>
+      </c>
+      <c r="H80" s="4"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="12">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="B81" s="15"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="17">
+        <v>1</v>
+      </c>
+      <c r="H81" s="4"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="12">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="B82" s="15"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="17">
+        <v>1</v>
+      </c>
+      <c r="H82" s="4"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="12">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="B83" s="15"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="17">
+        <v>1</v>
+      </c>
+      <c r="H83" s="4"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="12">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="B84" s="15"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="15"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="17">
+        <v>1</v>
+      </c>
+      <c r="H84" s="4"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="12">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="B85" s="15"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="16"/>
+      <c r="G85" s="17">
+        <v>1</v>
+      </c>
+      <c r="H85" s="4"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="12">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="B86" s="15"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="16"/>
+      <c r="G86" s="17">
+        <v>1</v>
+      </c>
+      <c r="H86" s="4"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="12">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="B87" s="15"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="17">
+        <v>1</v>
+      </c>
+      <c r="H87" s="4"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="12">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="B88" s="15"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="17">
+        <v>1</v>
+      </c>
+      <c r="H88" s="4"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="12">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="B89" s="15"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="17">
+        <v>1</v>
+      </c>
+      <c r="H89" s="4"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="12">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="B90" s="15"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="16"/>
+      <c r="G90" s="17">
+        <v>1</v>
+      </c>
+      <c r="H90" s="4"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="12">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="B91" s="15"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="17">
+        <v>1</v>
+      </c>
+      <c r="H91" s="4"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="12">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="B92" s="15"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="17">
+        <v>1</v>
+      </c>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="12">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="B93" s="15"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="17">
+        <v>1</v>
+      </c>
+      <c r="H93" s="4"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="12">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="B94" s="15"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="15"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="17">
+        <v>1</v>
+      </c>
+      <c r="H94" s="4"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="12">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="B95" s="15"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="15"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="17">
+        <v>1</v>
+      </c>
+      <c r="H95" s="4"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="12">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="B96" s="15"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="16"/>
+      <c r="G96" s="17">
+        <v>1</v>
+      </c>
+      <c r="H96" s="4"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="12">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="B97" s="15"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="16"/>
+      <c r="G97" s="17">
+        <v>1</v>
+      </c>
+      <c r="H97" s="4"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="12">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="B98" s="15"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="16"/>
+      <c r="G98" s="17">
+        <v>1</v>
+      </c>
+      <c r="H98" s="4"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="12">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="B99" s="15"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="15"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="17">
+        <v>1</v>
+      </c>
+      <c r="H99" s="4"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="12">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="B100" s="15"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="15"/>
+      <c r="F100" s="16"/>
+      <c r="G100" s="17">
+        <v>1</v>
+      </c>
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="12">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="B101" s="15"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="16"/>
+      <c r="G101" s="17">
+        <v>1</v>
+      </c>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="12">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="B102" s="15"/>
+      <c r="C102" s="13"/>
+      <c r="D102" s="14"/>
+      <c r="E102" s="15"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="17">
+        <v>1</v>
+      </c>
+      <c r="H102" s="4"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="12">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="B103" s="15"/>
+      <c r="C103" s="13"/>
+      <c r="D103" s="14"/>
+      <c r="E103" s="15"/>
+      <c r="F103" s="16"/>
+      <c r="G103" s="17">
+        <v>1</v>
+      </c>
+      <c r="H103" s="4"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="12">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="B104" s="15"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="22"/>
+      <c r="E104" s="15"/>
+      <c r="F104" s="16"/>
+      <c r="G104" s="17">
+        <v>1</v>
+      </c>
+      <c r="H104" s="4"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="12">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="B105" s="15"/>
+      <c r="C105" s="13"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="15"/>
+      <c r="F105" s="16"/>
+      <c r="G105" s="17">
+        <v>1</v>
+      </c>
+      <c r="H105" s="4"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="12">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="B106" s="15"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="15"/>
+      <c r="F106" s="16"/>
+      <c r="G106" s="17">
+        <v>1</v>
+      </c>
+      <c r="H106" s="4"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="12">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="B107" s="15"/>
+      <c r="C107" s="13"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="15"/>
+      <c r="F107" s="16"/>
+      <c r="G107" s="17">
+        <v>1</v>
+      </c>
+      <c r="H107" s="4"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="12">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="B108" s="15"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="14"/>
+      <c r="E108" s="15"/>
+      <c r="F108" s="16"/>
+      <c r="G108" s="17">
+        <v>1</v>
+      </c>
+      <c r="H108" s="4"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="12">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="B109" s="15"/>
+      <c r="C109" s="13"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="15"/>
+      <c r="F109" s="16"/>
+      <c r="G109" s="17">
+        <v>1</v>
+      </c>
+      <c r="H109" s="4"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="12">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="B110" s="15"/>
+      <c r="C110" s="13"/>
+      <c r="D110" s="14"/>
+      <c r="E110" s="15"/>
+      <c r="F110" s="16"/>
+      <c r="G110" s="17">
+        <v>1</v>
+      </c>
+      <c r="H110" s="4"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="12">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="B111" s="15"/>
+      <c r="C111" s="13"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="15"/>
+      <c r="F111" s="16"/>
+      <c r="G111" s="17">
+        <v>1</v>
+      </c>
+      <c r="H111" s="4"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="12">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="B112" s="15"/>
+      <c r="C112" s="13"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="15"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="17">
+        <v>1</v>
+      </c>
+      <c r="H112" s="4"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="12">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="B113" s="15"/>
+      <c r="C113" s="13"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="15"/>
+      <c r="F113" s="16"/>
+      <c r="G113" s="17">
+        <v>1</v>
+      </c>
+      <c r="H113" s="4"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="12">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="B114" s="15"/>
+      <c r="C114" s="13"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="15"/>
+      <c r="F114" s="16"/>
+      <c r="G114" s="17">
+        <v>1</v>
+      </c>
+      <c r="H114" s="4"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="12">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="B115" s="15"/>
+      <c r="C115" s="13"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="15"/>
+      <c r="F115" s="16"/>
+      <c r="G115" s="17">
+        <v>1</v>
+      </c>
+      <c r="H115" s="4"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="12">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="B116" s="15"/>
+      <c r="C116" s="13"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="15"/>
+      <c r="F116" s="16"/>
+      <c r="G116" s="17">
+        <v>1</v>
+      </c>
+      <c r="H116" s="4"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="12">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="B117" s="15"/>
+      <c r="C117" s="13"/>
+      <c r="D117" s="14"/>
+      <c r="E117" s="15"/>
+      <c r="F117" s="16"/>
+      <c r="G117" s="17">
+        <v>1</v>
+      </c>
+      <c r="H117" s="4"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I27">
+    <sortCondition ref="E7:E27"/>
+    <sortCondition ref="D7:D27"/>
+  </sortState>
+  <mergeCells count="9">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="I4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283472" right="0.45" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE4F4C1-59D3-4C1B-BA5C-E563FC2D0F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C532598-0D62-40B1-BDAD-5EA9BB1A8FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="756">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -2303,9 +2303,6 @@
     <t>Djedi med</t>
   </si>
   <si>
-    <t>rue emir aek</t>
-  </si>
-  <si>
     <r>
       <t>Mois de Mai</t>
     </r>
@@ -2339,9 +2336,6 @@
     <t>Ent bakhti dahmane</t>
   </si>
   <si>
-    <t>projet 80  logts lpa cité cheriet</t>
-  </si>
-  <si>
     <t>B50020</t>
   </si>
   <si>
@@ -2363,15 +2357,9 @@
     <t>Fergani sahraoui</t>
   </si>
   <si>
-    <t>ouled fergane</t>
-  </si>
-  <si>
     <t>Hannichi med</t>
   </si>
   <si>
-    <t>djenane tebbal</t>
-  </si>
-  <si>
     <t>NB(150/2025)</t>
   </si>
   <si>
@@ -2381,15 +2369,9 @@
     <t>Hamzaoui bachir</t>
   </si>
   <si>
-    <t>cité 720 logts b30 n19</t>
-  </si>
-  <si>
     <t>Bouamra brahim</t>
   </si>
   <si>
-    <t>residence chorfi A n12</t>
-  </si>
-  <si>
     <t>NB(159/2026)</t>
   </si>
   <si>
@@ -2399,94 +2381,64 @@
     <t>Merah mourad</t>
   </si>
   <si>
-    <t>la remonte</t>
-  </si>
-  <si>
     <t>Yahmi missoum</t>
   </si>
   <si>
-    <t>cité hantable n118</t>
-  </si>
-  <si>
     <t>NB(135/2026)</t>
   </si>
   <si>
     <t>Makhloufi med</t>
   </si>
   <si>
-    <t>cité 720 logts b6 n8</t>
-  </si>
-  <si>
-    <t>NB(168/2025)</t>
-  </si>
-  <si>
     <t>Rezkallah salima</t>
   </si>
   <si>
-    <t>cité 720 logts b 11 n20</t>
-  </si>
-  <si>
     <t>NB(167/2025)</t>
   </si>
   <si>
     <t>Askri med</t>
   </si>
   <si>
-    <t>cité 720 logts b 2 n15</t>
-  </si>
-  <si>
     <t>NB(025/2026)</t>
   </si>
   <si>
     <t>Benzayed hamza</t>
   </si>
   <si>
-    <t>cité 720 logts b 5 n11</t>
-  </si>
-  <si>
     <t>Bouchenafa ali</t>
   </si>
   <si>
-    <t>cité 720 logts b 7 n36</t>
-  </si>
-  <si>
     <t>NB(166/2026)</t>
   </si>
   <si>
     <t>Zerga benaissa</t>
   </si>
   <si>
-    <t>cité 720 logts b 10 n4</t>
-  </si>
-  <si>
     <t>NB(123/2026)</t>
   </si>
   <si>
     <t>Makhloufi med amine</t>
   </si>
   <si>
-    <t>cité 720 logts b 17 n32</t>
-  </si>
-  <si>
     <t>NB(152/2026)</t>
   </si>
   <si>
     <t>Benabderrahmane boulanouar</t>
   </si>
   <si>
-    <t>cité 720 logts b 19 n12</t>
-  </si>
-  <si>
     <t>NB(069/2026)</t>
   </si>
   <si>
     <t>Aneka hichem</t>
   </si>
   <si>
-    <t>cité 720 logts b 15 n34</t>
-  </si>
-  <si>
     <t>NB(753/2025)</t>
+  </si>
+  <si>
+    <t>NB(168/2026)</t>
+  </si>
+  <si>
+    <t>B21495</t>
   </si>
 </sst>
 </file>
@@ -2651,7 +2603,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2734,9 +2686,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -14664,7 +14613,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -14711,7 +14660,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="23"/>
@@ -14726,7 +14675,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -14783,9 +14732,7 @@
       <c r="H7" s="18" t="s">
         <v>716</v>
       </c>
-      <c r="I7" s="20" t="s">
-        <v>717</v>
-      </c>
+      <c r="I7" s="20"/>
       <c r="J7" s="19"/>
       <c r="K7" s="4"/>
     </row>
@@ -14795,7 +14742,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C8" s="13">
         <v>40</v>
@@ -14823,7 +14770,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>18</v>
@@ -14835,17 +14782,15 @@
         <v>46145</v>
       </c>
       <c r="F9" s="16" t="s">
+        <v>719</v>
+      </c>
+      <c r="G9" s="17">
+        <v>1</v>
+      </c>
+      <c r="H9" s="18" t="s">
         <v>720</v>
       </c>
-      <c r="G9" s="17">
-        <v>1</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>721</v>
-      </c>
-      <c r="I9" s="20" t="s">
-        <v>722</v>
-      </c>
+      <c r="I9" s="20"/>
       <c r="J9" s="20"/>
       <c r="K9" s="4"/>
     </row>
@@ -14855,7 +14800,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>18</v>
@@ -14882,7 +14827,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C11" s="13">
         <v>30</v>
@@ -14910,13 +14855,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C12" s="13">
         <v>100</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E12" s="15">
         <v>46146</v>
@@ -14949,17 +14894,15 @@
         <v>46148</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="G13" s="17">
         <v>1</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>735</v>
-      </c>
-      <c r="I13" s="20" t="s">
-        <v>736</v>
-      </c>
+        <v>731</v>
+      </c>
+      <c r="I13" s="20"/>
       <c r="J13" s="20"/>
       <c r="K13" s="4"/>
     </row>
@@ -14981,17 +14924,15 @@
         <v>46148</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>759</v>
+        <v>745</v>
       </c>
       <c r="G14" s="17">
         <v>1</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>757</v>
-      </c>
-      <c r="I14" s="20" t="s">
-        <v>758</v>
-      </c>
+        <v>744</v>
+      </c>
+      <c r="I14" s="20"/>
       <c r="J14" s="20"/>
       <c r="K14" s="4"/>
     </row>
@@ -15013,16 +14954,13 @@
         <v>46148</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="G15" s="17">
         <v>1</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>729</v>
-      </c>
-      <c r="I15" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="J15" s="20"/>
     </row>
@@ -15044,17 +14982,15 @@
         <v>46148</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G16" s="17">
         <v>1</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>737</v>
-      </c>
-      <c r="I16" s="29" t="s">
-        <v>738</v>
-      </c>
+        <v>732</v>
+      </c>
+      <c r="I16" s="20"/>
       <c r="J16" s="20"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15075,17 +15011,15 @@
         <v>46148</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>771</v>
+        <v>753</v>
       </c>
       <c r="G17" s="17">
         <v>1</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>769</v>
-      </c>
-      <c r="I17" s="20" t="s">
-        <v>770</v>
-      </c>
+        <v>752</v>
+      </c>
+      <c r="I17" s="20"/>
       <c r="J17" s="20"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15106,17 +15040,15 @@
         <v>46148</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>762</v>
+        <v>747</v>
       </c>
       <c r="G18" s="17">
         <v>1</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>760</v>
-      </c>
-      <c r="I18" s="20" t="s">
-        <v>761</v>
-      </c>
+        <v>746</v>
+      </c>
+      <c r="I18" s="20"/>
       <c r="J18" s="20"/>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15137,17 +15069,15 @@
         <v>46148</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>754</v>
+        <v>742</v>
       </c>
       <c r="G19" s="17">
         <v>1</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>752</v>
-      </c>
-      <c r="I19" s="20" t="s">
-        <v>753</v>
-      </c>
+        <v>741</v>
+      </c>
+      <c r="I19" s="20"/>
       <c r="J19" s="20"/>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15168,17 +15098,15 @@
         <v>46148</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="G20" s="17">
         <v>1</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>746</v>
-      </c>
-      <c r="I20" s="20" t="s">
-        <v>747</v>
-      </c>
+        <v>738</v>
+      </c>
+      <c r="I20" s="20"/>
       <c r="J20" s="20"/>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15199,17 +15127,15 @@
         <v>46148</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="G21" s="17">
         <v>1</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>755</v>
-      </c>
-      <c r="I21" s="20" t="s">
-        <v>756</v>
-      </c>
+        <v>743</v>
+      </c>
+      <c r="I21" s="20"/>
       <c r="J21" s="20"/>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15230,17 +15156,15 @@
         <v>46148</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="G22" s="17">
         <v>1</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>749</v>
-      </c>
-      <c r="I22" s="20" t="s">
-        <v>750</v>
-      </c>
+        <v>739</v>
+      </c>
+      <c r="I22" s="20"/>
       <c r="J22" s="20"/>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15261,17 +15185,15 @@
         <v>46148</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>768</v>
+        <v>751</v>
       </c>
       <c r="G23" s="17">
         <v>1</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>766</v>
-      </c>
-      <c r="I23" s="20" t="s">
-        <v>767</v>
-      </c>
+        <v>750</v>
+      </c>
+      <c r="I23" s="20"/>
       <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15292,17 +15214,15 @@
         <v>46148</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="G24" s="17">
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="I24" s="29" t="s">
-        <v>742</v>
-      </c>
+        <v>735</v>
+      </c>
+      <c r="I24" s="20"/>
       <c r="J24" s="20"/>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15323,17 +15243,15 @@
         <v>46148</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="G25" s="17">
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>743</v>
-      </c>
-      <c r="I25" s="29" t="s">
-        <v>744</v>
-      </c>
+        <v>736</v>
+      </c>
+      <c r="I25" s="20"/>
       <c r="J25" s="20"/>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15354,17 +15272,15 @@
         <v>46148</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="G26" s="17">
         <v>1</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>763</v>
-      </c>
-      <c r="I26" s="20" t="s">
-        <v>764</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="I26" s="20"/>
       <c r="J26" s="20"/>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15385,17 +15301,15 @@
         <v>46148</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="G27" s="17">
         <v>1</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>731</v>
-      </c>
-      <c r="I27" s="20" t="s">
-        <v>732</v>
-      </c>
+        <v>728</v>
+      </c>
+      <c r="I27" s="20"/>
       <c r="J27" s="20"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15403,11 +15317,21 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="16"/>
+      <c r="B28" s="13" t="s">
+        <v>755</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D28" s="13">
+        <v>2024004550</v>
+      </c>
+      <c r="E28" s="15">
+        <v>46151</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G28" s="17">
         <v>1</v>
       </c>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C532598-0D62-40B1-BDAD-5EA9BB1A8FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D029A3E1-5A0C-48EA-AF14-8EA7921DE7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="780">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -2439,6 +2439,78 @@
   </si>
   <si>
     <t>B21495</t>
+  </si>
+  <si>
+    <t>NB(698/2026)</t>
+  </si>
+  <si>
+    <t>Mag nefad benyahia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">800 logts </t>
+  </si>
+  <si>
+    <t>Hadj amar</t>
+  </si>
+  <si>
+    <t>720 logts bt 13n31</t>
+  </si>
+  <si>
+    <t>NB(582/2025)</t>
+  </si>
+  <si>
+    <t>Café medjber aek</t>
+  </si>
+  <si>
+    <t>cité 40 logts bt 31 n4</t>
+  </si>
+  <si>
+    <t>NB(005/2026)</t>
+  </si>
+  <si>
+    <t>Bendali brahim</t>
+  </si>
+  <si>
+    <t>720 logts bt 19 n9</t>
+  </si>
+  <si>
+    <t>NB(420/2025)</t>
+  </si>
+  <si>
+    <t>Tebouzi lyes</t>
+  </si>
+  <si>
+    <t>720 logts bt 12 n14</t>
+  </si>
+  <si>
+    <t>NB(597/2025)</t>
+  </si>
+  <si>
+    <t>Benchaabane soufiane</t>
+  </si>
+  <si>
+    <t>720 logts bt 7 n12</t>
+  </si>
+  <si>
+    <t>Benkahla ahmed</t>
+  </si>
+  <si>
+    <t>720 logts bt 3 n32</t>
+  </si>
+  <si>
+    <t>NB(176/2025)</t>
+  </si>
+  <si>
+    <t>NB(177/2026)</t>
+  </si>
+  <si>
+    <t>720 logts bt 2 n31</t>
+  </si>
+  <si>
+    <t>Bourial omar</t>
+  </si>
+  <si>
+    <t>NB(187/2026)</t>
   </si>
 </sst>
 </file>
@@ -14635,7 +14707,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -14675,7 +14747,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -15343,15 +15415,30 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="16"/>
+      <c r="B29" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="13">
+        <v>2025177291</v>
+      </c>
+      <c r="E29" s="15">
+        <v>46155</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>756</v>
+      </c>
       <c r="G29" s="17">
         <v>1</v>
       </c>
-      <c r="H29" s="4"/>
+      <c r="H29" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="I29" t="s">
+        <v>758</v>
+      </c>
       <c r="J29" s="20"/>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15359,15 +15446,30 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="16"/>
+      <c r="B30" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="13">
+        <v>2025177292</v>
+      </c>
+      <c r="E30" s="15">
+        <v>46155</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>761</v>
+      </c>
       <c r="G30" s="17">
         <v>1</v>
       </c>
-      <c r="H30" s="18"/>
+      <c r="H30" s="18" t="s">
+        <v>759</v>
+      </c>
+      <c r="I30" t="s">
+        <v>760</v>
+      </c>
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15375,16 +15477,30 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="16"/>
+      <c r="B31" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="13">
+        <v>2025177293</v>
+      </c>
+      <c r="E31" s="15">
+        <v>46155</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>767</v>
+      </c>
       <c r="G31" s="17">
         <v>1</v>
       </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="20"/>
+      <c r="H31" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="I31" t="s">
+        <v>766</v>
+      </c>
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15392,15 +15508,30 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="16"/>
+      <c r="B32" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="13">
+        <v>2025177294</v>
+      </c>
+      <c r="E32" s="15">
+        <v>46155</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>764</v>
+      </c>
       <c r="G32" s="17">
         <v>1</v>
       </c>
-      <c r="H32" s="4"/>
+      <c r="H32" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="I32" s="20" t="s">
+        <v>763</v>
+      </c>
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15408,15 +15539,30 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="16"/>
+      <c r="B33" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="13">
+        <v>2025177295</v>
+      </c>
+      <c r="E33" s="15">
+        <v>46155</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>770</v>
+      </c>
       <c r="G33" s="17">
         <v>1</v>
       </c>
-      <c r="H33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="I33" t="s">
+        <v>769</v>
+      </c>
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15424,15 +15570,30 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="16"/>
+      <c r="B34" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="13">
+        <v>2025177297</v>
+      </c>
+      <c r="E34" s="15">
+        <v>46155</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>776</v>
+      </c>
       <c r="G34" s="17">
         <v>1</v>
       </c>
-      <c r="H34" s="18"/>
+      <c r="H34" s="18" t="s">
+        <v>771</v>
+      </c>
+      <c r="I34" t="s">
+        <v>772</v>
+      </c>
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15440,15 +15601,30 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="16"/>
+      <c r="B35" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="13">
+        <v>2025177298</v>
+      </c>
+      <c r="E35" s="15">
+        <v>46155</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>779</v>
+      </c>
       <c r="G35" s="17">
         <v>1</v>
       </c>
-      <c r="H35" s="18"/>
+      <c r="H35" s="18" t="s">
+        <v>778</v>
+      </c>
+      <c r="I35" t="s">
+        <v>777</v>
+      </c>
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15456,15 +15632,30 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="16"/>
+      <c r="B36" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="13">
+        <v>2025177300</v>
+      </c>
+      <c r="E36" s="15">
+        <v>46155</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>775</v>
+      </c>
       <c r="G36" s="17">
         <v>1</v>
       </c>
-      <c r="H36" s="18"/>
+      <c r="H36" s="18" t="s">
+        <v>773</v>
+      </c>
+      <c r="I36" t="s">
+        <v>774</v>
+      </c>
       <c r="J36" s="4"/>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16700,9 +16891,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I27">
-    <sortCondition ref="E7:E27"/>
-    <sortCondition ref="D7:D27"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I36">
+    <sortCondition ref="E7:E36"/>
+    <sortCondition ref="D7:D36"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D029A3E1-5A0C-48EA-AF14-8EA7921DE7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41571575-D95A-4C53-90A1-68DE86399D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="783">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -2511,6 +2511,15 @@
   </si>
   <si>
     <t>NB(187/2026)</t>
+  </si>
+  <si>
+    <t>BC0485</t>
+  </si>
+  <si>
+    <t>B50058</t>
+  </si>
+  <si>
+    <t>B50037</t>
   </si>
 </sst>
 </file>
@@ -14644,7 +14653,7 @@
     <col min="4" max="4" width="14.140625" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" customWidth="1"/>
     <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="2.140625" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="29.85546875" customWidth="1"/>
     <col min="9" max="9" width="32.140625" customWidth="1"/>
   </cols>
@@ -14685,7 +14694,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -14747,7 +14756,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -15663,11 +15672,21 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="16"/>
+      <c r="B37" s="15" t="s">
+        <v>724</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="13">
+        <v>2025117461</v>
+      </c>
+      <c r="E37" s="15">
+        <v>46163</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G37" s="17">
         <v>1</v>
       </c>
@@ -15680,15 +15699,26 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="16"/>
+      <c r="B38" s="15" t="s">
+        <v>782</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="13">
+        <v>2025117462</v>
+      </c>
+      <c r="E38" s="15">
+        <v>46163</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G38" s="17">
         <v>1</v>
       </c>
       <c r="H38" s="4"/>
+      <c r="I38" s="20"/>
       <c r="J38" s="4"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -15696,31 +15726,50 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="16"/>
+      <c r="B39" s="15" t="s">
+        <v>780</v>
+      </c>
+      <c r="C39" s="13">
+        <v>30</v>
+      </c>
+      <c r="D39" s="13">
+        <v>18041008042</v>
+      </c>
+      <c r="E39" s="15">
+        <v>46163</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G39" s="17">
         <v>1</v>
       </c>
-      <c r="H39" s="18"/>
-      <c r="I39" s="20"/>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
         <f>+A39+1</f>
         <v>34</v>
       </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="16"/>
+      <c r="B40" s="15" t="s">
+        <v>781</v>
+      </c>
+      <c r="C40" s="13">
+        <v>30</v>
+      </c>
+      <c r="D40" s="13">
+        <v>18041008044</v>
+      </c>
+      <c r="E40" s="15">
+        <v>46163</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G40" s="17">
         <v>1</v>
       </c>
-      <c r="H40" s="4"/>
+      <c r="H40" s="18"/>
       <c r="I40" s="20"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -16891,9 +16940,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I36">
-    <sortCondition ref="E7:E36"/>
-    <sortCondition ref="D7:D36"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I40">
+    <sortCondition ref="E7:E40"/>
+    <sortCondition ref="D7:D40"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41571575-D95A-4C53-90A1-68DE86399D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EB9055-FB11-4214-8935-C94B00E24915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Janvier 2026 " sheetId="2" r:id="rId1"/>
@@ -18,11 +18,13 @@
     <sheet name="Mars 2026" sheetId="3" r:id="rId3"/>
     <sheet name="Avril 2026" sheetId="4" r:id="rId4"/>
     <sheet name="Mai 2026" sheetId="5" r:id="rId5"/>
+    <sheet name="Juin 2026" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Avril 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Février 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Janvier 2026 '!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Juin 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Mai 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mars 2026'!$1:$6</definedName>
   </definedNames>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="806">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -2520,6 +2522,96 @@
   </si>
   <si>
     <t>B50037</t>
+  </si>
+  <si>
+    <t>BB0269</t>
+  </si>
+  <si>
+    <r>
+      <t>Mois de Juin</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <t>BC0477</t>
+  </si>
+  <si>
+    <t>BC0392</t>
+  </si>
+  <si>
+    <t>B21252</t>
+  </si>
+  <si>
+    <t>B21403</t>
+  </si>
+  <si>
+    <t>B21416</t>
+  </si>
+  <si>
+    <t>BC0818</t>
+  </si>
+  <si>
+    <t>NB(181/2026)</t>
+  </si>
+  <si>
+    <t>Yekhlef dalila</t>
+  </si>
+  <si>
+    <t>720 logts bt 14 n33</t>
+  </si>
+  <si>
+    <t>B21388</t>
+  </si>
+  <si>
+    <t>2024004658</t>
+  </si>
+  <si>
+    <t>B21385</t>
+  </si>
+  <si>
+    <t>2024004546</t>
+  </si>
+  <si>
+    <t>B21405</t>
+  </si>
+  <si>
+    <t>2024004548</t>
+  </si>
+  <si>
+    <t>Bouraki fodhil</t>
+  </si>
+  <si>
+    <t>720 logts bt 6 n7</t>
+  </si>
+  <si>
+    <t>NB</t>
+  </si>
+  <si>
+    <t>NB(308/2020)</t>
+  </si>
+  <si>
+    <t>Slimani samir</t>
+  </si>
+  <si>
+    <t>100 Locaux Commercial oued guelet</t>
   </si>
 </sst>
 </file>
@@ -3109,6 +3201,111 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Connecteur droit 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FDD2328-EC47-64BB-1D4E-A51B4E11955E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="619125" y="8001000"/>
+          <a:ext cx="4610100" cy="933450"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>104785</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connecteur droit 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4C486ED-B088-4BC2-9492-B3D31507D542}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="695335" y="21678900"/>
+          <a:ext cx="4648190" cy="238125"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -10656,7 +10853,7 @@
         <v>39</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>257</v>
+        <v>790</v>
       </c>
       <c r="C45" s="13" t="s">
         <v>18</v>
@@ -14716,7 +14913,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -14756,7 +14953,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -14936,7 +15133,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>724</v>
+        <v>783</v>
       </c>
       <c r="C12" s="13">
         <v>100</v>
@@ -15777,16 +15974,30 @@
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="16"/>
+      <c r="B41" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="13">
+        <v>2025117732</v>
+      </c>
+      <c r="E41" s="15">
+        <v>46168</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>791</v>
+      </c>
       <c r="G41" s="17">
         <v>1</v>
       </c>
-      <c r="H41" s="4"/>
-      <c r="I41" s="20"/>
+      <c r="H41" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="I41" t="s">
+        <v>793</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
@@ -16962,4 +17173,2021 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C1F597-77EB-4611-903C-E179A2348B42}">
+  <dimension ref="A1:K117"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="2.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+    <col min="9" max="9" width="32.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="25"/>
+      <c r="K2" s="6">
+        <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="25"/>
+      <c r="K3" s="6">
+        <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="25"/>
+      <c r="K4" s="6">
+        <f>SUMIF(F7:F364,"Ve*",G7:G364)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>784</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="8">
+        <f>SUM(K2:K4)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>1</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>786</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="13">
+        <v>2025117733</v>
+      </c>
+      <c r="E7" s="15">
+        <v>46174</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G7" s="17">
+        <v>1</v>
+      </c>
+      <c r="H7" s="18"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <f t="shared" ref="A8:A71" si="0">+A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>785</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="13">
+        <v>2025117734</v>
+      </c>
+      <c r="E8" s="15">
+        <v>46174</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G8" s="17">
+        <v>1</v>
+      </c>
+      <c r="H8" s="18"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>787</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="13">
+        <v>2025117735</v>
+      </c>
+      <c r="E9" s="15">
+        <v>46174</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G9" s="17">
+        <v>1</v>
+      </c>
+      <c r="H9" s="18"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>789</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D10" s="13">
+        <v>2024004653</v>
+      </c>
+      <c r="E10" s="15">
+        <v>46179</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G10" s="17">
+        <v>1</v>
+      </c>
+      <c r="H10" s="18"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>788</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D11" s="13">
+        <v>2024004688</v>
+      </c>
+      <c r="E11" s="15">
+        <v>46179</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G11" s="17">
+        <v>1</v>
+      </c>
+      <c r="H11" s="18"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>797</v>
+      </c>
+      <c r="E12" s="15">
+        <v>46182</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G12" s="17">
+        <v>1</v>
+      </c>
+      <c r="H12" s="18"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>798</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>799</v>
+      </c>
+      <c r="E13" s="15">
+        <v>46182</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G13" s="17">
+        <v>1</v>
+      </c>
+      <c r="H13" s="18"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>794</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>795</v>
+      </c>
+      <c r="E14" s="15">
+        <v>46182</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G14" s="17">
+        <v>1</v>
+      </c>
+      <c r="H14" s="18"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="13">
+        <v>2025117740</v>
+      </c>
+      <c r="E15" s="15">
+        <v>46183</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>802</v>
+      </c>
+      <c r="G15" s="17">
+        <v>1</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>800</v>
+      </c>
+      <c r="I15" t="s">
+        <v>801</v>
+      </c>
+      <c r="J15" s="20"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="13">
+        <v>2025117739</v>
+      </c>
+      <c r="E16" s="15">
+        <v>46186</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>803</v>
+      </c>
+      <c r="G16" s="17">
+        <v>1</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>805</v>
+      </c>
+      <c r="J16" s="20"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17">
+        <v>1</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="17">
+        <v>1</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="17">
+        <v>1</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="17">
+        <v>1</v>
+      </c>
+      <c r="H20" s="18"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="17">
+        <v>1</v>
+      </c>
+      <c r="H21" s="18"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17">
+        <v>1</v>
+      </c>
+      <c r="H22" s="18"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="17">
+        <v>1</v>
+      </c>
+      <c r="H23" s="18"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="17">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="17">
+        <v>1</v>
+      </c>
+      <c r="H26" s="18"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17">
+        <v>1</v>
+      </c>
+      <c r="H27" s="18"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4"/>
+      <c r="J28" s="20"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="12">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="15"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4"/>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17">
+        <v>1</v>
+      </c>
+      <c r="H30" s="18"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="17">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="15"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="17">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="12">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="17">
+        <v>1</v>
+      </c>
+      <c r="H33" s="4"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="12">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="17">
+        <v>1</v>
+      </c>
+      <c r="H34" s="18"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="12">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="17">
+        <v>1</v>
+      </c>
+      <c r="H35" s="18"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="12">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="17">
+        <v>1</v>
+      </c>
+      <c r="H36" s="18"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="12">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="15"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="17">
+        <v>1</v>
+      </c>
+      <c r="H37" s="18"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="12">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="15"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="17">
+        <v>1</v>
+      </c>
+      <c r="H38" s="4"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="12">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B39" s="15"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="17">
+        <v>1</v>
+      </c>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="12">
+        <f>+A39+1</f>
+        <v>34</v>
+      </c>
+      <c r="B40" s="15"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="17">
+        <v>1</v>
+      </c>
+      <c r="H40" s="18"/>
+      <c r="I40" s="20"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="12">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="15"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="17">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="20"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="12">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="17">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4"/>
+      <c r="I42" s="20"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="12">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="17">
+        <v>1</v>
+      </c>
+      <c r="H43" s="18"/>
+      <c r="I43" s="20"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="12">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="17">
+        <v>1</v>
+      </c>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="12">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="17">
+        <v>1</v>
+      </c>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="12">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="15"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="17">
+        <v>1</v>
+      </c>
+      <c r="H46" s="4"/>
+      <c r="I46" s="20"/>
+    </row>
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="12">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B47" s="15"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="17">
+        <v>1</v>
+      </c>
+      <c r="H47" s="4"/>
+      <c r="I47" s="20"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="12">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B48" s="15"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="17">
+        <v>1</v>
+      </c>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="12">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B49" s="15"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="17">
+        <v>1</v>
+      </c>
+      <c r="H49" s="4"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="12">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B50" s="15"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="17">
+        <v>1</v>
+      </c>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="12">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B51" s="15"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="17">
+        <v>1</v>
+      </c>
+      <c r="H51" s="4"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="12">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B52" s="15"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="17">
+        <v>1</v>
+      </c>
+      <c r="H52" s="4"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="12">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B53" s="15"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="17">
+        <v>1</v>
+      </c>
+      <c r="H53" s="4"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="12">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B54" s="15"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="17">
+        <v>1</v>
+      </c>
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="12">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B55" s="15"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="17">
+        <v>1</v>
+      </c>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="12">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B56" s="15"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="17">
+        <v>1</v>
+      </c>
+      <c r="H56" s="4"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="12">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="17">
+        <v>1</v>
+      </c>
+      <c r="H57" s="4"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="12">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B58" s="15"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="17">
+        <v>1</v>
+      </c>
+      <c r="H58" s="4"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="12">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B59" s="15"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="17">
+        <v>1</v>
+      </c>
+      <c r="H59" s="4"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="12">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B60" s="15"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="17">
+        <v>1</v>
+      </c>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="12">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B61" s="15"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="17">
+        <v>1</v>
+      </c>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="12">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B62" s="15"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="17">
+        <v>1</v>
+      </c>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="12">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B63" s="15"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="17">
+        <v>1</v>
+      </c>
+      <c r="H63" s="4"/>
+      <c r="I63" s="20"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="12">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B64" s="15"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="15"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="17">
+        <v>1</v>
+      </c>
+      <c r="H64" s="4"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="12">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B65" s="15"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="17">
+        <v>1</v>
+      </c>
+      <c r="H65" s="4"/>
+      <c r="I65" s="20"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="12">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="17">
+        <v>1</v>
+      </c>
+      <c r="H66" s="4"/>
+      <c r="I66" s="20"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="12">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B67" s="15"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="15"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="17">
+        <v>1</v>
+      </c>
+      <c r="H67" s="4"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="12">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B68" s="15"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="17">
+        <v>1</v>
+      </c>
+      <c r="H68" s="4"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="12">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B69" s="15"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="17">
+        <v>1</v>
+      </c>
+      <c r="H69" s="4"/>
+      <c r="I69" s="20"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="12">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B70" s="15"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="17">
+        <v>1</v>
+      </c>
+      <c r="H70" s="4"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="12">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B71" s="15"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="17">
+        <v>1</v>
+      </c>
+      <c r="H71" s="4"/>
+      <c r="I71" s="20"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="12">
+        <f t="shared" ref="A72:A117" si="1">+A71+1</f>
+        <v>66</v>
+      </c>
+      <c r="B72" s="15"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="17">
+        <v>1</v>
+      </c>
+      <c r="H72" s="4"/>
+      <c r="I72" s="20"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="12">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="B73" s="15"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="17">
+        <v>1</v>
+      </c>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="12">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="B74" s="15"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="17">
+        <v>1</v>
+      </c>
+      <c r="H74" s="4"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="12">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B75" s="15"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="17">
+        <v>1</v>
+      </c>
+      <c r="H75" s="4"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="12">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="B76" s="15"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="17">
+        <v>1</v>
+      </c>
+      <c r="H76" s="4"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="12">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="B77" s="15"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="17">
+        <v>1</v>
+      </c>
+      <c r="H77" s="4"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="12">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="B78" s="15"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="17">
+        <v>1</v>
+      </c>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="12">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="B79" s="15"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="17">
+        <v>1</v>
+      </c>
+      <c r="H79" s="4"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="12">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="B80" s="15"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="17">
+        <v>1</v>
+      </c>
+      <c r="H80" s="4"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="12">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="B81" s="15"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="17">
+        <v>1</v>
+      </c>
+      <c r="H81" s="4"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="12">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="B82" s="15"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="17">
+        <v>1</v>
+      </c>
+      <c r="H82" s="4"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="12">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="B83" s="15"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="17">
+        <v>1</v>
+      </c>
+      <c r="H83" s="4"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="12">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="B84" s="15"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="15"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="17">
+        <v>1</v>
+      </c>
+      <c r="H84" s="4"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="12">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="B85" s="15"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="16"/>
+      <c r="G85" s="17">
+        <v>1</v>
+      </c>
+      <c r="H85" s="4"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="12">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="B86" s="15"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="16"/>
+      <c r="G86" s="17">
+        <v>1</v>
+      </c>
+      <c r="H86" s="4"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="12">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="B87" s="15"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="17">
+        <v>1</v>
+      </c>
+      <c r="H87" s="4"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="12">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="B88" s="15"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="17">
+        <v>1</v>
+      </c>
+      <c r="H88" s="4"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="12">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="B89" s="15"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="17">
+        <v>1</v>
+      </c>
+      <c r="H89" s="4"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="12">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="B90" s="15"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="16"/>
+      <c r="G90" s="17">
+        <v>1</v>
+      </c>
+      <c r="H90" s="4"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="12">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="B91" s="15"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="17">
+        <v>1</v>
+      </c>
+      <c r="H91" s="4"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="12">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="B92" s="15"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="17">
+        <v>1</v>
+      </c>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="12">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="B93" s="15"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="17">
+        <v>1</v>
+      </c>
+      <c r="H93" s="4"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="12">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="B94" s="15"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="15"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="17">
+        <v>1</v>
+      </c>
+      <c r="H94" s="4"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="12">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="B95" s="15"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="15"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="17">
+        <v>1</v>
+      </c>
+      <c r="H95" s="4"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="12">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="B96" s="15"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="16"/>
+      <c r="G96" s="17">
+        <v>1</v>
+      </c>
+      <c r="H96" s="4"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="12">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="B97" s="15"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="16"/>
+      <c r="G97" s="17">
+        <v>1</v>
+      </c>
+      <c r="H97" s="4"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="12">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="B98" s="15"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="16"/>
+      <c r="G98" s="17">
+        <v>1</v>
+      </c>
+      <c r="H98" s="4"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="12">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="B99" s="15"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="15"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="17">
+        <v>1</v>
+      </c>
+      <c r="H99" s="4"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="12">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="B100" s="15"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="15"/>
+      <c r="F100" s="16"/>
+      <c r="G100" s="17">
+        <v>1</v>
+      </c>
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="12">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="B101" s="15"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="16"/>
+      <c r="G101" s="17">
+        <v>1</v>
+      </c>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="12">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="B102" s="15"/>
+      <c r="C102" s="13"/>
+      <c r="D102" s="14"/>
+      <c r="E102" s="15"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="17">
+        <v>1</v>
+      </c>
+      <c r="H102" s="4"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="12">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="B103" s="15"/>
+      <c r="C103" s="13"/>
+      <c r="D103" s="14"/>
+      <c r="E103" s="15"/>
+      <c r="F103" s="16"/>
+      <c r="G103" s="17">
+        <v>1</v>
+      </c>
+      <c r="H103" s="4"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="12">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="B104" s="15"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="22"/>
+      <c r="E104" s="15"/>
+      <c r="F104" s="16"/>
+      <c r="G104" s="17">
+        <v>1</v>
+      </c>
+      <c r="H104" s="4"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="12">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="B105" s="15"/>
+      <c r="C105" s="13"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="15"/>
+      <c r="F105" s="16"/>
+      <c r="G105" s="17">
+        <v>1</v>
+      </c>
+      <c r="H105" s="4"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="12">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="B106" s="15"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="15"/>
+      <c r="F106" s="16"/>
+      <c r="G106" s="17">
+        <v>1</v>
+      </c>
+      <c r="H106" s="4"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="12">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="B107" s="15"/>
+      <c r="C107" s="13"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="15"/>
+      <c r="F107" s="16"/>
+      <c r="G107" s="17">
+        <v>1</v>
+      </c>
+      <c r="H107" s="4"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="12">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="B108" s="15"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="14"/>
+      <c r="E108" s="15"/>
+      <c r="F108" s="16"/>
+      <c r="G108" s="17">
+        <v>1</v>
+      </c>
+      <c r="H108" s="4"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="12">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="B109" s="15"/>
+      <c r="C109" s="13"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="15"/>
+      <c r="F109" s="16"/>
+      <c r="G109" s="17">
+        <v>1</v>
+      </c>
+      <c r="H109" s="4"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="12">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="B110" s="15"/>
+      <c r="C110" s="13"/>
+      <c r="D110" s="14"/>
+      <c r="E110" s="15"/>
+      <c r="F110" s="16"/>
+      <c r="G110" s="17">
+        <v>1</v>
+      </c>
+      <c r="H110" s="4"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="12">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="B111" s="15"/>
+      <c r="C111" s="13"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="15"/>
+      <c r="F111" s="16"/>
+      <c r="G111" s="17">
+        <v>1</v>
+      </c>
+      <c r="H111" s="4"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="12">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="B112" s="15"/>
+      <c r="C112" s="13"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="15"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="17">
+        <v>1</v>
+      </c>
+      <c r="H112" s="4"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="12">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="B113" s="15"/>
+      <c r="C113" s="13"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="15"/>
+      <c r="F113" s="16"/>
+      <c r="G113" s="17">
+        <v>1</v>
+      </c>
+      <c r="H113" s="4"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="12">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="B114" s="15"/>
+      <c r="C114" s="13"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="15"/>
+      <c r="F114" s="16"/>
+      <c r="G114" s="17">
+        <v>1</v>
+      </c>
+      <c r="H114" s="4"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="12">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="B115" s="15"/>
+      <c r="C115" s="13"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="15"/>
+      <c r="F115" s="16"/>
+      <c r="G115" s="17">
+        <v>1</v>
+      </c>
+      <c r="H115" s="4"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="12">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="B116" s="15"/>
+      <c r="C116" s="13"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="15"/>
+      <c r="F116" s="16"/>
+      <c r="G116" s="17">
+        <v>1</v>
+      </c>
+      <c r="H116" s="4"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="12">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="B117" s="15"/>
+      <c r="C117" s="13"/>
+      <c r="D117" s="14"/>
+      <c r="E117" s="15"/>
+      <c r="F117" s="16"/>
+      <c r="G117" s="17">
+        <v>1</v>
+      </c>
+      <c r="H117" s="4"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:F14">
+    <sortCondition ref="E7:E14"/>
+    <sortCondition ref="D7:D14"/>
+  </sortState>
+  <mergeCells count="9">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="I4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283472" right="0.45" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EB9055-FB11-4214-8935-C94B00E24915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AAEC350-7869-492D-ACC7-9BCE55EE6E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Janvier 2026 " sheetId="2" r:id="rId1"/>
@@ -19,11 +19,13 @@
     <sheet name="Avril 2026" sheetId="4" r:id="rId4"/>
     <sheet name="Mai 2026" sheetId="5" r:id="rId5"/>
     <sheet name="Juin 2026" sheetId="6" r:id="rId6"/>
+    <sheet name="Juillet 2026" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Avril 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Février 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Janvier 2026 '!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Juillet 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Juin 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Mai 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mars 2026'!$1:$6</definedName>
@@ -49,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="863">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -2359,9 +2361,6 @@
     <t>Fergani sahraoui</t>
   </si>
   <si>
-    <t>Hannichi med</t>
-  </si>
-  <si>
     <t>NB(150/2025)</t>
   </si>
   <si>
@@ -2449,64 +2448,40 @@
     <t>Mag nefad benyahia</t>
   </si>
   <si>
-    <t xml:space="preserve">800 logts </t>
-  </si>
-  <si>
     <t>Hadj amar</t>
   </si>
   <si>
-    <t>720 logts bt 13n31</t>
-  </si>
-  <si>
     <t>NB(582/2025)</t>
   </si>
   <si>
     <t>Café medjber aek</t>
   </si>
   <si>
-    <t>cité 40 logts bt 31 n4</t>
-  </si>
-  <si>
     <t>NB(005/2026)</t>
   </si>
   <si>
     <t>Bendali brahim</t>
   </si>
   <si>
-    <t>720 logts bt 19 n9</t>
-  </si>
-  <si>
     <t>NB(420/2025)</t>
   </si>
   <si>
     <t>Tebouzi lyes</t>
   </si>
   <si>
-    <t>720 logts bt 12 n14</t>
-  </si>
-  <si>
     <t>NB(597/2025)</t>
   </si>
   <si>
     <t>Benchaabane soufiane</t>
   </si>
   <si>
-    <t>720 logts bt 7 n12</t>
-  </si>
-  <si>
     <t>Benkahla ahmed</t>
   </si>
   <si>
-    <t>720 logts bt 3 n32</t>
-  </si>
-  <si>
     <t>NB(176/2025)</t>
   </si>
   <si>
     <t>NB(177/2026)</t>
-  </si>
-  <si>
-    <t>720 logts bt 2 n31</t>
   </si>
   <si>
     <t>Bourial omar</t>
@@ -2575,9 +2550,6 @@
     <t>Yekhlef dalila</t>
   </si>
   <si>
-    <t>720 logts bt 14 n33</t>
-  </si>
-  <si>
     <t>B21388</t>
   </si>
   <si>
@@ -2612,6 +2584,228 @@
   </si>
   <si>
     <t>100 Locaux Commercial oued guelet</t>
+  </si>
+  <si>
+    <t>NB(219/2026)</t>
+  </si>
+  <si>
+    <t>Benaissa ali</t>
+  </si>
+  <si>
+    <t>djennane Tebbal n384</t>
+  </si>
+  <si>
+    <t>BB</t>
+  </si>
+  <si>
+    <t>NB(071/2025)</t>
+  </si>
+  <si>
+    <t>marché batimetal b/ghia</t>
+  </si>
+  <si>
+    <t>Apc b/ghia marché 1er nov</t>
+  </si>
+  <si>
+    <t>Lakhal med</t>
+  </si>
+  <si>
+    <t>cité mohamedi n51</t>
+  </si>
+  <si>
+    <t>NB(206/2026)</t>
+  </si>
+  <si>
+    <t>Rais med</t>
+  </si>
+  <si>
+    <t>route el khemis</t>
+  </si>
+  <si>
+    <t>NB(238/2026)</t>
+  </si>
+  <si>
+    <t>B11438</t>
+  </si>
+  <si>
+    <t>B23204</t>
+  </si>
+  <si>
+    <t>NB(226/2026)</t>
+  </si>
+  <si>
+    <t>Deridji med</t>
+  </si>
+  <si>
+    <t>720 logts bt 14 n36</t>
+  </si>
+  <si>
+    <t>Merakchi med</t>
+  </si>
+  <si>
+    <t>720 logts bt 6 n12</t>
+  </si>
+  <si>
+    <t>NB(202/2026)</t>
+  </si>
+  <si>
+    <t>Boukhedimi hichem</t>
+  </si>
+  <si>
+    <t>720 logts bt 18 n18</t>
+  </si>
+  <si>
+    <t>NB(174/2026)</t>
+  </si>
+  <si>
+    <t>NB(161/2026)</t>
+  </si>
+  <si>
+    <t>Hadjersi rachid</t>
+  </si>
+  <si>
+    <t>720 logts bt 12 n12</t>
+  </si>
+  <si>
+    <t>Belghouini tahar</t>
+  </si>
+  <si>
+    <t>720 logts bt 13 n18</t>
+  </si>
+  <si>
+    <t>NB(592/2025)</t>
+  </si>
+  <si>
+    <t>Sahlaoui hacene</t>
+  </si>
+  <si>
+    <t>720 logts bt 12 n11</t>
+  </si>
+  <si>
+    <t>NB(533/2025)</t>
+  </si>
+  <si>
+    <t>Tahraoui zohra</t>
+  </si>
+  <si>
+    <t>720 logts bt 5 n18</t>
+  </si>
+  <si>
+    <t>NB(151/2026)</t>
+  </si>
+  <si>
+    <t>Saadi rafiq</t>
+  </si>
+  <si>
+    <t>720 logts bt 01 n09</t>
+  </si>
+  <si>
+    <t>NB(191/2026)</t>
+  </si>
+  <si>
+    <t>Djebnoun nabil</t>
+  </si>
+  <si>
+    <t>720 logts bt 10 n29</t>
+  </si>
+  <si>
+    <t>NB(185/2026)</t>
+  </si>
+  <si>
+    <t>Berber tayeb</t>
+  </si>
+  <si>
+    <t>720 logts bt 02 n4</t>
+  </si>
+  <si>
+    <t>NB(189/2026)</t>
+  </si>
+  <si>
+    <t>Hammouche hakim</t>
+  </si>
+  <si>
+    <t>720 logts bt 15 n19</t>
+  </si>
+  <si>
+    <t>NB(171/2026)</t>
+  </si>
+  <si>
+    <t>Boukhari souheyr</t>
+  </si>
+  <si>
+    <t>720 logts bt 9 n27</t>
+  </si>
+  <si>
+    <t>NB(182/2026)</t>
+  </si>
+  <si>
+    <t>Berrichi ali</t>
+  </si>
+  <si>
+    <t>720 logts bt 18 n38</t>
+  </si>
+  <si>
+    <t>NB(192/2026)</t>
+  </si>
+  <si>
+    <t>Mazou med</t>
+  </si>
+  <si>
+    <t>NB(661/2025)</t>
+  </si>
+  <si>
+    <t>Hannichi med aadl bt 19 n13</t>
+  </si>
+  <si>
+    <r>
+      <t>Mois de Juillet</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <t>NB(229/2026)</t>
+  </si>
+  <si>
+    <t>Sarl kmbs hotel</t>
+  </si>
+  <si>
+    <t>zone ind</t>
+  </si>
+  <si>
+    <t>NB(154/2026)</t>
+  </si>
+  <si>
+    <t>Tandjaoui mahfoud</t>
+  </si>
+  <si>
+    <t>Ait djamila</t>
+  </si>
+  <si>
+    <t>oued guelet</t>
+  </si>
+  <si>
+    <t>djenane tebbal n19</t>
+  </si>
+  <si>
+    <t>NB(218/2026)</t>
   </si>
 </sst>
 </file>
@@ -3306,6 +3500,111 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Connecteur droit 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{080CB462-0A87-BB36-218C-B26725D33C98}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="638175" y="6629400"/>
+          <a:ext cx="4591050" cy="2286000"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>104785</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connecteur droit 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B8DDF12-7A6F-4D05-8705-3F53E0D7D234}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="695335" y="21678900"/>
+          <a:ext cx="4648190" cy="238125"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4510,7 +4809,7 @@
         <v>28</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>93</v>
+        <v>630</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>18</v>
@@ -10076,7 +10375,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>93</v>
+        <v>810</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>18</v>
@@ -10242,7 +10541,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>18</v>
@@ -10853,7 +11152,7 @@
         <v>39</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
       <c r="C45" s="13" t="s">
         <v>18</v>
@@ -15133,7 +15432,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="C12" s="13">
         <v>100</v>
@@ -15172,13 +15471,13 @@
         <v>46148</v>
       </c>
       <c r="F13" s="16" t="s">
+        <v>729</v>
+      </c>
+      <c r="G13" s="17">
+        <v>1</v>
+      </c>
+      <c r="H13" s="18" t="s">
         <v>730</v>
-      </c>
-      <c r="G13" s="17">
-        <v>1</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>731</v>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="20"/>
@@ -15202,13 +15501,13 @@
         <v>46148</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G14" s="17">
         <v>1</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="I14" s="20"/>
       <c r="J14" s="20"/>
@@ -15260,13 +15559,13 @@
         <v>46148</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G16" s="17">
         <v>1</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="I16" s="20"/>
       <c r="J16" s="20"/>
@@ -15289,13 +15588,13 @@
         <v>46148</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="G17" s="17">
         <v>1</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="I17" s="20"/>
       <c r="J17" s="20"/>
@@ -15318,13 +15617,13 @@
         <v>46148</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G18" s="17">
         <v>1</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="I18" s="20"/>
       <c r="J18" s="20"/>
@@ -15347,13 +15646,13 @@
         <v>46148</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G19" s="17">
         <v>1</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="I19" s="20"/>
       <c r="J19" s="20"/>
@@ -15376,13 +15675,13 @@
         <v>46148</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G20" s="17">
         <v>1</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="I20" s="20"/>
       <c r="J20" s="20"/>
@@ -15405,13 +15704,13 @@
         <v>46148</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G21" s="17">
         <v>1</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="I21" s="20"/>
       <c r="J21" s="20"/>
@@ -15434,13 +15733,13 @@
         <v>46148</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G22" s="17">
         <v>1</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="I22" s="20"/>
       <c r="J22" s="20"/>
@@ -15463,13 +15762,13 @@
         <v>46148</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G23" s="17">
         <v>1</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="I23" s="20"/>
       <c r="J23" s="20"/>
@@ -15492,13 +15791,13 @@
         <v>46148</v>
       </c>
       <c r="F24" s="16" t="s">
+        <v>733</v>
+      </c>
+      <c r="G24" s="17">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>734</v>
-      </c>
-      <c r="G24" s="17">
-        <v>1</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>735</v>
       </c>
       <c r="I24" s="20"/>
       <c r="J24" s="20"/>
@@ -15521,13 +15820,13 @@
         <v>46148</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G25" s="17">
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="I25" s="20"/>
       <c r="J25" s="20"/>
@@ -15550,13 +15849,13 @@
         <v>46148</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G26" s="17">
         <v>1</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="I26" s="20"/>
       <c r="J26" s="20"/>
@@ -15579,16 +15878,20 @@
         <v>46148</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>729</v>
+        <v>851</v>
       </c>
       <c r="G27" s="17">
         <v>1</v>
       </c>
       <c r="H27" s="18" t="s">
+        <v>850</v>
+      </c>
+      <c r="I27" s="18" t="s">
+        <v>852</v>
+      </c>
+      <c r="J27" s="16" t="s">
         <v>728</v>
       </c>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
@@ -15596,7 +15899,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>284</v>
@@ -15634,16 +15937,13 @@
         <v>46155</v>
       </c>
       <c r="F29" s="16" t="s">
+        <v>755</v>
+      </c>
+      <c r="G29" s="17">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4" t="s">
         <v>756</v>
-      </c>
-      <c r="G29" s="17">
-        <v>1</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>757</v>
-      </c>
-      <c r="I29" t="s">
-        <v>758</v>
       </c>
       <c r="J29" s="20"/>
     </row>
@@ -15665,16 +15965,13 @@
         <v>46155</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="G30" s="17">
         <v>1</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>759</v>
-      </c>
-      <c r="I30" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="J30" s="4"/>
     </row>
@@ -15696,16 +15993,13 @@
         <v>46155</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="G31" s="17">
         <v>1</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>765</v>
-      </c>
-      <c r="I31" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="J31" s="4"/>
     </row>
@@ -15727,17 +16021,15 @@
         <v>46155</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="G32" s="17">
         <v>1</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>762</v>
-      </c>
-      <c r="I32" s="20" t="s">
-        <v>763</v>
-      </c>
+        <v>759</v>
+      </c>
+      <c r="I32" s="20"/>
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15758,16 +16050,13 @@
         <v>46155</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="G33" s="17">
         <v>1</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>768</v>
-      </c>
-      <c r="I33" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="J33" s="4"/>
     </row>
@@ -15789,16 +16078,13 @@
         <v>46155</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="G34" s="17">
         <v>1</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>771</v>
-      </c>
-      <c r="I34" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -15820,16 +16106,13 @@
         <v>46155</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
       <c r="G35" s="17">
         <v>1</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>778</v>
-      </c>
-      <c r="I35" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="J35" s="4"/>
     </row>
@@ -15851,16 +16134,13 @@
         <v>46155</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="G36" s="17">
         <v>1</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>773</v>
-      </c>
-      <c r="I36" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="J36" s="4"/>
     </row>
@@ -15897,7 +16177,7 @@
         <v>32</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="C38" s="13" t="s">
         <v>18</v>
@@ -15924,7 +16204,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
       <c r="C39" s="13">
         <v>30</v>
@@ -15949,7 +16229,7 @@
         <v>34</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="C40" s="13">
         <v>30</v>
@@ -15987,16 +16267,13 @@
         <v>46168</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
       <c r="G41" s="17">
         <v>1</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>792</v>
-      </c>
-      <c r="I41" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -17226,7 +17503,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -17248,7 +17525,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -17273,7 +17550,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="23"/>
@@ -17288,7 +17565,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -17325,7 +17602,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>786</v>
+        <v>777</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>18</v>
@@ -17353,7 +17630,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>18</v>
@@ -17381,7 +17658,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>787</v>
+        <v>778</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>18</v>
@@ -17409,7 +17686,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>284</v>
@@ -17436,7 +17713,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>284</v>
@@ -17464,13 +17741,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>284</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="E12" s="15">
         <v>46182</v>
@@ -17491,13 +17768,13 @@
         <v>7</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>284</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="E13" s="15">
         <v>46182</v>
@@ -17519,13 +17796,13 @@
         <v>8</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>284</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="E14" s="15">
         <v>46182</v>
@@ -17559,16 +17836,16 @@
         <v>46183</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="G15" s="17">
         <v>1</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="I15" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
       <c r="J15" s="20"/>
     </row>
@@ -17590,16 +17867,16 @@
         <v>46186</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="G16" s="17">
         <v>1</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="J16" s="20"/>
     </row>
@@ -17608,16 +17885,30 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="16"/>
+      <c r="B17" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D17" s="13">
+        <v>2024004655</v>
+      </c>
+      <c r="E17" s="15">
+        <v>46190</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>796</v>
+      </c>
       <c r="G17" s="17">
         <v>1</v>
       </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="20"/>
+      <c r="H17" s="18" t="s">
+        <v>797</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>798</v>
+      </c>
       <c r="J17" s="20"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17625,16 +17916,30 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="16"/>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D18" s="13">
+        <v>2024004542</v>
+      </c>
+      <c r="E18" s="15">
+        <v>46197</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>808</v>
+      </c>
       <c r="G18" s="17">
         <v>1</v>
       </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="20"/>
+      <c r="H18" s="18" t="s">
+        <v>806</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>807</v>
+      </c>
       <c r="J18" s="20"/>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17642,16 +17947,30 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
+      <c r="B19" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D19" s="13">
+        <v>2024004651</v>
+      </c>
+      <c r="E19" s="15">
+        <v>46197</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>805</v>
+      </c>
       <c r="G19" s="17">
         <v>1</v>
       </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="20"/>
+      <c r="H19" s="18" t="s">
+        <v>803</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>804</v>
+      </c>
       <c r="J19" s="20"/>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17659,16 +17978,30 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="16"/>
+      <c r="B20" s="13" t="s">
+        <v>799</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D20" s="13">
+        <v>2024004657</v>
+      </c>
+      <c r="E20" s="15">
+        <v>46197</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>800</v>
+      </c>
       <c r="G20" s="17">
         <v>1</v>
       </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="20"/>
+      <c r="H20" s="18" t="s">
+        <v>802</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>801</v>
+      </c>
       <c r="J20" s="20"/>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17676,11 +18009,21 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="16"/>
+      <c r="B21" s="13" t="s">
+        <v>809</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D21" s="13">
+        <v>2024004660</v>
+      </c>
+      <c r="E21" s="15">
+        <v>46200</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G21" s="17">
         <v>1</v>
       </c>
@@ -17693,16 +18036,30 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="16"/>
+      <c r="B22" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="13">
+        <v>2025003991</v>
+      </c>
+      <c r="E22" s="15">
+        <v>46202</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>811</v>
+      </c>
       <c r="G22" s="17">
         <v>1</v>
       </c>
-      <c r="H22" s="18"/>
-      <c r="I22" s="20"/>
+      <c r="H22" s="18" t="s">
+        <v>812</v>
+      </c>
+      <c r="I22" t="s">
+        <v>813</v>
+      </c>
       <c r="J22" s="20"/>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17710,16 +18067,30 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="16"/>
+      <c r="B23" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="13">
+        <v>2025003992</v>
+      </c>
+      <c r="E23" s="15">
+        <v>46202</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>816</v>
+      </c>
       <c r="G23" s="17">
         <v>1</v>
       </c>
-      <c r="H23" s="18"/>
-      <c r="I23" s="20"/>
+      <c r="H23" s="18" t="s">
+        <v>814</v>
+      </c>
+      <c r="I23" t="s">
+        <v>815</v>
+      </c>
       <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17727,16 +18098,30 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="16"/>
+      <c r="B24" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="13">
+        <v>2025003993</v>
+      </c>
+      <c r="E24" s="15">
+        <v>46202</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>819</v>
+      </c>
       <c r="G24" s="17">
         <v>1</v>
       </c>
-      <c r="H24" s="4"/>
-      <c r="I24" s="20"/>
+      <c r="H24" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="I24" t="s">
+        <v>818</v>
+      </c>
       <c r="J24" s="20"/>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17744,16 +18129,30 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="16"/>
+      <c r="B25" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="13">
+        <v>2025117465</v>
+      </c>
+      <c r="E25" s="15">
+        <v>46202</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>820</v>
+      </c>
       <c r="G25" s="17">
         <v>1</v>
       </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="20"/>
+      <c r="H25" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="I25" t="s">
+        <v>822</v>
+      </c>
       <c r="J25" s="20"/>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17761,16 +18160,30 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="16"/>
+      <c r="B26" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="13">
+        <v>2025117466</v>
+      </c>
+      <c r="E26" s="15">
+        <v>46202</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>837</v>
+      </c>
       <c r="G26" s="17">
         <v>1</v>
       </c>
-      <c r="H26" s="18"/>
-      <c r="I26" s="20"/>
+      <c r="H26" s="18" t="s">
+        <v>835</v>
+      </c>
+      <c r="I26" t="s">
+        <v>836</v>
+      </c>
       <c r="J26" s="20"/>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17778,16 +18191,30 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="16"/>
+      <c r="B27" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="13">
+        <v>2025117467</v>
+      </c>
+      <c r="E27" s="15">
+        <v>46202</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>840</v>
+      </c>
       <c r="G27" s="17">
         <v>1</v>
       </c>
-      <c r="H27" s="18"/>
-      <c r="I27" s="20"/>
+      <c r="H27" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="I27" t="s">
+        <v>839</v>
+      </c>
       <c r="J27" s="20"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17795,15 +18222,30 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="16"/>
+      <c r="B28" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="13">
+        <v>2025117468</v>
+      </c>
+      <c r="E28" s="15">
+        <v>46202</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>843</v>
+      </c>
       <c r="G28" s="17">
         <v>1</v>
       </c>
-      <c r="H28" s="4"/>
+      <c r="H28" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="I28" t="s">
+        <v>842</v>
+      </c>
       <c r="J28" s="20"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17811,15 +18253,30 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="16"/>
+      <c r="B29" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="13">
+        <v>2025117469</v>
+      </c>
+      <c r="E29" s="15">
+        <v>46202</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>846</v>
+      </c>
       <c r="G29" s="17">
         <v>1</v>
       </c>
-      <c r="H29" s="4"/>
+      <c r="H29" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="I29" t="s">
+        <v>845</v>
+      </c>
       <c r="J29" s="20"/>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17827,15 +18284,30 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="16"/>
+      <c r="B30" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="13">
+        <v>2025117470</v>
+      </c>
+      <c r="E30" s="15">
+        <v>46202</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>849</v>
+      </c>
       <c r="G30" s="17">
         <v>1</v>
       </c>
-      <c r="H30" s="18"/>
+      <c r="H30" s="18" t="s">
+        <v>847</v>
+      </c>
+      <c r="I30" t="s">
+        <v>848</v>
+      </c>
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17843,15 +18315,30 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="16"/>
+      <c r="B31" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="13">
+        <v>2025117731</v>
+      </c>
+      <c r="E31" s="15">
+        <v>46202</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>825</v>
+      </c>
       <c r="G31" s="17">
         <v>1</v>
       </c>
-      <c r="H31" s="4"/>
+      <c r="H31" s="18" t="s">
+        <v>823</v>
+      </c>
+      <c r="I31" t="s">
+        <v>824</v>
+      </c>
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17859,16 +18346,30 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="16"/>
+      <c r="B32" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="13">
+        <v>2025117736</v>
+      </c>
+      <c r="E32" s="15">
+        <v>46202</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>828</v>
+      </c>
       <c r="G32" s="17">
         <v>1</v>
       </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="20"/>
+      <c r="H32" s="18" t="s">
+        <v>826</v>
+      </c>
+      <c r="I32" t="s">
+        <v>827</v>
+      </c>
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17876,15 +18377,30 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="16"/>
+      <c r="B33" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="13">
+        <v>2025117737</v>
+      </c>
+      <c r="E33" s="15">
+        <v>46202</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>831</v>
+      </c>
       <c r="G33" s="17">
         <v>1</v>
       </c>
-      <c r="H33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="I33" t="s">
+        <v>830</v>
+      </c>
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17892,15 +18408,30 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="16"/>
+      <c r="B34" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="13">
+        <v>2025117738</v>
+      </c>
+      <c r="E34" s="15">
+        <v>46202</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>834</v>
+      </c>
       <c r="G34" s="17">
         <v>1</v>
       </c>
-      <c r="H34" s="18"/>
+      <c r="H34" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="I34" t="s">
+        <v>833</v>
+      </c>
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19168,9 +19699,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:F14">
-    <sortCondition ref="E7:E14"/>
-    <sortCondition ref="D7:D14"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I34">
+    <sortCondition ref="E7:E34"/>
+    <sortCondition ref="D7:D34"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>
@@ -19190,4 +19721,1943 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7630F48-0C14-4FCD-9A74-D757E8B486BD}">
+  <dimension ref="A1:K117"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="2.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+    <col min="9" max="9" width="32.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="25"/>
+      <c r="K2" s="6">
+        <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="25"/>
+      <c r="K3" s="6">
+        <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="25"/>
+      <c r="K4" s="6">
+        <f>SUMIF(F7:F364,"Ve*",G7:G364)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>853</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="8">
+        <f>SUM(K2:K4)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>1</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>718</v>
+      </c>
+      <c r="C7" s="13">
+        <v>30</v>
+      </c>
+      <c r="D7" s="13">
+        <v>18041008043</v>
+      </c>
+      <c r="E7" s="15">
+        <v>46211</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>854</v>
+      </c>
+      <c r="G7" s="17">
+        <v>1</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>855</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>856</v>
+      </c>
+      <c r="J7" s="19"/>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <f t="shared" ref="A8:A71" si="0">+A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D8" s="13">
+        <v>2024004656</v>
+      </c>
+      <c r="E8" s="15">
+        <v>46211</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>857</v>
+      </c>
+      <c r="G8" s="17">
+        <v>1</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>858</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>861</v>
+      </c>
+      <c r="J8" s="20"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D9" s="13">
+        <v>2026003602</v>
+      </c>
+      <c r="E9" s="15">
+        <v>46211</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>862</v>
+      </c>
+      <c r="G9" s="17">
+        <v>1</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>859</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>860</v>
+      </c>
+      <c r="J9" s="20"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="17">
+        <v>1</v>
+      </c>
+      <c r="H10" s="18"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="17">
+        <v>1</v>
+      </c>
+      <c r="H11" s="18"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="17">
+        <v>1</v>
+      </c>
+      <c r="H12" s="18"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17">
+        <v>1</v>
+      </c>
+      <c r="H13" s="18"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="17">
+        <v>1</v>
+      </c>
+      <c r="H14" s="18"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17">
+        <v>1</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="J15" s="20"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="17">
+        <v>1</v>
+      </c>
+      <c r="H16" s="18"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17">
+        <v>1</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="17">
+        <v>1</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="17">
+        <v>1</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="17">
+        <v>1</v>
+      </c>
+      <c r="H20" s="18"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="17">
+        <v>1</v>
+      </c>
+      <c r="H21" s="18"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17">
+        <v>1</v>
+      </c>
+      <c r="H22" s="18"/>
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="17">
+        <v>1</v>
+      </c>
+      <c r="H23" s="18"/>
+      <c r="J23" s="20"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="17">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4"/>
+      <c r="J24" s="20"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="J25" s="20"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="17">
+        <v>1</v>
+      </c>
+      <c r="H26" s="18"/>
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17">
+        <v>1</v>
+      </c>
+      <c r="H27" s="4"/>
+      <c r="J27" s="20"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4"/>
+      <c r="J28" s="20"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="12">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4"/>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17">
+        <v>1</v>
+      </c>
+      <c r="H30" s="18"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="17">
+        <v>1</v>
+      </c>
+      <c r="H31" s="18"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="17">
+        <v>1</v>
+      </c>
+      <c r="H32" s="18"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="12">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="17">
+        <v>1</v>
+      </c>
+      <c r="H33" s="4"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="12">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="17">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="12">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="17">
+        <v>1</v>
+      </c>
+      <c r="H35" s="18"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="12">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="17">
+        <v>1</v>
+      </c>
+      <c r="H36" s="18"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="12">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="15"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="17">
+        <v>1</v>
+      </c>
+      <c r="H37" s="18"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="12">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="15"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="17">
+        <v>1</v>
+      </c>
+      <c r="H38" s="4"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="12">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B39" s="15"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="17">
+        <v>1</v>
+      </c>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="12">
+        <f>+A39+1</f>
+        <v>34</v>
+      </c>
+      <c r="B40" s="15"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="17">
+        <v>1</v>
+      </c>
+      <c r="H40" s="18"/>
+      <c r="I40" s="20"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="12">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="15"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="17">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="20"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="12">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="17">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4"/>
+      <c r="I42" s="20"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="12">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="17">
+        <v>1</v>
+      </c>
+      <c r="H43" s="18"/>
+      <c r="I43" s="20"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="12">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="17">
+        <v>1</v>
+      </c>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="12">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="17">
+        <v>1</v>
+      </c>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="12">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="15"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="17">
+        <v>1</v>
+      </c>
+      <c r="H46" s="4"/>
+      <c r="I46" s="20"/>
+    </row>
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="12">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B47" s="15"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="17">
+        <v>1</v>
+      </c>
+      <c r="H47" s="4"/>
+      <c r="I47" s="20"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="12">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B48" s="15"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="17">
+        <v>1</v>
+      </c>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="12">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B49" s="15"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="17">
+        <v>1</v>
+      </c>
+      <c r="H49" s="4"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="12">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B50" s="15"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="17">
+        <v>1</v>
+      </c>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="12">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B51" s="15"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="17">
+        <v>1</v>
+      </c>
+      <c r="H51" s="4"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="12">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B52" s="15"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="17">
+        <v>1</v>
+      </c>
+      <c r="H52" s="4"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="12">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B53" s="15"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="17">
+        <v>1</v>
+      </c>
+      <c r="H53" s="4"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="12">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B54" s="15"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="17">
+        <v>1</v>
+      </c>
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="12">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B55" s="15"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="17">
+        <v>1</v>
+      </c>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="12">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B56" s="15"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="17">
+        <v>1</v>
+      </c>
+      <c r="H56" s="4"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="12">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="17">
+        <v>1</v>
+      </c>
+      <c r="H57" s="4"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="12">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B58" s="15"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="17">
+        <v>1</v>
+      </c>
+      <c r="H58" s="4"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="12">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B59" s="15"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="17">
+        <v>1</v>
+      </c>
+      <c r="H59" s="4"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="12">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B60" s="15"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="17">
+        <v>1</v>
+      </c>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="12">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B61" s="15"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="17">
+        <v>1</v>
+      </c>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="12">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B62" s="15"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="17">
+        <v>1</v>
+      </c>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="12">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B63" s="15"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="17">
+        <v>1</v>
+      </c>
+      <c r="H63" s="4"/>
+      <c r="I63" s="20"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="12">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B64" s="15"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="15"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="17">
+        <v>1</v>
+      </c>
+      <c r="H64" s="4"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="12">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B65" s="15"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="17">
+        <v>1</v>
+      </c>
+      <c r="H65" s="4"/>
+      <c r="I65" s="20"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="12">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="17">
+        <v>1</v>
+      </c>
+      <c r="H66" s="4"/>
+      <c r="I66" s="20"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="12">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B67" s="15"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="15"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="17">
+        <v>1</v>
+      </c>
+      <c r="H67" s="4"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="12">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B68" s="15"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="17">
+        <v>1</v>
+      </c>
+      <c r="H68" s="4"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="12">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B69" s="15"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="17">
+        <v>1</v>
+      </c>
+      <c r="H69" s="4"/>
+      <c r="I69" s="20"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="12">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B70" s="15"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="17">
+        <v>1</v>
+      </c>
+      <c r="H70" s="4"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="12">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B71" s="15"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="17">
+        <v>1</v>
+      </c>
+      <c r="H71" s="4"/>
+      <c r="I71" s="20"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="12">
+        <f t="shared" ref="A72:A117" si="1">+A71+1</f>
+        <v>66</v>
+      </c>
+      <c r="B72" s="15"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="17">
+        <v>1</v>
+      </c>
+      <c r="H72" s="4"/>
+      <c r="I72" s="20"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="12">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="B73" s="15"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="17">
+        <v>1</v>
+      </c>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="12">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="B74" s="15"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="17">
+        <v>1</v>
+      </c>
+      <c r="H74" s="4"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="12">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B75" s="15"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="17">
+        <v>1</v>
+      </c>
+      <c r="H75" s="4"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="12">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="B76" s="15"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="17">
+        <v>1</v>
+      </c>
+      <c r="H76" s="4"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="12">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="B77" s="15"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="17">
+        <v>1</v>
+      </c>
+      <c r="H77" s="4"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="12">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="B78" s="15"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="17">
+        <v>1</v>
+      </c>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="12">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="B79" s="15"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="17">
+        <v>1</v>
+      </c>
+      <c r="H79" s="4"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="12">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="B80" s="15"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="17">
+        <v>1</v>
+      </c>
+      <c r="H80" s="4"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="12">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="B81" s="15"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="17">
+        <v>1</v>
+      </c>
+      <c r="H81" s="4"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="12">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="B82" s="15"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="17">
+        <v>1</v>
+      </c>
+      <c r="H82" s="4"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="12">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="B83" s="15"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="17">
+        <v>1</v>
+      </c>
+      <c r="H83" s="4"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="12">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="B84" s="15"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="15"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="17">
+        <v>1</v>
+      </c>
+      <c r="H84" s="4"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="12">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="B85" s="15"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="16"/>
+      <c r="G85" s="17">
+        <v>1</v>
+      </c>
+      <c r="H85" s="4"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="12">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="B86" s="15"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="16"/>
+      <c r="G86" s="17">
+        <v>1</v>
+      </c>
+      <c r="H86" s="4"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="12">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="B87" s="15"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="17">
+        <v>1</v>
+      </c>
+      <c r="H87" s="4"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="12">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="B88" s="15"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="17">
+        <v>1</v>
+      </c>
+      <c r="H88" s="4"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="12">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="B89" s="15"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="17">
+        <v>1</v>
+      </c>
+      <c r="H89" s="4"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="12">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="B90" s="15"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="16"/>
+      <c r="G90" s="17">
+        <v>1</v>
+      </c>
+      <c r="H90" s="4"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="12">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="B91" s="15"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="17">
+        <v>1</v>
+      </c>
+      <c r="H91" s="4"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="12">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="B92" s="15"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="17">
+        <v>1</v>
+      </c>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="12">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="B93" s="15"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="17">
+        <v>1</v>
+      </c>
+      <c r="H93" s="4"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="12">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="B94" s="15"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="15"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="17">
+        <v>1</v>
+      </c>
+      <c r="H94" s="4"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="12">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="B95" s="15"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="15"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="17">
+        <v>1</v>
+      </c>
+      <c r="H95" s="4"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="12">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="B96" s="15"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="16"/>
+      <c r="G96" s="17">
+        <v>1</v>
+      </c>
+      <c r="H96" s="4"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="12">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="B97" s="15"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="16"/>
+      <c r="G97" s="17">
+        <v>1</v>
+      </c>
+      <c r="H97" s="4"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="12">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="B98" s="15"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="16"/>
+      <c r="G98" s="17">
+        <v>1</v>
+      </c>
+      <c r="H98" s="4"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="12">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="B99" s="15"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="15"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="17">
+        <v>1</v>
+      </c>
+      <c r="H99" s="4"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="12">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="B100" s="15"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="15"/>
+      <c r="F100" s="16"/>
+      <c r="G100" s="17">
+        <v>1</v>
+      </c>
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="12">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="B101" s="15"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="16"/>
+      <c r="G101" s="17">
+        <v>1</v>
+      </c>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="12">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="B102" s="15"/>
+      <c r="C102" s="13"/>
+      <c r="D102" s="14"/>
+      <c r="E102" s="15"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="17">
+        <v>1</v>
+      </c>
+      <c r="H102" s="4"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="12">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="B103" s="15"/>
+      <c r="C103" s="13"/>
+      <c r="D103" s="14"/>
+      <c r="E103" s="15"/>
+      <c r="F103" s="16"/>
+      <c r="G103" s="17">
+        <v>1</v>
+      </c>
+      <c r="H103" s="4"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="12">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="B104" s="15"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="22"/>
+      <c r="E104" s="15"/>
+      <c r="F104" s="16"/>
+      <c r="G104" s="17">
+        <v>1</v>
+      </c>
+      <c r="H104" s="4"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="12">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="B105" s="15"/>
+      <c r="C105" s="13"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="15"/>
+      <c r="F105" s="16"/>
+      <c r="G105" s="17">
+        <v>1</v>
+      </c>
+      <c r="H105" s="4"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="12">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="B106" s="15"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="15"/>
+      <c r="F106" s="16"/>
+      <c r="G106" s="17">
+        <v>1</v>
+      </c>
+      <c r="H106" s="4"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="12">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="B107" s="15"/>
+      <c r="C107" s="13"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="15"/>
+      <c r="F107" s="16"/>
+      <c r="G107" s="17">
+        <v>1</v>
+      </c>
+      <c r="H107" s="4"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="12">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="B108" s="15"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="14"/>
+      <c r="E108" s="15"/>
+      <c r="F108" s="16"/>
+      <c r="G108" s="17">
+        <v>1</v>
+      </c>
+      <c r="H108" s="4"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="12">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="B109" s="15"/>
+      <c r="C109" s="13"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="15"/>
+      <c r="F109" s="16"/>
+      <c r="G109" s="17">
+        <v>1</v>
+      </c>
+      <c r="H109" s="4"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="12">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="B110" s="15"/>
+      <c r="C110" s="13"/>
+      <c r="D110" s="14"/>
+      <c r="E110" s="15"/>
+      <c r="F110" s="16"/>
+      <c r="G110" s="17">
+        <v>1</v>
+      </c>
+      <c r="H110" s="4"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="12">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="B111" s="15"/>
+      <c r="C111" s="13"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="15"/>
+      <c r="F111" s="16"/>
+      <c r="G111" s="17">
+        <v>1</v>
+      </c>
+      <c r="H111" s="4"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="12">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="B112" s="15"/>
+      <c r="C112" s="13"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="15"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="17">
+        <v>1</v>
+      </c>
+      <c r="H112" s="4"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="12">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="B113" s="15"/>
+      <c r="C113" s="13"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="15"/>
+      <c r="F113" s="16"/>
+      <c r="G113" s="17">
+        <v>1</v>
+      </c>
+      <c r="H113" s="4"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="12">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="B114" s="15"/>
+      <c r="C114" s="13"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="15"/>
+      <c r="F114" s="16"/>
+      <c r="G114" s="17">
+        <v>1</v>
+      </c>
+      <c r="H114" s="4"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="12">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="B115" s="15"/>
+      <c r="C115" s="13"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="15"/>
+      <c r="F115" s="16"/>
+      <c r="G115" s="17">
+        <v>1</v>
+      </c>
+      <c r="H115" s="4"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="12">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="B116" s="15"/>
+      <c r="C116" s="13"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="15"/>
+      <c r="F116" s="16"/>
+      <c r="G116" s="17">
+        <v>1</v>
+      </c>
+      <c r="H116" s="4"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="12">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="B117" s="15"/>
+      <c r="C117" s="13"/>
+      <c r="D117" s="14"/>
+      <c r="E117" s="15"/>
+      <c r="F117" s="16"/>
+      <c r="G117" s="17">
+        <v>1</v>
+      </c>
+      <c r="H117" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="I4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283472" right="0.45" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AAEC350-7869-492D-ACC7-9BCE55EE6E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24035501-CE8F-4BD1-B38D-585504BB7CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Janvier 2026 " sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="886">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -2571,9 +2571,6 @@
     <t>Bouraki fodhil</t>
   </si>
   <si>
-    <t>720 logts bt 6 n7</t>
-  </si>
-  <si>
     <t>NB</t>
   </si>
   <si>
@@ -2583,45 +2580,30 @@
     <t>Slimani samir</t>
   </si>
   <si>
-    <t>100 Locaux Commercial oued guelet</t>
-  </si>
-  <si>
     <t>NB(219/2026)</t>
   </si>
   <si>
     <t>Benaissa ali</t>
   </si>
   <si>
-    <t>djennane Tebbal n384</t>
-  </si>
-  <si>
     <t>BB</t>
   </si>
   <si>
     <t>NB(071/2025)</t>
   </si>
   <si>
-    <t>marché batimetal b/ghia</t>
-  </si>
-  <si>
     <t>Apc b/ghia marché 1er nov</t>
   </si>
   <si>
     <t>Lakhal med</t>
   </si>
   <si>
-    <t>cité mohamedi n51</t>
-  </si>
-  <si>
     <t>NB(206/2026)</t>
   </si>
   <si>
     <t>Rais med</t>
   </si>
   <si>
-    <t>route el khemis</t>
-  </si>
-  <si>
     <t>NB(238/2026)</t>
   </si>
   <si>
@@ -2637,24 +2619,15 @@
     <t>Deridji med</t>
   </si>
   <si>
-    <t>720 logts bt 14 n36</t>
-  </si>
-  <si>
     <t>Merakchi med</t>
   </si>
   <si>
-    <t>720 logts bt 6 n12</t>
-  </si>
-  <si>
     <t>NB(202/2026)</t>
   </si>
   <si>
     <t>Boukhedimi hichem</t>
   </si>
   <si>
-    <t>720 logts bt 18 n18</t>
-  </si>
-  <si>
     <t>NB(174/2026)</t>
   </si>
   <si>
@@ -2664,85 +2637,52 @@
     <t>Hadjersi rachid</t>
   </si>
   <si>
-    <t>720 logts bt 12 n12</t>
-  </si>
-  <si>
     <t>Belghouini tahar</t>
   </si>
   <si>
-    <t>720 logts bt 13 n18</t>
-  </si>
-  <si>
     <t>NB(592/2025)</t>
   </si>
   <si>
     <t>Sahlaoui hacene</t>
   </si>
   <si>
-    <t>720 logts bt 12 n11</t>
-  </si>
-  <si>
     <t>NB(533/2025)</t>
   </si>
   <si>
     <t>Tahraoui zohra</t>
   </si>
   <si>
-    <t>720 logts bt 5 n18</t>
-  </si>
-  <si>
     <t>NB(151/2026)</t>
   </si>
   <si>
     <t>Saadi rafiq</t>
   </si>
   <si>
-    <t>720 logts bt 01 n09</t>
-  </si>
-  <si>
     <t>NB(191/2026)</t>
   </si>
   <si>
-    <t>Djebnoun nabil</t>
-  </si>
-  <si>
-    <t>720 logts bt 10 n29</t>
-  </si>
-  <si>
     <t>NB(185/2026)</t>
   </si>
   <si>
     <t>Berber tayeb</t>
   </si>
   <si>
-    <t>720 logts bt 02 n4</t>
-  </si>
-  <si>
     <t>NB(189/2026)</t>
   </si>
   <si>
     <t>Hammouche hakim</t>
   </si>
   <si>
-    <t>720 logts bt 15 n19</t>
-  </si>
-  <si>
     <t>NB(171/2026)</t>
   </si>
   <si>
     <t>Boukhari souheyr</t>
   </si>
   <si>
-    <t>720 logts bt 9 n27</t>
-  </si>
-  <si>
     <t>NB(182/2026)</t>
   </si>
   <si>
     <t>Berrichi ali</t>
-  </si>
-  <si>
-    <t>720 logts bt 18 n38</t>
   </si>
   <si>
     <t>NB(192/2026)</t>
@@ -2787,9 +2727,6 @@
     <t>Sarl kmbs hotel</t>
   </si>
   <si>
-    <t>zone ind</t>
-  </si>
-  <si>
     <t>NB(154/2026)</t>
   </si>
   <si>
@@ -2799,13 +2736,145 @@
     <t>Ait djamila</t>
   </si>
   <si>
-    <t>oued guelet</t>
-  </si>
-  <si>
-    <t>djenane tebbal n19</t>
-  </si>
-  <si>
     <t>NB(218/2026)</t>
+  </si>
+  <si>
+    <t>Djebloun nabil</t>
+  </si>
+  <si>
+    <t>NB(216/2026)</t>
+  </si>
+  <si>
+    <t>Belkhelfa kheira</t>
+  </si>
+  <si>
+    <t>NB(016/2026)</t>
+  </si>
+  <si>
+    <t>Lamri med</t>
+  </si>
+  <si>
+    <t>NB(714/2025)</t>
+  </si>
+  <si>
+    <t>Lamri kamel</t>
+  </si>
+  <si>
+    <t>Abdellah a/rezzak</t>
+  </si>
+  <si>
+    <t>NB(128/2026)</t>
+  </si>
+  <si>
+    <t>2026003609</t>
+  </si>
+  <si>
+    <t>NB(702/2025)</t>
+  </si>
+  <si>
+    <t>Labidi fatima</t>
+  </si>
+  <si>
+    <t>2026003608</t>
+  </si>
+  <si>
+    <t>Meghsel amal</t>
+  </si>
+  <si>
+    <t>NB(253/2026)</t>
+  </si>
+  <si>
+    <t>2024004687</t>
+  </si>
+  <si>
+    <t>Ould kouider</t>
+  </si>
+  <si>
+    <t>NB(234/2026)</t>
+  </si>
+  <si>
+    <t>2026003607</t>
+  </si>
+  <si>
+    <t>Lamri mahmoud</t>
+  </si>
+  <si>
+    <t>NB(265/2026)</t>
+  </si>
+  <si>
+    <t>2026003610</t>
+  </si>
+  <si>
+    <t>NB(225/2026)</t>
+  </si>
+  <si>
+    <t>Besdsam ali</t>
+  </si>
+  <si>
+    <t>NB(267/2026)</t>
+  </si>
+  <si>
+    <t>Boudjebbour med</t>
+  </si>
+  <si>
+    <t>Messaoudi el mahdi</t>
+  </si>
+  <si>
+    <t>NB(300/2026)</t>
+  </si>
+  <si>
+    <t>Benahmadi a/rezak</t>
+  </si>
+  <si>
+    <t>NB(277/2026)</t>
+  </si>
+  <si>
+    <t>Hantabli med</t>
+  </si>
+  <si>
+    <t>NB(581/2025)</t>
+  </si>
+  <si>
+    <t>Boudersaoui benali</t>
+  </si>
+  <si>
+    <t>NB(232/2026)</t>
+  </si>
+  <si>
+    <t>Hatchane farouk</t>
+  </si>
+  <si>
+    <t>NB(613/2025)</t>
+  </si>
+  <si>
+    <t>Bouguessa mahfoud</t>
+  </si>
+  <si>
+    <t>NB(240/2026)</t>
+  </si>
+  <si>
+    <t>Sayah rabah</t>
+  </si>
+  <si>
+    <t>NB(306/2026)</t>
+  </si>
+  <si>
+    <t>Saidj abdelmonaim</t>
+  </si>
+  <si>
+    <t>NB(280/2026)</t>
+  </si>
+  <si>
+    <t>Laref benaissa</t>
+  </si>
+  <si>
+    <t>NB(139/2026)</t>
+  </si>
+  <si>
+    <t>Boucherit omar</t>
+  </si>
+  <si>
+    <t>NB(213/2026)</t>
   </si>
 </sst>
 </file>
@@ -10375,7 +10444,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>18</v>
@@ -15878,16 +15947,16 @@
         <v>46148</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>851</v>
+        <v>831</v>
       </c>
       <c r="G27" s="17">
         <v>1</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>850</v>
+        <v>830</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>852</v>
+        <v>832</v>
       </c>
       <c r="J27" s="16" t="s">
         <v>728</v>
@@ -17836,7 +17905,7 @@
         <v>46183</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="G15" s="17">
         <v>1</v>
@@ -17844,9 +17913,6 @@
       <c r="H15" s="18" t="s">
         <v>790</v>
       </c>
-      <c r="I15" t="s">
-        <v>791</v>
-      </c>
       <c r="J15" s="20"/>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17867,17 +17933,15 @@
         <v>46186</v>
       </c>
       <c r="F16" s="16" t="s">
+        <v>792</v>
+      </c>
+      <c r="G16" s="17">
+        <v>1</v>
+      </c>
+      <c r="H16" s="18" t="s">
         <v>793</v>
       </c>
-      <c r="G16" s="17">
-        <v>1</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>794</v>
-      </c>
-      <c r="I16" s="20" t="s">
-        <v>795</v>
-      </c>
+      <c r="I16" s="20"/>
       <c r="J16" s="20"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17898,17 +17962,15 @@
         <v>46190</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="G17" s="17">
         <v>1</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>797</v>
-      </c>
-      <c r="I17" s="20" t="s">
-        <v>798</v>
-      </c>
+        <v>795</v>
+      </c>
+      <c r="I17" s="20"/>
       <c r="J17" s="20"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17929,17 +17991,15 @@
         <v>46197</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G18" s="17">
         <v>1</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>806</v>
-      </c>
-      <c r="I18" s="20" t="s">
-        <v>807</v>
-      </c>
+        <v>801</v>
+      </c>
+      <c r="I18" s="20"/>
       <c r="J18" s="20"/>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17960,17 +18020,15 @@
         <v>46197</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="G19" s="17">
         <v>1</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>803</v>
-      </c>
-      <c r="I19" s="20" t="s">
-        <v>804</v>
-      </c>
+        <v>799</v>
+      </c>
+      <c r="I19" s="20"/>
       <c r="J19" s="20"/>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17979,7 +18037,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>284</v>
@@ -17991,17 +18049,15 @@
         <v>46197</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="G20" s="17">
         <v>1</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>802</v>
-      </c>
-      <c r="I20" s="20" t="s">
-        <v>801</v>
-      </c>
+        <v>798</v>
+      </c>
+      <c r="I20" s="20"/>
       <c r="J20" s="20"/>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18010,7 +18066,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>284</v>
@@ -18049,16 +18105,13 @@
         <v>46202</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="G22" s="17">
         <v>1</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>812</v>
-      </c>
-      <c r="I22" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="J22" s="20"/>
     </row>
@@ -18080,16 +18133,13 @@
         <v>46202</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="G23" s="17">
         <v>1</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>814</v>
-      </c>
-      <c r="I23" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="J23" s="20"/>
     </row>
@@ -18111,16 +18161,13 @@
         <v>46202</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
       <c r="G24" s="17">
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>817</v>
-      </c>
-      <c r="I24" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
       <c r="J24" s="20"/>
     </row>
@@ -18142,16 +18189,13 @@
         <v>46202</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="G25" s="17">
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="I25" t="s">
-        <v>822</v>
+        <v>812</v>
       </c>
       <c r="J25" s="20"/>
     </row>
@@ -18173,16 +18217,13 @@
         <v>46202</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>837</v>
+        <v>821</v>
       </c>
       <c r="G26" s="17">
         <v>1</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>835</v>
-      </c>
-      <c r="I26" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="J26" s="20"/>
     </row>
@@ -18204,16 +18245,13 @@
         <v>46202</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>840</v>
+        <v>823</v>
       </c>
       <c r="G27" s="17">
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>838</v>
-      </c>
-      <c r="I27" t="s">
-        <v>839</v>
+        <v>822</v>
       </c>
       <c r="J27" s="20"/>
     </row>
@@ -18235,16 +18273,13 @@
         <v>46202</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>843</v>
+        <v>825</v>
       </c>
       <c r="G28" s="17">
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>841</v>
-      </c>
-      <c r="I28" t="s">
-        <v>842</v>
+        <v>824</v>
       </c>
       <c r="J28" s="20"/>
     </row>
@@ -18266,16 +18301,13 @@
         <v>46202</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>846</v>
+        <v>827</v>
       </c>
       <c r="G29" s="17">
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="I29" t="s">
-        <v>845</v>
+        <v>826</v>
       </c>
       <c r="J29" s="20"/>
     </row>
@@ -18297,16 +18329,13 @@
         <v>46202</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>849</v>
+        <v>829</v>
       </c>
       <c r="G30" s="17">
         <v>1</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>847</v>
-      </c>
-      <c r="I30" t="s">
-        <v>848</v>
+        <v>828</v>
       </c>
       <c r="J30" s="4"/>
     </row>
@@ -18328,16 +18357,13 @@
         <v>46202</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>825</v>
+        <v>814</v>
       </c>
       <c r="G31" s="17">
         <v>1</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>823</v>
-      </c>
-      <c r="I31" t="s">
-        <v>824</v>
+        <v>813</v>
       </c>
       <c r="J31" s="4"/>
     </row>
@@ -18359,16 +18385,13 @@
         <v>46202</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
       <c r="G32" s="17">
         <v>1</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>826</v>
-      </c>
-      <c r="I32" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="J32" s="4"/>
     </row>
@@ -18390,16 +18413,13 @@
         <v>46202</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
       <c r="G33" s="17">
         <v>1</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>829</v>
-      </c>
-      <c r="I33" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="J33" s="4"/>
     </row>
@@ -18421,16 +18441,13 @@
         <v>46202</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>834</v>
+        <v>820</v>
       </c>
       <c r="G34" s="17">
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>832</v>
-      </c>
-      <c r="I34" t="s">
-        <v>833</v>
+        <v>819</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -19796,7 +19813,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -19821,7 +19838,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>853</v>
+        <v>833</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="23"/>
@@ -19836,7 +19853,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -19873,29 +19890,27 @@
         <v>1</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>718</v>
-      </c>
-      <c r="C7" s="13">
-        <v>30</v>
+        <v>93</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>284</v>
       </c>
       <c r="D7" s="13">
-        <v>18041008043</v>
+        <v>2024004656</v>
       </c>
       <c r="E7" s="15">
         <v>46211</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>854</v>
+        <v>836</v>
       </c>
       <c r="G7" s="17">
         <v>1</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>855</v>
-      </c>
-      <c r="I7" s="20" t="s">
-        <v>856</v>
-      </c>
+        <v>837</v>
+      </c>
+      <c r="I7" s="20"/>
       <c r="J7" s="19"/>
       <c r="K7" s="4"/>
     </row>
@@ -19911,23 +19926,21 @@
         <v>284</v>
       </c>
       <c r="D8" s="13">
-        <v>2024004656</v>
+        <v>2026003602</v>
       </c>
       <c r="E8" s="15">
         <v>46211</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>857</v>
+        <v>839</v>
       </c>
       <c r="G8" s="17">
         <v>1</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>858</v>
-      </c>
-      <c r="I8" s="20" t="s">
-        <v>861</v>
-      </c>
+        <v>838</v>
+      </c>
+      <c r="I8" s="20"/>
       <c r="J8" s="20"/>
       <c r="K8" s="4"/>
     </row>
@@ -19937,29 +19950,27 @@
         <v>3</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>284</v>
+        <v>718</v>
+      </c>
+      <c r="C9" s="13">
+        <v>30</v>
       </c>
       <c r="D9" s="13">
-        <v>2026003602</v>
+        <v>18041008043</v>
       </c>
       <c r="E9" s="15">
         <v>46211</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>862</v>
+        <v>834</v>
       </c>
       <c r="G9" s="17">
         <v>1</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>859</v>
-      </c>
-      <c r="I9" s="20" t="s">
-        <v>860</v>
-      </c>
+        <v>835</v>
+      </c>
+      <c r="I9" s="20"/>
       <c r="J9" s="20"/>
       <c r="K9" s="4"/>
     </row>
@@ -19968,15 +19979,28 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="16"/>
+      <c r="B10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D10" s="13">
+        <v>2026003601</v>
+      </c>
+      <c r="E10" s="15">
+        <v>46218</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>845</v>
+      </c>
       <c r="G10" s="17">
         <v>1</v>
       </c>
-      <c r="H10" s="18"/>
+      <c r="H10" s="18" t="s">
+        <v>846</v>
+      </c>
+      <c r="I10" s="20"/>
       <c r="J10" s="20"/>
       <c r="K10" s="4"/>
     </row>
@@ -19985,15 +20009,27 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="16"/>
+      <c r="B11" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D11" s="13">
+        <v>2026003603</v>
+      </c>
+      <c r="E11" s="15">
+        <v>46218</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>841</v>
+      </c>
       <c r="G11" s="17">
         <v>1</v>
       </c>
-      <c r="H11" s="18"/>
+      <c r="H11" s="18" t="s">
+        <v>842</v>
+      </c>
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
       <c r="K11" s="4"/>
@@ -20003,15 +20039,28 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="16"/>
+      <c r="B12" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D12" s="13">
+        <v>2026003604</v>
+      </c>
+      <c r="E12" s="15">
+        <v>46218</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>843</v>
+      </c>
       <c r="G12" s="17">
         <v>1</v>
       </c>
-      <c r="H12" s="18"/>
+      <c r="H12" s="18" t="s">
+        <v>844</v>
+      </c>
+      <c r="I12" s="20"/>
       <c r="J12" s="20"/>
       <c r="K12" s="4"/>
     </row>
@@ -20020,15 +20069,27 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="16"/>
+      <c r="B13" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D13" s="13">
+        <v>2026003605</v>
+      </c>
+      <c r="E13" s="15">
+        <v>46218</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>848</v>
+      </c>
       <c r="G13" s="17">
         <v>1</v>
       </c>
-      <c r="H13" s="18"/>
+      <c r="H13" s="18" t="s">
+        <v>847</v>
+      </c>
       <c r="I13" s="20"/>
       <c r="J13" s="20"/>
       <c r="K13" s="4"/>
@@ -20038,15 +20099,27 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="16"/>
+      <c r="B14" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>849</v>
+      </c>
+      <c r="E14" s="15">
+        <v>46219</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>850</v>
+      </c>
       <c r="G14" s="17">
         <v>1</v>
       </c>
-      <c r="H14" s="18"/>
+      <c r="H14" s="18" t="s">
+        <v>851</v>
+      </c>
       <c r="I14" s="20"/>
       <c r="J14" s="20"/>
       <c r="K14" s="4"/>
@@ -20056,15 +20129,28 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="16"/>
+      <c r="B15" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>852</v>
+      </c>
+      <c r="E15" s="15">
+        <v>46224</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>854</v>
+      </c>
       <c r="G15" s="17">
         <v>1</v>
       </c>
-      <c r="H15" s="18"/>
+      <c r="H15" s="18" t="s">
+        <v>853</v>
+      </c>
+      <c r="I15" s="20"/>
       <c r="J15" s="20"/>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20072,15 +20158,27 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="16"/>
+      <c r="B16" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>855</v>
+      </c>
+      <c r="E16" s="15">
+        <v>46225</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>857</v>
+      </c>
       <c r="G16" s="17">
         <v>1</v>
       </c>
-      <c r="H16" s="18"/>
+      <c r="H16" s="18" t="s">
+        <v>856</v>
+      </c>
       <c r="I16" s="20"/>
       <c r="J16" s="20"/>
     </row>
@@ -20089,15 +20187,27 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="16"/>
+      <c r="B17" s="13" t="s">
+        <v>630</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>858</v>
+      </c>
+      <c r="E17" s="15">
+        <v>46225</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>860</v>
+      </c>
       <c r="G17" s="17">
         <v>1</v>
       </c>
-      <c r="H17" s="18"/>
+      <c r="H17" s="18" t="s">
+        <v>859</v>
+      </c>
       <c r="I17" s="20"/>
       <c r="J17" s="20"/>
     </row>
@@ -20106,15 +20216,27 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="16"/>
+      <c r="B18" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>861</v>
+      </c>
+      <c r="E18" s="15">
+        <v>46225</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>862</v>
+      </c>
       <c r="G18" s="17">
         <v>1</v>
       </c>
-      <c r="H18" s="18"/>
+      <c r="H18" s="18" t="s">
+        <v>863</v>
+      </c>
       <c r="I18" s="20"/>
       <c r="J18" s="20"/>
     </row>
@@ -20123,15 +20245,27 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
+      <c r="B19" s="13" t="s">
+        <v>630</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D19" s="13">
+        <v>2024004654</v>
+      </c>
+      <c r="E19" s="15">
+        <v>46226</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>883</v>
+      </c>
       <c r="G19" s="17">
         <v>1</v>
       </c>
-      <c r="H19" s="18"/>
+      <c r="H19" s="4" t="s">
+        <v>882</v>
+      </c>
       <c r="I19" s="20"/>
       <c r="J19" s="20"/>
     </row>
@@ -20140,15 +20274,27 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="16"/>
+      <c r="B20" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D20" s="13">
+        <v>2026003469</v>
+      </c>
+      <c r="E20" s="15">
+        <v>46226</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>885</v>
+      </c>
       <c r="G20" s="17">
         <v>1</v>
       </c>
-      <c r="H20" s="18"/>
+      <c r="H20" s="4" t="s">
+        <v>884</v>
+      </c>
       <c r="I20" s="20"/>
       <c r="J20" s="20"/>
     </row>
@@ -20157,15 +20303,27 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="16"/>
+      <c r="B21" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D21" s="13">
+        <v>2026003641</v>
+      </c>
+      <c r="E21" s="15">
+        <v>46226</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>875</v>
+      </c>
       <c r="G21" s="17">
         <v>1</v>
       </c>
-      <c r="H21" s="18"/>
+      <c r="H21" s="4" t="s">
+        <v>874</v>
+      </c>
       <c r="I21" s="20"/>
       <c r="J21" s="20"/>
     </row>
@@ -20174,15 +20332,28 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="16"/>
+      <c r="B22" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D22" s="13">
+        <v>2026003642</v>
+      </c>
+      <c r="E22" s="15">
+        <v>46226</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>871</v>
+      </c>
       <c r="G22" s="17">
         <v>1</v>
       </c>
-      <c r="H22" s="18"/>
+      <c r="H22" s="18" t="s">
+        <v>870</v>
+      </c>
+      <c r="I22" s="20"/>
       <c r="J22" s="20"/>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20190,15 +20361,28 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="16"/>
+      <c r="B23" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D23" s="13">
+        <v>2026003643</v>
+      </c>
+      <c r="E23" s="15">
+        <v>46226</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>879</v>
+      </c>
       <c r="G23" s="17">
         <v>1</v>
       </c>
-      <c r="H23" s="18"/>
+      <c r="H23" s="18" t="s">
+        <v>878</v>
+      </c>
+      <c r="I23" s="20"/>
       <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20206,15 +20390,28 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="16"/>
+      <c r="B24" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D24" s="13">
+        <v>2026003644</v>
+      </c>
+      <c r="E24" s="15">
+        <v>46226</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>867</v>
+      </c>
       <c r="G24" s="17">
         <v>1</v>
       </c>
-      <c r="H24" s="4"/>
+      <c r="H24" s="18" t="s">
+        <v>866</v>
+      </c>
+      <c r="I24" s="20"/>
       <c r="J24" s="20"/>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20222,15 +20419,28 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="16"/>
+      <c r="B25" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D25" s="13">
+        <v>2026003645</v>
+      </c>
+      <c r="E25" s="15">
+        <v>46226</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>881</v>
+      </c>
       <c r="G25" s="17">
         <v>1</v>
       </c>
-      <c r="H25" s="4"/>
+      <c r="H25" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="I25" s="20"/>
       <c r="J25" s="20"/>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20238,15 +20448,28 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="16"/>
+      <c r="B26" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D26" s="13">
+        <v>2026003646</v>
+      </c>
+      <c r="E26" s="15">
+        <v>46226</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>869</v>
+      </c>
       <c r="G26" s="17">
         <v>1</v>
       </c>
-      <c r="H26" s="18"/>
+      <c r="H26" s="18" t="s">
+        <v>868</v>
+      </c>
+      <c r="I26" s="20"/>
       <c r="J26" s="20"/>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20254,15 +20477,28 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="16"/>
+      <c r="B27" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D27" s="13">
+        <v>2026003648</v>
+      </c>
+      <c r="E27" s="15">
+        <v>46226</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>877</v>
+      </c>
       <c r="G27" s="17">
         <v>1</v>
       </c>
-      <c r="H27" s="4"/>
+      <c r="H27" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="I27" s="20"/>
       <c r="J27" s="20"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20270,15 +20506,28 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="16"/>
+      <c r="B28" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D28" s="13">
+        <v>2026003649</v>
+      </c>
+      <c r="E28" s="15">
+        <v>46226</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>864</v>
+      </c>
       <c r="G28" s="17">
         <v>1</v>
       </c>
-      <c r="H28" s="4"/>
+      <c r="H28" s="18" t="s">
+        <v>865</v>
+      </c>
+      <c r="I28" s="20"/>
       <c r="J28" s="20"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20286,15 +20535,28 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="16"/>
+      <c r="B29" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D29" s="13">
+        <v>2026003650</v>
+      </c>
+      <c r="E29" s="15">
+        <v>46226</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>873</v>
+      </c>
       <c r="G29" s="17">
         <v>1</v>
       </c>
-      <c r="H29" s="4"/>
+      <c r="H29" s="18" t="s">
+        <v>872</v>
+      </c>
+      <c r="I29" s="20"/>
       <c r="J29" s="20"/>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21642,6 +21904,10 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I29">
+    <sortCondition ref="E7:E29"/>
+    <sortCondition ref="D7:D29"/>
+  </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="I5:J5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24035501-CE8F-4BD1-B38D-585504BB7CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF05AC9D-8AA7-450A-A104-D1730507EBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1866" uniqueCount="918">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -2875,6 +2875,102 @@
   </si>
   <si>
     <t>NB(213/2026)</t>
+  </si>
+  <si>
+    <t>NB(634/2024)</t>
+  </si>
+  <si>
+    <t>Sali belkacem</t>
+  </si>
+  <si>
+    <t>djenane tebbal</t>
+  </si>
+  <si>
+    <t>Mag tebbel redouane</t>
+  </si>
+  <si>
+    <t>bd la republique n110</t>
+  </si>
+  <si>
+    <t>NB(660/2024)</t>
+  </si>
+  <si>
+    <t>Bouchenaf halim</t>
+  </si>
+  <si>
+    <t>aadl 720 bt 7 n4</t>
+  </si>
+  <si>
+    <t>NB(504/2025)</t>
+  </si>
+  <si>
+    <t>Safia el hadi</t>
+  </si>
+  <si>
+    <t>NB(208/2026)</t>
+  </si>
+  <si>
+    <t>aadl 720 bt 14 n7</t>
+  </si>
+  <si>
+    <t>Zater souad</t>
+  </si>
+  <si>
+    <t>aadl 720 bt 3 n24</t>
+  </si>
+  <si>
+    <t>Ammad lyes</t>
+  </si>
+  <si>
+    <t>aadl 720 bt 12 n01</t>
+  </si>
+  <si>
+    <t>NB(385/2025)</t>
+  </si>
+  <si>
+    <t>Guendouzi omrane</t>
+  </si>
+  <si>
+    <t>aadl 720 bt 9 n11</t>
+  </si>
+  <si>
+    <t>NB(616/2025)</t>
+  </si>
+  <si>
+    <t>Benzayed ridha</t>
+  </si>
+  <si>
+    <t>aadl 720 bt 4 n15</t>
+  </si>
+  <si>
+    <t>NB(572/2025)</t>
+  </si>
+  <si>
+    <t>Slimane taki eddine</t>
+  </si>
+  <si>
+    <t>aadl 720 bt 16 n38</t>
+  </si>
+  <si>
+    <t>NB(302/2026)</t>
+  </si>
+  <si>
+    <t>NB(200/2026)</t>
+  </si>
+  <si>
+    <t>Mag krab bakhta</t>
+  </si>
+  <si>
+    <t>cite 40 logts bt B n24</t>
+  </si>
+  <si>
+    <t>NB(201/2026)</t>
+  </si>
+  <si>
+    <t>Ziani a/rahmane</t>
+  </si>
+  <si>
+    <t>aadl 720 bt 1 n1</t>
   </si>
 </sst>
 </file>
@@ -19813,7 +19909,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -19853,7 +19949,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -20564,15 +20660,30 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="16"/>
+      <c r="B30" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D30" s="13">
+        <v>2026003606</v>
+      </c>
+      <c r="E30" s="15">
+        <v>46230</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>912</v>
+      </c>
       <c r="G30" s="17">
         <v>1</v>
       </c>
-      <c r="H30" s="18"/>
+      <c r="H30" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="I30" t="s">
+        <v>914</v>
+      </c>
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20580,15 +20691,30 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="16"/>
+      <c r="B31" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D31" s="13">
+        <v>2026004041</v>
+      </c>
+      <c r="E31" s="15">
+        <v>46230</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>886</v>
+      </c>
       <c r="G31" s="17">
         <v>1</v>
       </c>
-      <c r="H31" s="18"/>
+      <c r="H31" s="18" t="s">
+        <v>887</v>
+      </c>
+      <c r="I31" t="s">
+        <v>888</v>
+      </c>
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20596,15 +20722,30 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="16"/>
+      <c r="B32" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D32" s="13">
+        <v>2026004043</v>
+      </c>
+      <c r="E32" s="15">
+        <v>46230</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>894</v>
+      </c>
       <c r="G32" s="17">
         <v>1</v>
       </c>
-      <c r="H32" s="18"/>
+      <c r="H32" s="18" t="s">
+        <v>892</v>
+      </c>
+      <c r="I32" t="s">
+        <v>893</v>
+      </c>
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20612,15 +20753,30 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="16"/>
+      <c r="B33" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D33" s="13">
+        <v>2026004044</v>
+      </c>
+      <c r="E33" s="15">
+        <v>46230</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>891</v>
+      </c>
       <c r="G33" s="17">
         <v>1</v>
       </c>
-      <c r="H33" s="4"/>
+      <c r="H33" s="18" t="s">
+        <v>889</v>
+      </c>
+      <c r="I33" t="s">
+        <v>890</v>
+      </c>
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20628,15 +20784,30 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="16"/>
+      <c r="B34" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D34" s="13">
+        <v>2026004046</v>
+      </c>
+      <c r="E34" s="15">
+        <v>46230</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>896</v>
+      </c>
       <c r="G34" s="17">
         <v>1</v>
       </c>
-      <c r="H34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="I34" t="s">
+        <v>897</v>
+      </c>
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20644,15 +20815,30 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="16"/>
+      <c r="B35" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D35" s="13">
+        <v>2026004047</v>
+      </c>
+      <c r="E35" s="15">
+        <v>46230</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>211</v>
+      </c>
       <c r="G35" s="17">
         <v>1</v>
       </c>
-      <c r="H35" s="18"/>
+      <c r="H35" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="I35" t="s">
+        <v>899</v>
+      </c>
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20660,15 +20846,30 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="16"/>
+      <c r="B36" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D36" s="13">
+        <v>2026004048</v>
+      </c>
+      <c r="E36" s="15">
+        <v>46230</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>902</v>
+      </c>
       <c r="G36" s="17">
         <v>1</v>
       </c>
-      <c r="H36" s="18"/>
+      <c r="H36" s="18" t="s">
+        <v>900</v>
+      </c>
+      <c r="I36" t="s">
+        <v>901</v>
+      </c>
       <c r="J36" s="4"/>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20676,16 +20877,30 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="16"/>
+      <c r="B37" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D37" s="13">
+        <v>2026004049</v>
+      </c>
+      <c r="E37" s="15">
+        <v>46230</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>905</v>
+      </c>
       <c r="G37" s="17">
         <v>1</v>
       </c>
-      <c r="H37" s="18"/>
-      <c r="I37" s="20"/>
+      <c r="H37" s="18" t="s">
+        <v>903</v>
+      </c>
+      <c r="I37" t="s">
+        <v>904</v>
+      </c>
       <c r="J37" s="4"/>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20693,16 +20908,30 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="16"/>
+      <c r="B38" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D38" s="13">
+        <v>2026004050</v>
+      </c>
+      <c r="E38" s="15">
+        <v>46230</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>908</v>
+      </c>
       <c r="G38" s="17">
         <v>1</v>
       </c>
-      <c r="H38" s="4"/>
-      <c r="I38" s="20"/>
+      <c r="H38" s="18" t="s">
+        <v>906</v>
+      </c>
+      <c r="I38" t="s">
+        <v>907</v>
+      </c>
       <c r="J38" s="4"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -20710,38 +20939,67 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="16"/>
+      <c r="B39" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D39" s="13">
+        <v>2026003623</v>
+      </c>
+      <c r="E39" s="15">
+        <v>46231</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>915</v>
+      </c>
       <c r="G39" s="17">
         <v>1</v>
       </c>
-      <c r="H39" s="4"/>
+      <c r="H39" s="18" t="s">
+        <v>916</v>
+      </c>
+      <c r="I39" t="s">
+        <v>917</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
         <f>+A39+1</f>
         <v>34</v>
       </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="16"/>
+      <c r="B40" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D40" s="13">
+        <v>2026003624</v>
+      </c>
+      <c r="E40" s="15">
+        <v>46231</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>911</v>
+      </c>
       <c r="G40" s="17">
         <v>1</v>
       </c>
-      <c r="H40" s="18"/>
-      <c r="I40" s="20"/>
+      <c r="H40" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="I40" t="s">
+        <v>910</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B41" s="15"/>
+      <c r="B41" s="13"/>
       <c r="C41" s="13"/>
       <c r="D41" s="13"/>
       <c r="E41" s="15"/>
@@ -20750,7 +21008,6 @@
         <v>1</v>
       </c>
       <c r="H41" s="4"/>
-      <c r="I41" s="20"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
@@ -21904,9 +22161,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I29">
-    <sortCondition ref="E7:E29"/>
-    <sortCondition ref="D7:D29"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I40">
+    <sortCondition ref="E7:E40"/>
+    <sortCondition ref="D7:D40"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF05AC9D-8AA7-450A-A104-D1730507EBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A89E894-E413-4A84-A468-D02B645EAEDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1866" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="925">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -2883,24 +2883,15 @@
     <t>Sali belkacem</t>
   </si>
   <si>
-    <t>djenane tebbal</t>
-  </si>
-  <si>
     <t>Mag tebbel redouane</t>
   </si>
   <si>
-    <t>bd la republique n110</t>
-  </si>
-  <si>
     <t>NB(660/2024)</t>
   </si>
   <si>
     <t>Bouchenaf halim</t>
   </si>
   <si>
-    <t>aadl 720 bt 7 n4</t>
-  </si>
-  <si>
     <t>NB(504/2025)</t>
   </si>
   <si>
@@ -2910,48 +2901,30 @@
     <t>NB(208/2026)</t>
   </si>
   <si>
-    <t>aadl 720 bt 14 n7</t>
-  </si>
-  <si>
     <t>Zater souad</t>
   </si>
   <si>
-    <t>aadl 720 bt 3 n24</t>
-  </si>
-  <si>
     <t>Ammad lyes</t>
   </si>
   <si>
-    <t>aadl 720 bt 12 n01</t>
-  </si>
-  <si>
     <t>NB(385/2025)</t>
   </si>
   <si>
     <t>Guendouzi omrane</t>
   </si>
   <si>
-    <t>aadl 720 bt 9 n11</t>
-  </si>
-  <si>
     <t>NB(616/2025)</t>
   </si>
   <si>
     <t>Benzayed ridha</t>
   </si>
   <si>
-    <t>aadl 720 bt 4 n15</t>
-  </si>
-  <si>
     <t>NB(572/2025)</t>
   </si>
   <si>
     <t>Slimane taki eddine</t>
   </si>
   <si>
-    <t>aadl 720 bt 16 n38</t>
-  </si>
-  <si>
     <t>NB(302/2026)</t>
   </si>
   <si>
@@ -2961,16 +2934,64 @@
     <t>Mag krab bakhta</t>
   </si>
   <si>
-    <t>cite 40 logts bt B n24</t>
-  </si>
-  <si>
     <t>NB(201/2026)</t>
   </si>
   <si>
     <t>Ziani a/rahmane</t>
   </si>
   <si>
-    <t>aadl 720 bt 1 n1</t>
+    <t>NB(660/2025)</t>
+  </si>
+  <si>
+    <t>Bentaleb fatiha</t>
+  </si>
+  <si>
+    <t>NB(262/2026)</t>
+  </si>
+  <si>
+    <t>Coiff hellal ,rafik</t>
+  </si>
+  <si>
+    <t>Houari med</t>
+  </si>
+  <si>
+    <t>NB(179/2026)</t>
+  </si>
+  <si>
+    <t>Boumediene aek</t>
+  </si>
+  <si>
+    <t>NB(560/2025)</t>
+  </si>
+  <si>
+    <t>Seknder sara</t>
+  </si>
+  <si>
+    <t>NB(323/2026)</t>
+  </si>
+  <si>
+    <t>Lakhal ahmed</t>
+  </si>
+  <si>
+    <t>NB(054/2026)</t>
+  </si>
+  <si>
+    <t>Lakhal djamel</t>
+  </si>
+  <si>
+    <t>NB(053/2026)</t>
+  </si>
+  <si>
+    <t>NB(056/2026)</t>
+  </si>
+  <si>
+    <t>Daya boudjemaa</t>
+  </si>
+  <si>
+    <t>Ganid kaddour</t>
+  </si>
+  <si>
+    <t>NB(244/2026)</t>
   </si>
 </sst>
 </file>
@@ -19909,7 +19930,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -19949,7 +19970,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -20673,16 +20694,13 @@
         <v>46230</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
       <c r="G30" s="17">
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="I30" t="s">
-        <v>914</v>
+        <v>904</v>
       </c>
       <c r="J30" s="4"/>
     </row>
@@ -20712,9 +20730,6 @@
       <c r="H31" s="18" t="s">
         <v>887</v>
       </c>
-      <c r="I31" t="s">
-        <v>888</v>
-      </c>
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20735,16 +20750,13 @@
         <v>46230</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="G32" s="17">
         <v>1</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>892</v>
-      </c>
-      <c r="I32" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="J32" s="4"/>
     </row>
@@ -20766,16 +20778,13 @@
         <v>46230</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G33" s="17">
         <v>1</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>889</v>
-      </c>
-      <c r="I33" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="J33" s="4"/>
     </row>
@@ -20797,16 +20806,13 @@
         <v>46230</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="G34" s="17">
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>895</v>
-      </c>
-      <c r="I34" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -20834,10 +20840,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>898</v>
-      </c>
-      <c r="I35" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="J35" s="4"/>
     </row>
@@ -20859,16 +20862,13 @@
         <v>46230</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="G36" s="17">
         <v>1</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>900</v>
-      </c>
-      <c r="I36" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="J36" s="4"/>
     </row>
@@ -20890,16 +20890,13 @@
         <v>46230</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>905</v>
+        <v>898</v>
       </c>
       <c r="G37" s="17">
         <v>1</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>903</v>
-      </c>
-      <c r="I37" t="s">
-        <v>904</v>
+        <v>897</v>
       </c>
       <c r="J37" s="4"/>
     </row>
@@ -20921,16 +20918,13 @@
         <v>46230</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="G38" s="17">
         <v>1</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>906</v>
-      </c>
-      <c r="I38" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="J38" s="4"/>
     </row>
@@ -20946,23 +20940,21 @@
         <v>284</v>
       </c>
       <c r="D39" s="13">
-        <v>2026003623</v>
+        <v>2026003622</v>
       </c>
       <c r="E39" s="15">
         <v>46231</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="G39" s="17">
         <v>1</v>
       </c>
-      <c r="H39" s="18" t="s">
-        <v>916</v>
-      </c>
-      <c r="I39" t="s">
-        <v>917</v>
-      </c>
+      <c r="H39" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="I39" s="20"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
@@ -20976,22 +20968,19 @@
         <v>284</v>
       </c>
       <c r="D40" s="13">
-        <v>2026003624</v>
+        <v>2026003623</v>
       </c>
       <c r="E40" s="15">
         <v>46231</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="G40" s="17">
         <v>1</v>
       </c>
-      <c r="H40" s="4" t="s">
-        <v>909</v>
-      </c>
-      <c r="I40" t="s">
-        <v>910</v>
+      <c r="H40" s="18" t="s">
+        <v>906</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -20999,30 +20988,54 @@
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="16"/>
+      <c r="B41" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D41" s="13">
+        <v>2026003624</v>
+      </c>
+      <c r="E41" s="15">
+        <v>46231</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>902</v>
+      </c>
       <c r="G41" s="17">
         <v>1</v>
       </c>
-      <c r="H41" s="4"/>
+      <c r="H41" s="4" t="s">
+        <v>901</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="16"/>
+      <c r="B42" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D42" s="13">
+        <v>2026003625</v>
+      </c>
+      <c r="E42" s="15">
+        <v>46231</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>918</v>
+      </c>
       <c r="G42" s="17">
         <v>1</v>
       </c>
-      <c r="H42" s="4"/>
+      <c r="H42" s="4" t="s">
+        <v>917</v>
+      </c>
       <c r="I42" s="20"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -21030,61 +21043,110 @@
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="16"/>
+      <c r="B43" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D43" s="13">
+        <v>2026004045</v>
+      </c>
+      <c r="E43" s="15">
+        <v>46231</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>916</v>
+      </c>
       <c r="G43" s="17">
         <v>1</v>
       </c>
-      <c r="H43" s="18"/>
-      <c r="I43" s="20"/>
+      <c r="H43" s="4" t="s">
+        <v>915</v>
+      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="12">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="16"/>
+      <c r="B44" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D44" s="13">
+        <v>2026003626</v>
+      </c>
+      <c r="E44" s="15">
+        <v>46232</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>909</v>
+      </c>
       <c r="G44" s="17">
         <v>1</v>
       </c>
-      <c r="H44" s="4"/>
+      <c r="H44" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="I44" s="20"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="12">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="16"/>
+      <c r="B45" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D45" s="13">
+        <v>2026003627</v>
+      </c>
+      <c r="E45" s="15">
+        <v>46232</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>921</v>
+      </c>
       <c r="G45" s="17">
         <v>1</v>
       </c>
-      <c r="H45" s="4"/>
+      <c r="H45" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="I45" s="20"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="12">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B46" s="15"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="16"/>
+      <c r="B46" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D46" s="13">
+        <v>2026003662</v>
+      </c>
+      <c r="E46" s="15">
+        <v>46232</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>912</v>
+      </c>
       <c r="G46" s="17">
         <v>1</v>
       </c>
-      <c r="H46" s="4"/>
+      <c r="H46" s="18" t="s">
+        <v>911</v>
+      </c>
       <c r="I46" s="20"/>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21092,46 +21154,81 @@
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B47" s="15"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="16"/>
+      <c r="B47" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D47" s="13">
+        <v>2026003663</v>
+      </c>
+      <c r="E47" s="15">
+        <v>46232</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>914</v>
+      </c>
       <c r="G47" s="17">
         <v>1</v>
       </c>
-      <c r="H47" s="4"/>
-      <c r="I47" s="20"/>
+      <c r="H47" s="4" t="s">
+        <v>913</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="12">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="16"/>
+      <c r="B48" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D48" s="13">
+        <v>2026003664</v>
+      </c>
+      <c r="E48" s="15">
+        <v>46232</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>907</v>
+      </c>
       <c r="G48" s="17">
         <v>1</v>
       </c>
-      <c r="H48" s="4"/>
+      <c r="H48" s="4" t="s">
+        <v>908</v>
+      </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="12">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="16"/>
+      <c r="B49" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D49" s="13">
+        <v>2026004042</v>
+      </c>
+      <c r="E49" s="15">
+        <v>46232</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>924</v>
+      </c>
       <c r="G49" s="17">
         <v>1</v>
       </c>
-      <c r="H49" s="4"/>
+      <c r="H49" s="4" t="s">
+        <v>923</v>
+      </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="12">
@@ -22161,9 +22258,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I40">
-    <sortCondition ref="E7:E40"/>
-    <sortCondition ref="D7:D40"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I49">
+    <sortCondition ref="E7:E49"/>
+    <sortCondition ref="D7:D49"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A89E894-E413-4A84-A468-D02B645EAEDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E2E397-EDBA-457D-AB2A-CB9D899F2BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Janvier 2026 " sheetId="2" r:id="rId1"/>
@@ -20,8 +20,10 @@
     <sheet name="Mai 2026" sheetId="5" r:id="rId5"/>
     <sheet name="Juin 2026" sheetId="6" r:id="rId6"/>
     <sheet name="Juillet 2026" sheetId="7" r:id="rId7"/>
+    <sheet name="Aout 2026" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Aout 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Avril 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Février 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Janvier 2026 '!$1:$6</definedName>
@@ -51,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="1040">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -2992,6 +2994,372 @@
   </si>
   <si>
     <t>NB(244/2026)</t>
+  </si>
+  <si>
+    <r>
+      <t>Mois de Aout</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <t>NB(317/2026)</t>
+  </si>
+  <si>
+    <t>Talbi hichem</t>
+  </si>
+  <si>
+    <t>Tadjini omar</t>
+  </si>
+  <si>
+    <t>NB(210/2026)</t>
+  </si>
+  <si>
+    <t>NB(310/2026)</t>
+  </si>
+  <si>
+    <t>Hamimeche imed</t>
+  </si>
+  <si>
+    <t>NB(318/2026)</t>
+  </si>
+  <si>
+    <t>Bensalah slimane</t>
+  </si>
+  <si>
+    <t>NB(212/2023)</t>
+  </si>
+  <si>
+    <t>Talbi fathi</t>
+  </si>
+  <si>
+    <t>rue korteby</t>
+  </si>
+  <si>
+    <t>Ziouache med</t>
+  </si>
+  <si>
+    <t>720 aadl bt 5 n9</t>
+  </si>
+  <si>
+    <t>NB(184/2026)</t>
+  </si>
+  <si>
+    <t>Adjal yekhlef</t>
+  </si>
+  <si>
+    <t>720 aadl bt 15 n3</t>
+  </si>
+  <si>
+    <t>NB(298/2023)</t>
+  </si>
+  <si>
+    <t>Ali hamza abdenour</t>
+  </si>
+  <si>
+    <t>720 aadl bt 14 n38</t>
+  </si>
+  <si>
+    <t>NB(321/2026)</t>
+  </si>
+  <si>
+    <t>Belaissa med</t>
+  </si>
+  <si>
+    <t>cité hantabli</t>
+  </si>
+  <si>
+    <t>Belaissa foudil</t>
+  </si>
+  <si>
+    <t>NB(320/2026)</t>
+  </si>
+  <si>
+    <t>Toumi faycel</t>
+  </si>
+  <si>
+    <t>NB(324/2026)</t>
+  </si>
+  <si>
+    <t>Toumi missoum</t>
+  </si>
+  <si>
+    <t>NB(322/2026)</t>
+  </si>
+  <si>
+    <t>Bahi noureddine</t>
+  </si>
+  <si>
+    <t>oued guelet</t>
+  </si>
+  <si>
+    <t>NB(121/2026)</t>
+  </si>
+  <si>
+    <t>NB(299/2026)</t>
+  </si>
+  <si>
+    <t>Guernina fatiha</t>
+  </si>
+  <si>
+    <t>720 aadl bt 18 n5</t>
+  </si>
+  <si>
+    <t>Kardou med</t>
+  </si>
+  <si>
+    <t>NB(239/2026)</t>
+  </si>
+  <si>
+    <t>El kous med mounsif</t>
+  </si>
+  <si>
+    <t>cité hantabli n75</t>
+  </si>
+  <si>
+    <t>NB(221/2026)</t>
+  </si>
+  <si>
+    <t>Becherirat mokhtar</t>
+  </si>
+  <si>
+    <t>rue de l'aln</t>
+  </si>
+  <si>
+    <t>NB(361/2025)</t>
+  </si>
+  <si>
+    <t>Saidi amar</t>
+  </si>
+  <si>
+    <t>NB(284/2026)</t>
+  </si>
+  <si>
+    <t>NB(001/2026)</t>
+  </si>
+  <si>
+    <t>Maamri hamza</t>
+  </si>
+  <si>
+    <t>bungalow chorfa n°02</t>
+  </si>
+  <si>
+    <t>Zerkani ahmed</t>
+  </si>
+  <si>
+    <t>720 aadl bt 15 n02</t>
+  </si>
+  <si>
+    <t>NB(305/2026)</t>
+  </si>
+  <si>
+    <t>Krelifaoui mhamed</t>
+  </si>
+  <si>
+    <t>720 aadl bt 14 n08</t>
+  </si>
+  <si>
+    <t>NB(355/2026)</t>
+  </si>
+  <si>
+    <t>NB(243/2026)</t>
+  </si>
+  <si>
+    <t>Dameche zoheir</t>
+  </si>
+  <si>
+    <t>720 aadl bt 11 n08</t>
+  </si>
+  <si>
+    <t>NB(207/2026)</t>
+  </si>
+  <si>
+    <t>Habat med</t>
+  </si>
+  <si>
+    <t>720 aadl bt 08 n13</t>
+  </si>
+  <si>
+    <t>Atil hadjer</t>
+  </si>
+  <si>
+    <t>720 aadl bt 19 n25</t>
+  </si>
+  <si>
+    <t>NB(233/2026)</t>
+  </si>
+  <si>
+    <t>Kerbouci aek</t>
+  </si>
+  <si>
+    <t>720 aadl bt 07 n17</t>
+  </si>
+  <si>
+    <t>NB(510/2025)</t>
+  </si>
+  <si>
+    <t>Bourghaia khatir</t>
+  </si>
+  <si>
+    <t>720 aadl bt 19 n06</t>
+  </si>
+  <si>
+    <t>NB(469/2025)</t>
+  </si>
+  <si>
+    <t>Benslimane hannachi</t>
+  </si>
+  <si>
+    <t>720 aadl bt 05 n20</t>
+  </si>
+  <si>
+    <t>NB(197/2026)</t>
+  </si>
+  <si>
+    <t>Djillali rabea</t>
+  </si>
+  <si>
+    <t>720 aadl bt 01 n06</t>
+  </si>
+  <si>
+    <t>NB(228/2026)</t>
+  </si>
+  <si>
+    <t>Mokdad sid ahmed</t>
+  </si>
+  <si>
+    <t>720 aadl bt 11 n26</t>
+  </si>
+  <si>
+    <t>NB(269/2026)</t>
+  </si>
+  <si>
+    <t>Kassimi med</t>
+  </si>
+  <si>
+    <t>720 aadl bt 10 n25</t>
+  </si>
+  <si>
+    <t>NB(237/2026)</t>
+  </si>
+  <si>
+    <t>Debbah moussaab</t>
+  </si>
+  <si>
+    <t>720 aadl bt 19 n33</t>
+  </si>
+  <si>
+    <t>NB(266/2026)</t>
+  </si>
+  <si>
+    <t>Mazari kheira</t>
+  </si>
+  <si>
+    <t>720 aadl bt 9 n28</t>
+  </si>
+  <si>
+    <t>Hachemi habib</t>
+  </si>
+  <si>
+    <t>720 aadl bt 13 n08</t>
+  </si>
+  <si>
+    <t>NB(235/2026)</t>
+  </si>
+  <si>
+    <t>Daya aek</t>
+  </si>
+  <si>
+    <t>NB(509/2025)</t>
+  </si>
+  <si>
+    <t>720 aadl bt 09 n14</t>
+  </si>
+  <si>
+    <t>Zoulikha hafidha</t>
+  </si>
+  <si>
+    <t>720 aadl bt 15 n27</t>
+  </si>
+  <si>
+    <t>NB(419/2025)</t>
+  </si>
+  <si>
+    <t>Kadri med</t>
+  </si>
+  <si>
+    <t>720 aadl bt 04 n37</t>
+  </si>
+  <si>
+    <t>NB(303/2026)</t>
+  </si>
+  <si>
+    <t>Djamel med</t>
+  </si>
+  <si>
+    <t>720 aadl bt 05 n35</t>
+  </si>
+  <si>
+    <t>NB(325/2026)</t>
+  </si>
+  <si>
+    <t>Benzekkour benaissa</t>
+  </si>
+  <si>
+    <t>720 aadl bt 04 n01</t>
+  </si>
+  <si>
+    <t>NB(211/2026)</t>
+  </si>
+  <si>
+    <t>Yahiaoui hamid</t>
+  </si>
+  <si>
+    <t>720 aadl bt 16 n16</t>
+  </si>
+  <si>
+    <t>NB(214/2026)</t>
+  </si>
+  <si>
+    <t>Benkhaoua meriem</t>
+  </si>
+  <si>
+    <t>720 aadl bt 19 n36</t>
+  </si>
+  <si>
+    <t>NB(472/2025)</t>
+  </si>
+  <si>
+    <t>Benlakhdar aissa</t>
+  </si>
+  <si>
+    <t>720 aadl bt 08 n11</t>
+  </si>
+  <si>
+    <t>NB(548/2025)</t>
+  </si>
+  <si>
+    <t>Toumi boualem</t>
+  </si>
+  <si>
+    <t>06eme Tranche n31</t>
   </si>
 </sst>
 </file>
@@ -3156,7 +3524,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3239,6 +3607,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3744,6 +4115,61 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connecteur droit 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B8DDF12-7A6F-4D05-8705-3F53E0D7D234}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="628650" y="9705975"/>
+          <a:ext cx="4610100" cy="6819900"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>104785</xdr:colOff>
       <xdr:row>112</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -3759,7 +4185,7 @@
         <xdr:cNvPr id="2" name="Connecteur droit 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B8DDF12-7A6F-4D05-8705-3F53E0D7D234}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADB3B030-03B4-4554-B513-DED113D082B0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19930,7 +20356,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -19970,7 +20396,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -20594,28 +21020,27 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="15" t="s">
         <v>19</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>284</v>
       </c>
       <c r="D27" s="13">
-        <v>2026003648</v>
+        <v>2026003647</v>
       </c>
       <c r="E27" s="15">
         <v>46226</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>877</v>
+        <v>930</v>
       </c>
       <c r="G27" s="17">
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>876</v>
-      </c>
-      <c r="I27" s="20"/>
+        <v>931</v>
+      </c>
       <c r="J27" s="20"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20630,19 +21055,19 @@
         <v>284</v>
       </c>
       <c r="D28" s="13">
-        <v>2026003649</v>
+        <v>2026003648</v>
       </c>
       <c r="E28" s="15">
         <v>46226</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>864</v>
+        <v>877</v>
       </c>
       <c r="G28" s="17">
         <v>1</v>
       </c>
-      <c r="H28" s="18" t="s">
-        <v>865</v>
+      <c r="H28" s="4" t="s">
+        <v>876</v>
       </c>
       <c r="I28" s="20"/>
       <c r="J28" s="20"/>
@@ -20659,19 +21084,19 @@
         <v>284</v>
       </c>
       <c r="D29" s="13">
-        <v>2026003650</v>
+        <v>2026003649</v>
       </c>
       <c r="E29" s="15">
         <v>46226</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="G29" s="17">
         <v>1</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="I29" s="20"/>
       <c r="J29" s="20"/>
@@ -20681,27 +21106,28 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B30" s="15" t="s">
-        <v>257</v>
+      <c r="B30" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>284</v>
       </c>
       <c r="D30" s="13">
-        <v>2026003606</v>
+        <v>2026003650</v>
       </c>
       <c r="E30" s="15">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>903</v>
+        <v>873</v>
       </c>
       <c r="G30" s="17">
         <v>1</v>
       </c>
-      <c r="H30" s="4" t="s">
-        <v>904</v>
-      </c>
+      <c r="H30" s="18" t="s">
+        <v>872</v>
+      </c>
+      <c r="I30" s="20"/>
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20709,26 +21135,26 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B31" s="13" t="s">
-        <v>19</v>
+      <c r="B31" s="15" t="s">
+        <v>257</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>284</v>
       </c>
       <c r="D31" s="13">
-        <v>2026004041</v>
+        <v>2026003606</v>
       </c>
       <c r="E31" s="15">
         <v>46230</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>886</v>
+        <v>903</v>
       </c>
       <c r="G31" s="17">
         <v>1</v>
       </c>
-      <c r="H31" s="18" t="s">
-        <v>887</v>
+      <c r="H31" s="4" t="s">
+        <v>904</v>
       </c>
       <c r="J31" s="4"/>
     </row>
@@ -20744,19 +21170,19 @@
         <v>284</v>
       </c>
       <c r="D32" s="13">
-        <v>2026004043</v>
+        <v>2026004041</v>
       </c>
       <c r="E32" s="15">
         <v>46230</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="G32" s="17">
         <v>1</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="J32" s="4"/>
     </row>
@@ -20766,25 +21192,25 @@
         <v>27</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>284</v>
       </c>
       <c r="D33" s="13">
-        <v>2026004044</v>
+        <v>2026004043</v>
       </c>
       <c r="E33" s="15">
         <v>46230</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="G33" s="17">
         <v>1</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="J33" s="4"/>
     </row>
@@ -20794,25 +21220,25 @@
         <v>28</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>284</v>
       </c>
       <c r="D34" s="13">
-        <v>2026004046</v>
+        <v>2026004044</v>
       </c>
       <c r="E34" s="15">
         <v>46230</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="G34" s="17">
         <v>1</v>
       </c>
-      <c r="H34" s="4" t="s">
-        <v>892</v>
+      <c r="H34" s="18" t="s">
+        <v>888</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -20828,19 +21254,19 @@
         <v>284</v>
       </c>
       <c r="D35" s="13">
-        <v>2026004047</v>
+        <v>2026004046</v>
       </c>
       <c r="E35" s="15">
         <v>46230</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>211</v>
+        <v>893</v>
       </c>
       <c r="G35" s="17">
         <v>1</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="J35" s="4"/>
     </row>
@@ -20856,19 +21282,19 @@
         <v>284</v>
       </c>
       <c r="D36" s="13">
-        <v>2026004048</v>
+        <v>2026004047</v>
       </c>
       <c r="E36" s="15">
         <v>46230</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>896</v>
+        <v>211</v>
       </c>
       <c r="G36" s="17">
         <v>1</v>
       </c>
-      <c r="H36" s="18" t="s">
-        <v>895</v>
+      <c r="H36" s="4" t="s">
+        <v>894</v>
       </c>
       <c r="J36" s="4"/>
     </row>
@@ -20884,19 +21310,19 @@
         <v>284</v>
       </c>
       <c r="D37" s="13">
-        <v>2026004049</v>
+        <v>2026004048</v>
       </c>
       <c r="E37" s="15">
         <v>46230</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="G37" s="17">
         <v>1</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="J37" s="4"/>
     </row>
@@ -20912,19 +21338,19 @@
         <v>284</v>
       </c>
       <c r="D38" s="13">
-        <v>2026004050</v>
+        <v>2026004049</v>
       </c>
       <c r="E38" s="15">
         <v>46230</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="G38" s="17">
         <v>1</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="J38" s="4"/>
     </row>
@@ -20940,21 +21366,20 @@
         <v>284</v>
       </c>
       <c r="D39" s="13">
-        <v>2026003622</v>
+        <v>2026004050</v>
       </c>
       <c r="E39" s="15">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>920</v>
+        <v>900</v>
       </c>
       <c r="G39" s="17">
         <v>1</v>
       </c>
-      <c r="H39" s="4" t="s">
-        <v>919</v>
-      </c>
-      <c r="I39" s="20"/>
+      <c r="H39" s="18" t="s">
+        <v>899</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
@@ -20968,20 +21393,21 @@
         <v>284</v>
       </c>
       <c r="D40" s="13">
-        <v>2026003623</v>
+        <v>2026003622</v>
       </c>
       <c r="E40" s="15">
         <v>46231</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="G40" s="17">
         <v>1</v>
       </c>
-      <c r="H40" s="18" t="s">
-        <v>906</v>
-      </c>
+      <c r="H40" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="I40" s="20"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
@@ -20995,19 +21421,19 @@
         <v>284</v>
       </c>
       <c r="D41" s="13">
-        <v>2026003624</v>
+        <v>2026003623</v>
       </c>
       <c r="E41" s="15">
         <v>46231</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="G41" s="17">
         <v>1</v>
       </c>
-      <c r="H41" s="4" t="s">
-        <v>901</v>
+      <c r="H41" s="18" t="s">
+        <v>906</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -21022,21 +21448,20 @@
         <v>284</v>
       </c>
       <c r="D42" s="13">
-        <v>2026003625</v>
+        <v>2026003624</v>
       </c>
       <c r="E42" s="15">
         <v>46231</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>918</v>
+        <v>902</v>
       </c>
       <c r="G42" s="17">
         <v>1</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>917</v>
-      </c>
-      <c r="I42" s="20"/>
+        <v>901</v>
+      </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
@@ -21050,20 +21475,21 @@
         <v>284</v>
       </c>
       <c r="D43" s="13">
-        <v>2026004045</v>
+        <v>2026003625</v>
       </c>
       <c r="E43" s="15">
         <v>46231</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="G43" s="17">
         <v>1</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>915</v>
-      </c>
+        <v>917</v>
+      </c>
+      <c r="I43" s="20"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="12">
@@ -21071,53 +21497,52 @@
         <v>38</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>284</v>
       </c>
       <c r="D44" s="13">
-        <v>2026003626</v>
+        <v>2026004045</v>
       </c>
       <c r="E44" s="15">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="G44" s="17">
         <v>1</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="I44" s="20"/>
+        <v>915</v>
+      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="12">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B45" s="15" t="s">
-        <v>93</v>
+      <c r="B45" s="13" t="s">
+        <v>257</v>
       </c>
       <c r="C45" s="13" t="s">
         <v>284</v>
       </c>
       <c r="D45" s="13">
-        <v>2026003627</v>
+        <v>2026003626</v>
       </c>
       <c r="E45" s="15">
         <v>46232</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>921</v>
+        <v>909</v>
       </c>
       <c r="G45" s="17">
         <v>1</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>922</v>
+        <v>910</v>
       </c>
       <c r="I45" s="20"/>
     </row>
@@ -21126,26 +21551,26 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B46" s="13" t="s">
-        <v>19</v>
+      <c r="B46" s="15" t="s">
+        <v>93</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>284</v>
       </c>
       <c r="D46" s="13">
-        <v>2026003662</v>
+        <v>2026003627</v>
       </c>
       <c r="E46" s="15">
         <v>46232</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>912</v>
+        <v>921</v>
       </c>
       <c r="G46" s="17">
         <v>1</v>
       </c>
-      <c r="H46" s="18" t="s">
-        <v>911</v>
+      <c r="H46" s="4" t="s">
+        <v>922</v>
       </c>
       <c r="I46" s="20"/>
     </row>
@@ -21161,20 +21586,21 @@
         <v>284</v>
       </c>
       <c r="D47" s="13">
-        <v>2026003663</v>
+        <v>2026003662</v>
       </c>
       <c r="E47" s="15">
         <v>46232</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="G47" s="17">
         <v>1</v>
       </c>
-      <c r="H47" s="4" t="s">
-        <v>913</v>
-      </c>
+      <c r="H47" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="I47" s="20"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="12">
@@ -21182,25 +21608,25 @@
         <v>42</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="C48" s="13" t="s">
         <v>284</v>
       </c>
       <c r="D48" s="13">
-        <v>2026003664</v>
+        <v>2026003663</v>
       </c>
       <c r="E48" s="15">
         <v>46232</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="G48" s="17">
         <v>1</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -21208,27 +21634,2529 @@
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B49" s="15" t="s">
-        <v>19</v>
+      <c r="B49" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>284</v>
       </c>
       <c r="D49" s="13">
-        <v>2026004042</v>
+        <v>2026003664</v>
       </c>
       <c r="E49" s="15">
         <v>46232</v>
       </c>
       <c r="F49" s="16" t="s">
+        <v>907</v>
+      </c>
+      <c r="G49" s="17">
+        <v>1</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="12">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D50" s="13">
+        <v>2026004042</v>
+      </c>
+      <c r="E50" s="15">
+        <v>46232</v>
+      </c>
+      <c r="F50" s="16" t="s">
         <v>924</v>
       </c>
+      <c r="G50" s="17">
+        <v>1</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="12">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B51" s="15"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="17">
+        <v>1</v>
+      </c>
+      <c r="H51" s="4"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="12">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B52" s="15"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="17">
+        <v>1</v>
+      </c>
+      <c r="H52" s="4"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="12">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B53" s="15"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="17">
+        <v>1</v>
+      </c>
+      <c r="H53" s="4"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="12">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B54" s="15"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="17">
+        <v>1</v>
+      </c>
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="12">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B55" s="15"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="17">
+        <v>1</v>
+      </c>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="12">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B56" s="15"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="17">
+        <v>1</v>
+      </c>
+      <c r="H56" s="4"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="12">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="17">
+        <v>1</v>
+      </c>
+      <c r="H57" s="4"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="12">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B58" s="15"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="17">
+        <v>1</v>
+      </c>
+      <c r="H58" s="4"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="12">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B59" s="15"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="17">
+        <v>1</v>
+      </c>
+      <c r="H59" s="4"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="12">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B60" s="15"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="17">
+        <v>1</v>
+      </c>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="12">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B61" s="15"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="17">
+        <v>1</v>
+      </c>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="12">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B62" s="15"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="17">
+        <v>1</v>
+      </c>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="12">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B63" s="15"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="17">
+        <v>1</v>
+      </c>
+      <c r="H63" s="4"/>
+      <c r="I63" s="20"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="12">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B64" s="15"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="15"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="17">
+        <v>1</v>
+      </c>
+      <c r="H64" s="4"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="12">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B65" s="15"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="17">
+        <v>1</v>
+      </c>
+      <c r="H65" s="4"/>
+      <c r="I65" s="20"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="12">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="17">
+        <v>1</v>
+      </c>
+      <c r="H66" s="4"/>
+      <c r="I66" s="20"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="12">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B67" s="15"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="15"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="17">
+        <v>1</v>
+      </c>
+      <c r="H67" s="4"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="12">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B68" s="15"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="17">
+        <v>1</v>
+      </c>
+      <c r="H68" s="4"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="12">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B69" s="15"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="17">
+        <v>1</v>
+      </c>
+      <c r="H69" s="4"/>
+      <c r="I69" s="20"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="12">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B70" s="15"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="17">
+        <v>1</v>
+      </c>
+      <c r="H70" s="4"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="12">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B71" s="15"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="17">
+        <v>1</v>
+      </c>
+      <c r="H71" s="4"/>
+      <c r="I71" s="20"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="12">
+        <f t="shared" ref="A72:A117" si="1">+A71+1</f>
+        <v>66</v>
+      </c>
+      <c r="B72" s="15"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="17">
+        <v>1</v>
+      </c>
+      <c r="H72" s="4"/>
+      <c r="I72" s="20"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="12">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="B73" s="15"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="17">
+        <v>1</v>
+      </c>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="12">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="B74" s="15"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="17">
+        <v>1</v>
+      </c>
+      <c r="H74" s="4"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="12">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B75" s="15"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="17">
+        <v>1</v>
+      </c>
+      <c r="H75" s="4"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="12">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="B76" s="15"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="17">
+        <v>1</v>
+      </c>
+      <c r="H76" s="4"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="12">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="B77" s="15"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="17">
+        <v>1</v>
+      </c>
+      <c r="H77" s="4"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="12">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="B78" s="15"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="17">
+        <v>1</v>
+      </c>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="12">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="B79" s="15"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="17">
+        <v>1</v>
+      </c>
+      <c r="H79" s="4"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="12">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="B80" s="15"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="17">
+        <v>1</v>
+      </c>
+      <c r="H80" s="4"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="12">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="B81" s="15"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="17">
+        <v>1</v>
+      </c>
+      <c r="H81" s="4"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="12">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="B82" s="15"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="17">
+        <v>1</v>
+      </c>
+      <c r="H82" s="4"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="12">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="B83" s="15"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="17">
+        <v>1</v>
+      </c>
+      <c r="H83" s="4"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="12">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="B84" s="15"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="15"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="17">
+        <v>1</v>
+      </c>
+      <c r="H84" s="4"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="12">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="B85" s="15"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="16"/>
+      <c r="G85" s="17">
+        <v>1</v>
+      </c>
+      <c r="H85" s="4"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="12">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="B86" s="15"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="16"/>
+      <c r="G86" s="17">
+        <v>1</v>
+      </c>
+      <c r="H86" s="4"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="12">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="B87" s="15"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="17">
+        <v>1</v>
+      </c>
+      <c r="H87" s="4"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="12">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="B88" s="15"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="17">
+        <v>1</v>
+      </c>
+      <c r="H88" s="4"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="12">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="B89" s="15"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="17">
+        <v>1</v>
+      </c>
+      <c r="H89" s="4"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="12">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="B90" s="15"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="16"/>
+      <c r="G90" s="17">
+        <v>1</v>
+      </c>
+      <c r="H90" s="4"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="12">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="B91" s="15"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="17">
+        <v>1</v>
+      </c>
+      <c r="H91" s="4"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="12">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="B92" s="15"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="17">
+        <v>1</v>
+      </c>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="12">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="B93" s="15"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="17">
+        <v>1</v>
+      </c>
+      <c r="H93" s="4"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="12">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="B94" s="15"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="15"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="17">
+        <v>1</v>
+      </c>
+      <c r="H94" s="4"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="12">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="B95" s="15"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="15"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="17">
+        <v>1</v>
+      </c>
+      <c r="H95" s="4"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="12">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="B96" s="15"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="16"/>
+      <c r="G96" s="17">
+        <v>1</v>
+      </c>
+      <c r="H96" s="4"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="12">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="B97" s="15"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="16"/>
+      <c r="G97" s="17">
+        <v>1</v>
+      </c>
+      <c r="H97" s="4"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="12">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="B98" s="15"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="16"/>
+      <c r="G98" s="17">
+        <v>1</v>
+      </c>
+      <c r="H98" s="4"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="12">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="B99" s="15"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="15"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="17">
+        <v>1</v>
+      </c>
+      <c r="H99" s="4"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="12">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="B100" s="15"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="15"/>
+      <c r="F100" s="16"/>
+      <c r="G100" s="17">
+        <v>1</v>
+      </c>
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="12">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="B101" s="15"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="16"/>
+      <c r="G101" s="17">
+        <v>1</v>
+      </c>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="12">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="B102" s="15"/>
+      <c r="C102" s="13"/>
+      <c r="D102" s="14"/>
+      <c r="E102" s="15"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="17">
+        <v>1</v>
+      </c>
+      <c r="H102" s="4"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="12">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="B103" s="15"/>
+      <c r="C103" s="13"/>
+      <c r="D103" s="14"/>
+      <c r="E103" s="15"/>
+      <c r="F103" s="16"/>
+      <c r="G103" s="17">
+        <v>1</v>
+      </c>
+      <c r="H103" s="4"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="12">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="B104" s="15"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="22"/>
+      <c r="E104" s="15"/>
+      <c r="F104" s="16"/>
+      <c r="G104" s="17">
+        <v>1</v>
+      </c>
+      <c r="H104" s="4"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="12">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="B105" s="15"/>
+      <c r="C105" s="13"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="15"/>
+      <c r="F105" s="16"/>
+      <c r="G105" s="17">
+        <v>1</v>
+      </c>
+      <c r="H105" s="4"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="12">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="B106" s="15"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="15"/>
+      <c r="F106" s="16"/>
+      <c r="G106" s="17">
+        <v>1</v>
+      </c>
+      <c r="H106" s="4"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="12">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="B107" s="15"/>
+      <c r="C107" s="13"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="15"/>
+      <c r="F107" s="16"/>
+      <c r="G107" s="17">
+        <v>1</v>
+      </c>
+      <c r="H107" s="4"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="12">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="B108" s="15"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="14"/>
+      <c r="E108" s="15"/>
+      <c r="F108" s="16"/>
+      <c r="G108" s="17">
+        <v>1</v>
+      </c>
+      <c r="H108" s="4"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="12">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="B109" s="15"/>
+      <c r="C109" s="13"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="15"/>
+      <c r="F109" s="16"/>
+      <c r="G109" s="17">
+        <v>1</v>
+      </c>
+      <c r="H109" s="4"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="12">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="B110" s="15"/>
+      <c r="C110" s="13"/>
+      <c r="D110" s="14"/>
+      <c r="E110" s="15"/>
+      <c r="F110" s="16"/>
+      <c r="G110" s="17">
+        <v>1</v>
+      </c>
+      <c r="H110" s="4"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="12">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="B111" s="15"/>
+      <c r="C111" s="13"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="15"/>
+      <c r="F111" s="16"/>
+      <c r="G111" s="17">
+        <v>1</v>
+      </c>
+      <c r="H111" s="4"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="12">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="B112" s="15"/>
+      <c r="C112" s="13"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="15"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="17">
+        <v>1</v>
+      </c>
+      <c r="H112" s="4"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="12">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="B113" s="15"/>
+      <c r="C113" s="13"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="15"/>
+      <c r="F113" s="16"/>
+      <c r="G113" s="17">
+        <v>1</v>
+      </c>
+      <c r="H113" s="4"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="12">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="B114" s="15"/>
+      <c r="C114" s="13"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="15"/>
+      <c r="F114" s="16"/>
+      <c r="G114" s="17">
+        <v>1</v>
+      </c>
+      <c r="H114" s="4"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="12">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="B115" s="15"/>
+      <c r="C115" s="13"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="15"/>
+      <c r="F115" s="16"/>
+      <c r="G115" s="17">
+        <v>1</v>
+      </c>
+      <c r="H115" s="4"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="12">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="B116" s="15"/>
+      <c r="C116" s="13"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="15"/>
+      <c r="F116" s="16"/>
+      <c r="G116" s="17">
+        <v>1</v>
+      </c>
+      <c r="H116" s="4"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="12">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="B117" s="15"/>
+      <c r="C117" s="13"/>
+      <c r="D117" s="14"/>
+      <c r="E117" s="15"/>
+      <c r="F117" s="16"/>
+      <c r="G117" s="17">
+        <v>1</v>
+      </c>
+      <c r="H117" s="4"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I50">
+    <sortCondition ref="E7:E50"/>
+    <sortCondition ref="D7:D50"/>
+  </sortState>
+  <mergeCells count="9">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="I4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283472" right="0.45" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70DDD32E-2E51-4B4B-9957-11A0B91F66C4}">
+  <dimension ref="A1:K117"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="2.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+    <col min="9" max="9" width="32.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="25"/>
+      <c r="K2" s="6">
+        <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="25"/>
+      <c r="K3" s="6">
+        <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="25"/>
+      <c r="K4" s="6">
+        <f>SUMIF(F7:F364,"Ve*",G7:G364)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>925</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="8">
+        <f>SUM(K2:K4)</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>1</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D7" s="13">
+        <v>2026003661</v>
+      </c>
+      <c r="E7" s="15">
+        <v>46235</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>926</v>
+      </c>
+      <c r="G7" s="17">
+        <v>1</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>927</v>
+      </c>
+      <c r="I7" s="20"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <f t="shared" ref="A8:A71" si="0">+A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D8" s="13">
+        <v>2026003665</v>
+      </c>
+      <c r="E8" s="15">
+        <v>46235</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>929</v>
+      </c>
+      <c r="G8" s="17">
+        <v>1</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>928</v>
+      </c>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D9" s="13">
+        <v>2026003545</v>
+      </c>
+      <c r="E9" s="15">
+        <v>46236</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>932</v>
+      </c>
+      <c r="G9" s="17">
+        <v>1</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>933</v>
+      </c>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D10" s="13">
+        <v>2026003544</v>
+      </c>
+      <c r="E10" s="15">
+        <v>46237</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>934</v>
+      </c>
+      <c r="G10" s="17">
+        <v>1</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>935</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>936</v>
+      </c>
+      <c r="J10" s="20"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D11" s="13">
+        <v>2026003463</v>
+      </c>
+      <c r="E11" s="15">
+        <v>46238</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>961</v>
+      </c>
+      <c r="G11" s="17">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>947</v>
+      </c>
+      <c r="J11" s="20"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D12" s="13">
+        <v>2026003468</v>
+      </c>
+      <c r="E12" s="15">
+        <v>46238</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>964</v>
+      </c>
+      <c r="G12" s="17">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>963</v>
+      </c>
+      <c r="J12" s="20"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D13" s="13">
+        <v>2026003470</v>
+      </c>
+      <c r="E13" s="15">
+        <v>46238</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>957</v>
+      </c>
+      <c r="G13" s="17">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>959</v>
+      </c>
+      <c r="J13" s="20"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D14" s="13">
+        <v>2026003541</v>
+      </c>
+      <c r="E14" s="15">
+        <v>46238</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>942</v>
+      </c>
+      <c r="G14" s="17">
+        <v>1</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>940</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>941</v>
+      </c>
+      <c r="J14" s="20"/>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D15" s="13">
+        <v>2026003542</v>
+      </c>
+      <c r="E15" s="15">
+        <v>46238</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>942</v>
+      </c>
+      <c r="G15" s="17">
+        <v>1</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>943</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>944</v>
+      </c>
+      <c r="J15" s="20"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D16" s="13">
+        <v>2026003543</v>
+      </c>
+      <c r="E16" s="15">
+        <v>46238</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>939</v>
+      </c>
+      <c r="G16" s="17">
+        <v>1</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>937</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>938</v>
+      </c>
+      <c r="J16" s="20"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D17" s="13">
+        <v>2026003546</v>
+      </c>
+      <c r="E17" s="15">
+        <v>46238</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>945</v>
+      </c>
+      <c r="G17" s="17">
+        <v>1</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>946</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>947</v>
+      </c>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D18" s="13">
+        <v>2026003547</v>
+      </c>
+      <c r="E18" s="15">
+        <v>46238</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>949</v>
+      </c>
+      <c r="G18" s="17">
+        <v>1</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>948</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>947</v>
+      </c>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D19" s="13">
+        <v>2026003548</v>
+      </c>
+      <c r="E19" s="15">
+        <v>46238</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="G19" s="17">
+        <v>1</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>950</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>947</v>
+      </c>
+      <c r="J19" s="20"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D20" s="13">
+        <v>2026003549</v>
+      </c>
+      <c r="E20" s="15">
+        <v>46238</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>953</v>
+      </c>
+      <c r="G20" s="17">
+        <v>1</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>952</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>947</v>
+      </c>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D21" s="13">
+        <v>2026003550</v>
+      </c>
+      <c r="E21" s="15">
+        <v>46238</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>956</v>
+      </c>
+      <c r="G21" s="17">
+        <v>1</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>954</v>
+      </c>
+      <c r="I21" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="J21" s="20"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D22" s="13">
+        <v>2026003461</v>
+      </c>
+      <c r="E22" s="15">
+        <v>46239</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>967</v>
+      </c>
+      <c r="G22" s="17">
+        <v>1</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>965</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>966</v>
+      </c>
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D23" s="13">
+        <v>2026003462</v>
+      </c>
+      <c r="E23" s="15">
+        <v>46239</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>969</v>
+      </c>
+      <c r="G23" s="17">
+        <v>1</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>968</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>966</v>
+      </c>
+      <c r="J23" s="20"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D24" s="13">
+        <v>2026003944</v>
+      </c>
+      <c r="E24" s="15">
+        <v>46242</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>970</v>
+      </c>
+      <c r="G24" s="17">
+        <v>1</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>971</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>972</v>
+      </c>
+      <c r="J24" s="20"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D25" s="13">
+        <v>2026003942</v>
+      </c>
+      <c r="E25" s="15">
+        <v>46243</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>975</v>
+      </c>
+      <c r="G25" s="17">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="I25" s="20" t="s">
+        <v>974</v>
+      </c>
+      <c r="J25" s="20"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D26" s="13">
+        <v>2026003943</v>
+      </c>
+      <c r="E26" s="15">
+        <v>46243</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>978</v>
+      </c>
+      <c r="G26" s="17">
+        <v>1</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>976</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>977</v>
+      </c>
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D27" s="13">
+        <v>2026003691</v>
+      </c>
+      <c r="E27" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>979</v>
+      </c>
+      <c r="G27" s="17">
+        <v>1</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="I27" s="20" t="s">
+        <v>981</v>
+      </c>
+      <c r="J27" s="20"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D28" s="13">
+        <v>2026003941</v>
+      </c>
+      <c r="E28" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>827</v>
+      </c>
+      <c r="G28" s="17">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I28" s="29" t="s">
+        <v>1039</v>
+      </c>
+      <c r="J28" s="20"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="12">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="13">
+        <v>2026143582</v>
+      </c>
+      <c r="E29" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G29" s="17">
+        <v>1</v>
+      </c>
+      <c r="H29" s="18" t="s">
+        <v>1011</v>
+      </c>
+      <c r="I29" s="20" t="s">
+        <v>1012</v>
+      </c>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="13">
+        <v>2026143583</v>
+      </c>
+      <c r="E30" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G30" s="17">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I30" s="20" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="13">
+        <v>2026143584</v>
+      </c>
+      <c r="E31" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G31" s="17">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>1027</v>
+      </c>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="13">
+        <v>2026143585</v>
+      </c>
+      <c r="E32" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G32" s="17">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I32" s="20" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="12">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="13">
+        <v>2026143586</v>
+      </c>
+      <c r="E33" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>860</v>
+      </c>
+      <c r="G33" s="17">
+        <v>1</v>
+      </c>
+      <c r="H33" s="18" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I33" s="20" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="12">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="13">
+        <v>2026143587</v>
+      </c>
+      <c r="E34" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G34" s="17">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I34" s="20" t="s">
+        <v>1024</v>
+      </c>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="12">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="13">
+        <v>2026143588</v>
+      </c>
+      <c r="E35" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G35" s="17">
+        <v>1</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I35" s="20" t="s">
+        <v>1021</v>
+      </c>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="12">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="13">
+        <v>2026143589</v>
+      </c>
+      <c r="E36" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G36" s="17">
+        <v>1</v>
+      </c>
+      <c r="H36" s="18" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I36" s="20" t="s">
+        <v>1018</v>
+      </c>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="12">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="13">
+        <v>2026143590</v>
+      </c>
+      <c r="E37" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G37" s="17">
+        <v>1</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="I37" s="20" t="s">
+        <v>1016</v>
+      </c>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="12">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="13">
+        <v>2026144297</v>
+      </c>
+      <c r="E38" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G38" s="17">
+        <v>1</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I38" s="20" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="12">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="13">
+        <v>2026144351</v>
+      </c>
+      <c r="E39" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>999</v>
+      </c>
+      <c r="G39" s="17">
+        <v>1</v>
+      </c>
+      <c r="H39" s="18" t="s">
+        <v>997</v>
+      </c>
+      <c r="I39" s="20" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="12">
+        <f>+A39+1</f>
+        <v>34</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="13">
+        <v>2026144352</v>
+      </c>
+      <c r="E40" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>996</v>
+      </c>
+      <c r="G40" s="17">
+        <v>1</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>994</v>
+      </c>
+      <c r="I40" s="20" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="12">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="13">
+        <v>2026144353</v>
+      </c>
+      <c r="E41" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G41" s="17">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I41" s="20" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="12">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="13">
+        <v>2026144354</v>
+      </c>
+      <c r="E42" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G42" s="17">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I42" s="20" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="12">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="13">
+        <v>2026144355</v>
+      </c>
+      <c r="E43" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G43" s="17">
+        <v>1</v>
+      </c>
+      <c r="H43" s="18" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I43" s="20" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="12">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="13">
+        <v>2026144356</v>
+      </c>
+      <c r="E44" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>982</v>
+      </c>
+      <c r="G44" s="17">
+        <v>1</v>
+      </c>
+      <c r="H44" s="18" t="s">
+        <v>983</v>
+      </c>
+      <c r="I44" s="20" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="12">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="13">
+        <v>2026144358</v>
+      </c>
+      <c r="E45" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>990</v>
+      </c>
+      <c r="G45" s="17">
+        <v>1</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="I45" s="20" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="12">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="13">
+        <v>2026144359</v>
+      </c>
+      <c r="E46" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>987</v>
+      </c>
+      <c r="G46" s="17">
+        <v>1</v>
+      </c>
+      <c r="H46" s="18" t="s">
+        <v>985</v>
+      </c>
+      <c r="I46" s="20" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="12">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" s="13">
+        <v>2026144360</v>
+      </c>
+      <c r="E47" s="15">
+        <v>46244</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>993</v>
+      </c>
+      <c r="G47" s="17">
+        <v>1</v>
+      </c>
+      <c r="H47" s="18" t="s">
+        <v>991</v>
+      </c>
+      <c r="I47" s="20" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="12">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="17">
+        <v>1</v>
+      </c>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="12">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B49" s="15"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="16"/>
       <c r="G49" s="17">
         <v>1</v>
       </c>
-      <c r="H49" s="4" t="s">
-        <v>923</v>
-      </c>
+      <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="12">
@@ -22258,9 +25186,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I49">
-    <sortCondition ref="E7:E49"/>
-    <sortCondition ref="D7:D49"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I47">
+    <sortCondition ref="E7:E47"/>
+    <sortCondition ref="D7:D47"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E2E397-EDBA-457D-AB2A-CB9D899F2BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51096C6F-E816-41C0-A0C0-611FA2496D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="1040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="1052">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -3360,6 +3360,42 @@
   </si>
   <si>
     <t>06eme Tranche n31</t>
+  </si>
+  <si>
+    <t>NB(186/2026)</t>
+  </si>
+  <si>
+    <t>Benoua dalila</t>
+  </si>
+  <si>
+    <t>6eme tranche n01</t>
+  </si>
+  <si>
+    <t>Nadj kheieddine</t>
+  </si>
+  <si>
+    <t>NB(326/2026)</t>
+  </si>
+  <si>
+    <t>Ophtalmo  Zekhref med amine</t>
+  </si>
+  <si>
+    <t>cité 483 logts</t>
+  </si>
+  <si>
+    <t>NB(270/2026)</t>
+  </si>
+  <si>
+    <t>Benaissa lyassine</t>
+  </si>
+  <si>
+    <t>NB(175/2026)</t>
+  </si>
+  <si>
+    <t>Tandjaoui fatma</t>
+  </si>
+  <si>
+    <t>NB(312/2026)</t>
   </si>
 </sst>
 </file>
@@ -22793,7 +22829,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -22833,7 +22869,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -23543,7 +23579,7 @@
       <c r="H28" s="4" t="s">
         <v>1038</v>
       </c>
-      <c r="I28" s="29" t="s">
+      <c r="I28" s="20" t="s">
         <v>1039</v>
       </c>
       <c r="J28" s="20"/>
@@ -24133,75 +24169,150 @@
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="16"/>
+      <c r="B48" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D48" s="13">
+        <v>2026003950</v>
+      </c>
+      <c r="E48" s="15">
+        <v>46246</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>1047</v>
+      </c>
       <c r="G48" s="17">
         <v>1</v>
       </c>
-      <c r="H48" s="4"/>
+      <c r="H48" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I48" s="29" t="s">
+        <v>1046</v>
+      </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="12">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="16"/>
+      <c r="B49" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D49" s="13">
+        <v>2026004019</v>
+      </c>
+      <c r="E49" s="15">
+        <v>46246</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>1051</v>
+      </c>
       <c r="G49" s="17">
         <v>1</v>
       </c>
-      <c r="H49" s="4"/>
+      <c r="H49" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I49" s="29" t="s">
+        <v>955</v>
+      </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="12">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="16"/>
+      <c r="B50" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D50" s="13">
+        <v>2026004020</v>
+      </c>
+      <c r="E50" s="15">
+        <v>46246</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>1049</v>
+      </c>
       <c r="G50" s="17">
         <v>1</v>
       </c>
-      <c r="H50" s="4"/>
+      <c r="H50" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I50" s="29" t="s">
+        <v>966</v>
+      </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="12">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="16"/>
+      <c r="B51" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D51" s="13">
+        <v>2026004063</v>
+      </c>
+      <c r="E51" s="15">
+        <v>46246</v>
+      </c>
+      <c r="F51" s="16" t="s">
+        <v>1040</v>
+      </c>
       <c r="G51" s="17">
         <v>1</v>
       </c>
-      <c r="H51" s="4"/>
+      <c r="H51" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I51" s="29" t="s">
+        <v>1042</v>
+      </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="12">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="16"/>
+      <c r="B52" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D52" s="13">
+        <v>2026004064</v>
+      </c>
+      <c r="E52" s="15">
+        <v>46246</v>
+      </c>
+      <c r="F52" s="16" t="s">
+        <v>1044</v>
+      </c>
       <c r="G52" s="17">
         <v>1</v>
       </c>
-      <c r="H52" s="4"/>
+      <c r="H52" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I52" s="29" t="s">
+        <v>955</v>
+      </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="12">
@@ -25186,9 +25297,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I47">
-    <sortCondition ref="E7:E47"/>
-    <sortCondition ref="D7:D47"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I52">
+    <sortCondition ref="E7:E52"/>
+    <sortCondition ref="D7:D52"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51096C6F-E816-41C0-A0C0-611FA2496D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F8EEEC-275A-4BFD-BB48-1675F23CBE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="1052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="1043">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -3050,42 +3050,27 @@
     <t>Talbi fathi</t>
   </si>
   <si>
-    <t>rue korteby</t>
-  </si>
-  <si>
     <t>Ziouache med</t>
   </si>
   <si>
-    <t>720 aadl bt 5 n9</t>
-  </si>
-  <si>
     <t>NB(184/2026)</t>
   </si>
   <si>
     <t>Adjal yekhlef</t>
   </si>
   <si>
-    <t>720 aadl bt 15 n3</t>
-  </si>
-  <si>
     <t>NB(298/2023)</t>
   </si>
   <si>
     <t>Ali hamza abdenour</t>
   </si>
   <si>
-    <t>720 aadl bt 14 n38</t>
-  </si>
-  <si>
     <t>NB(321/2026)</t>
   </si>
   <si>
     <t>Belaissa med</t>
   </si>
   <si>
-    <t>cité hantabli</t>
-  </si>
-  <si>
     <t>Belaissa foudil</t>
   </si>
   <si>
@@ -3119,9 +3104,6 @@
     <t>Guernina fatiha</t>
   </si>
   <si>
-    <t>720 aadl bt 18 n5</t>
-  </si>
-  <si>
     <t>Kardou med</t>
   </si>
   <si>
@@ -3131,9 +3113,6 @@
     <t>El kous med mounsif</t>
   </si>
   <si>
-    <t>cité hantabli n75</t>
-  </si>
-  <si>
     <t>NB(221/2026)</t>
   </si>
   <si>
@@ -3158,24 +3137,15 @@
     <t>Maamri hamza</t>
   </si>
   <si>
-    <t>bungalow chorfa n°02</t>
-  </si>
-  <si>
     <t>Zerkani ahmed</t>
   </si>
   <si>
-    <t>720 aadl bt 15 n02</t>
-  </si>
-  <si>
     <t>NB(305/2026)</t>
   </si>
   <si>
     <t>Krelifaoui mhamed</t>
   </si>
   <si>
-    <t>720 aadl bt 14 n08</t>
-  </si>
-  <si>
     <t>NB(355/2026)</t>
   </si>
   <si>
@@ -3185,102 +3155,66 @@
     <t>Dameche zoheir</t>
   </si>
   <si>
-    <t>720 aadl bt 11 n08</t>
-  </si>
-  <si>
     <t>NB(207/2026)</t>
   </si>
   <si>
     <t>Habat med</t>
   </si>
   <si>
-    <t>720 aadl bt 08 n13</t>
-  </si>
-  <si>
     <t>Atil hadjer</t>
   </si>
   <si>
-    <t>720 aadl bt 19 n25</t>
-  </si>
-  <si>
     <t>NB(233/2026)</t>
   </si>
   <si>
     <t>Kerbouci aek</t>
   </si>
   <si>
-    <t>720 aadl bt 07 n17</t>
-  </si>
-  <si>
     <t>NB(510/2025)</t>
   </si>
   <si>
     <t>Bourghaia khatir</t>
   </si>
   <si>
-    <t>720 aadl bt 19 n06</t>
-  </si>
-  <si>
     <t>NB(469/2025)</t>
   </si>
   <si>
     <t>Benslimane hannachi</t>
   </si>
   <si>
-    <t>720 aadl bt 05 n20</t>
-  </si>
-  <si>
     <t>NB(197/2026)</t>
   </si>
   <si>
     <t>Djillali rabea</t>
   </si>
   <si>
-    <t>720 aadl bt 01 n06</t>
-  </si>
-  <si>
     <t>NB(228/2026)</t>
   </si>
   <si>
     <t>Mokdad sid ahmed</t>
   </si>
   <si>
-    <t>720 aadl bt 11 n26</t>
-  </si>
-  <si>
     <t>NB(269/2026)</t>
   </si>
   <si>
     <t>Kassimi med</t>
   </si>
   <si>
-    <t>720 aadl bt 10 n25</t>
-  </si>
-  <si>
     <t>NB(237/2026)</t>
   </si>
   <si>
     <t>Debbah moussaab</t>
   </si>
   <si>
-    <t>720 aadl bt 19 n33</t>
-  </si>
-  <si>
     <t>NB(266/2026)</t>
   </si>
   <si>
     <t>Mazari kheira</t>
   </si>
   <si>
-    <t>720 aadl bt 9 n28</t>
-  </si>
-  <si>
     <t>Hachemi habib</t>
   </si>
   <si>
-    <t>720 aadl bt 13 n08</t>
-  </si>
-  <si>
     <t>NB(235/2026)</t>
   </si>
   <si>
@@ -3290,78 +3224,51 @@
     <t>NB(509/2025)</t>
   </si>
   <si>
-    <t>720 aadl bt 09 n14</t>
-  </si>
-  <si>
     <t>Zoulikha hafidha</t>
   </si>
   <si>
-    <t>720 aadl bt 15 n27</t>
-  </si>
-  <si>
     <t>NB(419/2025)</t>
   </si>
   <si>
     <t>Kadri med</t>
   </si>
   <si>
-    <t>720 aadl bt 04 n37</t>
-  </si>
-  <si>
     <t>NB(303/2026)</t>
   </si>
   <si>
     <t>Djamel med</t>
   </si>
   <si>
-    <t>720 aadl bt 05 n35</t>
-  </si>
-  <si>
     <t>NB(325/2026)</t>
   </si>
   <si>
     <t>Benzekkour benaissa</t>
   </si>
   <si>
-    <t>720 aadl bt 04 n01</t>
-  </si>
-  <si>
     <t>NB(211/2026)</t>
   </si>
   <si>
     <t>Yahiaoui hamid</t>
   </si>
   <si>
-    <t>720 aadl bt 16 n16</t>
-  </si>
-  <si>
     <t>NB(214/2026)</t>
   </si>
   <si>
     <t>Benkhaoua meriem</t>
   </si>
   <si>
-    <t>720 aadl bt 19 n36</t>
-  </si>
-  <si>
     <t>NB(472/2025)</t>
   </si>
   <si>
     <t>Benlakhdar aissa</t>
   </si>
   <si>
-    <t>720 aadl bt 08 n11</t>
-  </si>
-  <si>
     <t>NB(548/2025)</t>
   </si>
   <si>
     <t>Toumi boualem</t>
   </si>
   <si>
-    <t>06eme Tranche n31</t>
-  </si>
-  <si>
     <t>NB(186/2026)</t>
   </si>
   <si>
@@ -3396,6 +3303,72 @@
   </si>
   <si>
     <t>NB(312/2026)</t>
+  </si>
+  <si>
+    <t>NB(162/2026)</t>
+  </si>
+  <si>
+    <t>NB(338/2026)</t>
+  </si>
+  <si>
+    <t>Saidi a/rezzak</t>
+  </si>
+  <si>
+    <t>720 bloc 8 n 08</t>
+  </si>
+  <si>
+    <t>NB(628/2025)</t>
+  </si>
+  <si>
+    <t>Ammi med</t>
+  </si>
+  <si>
+    <t>720 bloc 6 n 04</t>
+  </si>
+  <si>
+    <t>Chabouti ismail</t>
+  </si>
+  <si>
+    <t>720 bloc 6 n 38</t>
+  </si>
+  <si>
+    <t>NB(212/2026)</t>
+  </si>
+  <si>
+    <t>Dali med</t>
+  </si>
+  <si>
+    <t>720 bloc 13 n 13</t>
+  </si>
+  <si>
+    <t>NB(358/2026)</t>
+  </si>
+  <si>
+    <t>Bahri hamza</t>
+  </si>
+  <si>
+    <t>720 bloc 08 n 29</t>
+  </si>
+  <si>
+    <t>NB(331/2026)</t>
+  </si>
+  <si>
+    <t>Yahiaoui soufiane</t>
+  </si>
+  <si>
+    <t>720 bloc 02 n 10</t>
+  </si>
+  <si>
+    <t>NB(360/2026)</t>
+  </si>
+  <si>
+    <t>Boudiaf houcine</t>
+  </si>
+  <si>
+    <t>720 bloc 03 n 15</t>
+  </si>
+  <si>
+    <t>NB(100/2026)</t>
   </si>
 </sst>
 </file>
@@ -22829,7 +22802,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -22869,7 +22842,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -23016,9 +22989,7 @@
       <c r="H10" s="18" t="s">
         <v>935</v>
       </c>
-      <c r="I10" s="20" t="s">
-        <v>936</v>
-      </c>
+      <c r="I10" s="20"/>
       <c r="J10" s="20"/>
       <c r="K10" s="4"/>
     </row>
@@ -23040,17 +23011,15 @@
         <v>46238</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="G11" s="17">
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>960</v>
-      </c>
-      <c r="I11" s="20" t="s">
-        <v>947</v>
-      </c>
+        <v>954</v>
+      </c>
+      <c r="I11" s="20"/>
       <c r="J11" s="20"/>
       <c r="K11" s="4"/>
     </row>
@@ -23072,17 +23041,15 @@
         <v>46238</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="G12" s="17">
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>962</v>
-      </c>
-      <c r="I12" s="20" t="s">
-        <v>963</v>
-      </c>
+        <v>956</v>
+      </c>
+      <c r="I12" s="20"/>
       <c r="J12" s="20"/>
       <c r="K12" s="4"/>
     </row>
@@ -23104,17 +23071,15 @@
         <v>46238</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="G13" s="17">
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>958</v>
-      </c>
-      <c r="I13" s="20" t="s">
-        <v>959</v>
-      </c>
+        <v>953</v>
+      </c>
+      <c r="I13" s="20"/>
       <c r="J13" s="20"/>
       <c r="K13" s="4"/>
     </row>
@@ -23136,17 +23101,15 @@
         <v>46238</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="G14" s="17">
         <v>1</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>940</v>
-      </c>
-      <c r="I14" s="20" t="s">
-        <v>941</v>
-      </c>
+        <v>938</v>
+      </c>
+      <c r="I14" s="20"/>
       <c r="J14" s="20"/>
       <c r="K14" s="4"/>
     </row>
@@ -23168,17 +23131,15 @@
         <v>46238</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>942</v>
+        <v>1021</v>
       </c>
       <c r="G15" s="17">
         <v>1</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>943</v>
-      </c>
-      <c r="I15" s="20" t="s">
-        <v>944</v>
-      </c>
+        <v>940</v>
+      </c>
+      <c r="I15" s="20"/>
       <c r="J15" s="20"/>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23199,17 +23160,15 @@
         <v>46238</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="G16" s="17">
         <v>1</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>937</v>
-      </c>
-      <c r="I16" s="20" t="s">
-        <v>938</v>
-      </c>
+        <v>936</v>
+      </c>
+      <c r="I16" s="20"/>
       <c r="J16" s="20"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23230,17 +23189,15 @@
         <v>46238</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="G17" s="17">
         <v>1</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>946</v>
-      </c>
-      <c r="I17" s="20" t="s">
-        <v>947</v>
-      </c>
+        <v>942</v>
+      </c>
+      <c r="I17" s="20"/>
       <c r="J17" s="20"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23261,17 +23218,15 @@
         <v>46238</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="G18" s="17">
         <v>1</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>948</v>
-      </c>
-      <c r="I18" s="20" t="s">
-        <v>947</v>
-      </c>
+        <v>943</v>
+      </c>
+      <c r="I18" s="20"/>
       <c r="J18" s="20"/>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23292,17 +23247,15 @@
         <v>46238</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="G19" s="17">
         <v>1</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>950</v>
-      </c>
-      <c r="I19" s="20" t="s">
-        <v>947</v>
-      </c>
+        <v>945</v>
+      </c>
+      <c r="I19" s="20"/>
       <c r="J19" s="20"/>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23323,17 +23276,15 @@
         <v>46238</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="G20" s="17">
         <v>1</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>952</v>
-      </c>
-      <c r="I20" s="20" t="s">
         <v>947</v>
       </c>
+      <c r="I20" s="20"/>
       <c r="J20" s="20"/>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23354,17 +23305,15 @@
         <v>46238</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="G21" s="17">
         <v>1</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>954</v>
-      </c>
-      <c r="I21" s="20" t="s">
-        <v>955</v>
-      </c>
+        <v>949</v>
+      </c>
+      <c r="I21" s="20"/>
       <c r="J21" s="20"/>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23373,7 +23322,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>284</v>
@@ -23385,17 +23334,15 @@
         <v>46239</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>967</v>
+        <v>960</v>
       </c>
       <c r="G22" s="17">
         <v>1</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>965</v>
-      </c>
-      <c r="I22" s="20" t="s">
-        <v>966</v>
-      </c>
+        <v>958</v>
+      </c>
+      <c r="I22" s="20"/>
       <c r="J22" s="20"/>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23404,7 +23351,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>284</v>
@@ -23416,17 +23363,15 @@
         <v>46239</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="G23" s="17">
         <v>1</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>968</v>
-      </c>
-      <c r="I23" s="20" t="s">
-        <v>966</v>
-      </c>
+        <v>961</v>
+      </c>
+      <c r="I23" s="20"/>
       <c r="J23" s="20"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23447,17 +23392,15 @@
         <v>46242</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="G24" s="17">
         <v>1</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>971</v>
-      </c>
-      <c r="I24" s="20" t="s">
-        <v>972</v>
-      </c>
+        <v>964</v>
+      </c>
+      <c r="I24" s="20"/>
       <c r="J24" s="20"/>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23478,17 +23421,15 @@
         <v>46243</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>975</v>
+        <v>966</v>
       </c>
       <c r="G25" s="17">
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>973</v>
-      </c>
-      <c r="I25" s="20" t="s">
-        <v>974</v>
-      </c>
+        <v>965</v>
+      </c>
+      <c r="I25" s="20"/>
       <c r="J25" s="20"/>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23509,17 +23450,15 @@
         <v>46243</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>978</v>
+        <v>968</v>
       </c>
       <c r="G26" s="17">
         <v>1</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>976</v>
-      </c>
-      <c r="I26" s="20" t="s">
-        <v>977</v>
-      </c>
+        <v>967</v>
+      </c>
+      <c r="I26" s="20"/>
       <c r="J26" s="20"/>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23540,17 +23479,15 @@
         <v>46244</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>979</v>
+        <v>969</v>
       </c>
       <c r="G27" s="17">
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>980</v>
-      </c>
-      <c r="I27" s="20" t="s">
-        <v>981</v>
-      </c>
+        <v>970</v>
+      </c>
+      <c r="I27" s="20"/>
       <c r="J27" s="20"/>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23577,11 +23514,9 @@
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>1038</v>
-      </c>
-      <c r="I28" s="20" t="s">
-        <v>1039</v>
-      </c>
+        <v>1008</v>
+      </c>
+      <c r="I28" s="20"/>
       <c r="J28" s="20"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23602,17 +23537,15 @@
         <v>46244</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>1013</v>
+        <v>991</v>
       </c>
       <c r="G29" s="17">
         <v>1</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>1011</v>
-      </c>
-      <c r="I29" s="20" t="s">
-        <v>1012</v>
-      </c>
+        <v>990</v>
+      </c>
+      <c r="I29" s="20"/>
       <c r="J29" s="20"/>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23633,17 +23566,15 @@
         <v>46244</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>1034</v>
+        <v>1005</v>
       </c>
       <c r="G30" s="17">
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>1032</v>
-      </c>
-      <c r="I30" s="20" t="s">
-        <v>1033</v>
-      </c>
+        <v>1004</v>
+      </c>
+      <c r="I30" s="20"/>
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23664,17 +23595,15 @@
         <v>46244</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>1028</v>
+        <v>1001</v>
       </c>
       <c r="G31" s="17">
         <v>1</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>1026</v>
-      </c>
-      <c r="I31" s="20" t="s">
-        <v>1027</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="I31" s="20"/>
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23695,17 +23624,15 @@
         <v>46244</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>1031</v>
+        <v>1003</v>
       </c>
       <c r="G32" s="17">
         <v>1</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>1029</v>
-      </c>
-      <c r="I32" s="20" t="s">
-        <v>1030</v>
-      </c>
+        <v>1002</v>
+      </c>
+      <c r="I32" s="20"/>
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23732,11 +23659,9 @@
         <v>1</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>1009</v>
-      </c>
-      <c r="I33" s="20" t="s">
-        <v>1010</v>
-      </c>
+        <v>989</v>
+      </c>
+      <c r="I33" s="20"/>
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23757,17 +23682,15 @@
         <v>46244</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>1025</v>
+        <v>999</v>
       </c>
       <c r="G34" s="17">
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>1023</v>
-      </c>
-      <c r="I34" s="20" t="s">
-        <v>1024</v>
-      </c>
+        <v>998</v>
+      </c>
+      <c r="I34" s="20"/>
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23788,17 +23711,15 @@
         <v>46244</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>1022</v>
+        <v>997</v>
       </c>
       <c r="G35" s="17">
         <v>1</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>1020</v>
-      </c>
-      <c r="I35" s="20" t="s">
-        <v>1021</v>
-      </c>
+        <v>996</v>
+      </c>
+      <c r="I35" s="20"/>
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23819,17 +23740,15 @@
         <v>46244</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>1019</v>
+        <v>995</v>
       </c>
       <c r="G36" s="17">
         <v>1</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>1017</v>
-      </c>
-      <c r="I36" s="20" t="s">
-        <v>1018</v>
-      </c>
+        <v>994</v>
+      </c>
+      <c r="I36" s="20"/>
       <c r="J36" s="4"/>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23850,17 +23769,15 @@
         <v>46244</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>1015</v>
+        <v>993</v>
       </c>
       <c r="G37" s="17">
         <v>1</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>1014</v>
-      </c>
-      <c r="I37" s="20" t="s">
-        <v>1016</v>
-      </c>
+        <v>992</v>
+      </c>
+      <c r="I37" s="20"/>
       <c r="J37" s="4"/>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23881,17 +23798,15 @@
         <v>46244</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>1037</v>
+        <v>1007</v>
       </c>
       <c r="G38" s="17">
         <v>1</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>1035</v>
-      </c>
-      <c r="I38" s="20" t="s">
-        <v>1036</v>
-      </c>
+        <v>1006</v>
+      </c>
+      <c r="I38" s="20"/>
       <c r="J38" s="4"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -23912,17 +23827,15 @@
         <v>46244</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>999</v>
+        <v>982</v>
       </c>
       <c r="G39" s="17">
         <v>1</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>997</v>
-      </c>
-      <c r="I39" s="20" t="s">
-        <v>998</v>
-      </c>
+        <v>981</v>
+      </c>
+      <c r="I39" s="20"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
@@ -23942,17 +23855,15 @@
         <v>46244</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="G40" s="17">
         <v>1</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>994</v>
-      </c>
-      <c r="I40" s="20" t="s">
-        <v>995</v>
-      </c>
+        <v>979</v>
+      </c>
+      <c r="I40" s="20"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
@@ -23972,17 +23883,15 @@
         <v>46244</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>1002</v>
+        <v>984</v>
       </c>
       <c r="G41" s="17">
         <v>1</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>1000</v>
-      </c>
-      <c r="I41" s="20" t="s">
-        <v>1001</v>
-      </c>
+        <v>983</v>
+      </c>
+      <c r="I41" s="20"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
@@ -24002,17 +23911,15 @@
         <v>46244</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>1005</v>
+        <v>986</v>
       </c>
       <c r="G42" s="17">
         <v>1</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>1003</v>
-      </c>
-      <c r="I42" s="20" t="s">
-        <v>1004</v>
-      </c>
+        <v>985</v>
+      </c>
+      <c r="I42" s="20"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
@@ -24032,17 +23939,15 @@
         <v>46244</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>1008</v>
+        <v>988</v>
       </c>
       <c r="G43" s="17">
         <v>1</v>
       </c>
       <c r="H43" s="18" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I43" s="20" t="s">
-        <v>1007</v>
-      </c>
+        <v>987</v>
+      </c>
+      <c r="I43" s="20"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="12">
@@ -24062,17 +23967,15 @@
         <v>46244</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>982</v>
+        <v>971</v>
       </c>
       <c r="G44" s="17">
         <v>1</v>
       </c>
       <c r="H44" s="18" t="s">
-        <v>983</v>
-      </c>
-      <c r="I44" s="20" t="s">
-        <v>984</v>
-      </c>
+        <v>972</v>
+      </c>
+      <c r="I44" s="20"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="12">
@@ -24092,17 +23995,15 @@
         <v>46244</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>990</v>
+        <v>976</v>
       </c>
       <c r="G45" s="17">
         <v>1</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>988</v>
-      </c>
-      <c r="I45" s="20" t="s">
-        <v>989</v>
-      </c>
+        <v>975</v>
+      </c>
+      <c r="I45" s="20"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="12">
@@ -24122,17 +24023,15 @@
         <v>46244</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>987</v>
+        <v>974</v>
       </c>
       <c r="G46" s="17">
         <v>1</v>
       </c>
       <c r="H46" s="18" t="s">
-        <v>985</v>
-      </c>
-      <c r="I46" s="20" t="s">
-        <v>986</v>
-      </c>
+        <v>973</v>
+      </c>
+      <c r="I46" s="20"/>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
@@ -24152,17 +24051,15 @@
         <v>46244</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>993</v>
+        <v>978</v>
       </c>
       <c r="G47" s="17">
         <v>1</v>
       </c>
       <c r="H47" s="18" t="s">
-        <v>991</v>
-      </c>
-      <c r="I47" s="20" t="s">
-        <v>992</v>
-      </c>
+        <v>977</v>
+      </c>
+      <c r="I47" s="20"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="12">
@@ -24182,16 +24079,16 @@
         <v>46246</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>1047</v>
+        <v>1016</v>
       </c>
       <c r="G48" s="17">
         <v>1</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>1045</v>
-      </c>
-      <c r="I48" s="29" t="s">
-        <v>1046</v>
+        <v>1014</v>
+      </c>
+      <c r="I48" s="20" t="s">
+        <v>1015</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -24212,16 +24109,16 @@
         <v>46246</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>1051</v>
+        <v>1020</v>
       </c>
       <c r="G49" s="17">
         <v>1</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>1050</v>
-      </c>
-      <c r="I49" s="29" t="s">
-        <v>955</v>
+        <v>1019</v>
+      </c>
+      <c r="I49" s="20" t="s">
+        <v>950</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -24242,16 +24139,16 @@
         <v>46246</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>1049</v>
+        <v>1018</v>
       </c>
       <c r="G50" s="17">
         <v>1</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>1048</v>
-      </c>
-      <c r="I50" s="29" t="s">
-        <v>966</v>
+        <v>1017</v>
+      </c>
+      <c r="I50" s="20" t="s">
+        <v>959</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -24272,16 +24169,16 @@
         <v>46246</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>1040</v>
+        <v>1009</v>
       </c>
       <c r="G51" s="17">
         <v>1</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>1041</v>
-      </c>
-      <c r="I51" s="29" t="s">
-        <v>1042</v>
+        <v>1010</v>
+      </c>
+      <c r="I51" s="20" t="s">
+        <v>1011</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -24302,16 +24199,16 @@
         <v>46246</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>1044</v>
+        <v>1013</v>
       </c>
       <c r="G52" s="17">
         <v>1</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>1043</v>
-      </c>
-      <c r="I52" s="29" t="s">
-        <v>955</v>
+        <v>1012</v>
+      </c>
+      <c r="I52" s="20" t="s">
+        <v>950</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -24319,106 +24216,210 @@
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B53" s="15"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="16"/>
+      <c r="B53" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D53" s="13">
+        <v>2026003698</v>
+      </c>
+      <c r="E53" s="15">
+        <v>46249</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>1022</v>
+      </c>
       <c r="G53" s="17">
         <v>1</v>
       </c>
-      <c r="H53" s="4"/>
+      <c r="H53" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I53" s="29" t="s">
+        <v>1024</v>
+      </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="12">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B54" s="15"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="16"/>
+      <c r="B54" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="13">
+        <v>2026144241</v>
+      </c>
+      <c r="E54" s="15">
+        <v>46249</v>
+      </c>
+      <c r="F54" s="16" t="s">
+        <v>1025</v>
+      </c>
       <c r="G54" s="17">
         <v>1</v>
       </c>
-      <c r="H54" s="4"/>
+      <c r="H54" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I54" s="29" t="s">
+        <v>1027</v>
+      </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="12">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B55" s="15"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="16"/>
+      <c r="B55" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D55" s="13">
+        <v>2026144242</v>
+      </c>
+      <c r="E55" s="15">
+        <v>46249</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>1036</v>
+      </c>
       <c r="G55" s="17">
         <v>1</v>
       </c>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
+      <c r="H55" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="I55" s="29" t="s">
+        <v>1035</v>
+      </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="12">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B56" s="15"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="16"/>
+      <c r="B56" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" s="13">
+        <v>2026144243</v>
+      </c>
+      <c r="E56" s="15">
+        <v>46249</v>
+      </c>
+      <c r="F56" s="16" t="s">
+        <v>1033</v>
+      </c>
       <c r="G56" s="17">
         <v>1</v>
       </c>
-      <c r="H56" s="4"/>
+      <c r="H56" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I56" s="29" t="s">
+        <v>1032</v>
+      </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="12">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B57" s="15"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="16"/>
+      <c r="B57" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" s="13">
+        <v>2026144244</v>
+      </c>
+      <c r="E57" s="15">
+        <v>46249</v>
+      </c>
+      <c r="F57" s="16" t="s">
+        <v>1030</v>
+      </c>
       <c r="G57" s="17">
         <v>1</v>
       </c>
-      <c r="H57" s="4"/>
+      <c r="H57" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I57" s="29" t="s">
+        <v>1029</v>
+      </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="12">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B58" s="15"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="16"/>
+      <c r="B58" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D58" s="13">
+        <v>2026144245</v>
+      </c>
+      <c r="E58" s="15">
+        <v>46249</v>
+      </c>
+      <c r="F58" s="16" t="s">
+        <v>1042</v>
+      </c>
       <c r="G58" s="17">
         <v>1</v>
       </c>
-      <c r="H58" s="4"/>
+      <c r="H58" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I58" s="29" t="s">
+        <v>1041</v>
+      </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="12">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B59" s="15"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="16"/>
+      <c r="B59" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" s="13">
+        <v>2026144250</v>
+      </c>
+      <c r="E59" s="15">
+        <v>46249</v>
+      </c>
+      <c r="F59" s="16" t="s">
+        <v>1039</v>
+      </c>
       <c r="G59" s="17">
         <v>1</v>
       </c>
-      <c r="H59" s="4"/>
+      <c r="H59" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I59" s="29" t="s">
+        <v>1038</v>
+      </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="12">
@@ -25297,9 +25298,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I52">
-    <sortCondition ref="E7:E52"/>
-    <sortCondition ref="D7:D52"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I59">
+    <sortCondition ref="E7:E59"/>
+    <sortCondition ref="D7:D59"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F8EEEC-275A-4BFD-BB48-1675F23CBE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BEB7BA3-0C4B-4EBF-A562-64C334139A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="1043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2176" uniqueCount="1065">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -3369,6 +3369,72 @@
   </si>
   <si>
     <t>NB(100/2026)</t>
+  </si>
+  <si>
+    <t>NB(314/2026)</t>
+  </si>
+  <si>
+    <t>Chergui med</t>
+  </si>
+  <si>
+    <t>03ème Tranche</t>
+  </si>
+  <si>
+    <t>Chergui fouad</t>
+  </si>
+  <si>
+    <t>NB(315/2026)</t>
+  </si>
+  <si>
+    <t>NB(164/2026)</t>
+  </si>
+  <si>
+    <t>Kefaifi ramdane</t>
+  </si>
+  <si>
+    <t>cité mohamedi</t>
+  </si>
+  <si>
+    <t>NB(242/2026)</t>
+  </si>
+  <si>
+    <t>Mag azzizi yahia</t>
+  </si>
+  <si>
+    <t>1058 bt 02 n2</t>
+  </si>
+  <si>
+    <t>Boudehina fatma</t>
+  </si>
+  <si>
+    <t>cité hantabli</t>
+  </si>
+  <si>
+    <t>NB(366/2026)</t>
+  </si>
+  <si>
+    <t>2026004065</t>
+  </si>
+  <si>
+    <t>NB(295/2026)</t>
+  </si>
+  <si>
+    <t>Mag benrebai el hadi</t>
+  </si>
+  <si>
+    <t>bd la republique</t>
+  </si>
+  <si>
+    <t>2026004061</t>
+  </si>
+  <si>
+    <t>NB(292/2026)</t>
+  </si>
+  <si>
+    <t>Ghacha kaddour</t>
+  </si>
+  <si>
+    <t>09eme tranche</t>
   </si>
 </sst>
 </file>
@@ -3533,7 +3599,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3616,9 +3682,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -22802,7 +22865,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -22842,7 +22905,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -24237,7 +24300,7 @@
       <c r="H53" s="4" t="s">
         <v>1023</v>
       </c>
-      <c r="I53" s="29" t="s">
+      <c r="I53" s="20" t="s">
         <v>1024</v>
       </c>
     </row>
@@ -24267,7 +24330,7 @@
       <c r="H54" s="4" t="s">
         <v>1026</v>
       </c>
-      <c r="I54" s="29" t="s">
+      <c r="I54" s="20" t="s">
         <v>1027</v>
       </c>
     </row>
@@ -24297,7 +24360,7 @@
       <c r="H55" s="4" t="s">
         <v>1034</v>
       </c>
-      <c r="I55" s="29" t="s">
+      <c r="I55" s="20" t="s">
         <v>1035</v>
       </c>
     </row>
@@ -24327,7 +24390,7 @@
       <c r="H56" s="4" t="s">
         <v>1031</v>
       </c>
-      <c r="I56" s="29" t="s">
+      <c r="I56" s="20" t="s">
         <v>1032</v>
       </c>
     </row>
@@ -24357,7 +24420,7 @@
       <c r="H57" s="4" t="s">
         <v>1028</v>
       </c>
-      <c r="I57" s="29" t="s">
+      <c r="I57" s="20" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -24387,7 +24450,7 @@
       <c r="H58" s="4" t="s">
         <v>1040</v>
       </c>
-      <c r="I58" s="29" t="s">
+      <c r="I58" s="20" t="s">
         <v>1041</v>
       </c>
     </row>
@@ -24417,7 +24480,7 @@
       <c r="H59" s="4" t="s">
         <v>1037</v>
       </c>
-      <c r="I59" s="29" t="s">
+      <c r="I59" s="20" t="s">
         <v>1038</v>
       </c>
     </row>
@@ -24426,108 +24489,210 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B60" s="15"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="16"/>
+      <c r="B60" s="15" t="s">
+        <v>630</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D60" s="13">
+        <v>2026003697</v>
+      </c>
+      <c r="E60" s="15">
+        <v>46251</v>
+      </c>
+      <c r="F60" s="16" t="s">
+        <v>1043</v>
+      </c>
       <c r="G60" s="17">
         <v>1</v>
       </c>
-      <c r="H60" s="4"/>
+      <c r="H60" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I60" s="20" t="s">
+        <v>1045</v>
+      </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="12">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B61" s="15"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="16"/>
+      <c r="B61" s="15" t="s">
+        <v>630</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D61" s="13">
+        <v>2026003700</v>
+      </c>
+      <c r="E61" s="15">
+        <v>46251</v>
+      </c>
+      <c r="F61" s="16" t="s">
+        <v>1047</v>
+      </c>
       <c r="G61" s="17">
         <v>1</v>
       </c>
-      <c r="H61" s="4"/>
+      <c r="H61" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I61" s="20" t="s">
+        <v>1045</v>
+      </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="12">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B62" s="15"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="16"/>
+      <c r="B62" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D62" s="13">
+        <v>2026003696</v>
+      </c>
+      <c r="E62" s="15">
+        <v>46253</v>
+      </c>
+      <c r="F62" s="16" t="s">
+        <v>1051</v>
+      </c>
       <c r="G62" s="17">
         <v>1</v>
       </c>
-      <c r="H62" s="4"/>
+      <c r="H62" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="I62" s="20" t="s">
+        <v>1053</v>
+      </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="12">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B63" s="15"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="16"/>
+      <c r="B63" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D63" s="13">
+        <v>2026004062</v>
+      </c>
+      <c r="E63" s="15">
+        <v>46253</v>
+      </c>
+      <c r="F63" s="16" t="s">
+        <v>1056</v>
+      </c>
       <c r="G63" s="17">
         <v>1</v>
       </c>
-      <c r="H63" s="4"/>
-      <c r="I63" s="20"/>
+      <c r="H63" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="I63" s="20" t="s">
+        <v>1055</v>
+      </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="12">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B64" s="15"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="15"/>
-      <c r="F64" s="16"/>
+      <c r="B64" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D64" s="13">
+        <v>2026144247</v>
+      </c>
+      <c r="E64" s="15">
+        <v>46253</v>
+      </c>
+      <c r="F64" s="16" t="s">
+        <v>1048</v>
+      </c>
       <c r="G64" s="17">
         <v>1</v>
       </c>
-      <c r="H64" s="4"/>
+      <c r="H64" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I64" s="20" t="s">
+        <v>1050</v>
+      </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="12">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B65" s="15"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="16"/>
+      <c r="B65" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D65" s="14" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E65" s="15">
+        <v>46253</v>
+      </c>
+      <c r="F65" s="16" t="s">
+        <v>1062</v>
+      </c>
       <c r="G65" s="17">
         <v>1</v>
       </c>
-      <c r="H65" s="4"/>
-      <c r="I65" s="20"/>
+      <c r="H65" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="I65" s="20" t="s">
+        <v>1064</v>
+      </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="12">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B66" s="15"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="16"/>
+      <c r="B66" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E66" s="15">
+        <v>46253</v>
+      </c>
+      <c r="F66" s="16" t="s">
+        <v>1058</v>
+      </c>
       <c r="G66" s="17">
         <v>1</v>
       </c>
-      <c r="H66" s="4"/>
-      <c r="I66" s="20"/>
+      <c r="H66" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="I66" s="20" t="s">
+        <v>1060</v>
+      </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="12">
@@ -25298,9 +25463,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I59">
-    <sortCondition ref="E7:E59"/>
-    <sortCondition ref="D7:D59"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I66">
+    <sortCondition ref="E7:E66"/>
+    <sortCondition ref="D7:D66"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BEB7BA3-0C4B-4EBF-A562-64C334139A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91139A0-FB32-442B-A820-B267A01051FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2176" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2218" uniqueCount="1092">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -3435,6 +3435,87 @@
   </si>
   <si>
     <t>09eme tranche</t>
+  </si>
+  <si>
+    <t>2026144332</t>
+  </si>
+  <si>
+    <t>NB(559/2025)</t>
+  </si>
+  <si>
+    <t>Djouabri akila</t>
+  </si>
+  <si>
+    <t>720 bloc 04 n 19</t>
+  </si>
+  <si>
+    <t>2026144333</t>
+  </si>
+  <si>
+    <t>Zemirline malik</t>
+  </si>
+  <si>
+    <t>720 bloc 10 n 36</t>
+  </si>
+  <si>
+    <t>NB(368/2026)</t>
+  </si>
+  <si>
+    <t>2026144335</t>
+  </si>
+  <si>
+    <t>Guessab hakim</t>
+  </si>
+  <si>
+    <t>720 bloc 04 n 14</t>
+  </si>
+  <si>
+    <t>NB(367/2026)</t>
+  </si>
+  <si>
+    <t>2026144246</t>
+  </si>
+  <si>
+    <t>Bendahib el hachemi</t>
+  </si>
+  <si>
+    <t>720 bloc 16 n 33</t>
+  </si>
+  <si>
+    <t>NB(356/2026)</t>
+  </si>
+  <si>
+    <t>2026144249</t>
+  </si>
+  <si>
+    <t>Memmi aek</t>
+  </si>
+  <si>
+    <t>720 bloc 05 n 24</t>
+  </si>
+  <si>
+    <t>NB(357/2026)</t>
+  </si>
+  <si>
+    <t>2026144336</t>
+  </si>
+  <si>
+    <t>Ferrah med</t>
+  </si>
+  <si>
+    <t>720 bloc 12 n 04</t>
+  </si>
+  <si>
+    <t>NB(425/2026)</t>
+  </si>
+  <si>
+    <t>2026144248</t>
+  </si>
+  <si>
+    <t>Hamimeche hichem</t>
+  </si>
+  <si>
+    <t>720 bloc 13 n 40</t>
   </si>
 </sst>
 </file>
@@ -22865,7 +22946,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -22905,7 +22986,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -24699,108 +24780,210 @@
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B67" s="15"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="16"/>
+      <c r="B67" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E67" s="15">
+        <v>46256</v>
+      </c>
+      <c r="F67" s="16" t="s">
+        <v>1080</v>
+      </c>
       <c r="G67" s="17">
         <v>1</v>
       </c>
-      <c r="H67" s="4"/>
+      <c r="H67" s="4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I67" s="20" t="s">
+        <v>1079</v>
+      </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="12">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B68" s="15"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="15"/>
-      <c r="F68" s="16"/>
+      <c r="B68" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E68" s="15">
+        <v>46256</v>
+      </c>
+      <c r="F68" s="16" t="s">
+        <v>1088</v>
+      </c>
       <c r="G68" s="17">
         <v>1</v>
       </c>
-      <c r="H68" s="4"/>
+      <c r="H68" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="I68" s="20" t="s">
+        <v>1091</v>
+      </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="12">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B69" s="15"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="15"/>
-      <c r="F69" s="16"/>
+      <c r="B69" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" s="14" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E69" s="15">
+        <v>46256</v>
+      </c>
+      <c r="F69" s="16" t="s">
+        <v>1084</v>
+      </c>
       <c r="G69" s="17">
         <v>1</v>
       </c>
-      <c r="H69" s="4"/>
-      <c r="I69" s="20"/>
+      <c r="H69" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I69" s="20" t="s">
+        <v>1083</v>
+      </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="12">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B70" s="15"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="16"/>
+      <c r="B70" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E70" s="15">
+        <v>46256</v>
+      </c>
+      <c r="F70" s="16" t="s">
+        <v>1066</v>
+      </c>
       <c r="G70" s="17">
         <v>1</v>
       </c>
-      <c r="H70" s="4"/>
+      <c r="H70" s="4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="I70" s="20" t="s">
+        <v>1068</v>
+      </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="12">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="13"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="16"/>
+      <c r="B71" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E71" s="15">
+        <v>46256</v>
+      </c>
+      <c r="F71" s="16" t="s">
+        <v>1072</v>
+      </c>
       <c r="G71" s="17">
         <v>1</v>
       </c>
-      <c r="H71" s="4"/>
-      <c r="I71" s="20"/>
+      <c r="H71" s="4" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I71" s="20" t="s">
+        <v>1071</v>
+      </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="12">
         <f t="shared" ref="A72:A117" si="1">+A71+1</f>
         <v>66</v>
       </c>
-      <c r="B72" s="15"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="16"/>
+      <c r="B72" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E72" s="15">
+        <v>46256</v>
+      </c>
+      <c r="F72" s="16" t="s">
+        <v>1076</v>
+      </c>
       <c r="G72" s="17">
         <v>1</v>
       </c>
-      <c r="H72" s="4"/>
-      <c r="I72" s="20"/>
+      <c r="H72" s="4" t="s">
+        <v>1074</v>
+      </c>
+      <c r="I72" s="20" t="s">
+        <v>1075</v>
+      </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="12">
         <f t="shared" si="1"/>
         <v>67</v>
       </c>
-      <c r="B73" s="15"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="15"/>
-      <c r="F73" s="16"/>
+      <c r="B73" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D73" s="14" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E73" s="15">
+        <v>46256</v>
+      </c>
+      <c r="F73" s="16" t="s">
+        <v>1088</v>
+      </c>
       <c r="G73" s="17">
         <v>1</v>
       </c>
-      <c r="H73" s="4"/>
+      <c r="H73" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="I73" s="20" t="s">
+        <v>1087</v>
+      </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="12">
@@ -25463,9 +25646,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I66">
-    <sortCondition ref="E7:E66"/>
-    <sortCondition ref="D7:D66"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I73">
+    <sortCondition ref="E7:E73"/>
+    <sortCondition ref="D7:D73"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91139A0-FB32-442B-A820-B267A01051FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9948C1DA-829B-4D83-87AE-02AFFF32305A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2218" uniqueCount="1092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2266" uniqueCount="1125">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -3516,6 +3516,105 @@
   </si>
   <si>
     <t>720 bloc 13 n 40</t>
+  </si>
+  <si>
+    <t>40/49</t>
+  </si>
+  <si>
+    <t>14855529</t>
+  </si>
+  <si>
+    <t>NB(289/2026)</t>
+  </si>
+  <si>
+    <t>Sarl Sonomak</t>
+  </si>
+  <si>
+    <t>zone industrielle</t>
+  </si>
+  <si>
+    <t>2026144337</t>
+  </si>
+  <si>
+    <t>NB(382/2026)</t>
+  </si>
+  <si>
+    <t>Sedari faiza</t>
+  </si>
+  <si>
+    <t>500 aadl bt 14 n22</t>
+  </si>
+  <si>
+    <t>2026144339</t>
+  </si>
+  <si>
+    <t>Laissaoui riadh</t>
+  </si>
+  <si>
+    <t>720 bloc 10 n 27</t>
+  </si>
+  <si>
+    <t>NB(337/2026)</t>
+  </si>
+  <si>
+    <t>2026144340</t>
+  </si>
+  <si>
+    <t>Madani khadidja</t>
+  </si>
+  <si>
+    <t>720 bloc 05 n 15</t>
+  </si>
+  <si>
+    <t>NB(374/2026)</t>
+  </si>
+  <si>
+    <t>2026144338</t>
+  </si>
+  <si>
+    <t>Agueb salah</t>
+  </si>
+  <si>
+    <t>720 bloc 03 n 04</t>
+  </si>
+  <si>
+    <t>NB(371/2026)</t>
+  </si>
+  <si>
+    <t>Abdelmalek med</t>
+  </si>
+  <si>
+    <t>720 bloc 05 n 05</t>
+  </si>
+  <si>
+    <t>2026144331</t>
+  </si>
+  <si>
+    <t>NB(372/2026)</t>
+  </si>
+  <si>
+    <t>2026144263</t>
+  </si>
+  <si>
+    <t>Mini aek</t>
+  </si>
+  <si>
+    <t>720 bloc 04 n 20</t>
+  </si>
+  <si>
+    <t>NB(386/2026)</t>
+  </si>
+  <si>
+    <t>2026144262</t>
+  </si>
+  <si>
+    <t>Ziani djelloul</t>
+  </si>
+  <si>
+    <t>720 bloc 08 n 37</t>
+  </si>
+  <si>
+    <t>NB(388/2026)</t>
   </si>
 </sst>
 </file>
@@ -3680,7 +3779,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3763,6 +3862,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -22946,7 +23048,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -22986,7 +23088,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -24990,122 +25092,242 @@
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
-      <c r="B74" s="15"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="15"/>
-      <c r="F74" s="16"/>
+      <c r="B74" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E74" s="15">
+        <v>46258</v>
+      </c>
+      <c r="F74" s="16" t="s">
+        <v>1094</v>
+      </c>
       <c r="G74" s="17">
         <v>1</v>
       </c>
-      <c r="H74" s="4"/>
+      <c r="H74" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="I74" s="20" t="s">
+        <v>1096</v>
+      </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="12">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
-      <c r="B75" s="15"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="15"/>
-      <c r="F75" s="16"/>
+      <c r="B75" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" s="14" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E75" s="15">
+        <v>46260</v>
+      </c>
+      <c r="F75" s="16" t="s">
+        <v>1124</v>
+      </c>
       <c r="G75" s="17">
         <v>1</v>
       </c>
-      <c r="H75" s="4"/>
+      <c r="H75" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="I75" s="20" t="s">
+        <v>1123</v>
+      </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="12">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="B76" s="15"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="15"/>
-      <c r="F76" s="16"/>
+      <c r="B76" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" s="14" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E76" s="15">
+        <v>46260</v>
+      </c>
+      <c r="F76" s="16" t="s">
+        <v>1120</v>
+      </c>
       <c r="G76" s="17">
         <v>1</v>
       </c>
-      <c r="H76" s="4"/>
+      <c r="H76" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="I76" s="20" t="s">
+        <v>1119</v>
+      </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="12">
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
-      <c r="B77" s="15"/>
-      <c r="C77" s="13"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="16"/>
+      <c r="B77" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D77" s="14" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E77" s="15">
+        <v>46260</v>
+      </c>
+      <c r="F77" s="16" t="s">
+        <v>1116</v>
+      </c>
       <c r="G77" s="17">
         <v>1</v>
       </c>
-      <c r="H77" s="4"/>
+      <c r="H77" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="I77" s="20" t="s">
+        <v>1114</v>
+      </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="12">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
-      <c r="B78" s="15"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="15"/>
-      <c r="F78" s="16"/>
+      <c r="B78" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E78" s="15">
+        <v>46260</v>
+      </c>
+      <c r="F78" s="16" t="s">
+        <v>1098</v>
+      </c>
       <c r="G78" s="17">
         <v>1</v>
       </c>
-      <c r="H78" s="4"/>
+      <c r="H78" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I78" s="29" t="s">
+        <v>1100</v>
+      </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="12">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
-      <c r="B79" s="15"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="16"/>
+      <c r="B79" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D79" s="14" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E79" s="15">
+        <v>46260</v>
+      </c>
+      <c r="F79" s="16" t="s">
+        <v>1112</v>
+      </c>
       <c r="G79" s="17">
         <v>1</v>
       </c>
-      <c r="H79" s="4"/>
+      <c r="H79" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I79" s="20" t="s">
+        <v>1111</v>
+      </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="12">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
-      <c r="B80" s="15"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="15"/>
-      <c r="F80" s="16"/>
+      <c r="B80" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D80" s="14" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E80" s="15">
+        <v>46260</v>
+      </c>
+      <c r="F80" s="16" t="s">
+        <v>1104</v>
+      </c>
       <c r="G80" s="17">
         <v>1</v>
       </c>
-      <c r="H80" s="4"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H80" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="I80" s="20" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="12">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
-      <c r="B81" s="15"/>
-      <c r="C81" s="13"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="15"/>
-      <c r="F81" s="16"/>
+      <c r="B81" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E81" s="15">
+        <v>46260</v>
+      </c>
+      <c r="F81" s="16" t="s">
+        <v>1108</v>
+      </c>
       <c r="G81" s="17">
         <v>1</v>
       </c>
-      <c r="H81" s="4"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H81" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I81" s="20" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="12">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -25120,7 +25342,7 @@
       </c>
       <c r="H82" s="4"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="12">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -25135,7 +25357,7 @@
       </c>
       <c r="H83" s="4"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="12">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -25150,7 +25372,7 @@
       </c>
       <c r="H84" s="4"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="12">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -25165,7 +25387,7 @@
       </c>
       <c r="H85" s="4"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="12">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -25180,7 +25402,7 @@
       </c>
       <c r="H86" s="4"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="12">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -25195,7 +25417,7 @@
       </c>
       <c r="H87" s="4"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="12">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -25210,7 +25432,7 @@
       </c>
       <c r="H88" s="4"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="12">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -25225,7 +25447,7 @@
       </c>
       <c r="H89" s="4"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="12">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -25240,7 +25462,7 @@
       </c>
       <c r="H90" s="4"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="12">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -25255,7 +25477,7 @@
       </c>
       <c r="H91" s="4"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="12">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -25270,7 +25492,7 @@
       </c>
       <c r="H92" s="4"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="12">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -25285,7 +25507,7 @@
       </c>
       <c r="H93" s="4"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="12">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -25300,7 +25522,7 @@
       </c>
       <c r="H94" s="4"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="12">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -25315,7 +25537,7 @@
       </c>
       <c r="H95" s="4"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="12">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -25646,9 +25868,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I73">
-    <sortCondition ref="E7:E73"/>
-    <sortCondition ref="D7:D73"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I81">
+    <sortCondition ref="E7:E81"/>
+    <sortCondition ref="D7:D81"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9948C1DA-829B-4D83-87AE-02AFFF32305A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDCDEFB0-D487-4725-8F98-2EADC234863D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2266" uniqueCount="1125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2296" uniqueCount="1145">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -3615,6 +3615,66 @@
   </si>
   <si>
     <t>NB(388/2026)</t>
+  </si>
+  <si>
+    <t>2026144268</t>
+  </si>
+  <si>
+    <t>NB(716/2025)</t>
+  </si>
+  <si>
+    <t>Mokrane hamid</t>
+  </si>
+  <si>
+    <t>720 bloc 01 n 13</t>
+  </si>
+  <si>
+    <t>2026144270</t>
+  </si>
+  <si>
+    <t>Ait hakim</t>
+  </si>
+  <si>
+    <t>720 bloc 10 n 23</t>
+  </si>
+  <si>
+    <t>NB(141/2026)</t>
+  </si>
+  <si>
+    <t>2026144265</t>
+  </si>
+  <si>
+    <t>Dameche med cherif</t>
+  </si>
+  <si>
+    <t>720 bloc 06 n 34</t>
+  </si>
+  <si>
+    <t>NB(485/2025)</t>
+  </si>
+  <si>
+    <t>2026144261</t>
+  </si>
+  <si>
+    <t>Laidani billel</t>
+  </si>
+  <si>
+    <t>720 bloc 09 n 35</t>
+  </si>
+  <si>
+    <t>NB(392/2026)</t>
+  </si>
+  <si>
+    <t>2026144264</t>
+  </si>
+  <si>
+    <t>Foudil houcine</t>
+  </si>
+  <si>
+    <t>720 bloc 04 n 11</t>
+  </si>
+  <si>
+    <t>NB(601/2025)</t>
   </si>
 </sst>
 </file>
@@ -3779,7 +3839,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3862,9 +3922,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -23048,7 +23105,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -23088,7 +23145,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -25233,7 +25290,7 @@
       <c r="H78" s="4" t="s">
         <v>1099</v>
       </c>
-      <c r="I78" s="29" t="s">
+      <c r="I78" s="20" t="s">
         <v>1100</v>
       </c>
     </row>
@@ -25332,75 +25389,150 @@
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
-      <c r="B82" s="15"/>
-      <c r="C82" s="13"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="15"/>
-      <c r="F82" s="16"/>
+      <c r="B82" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E82" s="15">
+        <v>46263</v>
+      </c>
+      <c r="F82" s="16" t="s">
+        <v>1140</v>
+      </c>
       <c r="G82" s="17">
         <v>1</v>
       </c>
-      <c r="H82" s="4"/>
+      <c r="H82" s="4" t="s">
+        <v>1138</v>
+      </c>
+      <c r="I82" s="20" t="s">
+        <v>1139</v>
+      </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="12">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
-      <c r="B83" s="15"/>
-      <c r="C83" s="13"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="15"/>
-      <c r="F83" s="16"/>
+      <c r="B83" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E83" s="15">
+        <v>46263</v>
+      </c>
+      <c r="F83" s="16" t="s">
+        <v>1144</v>
+      </c>
       <c r="G83" s="17">
         <v>1</v>
       </c>
-      <c r="H83" s="4"/>
+      <c r="H83" s="4" t="s">
+        <v>1142</v>
+      </c>
+      <c r="I83" s="20" t="s">
+        <v>1143</v>
+      </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="12">
         <f t="shared" si="1"/>
         <v>78</v>
       </c>
-      <c r="B84" s="15"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="15"/>
-      <c r="F84" s="16"/>
+      <c r="B84" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D84" s="14" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E84" s="15">
+        <v>46263</v>
+      </c>
+      <c r="F84" s="16" t="s">
+        <v>1136</v>
+      </c>
       <c r="G84" s="17">
         <v>1</v>
       </c>
-      <c r="H84" s="4"/>
+      <c r="H84" s="4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="I84" s="20" t="s">
+        <v>1135</v>
+      </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="12">
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
-      <c r="B85" s="15"/>
-      <c r="C85" s="13"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="15"/>
-      <c r="F85" s="16"/>
+      <c r="B85" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D85" s="14" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E85" s="15">
+        <v>46263</v>
+      </c>
+      <c r="F85" s="16" t="s">
+        <v>1126</v>
+      </c>
       <c r="G85" s="17">
         <v>1</v>
       </c>
-      <c r="H85" s="4"/>
+      <c r="H85" s="4" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I85" s="20" t="s">
+        <v>1128</v>
+      </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="12">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="B86" s="15"/>
-      <c r="C86" s="13"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="15"/>
-      <c r="F86" s="16"/>
+      <c r="B86" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D86" s="14" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E86" s="15">
+        <v>46263</v>
+      </c>
+      <c r="F86" s="16" t="s">
+        <v>1132</v>
+      </c>
       <c r="G86" s="17">
         <v>1</v>
       </c>
-      <c r="H86" s="4"/>
+      <c r="H86" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="I86" s="20" t="s">
+        <v>1131</v>
+      </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="12">
@@ -25868,9 +26000,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I81">
-    <sortCondition ref="E7:E81"/>
-    <sortCondition ref="D7:D81"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I86">
+    <sortCondition ref="E7:E86"/>
+    <sortCondition ref="D7:D86"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDCDEFB0-D487-4725-8F98-2EADC234863D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A22C92-D5D3-4BEC-9835-F178368411F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2296" uniqueCount="1145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2302" uniqueCount="1148">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -3675,6 +3675,15 @@
   </si>
   <si>
     <t>NB(601/2025)</t>
+  </si>
+  <si>
+    <t>2026004066</t>
+  </si>
+  <si>
+    <t>Parc bakhti</t>
+  </si>
+  <si>
+    <t>NB(225/2024)</t>
   </si>
 </sst>
 </file>
@@ -3839,7 +3848,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3922,6 +3931,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -23105,7 +23117,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -23145,7 +23157,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -25390,28 +25402,28 @@
         <v>76</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>19</v>
+        <v>718</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>18</v>
+        <v>284</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="E82" s="15">
         <v>46263</v>
       </c>
       <c r="F82" s="16" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="G82" s="17">
         <v>1</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>1138</v>
-      </c>
-      <c r="I82" s="20" t="s">
-        <v>1139</v>
+        <v>1146</v>
+      </c>
+      <c r="I82" s="29" t="s">
+        <v>1055</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
@@ -25426,22 +25438,22 @@
         <v>18</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="E83" s="15">
         <v>46263</v>
       </c>
       <c r="F83" s="16" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="G83" s="17">
         <v>1</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="I83" s="20" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -25456,22 +25468,22 @@
         <v>18</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="E84" s="15">
         <v>46263</v>
       </c>
       <c r="F84" s="16" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="G84" s="17">
         <v>1</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="I84" s="20" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
@@ -25486,22 +25498,22 @@
         <v>18</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="E85" s="15">
         <v>46263</v>
       </c>
       <c r="F85" s="16" t="s">
-        <v>1126</v>
+        <v>1136</v>
       </c>
       <c r="G85" s="17">
         <v>1</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>1127</v>
+        <v>1134</v>
       </c>
       <c r="I85" s="20" t="s">
-        <v>1128</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -25516,22 +25528,22 @@
         <v>18</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="E86" s="15">
         <v>46263</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="G86" s="17">
         <v>1</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="I86" s="20" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
@@ -25539,15 +25551,30 @@
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
-      <c r="B87" s="15"/>
-      <c r="C87" s="13"/>
-      <c r="D87" s="14"/>
-      <c r="E87" s="15"/>
-      <c r="F87" s="16"/>
+      <c r="B87" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D87" s="14" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E87" s="15">
+        <v>46263</v>
+      </c>
+      <c r="F87" s="16" t="s">
+        <v>1132</v>
+      </c>
       <c r="G87" s="17">
         <v>1</v>
       </c>
-      <c r="H87" s="4"/>
+      <c r="H87" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="I87" s="20" t="s">
+        <v>1131</v>
+      </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="12">
@@ -26000,9 +26027,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I86">
-    <sortCondition ref="E7:E86"/>
-    <sortCondition ref="D7:D86"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I87">
+    <sortCondition ref="E7:E87"/>
+    <sortCondition ref="D7:D87"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A22C92-D5D3-4BEC-9835-F178368411F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E35BEB-9A3C-4E91-B58F-34BA990C9446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2302" uniqueCount="1148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2312" uniqueCount="1154">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -3684,6 +3684,24 @@
   </si>
   <si>
     <t>NB(225/2024)</t>
+  </si>
+  <si>
+    <t>2026144269</t>
+  </si>
+  <si>
+    <t>NB(017/2025)</t>
+  </si>
+  <si>
+    <t>Zoulikha kais</t>
+  </si>
+  <si>
+    <t>diar echams</t>
+  </si>
+  <si>
+    <t>B21520</t>
+  </si>
+  <si>
+    <t>2026144267</t>
   </si>
 </sst>
 </file>
@@ -3848,7 +3866,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3931,9 +3949,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -23095,7 +23110,7 @@
       <c r="J2" s="25"/>
       <c r="K2" s="6">
         <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -23117,7 +23132,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -23157,7 +23172,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -25422,7 +25437,7 @@
       <c r="H82" s="4" t="s">
         <v>1146</v>
       </c>
-      <c r="I82" s="29" t="s">
+      <c r="I82" s="20" t="s">
         <v>1055</v>
       </c>
     </row>
@@ -25581,11 +25596,21 @@
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
-      <c r="B88" s="15"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="15"/>
-      <c r="F88" s="16"/>
+      <c r="B88" s="15" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" s="14" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E88" s="15">
+        <v>46264</v>
+      </c>
+      <c r="F88" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="G88" s="17">
         <v>1</v>
       </c>
@@ -25596,15 +25621,30 @@
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
-      <c r="B89" s="15"/>
-      <c r="C89" s="13"/>
-      <c r="D89" s="14"/>
-      <c r="E89" s="15"/>
-      <c r="F89" s="16"/>
+      <c r="B89" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D89" s="14" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E89" s="15">
+        <v>46264</v>
+      </c>
+      <c r="F89" s="16" t="s">
+        <v>1149</v>
+      </c>
       <c r="G89" s="17">
         <v>1</v>
       </c>
-      <c r="H89" s="4"/>
+      <c r="H89" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="I89" s="20" t="s">
+        <v>1151</v>
+      </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="12">
@@ -26027,9 +26067,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I87">
-    <sortCondition ref="E7:E87"/>
-    <sortCondition ref="D7:D87"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I89">
+    <sortCondition ref="E7:E89"/>
+    <sortCondition ref="D7:D89"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E35BEB-9A3C-4E91-B58F-34BA990C9446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3684D0C3-263F-4BB6-80F7-62B278C4578D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2312" uniqueCount="1154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2324" uniqueCount="1162">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -3702,6 +3702,30 @@
   </si>
   <si>
     <t>2026144267</t>
+  </si>
+  <si>
+    <t>2026004067</t>
+  </si>
+  <si>
+    <t>NB(383/2026)</t>
+  </si>
+  <si>
+    <t>Bouziani hafsa</t>
+  </si>
+  <si>
+    <t>djenane toubal</t>
+  </si>
+  <si>
+    <t>2026004068</t>
+  </si>
+  <si>
+    <t>Mag belhadj aek</t>
+  </si>
+  <si>
+    <t>cité cheriet bt 26 02</t>
+  </si>
+  <si>
+    <t>NB(247/2026)</t>
   </si>
 </sst>
 </file>
@@ -3866,7 +3890,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3949,6 +3973,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -23132,7 +23159,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -23172,7 +23199,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -25651,30 +25678,60 @@
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
-      <c r="B90" s="15"/>
-      <c r="C90" s="13"/>
-      <c r="D90" s="14"/>
-      <c r="E90" s="15"/>
-      <c r="F90" s="16"/>
+      <c r="B90" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E90" s="15">
+        <v>46265</v>
+      </c>
+      <c r="F90" s="16" t="s">
+        <v>1155</v>
+      </c>
       <c r="G90" s="17">
         <v>1</v>
       </c>
-      <c r="H90" s="4"/>
+      <c r="H90" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="I90" s="29" t="s">
+        <v>1157</v>
+      </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="12">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-      <c r="B91" s="15"/>
-      <c r="C91" s="13"/>
-      <c r="D91" s="14"/>
-      <c r="E91" s="15"/>
-      <c r="F91" s="16"/>
+      <c r="B91" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D91" s="14" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E91" s="15">
+        <v>46265</v>
+      </c>
+      <c r="F91" s="16" t="s">
+        <v>1161</v>
+      </c>
       <c r="G91" s="17">
         <v>1</v>
       </c>
-      <c r="H91" s="4"/>
+      <c r="H91" s="4" t="s">
+        <v>1159</v>
+      </c>
+      <c r="I91" s="29" t="s">
+        <v>1160</v>
+      </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="12">
@@ -26067,9 +26124,9 @@
       <c r="H117" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I89">
-    <sortCondition ref="E7:E89"/>
-    <sortCondition ref="D7:D89"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I91">
+    <sortCondition ref="E7:E91"/>
+    <sortCondition ref="D7:D91"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="A5:F5"/>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3684D0C3-263F-4BB6-80F7-62B278C4578D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2530064F-CE52-4801-872F-D1010C321307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Janvier 2026 " sheetId="2" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Juin 2026" sheetId="6" r:id="rId6"/>
     <sheet name="Juillet 2026" sheetId="7" r:id="rId7"/>
     <sheet name="Aout 2026" sheetId="8" r:id="rId8"/>
+    <sheet name="Septembre 2026" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Aout 2026'!$1:$6</definedName>
@@ -31,6 +32,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Juin 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Mai 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mars 2026'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Septembre 2026'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2324" uniqueCount="1162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2367" uniqueCount="1176">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -3726,6 +3728,69 @@
   </si>
   <si>
     <t>NB(247/2026)</t>
+  </si>
+  <si>
+    <r>
+      <t>Mois de Septembre</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <t>B21035</t>
+  </si>
+  <si>
+    <t>Sahraoui khaled</t>
+  </si>
+  <si>
+    <t>cite 720 bt 17 n22</t>
+  </si>
+  <si>
+    <t>NB(398/2026)</t>
+  </si>
+  <si>
+    <t>Fergani abdenasser</t>
+  </si>
+  <si>
+    <t>cite 720 bt 04 n02</t>
+  </si>
+  <si>
+    <t>NB(402/2026)</t>
+  </si>
+  <si>
+    <t>Abidi mouni</t>
+  </si>
+  <si>
+    <t>cite 720 bt 08 n07</t>
+  </si>
+  <si>
+    <t>NB(391/2026)</t>
+  </si>
+  <si>
+    <t>Hassam ahmed</t>
+  </si>
+  <si>
+    <t>ain omrane</t>
+  </si>
+  <si>
+    <t>NB(285/2026)</t>
   </si>
 </sst>
 </file>
@@ -3890,7 +3955,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3973,9 +4038,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4586,6 +4648,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>104785</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connecteur droit 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{922B400F-B408-4F54-AB5A-697C026C2D46}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="695335" y="21678900"/>
+          <a:ext cx="4648190" cy="238125"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -25699,7 +25816,7 @@
       <c r="H90" s="4" t="s">
         <v>1156</v>
       </c>
-      <c r="I90" s="29" t="s">
+      <c r="I90" s="20" t="s">
         <v>1157</v>
       </c>
     </row>
@@ -25729,7 +25846,7 @@
       <c r="H91" s="4" t="s">
         <v>1159</v>
       </c>
-      <c r="I91" s="29" t="s">
+      <c r="I91" s="20" t="s">
         <v>1160</v>
       </c>
     </row>
@@ -26146,4 +26263,2028 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E12532-A5D0-40AD-AD11-74DA11950253}">
+  <dimension ref="A1:K117"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="2.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+    <col min="9" max="9" width="32.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="25"/>
+      <c r="K2" s="6">
+        <f>SUMIF(F7:F364,"Elimination*",G7:G364)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="25"/>
+      <c r="K3" s="6">
+        <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="25"/>
+      <c r="K4" s="6">
+        <f>SUMIF(F7:F364,"Ve*",G7:G364)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="8">
+        <f>SUM(K2:K4)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>1</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="13">
+        <v>2026143453</v>
+      </c>
+      <c r="E7" s="15">
+        <v>46267</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G7" s="17">
+        <v>1</v>
+      </c>
+      <c r="H7" s="18"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <f t="shared" ref="A8:A71" si="0">+A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="13">
+        <v>2026143456</v>
+      </c>
+      <c r="E8" s="15">
+        <v>46267</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G8" s="17">
+        <v>1</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>1168</v>
+      </c>
+      <c r="J8" s="20"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="13">
+        <v>2026143457</v>
+      </c>
+      <c r="E9" s="15">
+        <v>46267</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G9" s="17">
+        <v>1</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>1165</v>
+      </c>
+      <c r="J9" s="20"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="13">
+        <v>2026143458</v>
+      </c>
+      <c r="E10" s="15">
+        <v>46267</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G10" s="17">
+        <v>1</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>1170</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J10" s="20"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D11" s="13">
+        <v>2026004070</v>
+      </c>
+      <c r="E11" s="15">
+        <v>46267</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G11" s="17">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>1173</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>1174</v>
+      </c>
+      <c r="J11" s="20"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="17">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="17">
+        <v>1</v>
+      </c>
+      <c r="H14" s="18"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17">
+        <v>1</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="17">
+        <v>1</v>
+      </c>
+      <c r="H16" s="18"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17">
+        <v>1</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="17">
+        <v>1</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="17">
+        <v>1</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="17">
+        <v>1</v>
+      </c>
+      <c r="H20" s="18"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="17">
+        <v>1</v>
+      </c>
+      <c r="H21" s="18"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17">
+        <v>1</v>
+      </c>
+      <c r="H22" s="18"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="17">
+        <v>1</v>
+      </c>
+      <c r="H23" s="18"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="17">
+        <v>1</v>
+      </c>
+      <c r="H24" s="18"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="17">
+        <v>1</v>
+      </c>
+      <c r="H26" s="18"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17">
+        <v>1</v>
+      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="12">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17">
+        <v>1</v>
+      </c>
+      <c r="H29" s="18"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="17">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="17">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="12">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="17">
+        <v>1</v>
+      </c>
+      <c r="H33" s="18"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="12">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="17">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="12">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="17">
+        <v>1</v>
+      </c>
+      <c r="H35" s="4"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="12">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="17">
+        <v>1</v>
+      </c>
+      <c r="H36" s="18"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="12">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="17">
+        <v>1</v>
+      </c>
+      <c r="H37" s="4"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="12">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="17">
+        <v>1</v>
+      </c>
+      <c r="H38" s="18"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="12">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="17">
+        <v>1</v>
+      </c>
+      <c r="H39" s="18"/>
+      <c r="I39" s="20"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="12">
+        <f>+A39+1</f>
+        <v>34</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="17">
+        <v>1</v>
+      </c>
+      <c r="H40" s="18"/>
+      <c r="I40" s="20"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="12">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="17">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="20"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="12">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="17">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4"/>
+      <c r="I42" s="20"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="12">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="17">
+        <v>1</v>
+      </c>
+      <c r="H43" s="18"/>
+      <c r="I43" s="20"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="12">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="17">
+        <v>1</v>
+      </c>
+      <c r="H44" s="18"/>
+      <c r="I44" s="20"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="12">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="17">
+        <v>1</v>
+      </c>
+      <c r="H45" s="4"/>
+      <c r="I45" s="20"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="12">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="17">
+        <v>1</v>
+      </c>
+      <c r="H46" s="18"/>
+      <c r="I46" s="20"/>
+    </row>
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="12">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="17">
+        <v>1</v>
+      </c>
+      <c r="H47" s="18"/>
+      <c r="I47" s="20"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="12">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="17">
+        <v>1</v>
+      </c>
+      <c r="H48" s="4"/>
+      <c r="I48" s="20"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="12">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="17">
+        <v>1</v>
+      </c>
+      <c r="H49" s="4"/>
+      <c r="I49" s="20"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="12">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="17">
+        <v>1</v>
+      </c>
+      <c r="H50" s="4"/>
+      <c r="I50" s="20"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="12">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="17">
+        <v>1</v>
+      </c>
+      <c r="H51" s="4"/>
+      <c r="I51" s="20"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="12">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="17">
+        <v>1</v>
+      </c>
+      <c r="H52" s="4"/>
+      <c r="I52" s="20"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="12">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B53" s="15"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="17">
+        <v>1</v>
+      </c>
+      <c r="H53" s="4"/>
+      <c r="I53" s="20"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="12">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B54" s="15"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="17">
+        <v>1</v>
+      </c>
+      <c r="H54" s="4"/>
+      <c r="I54" s="20"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="12">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B55" s="15"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="17">
+        <v>1</v>
+      </c>
+      <c r="H55" s="4"/>
+      <c r="I55" s="20"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="12">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B56" s="15"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="17">
+        <v>1</v>
+      </c>
+      <c r="H56" s="4"/>
+      <c r="I56" s="20"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="12">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="17">
+        <v>1</v>
+      </c>
+      <c r="H57" s="4"/>
+      <c r="I57" s="20"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="12">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B58" s="15"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="17">
+        <v>1</v>
+      </c>
+      <c r="H58" s="4"/>
+      <c r="I58" s="20"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="12">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B59" s="15"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="17">
+        <v>1</v>
+      </c>
+      <c r="H59" s="4"/>
+      <c r="I59" s="20"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="12">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B60" s="15"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="17">
+        <v>1</v>
+      </c>
+      <c r="H60" s="4"/>
+      <c r="I60" s="20"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="12">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B61" s="15"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="17">
+        <v>1</v>
+      </c>
+      <c r="H61" s="4"/>
+      <c r="I61" s="20"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="12">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B62" s="15"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="17">
+        <v>1</v>
+      </c>
+      <c r="H62" s="4"/>
+      <c r="I62" s="20"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="12">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B63" s="15"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="17">
+        <v>1</v>
+      </c>
+      <c r="H63" s="4"/>
+      <c r="I63" s="20"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="12">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B64" s="15"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="15"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="17">
+        <v>1</v>
+      </c>
+      <c r="H64" s="4"/>
+      <c r="I64" s="20"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="12">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B65" s="15"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="17">
+        <v>1</v>
+      </c>
+      <c r="H65" s="4"/>
+      <c r="I65" s="20"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="12">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="17">
+        <v>1</v>
+      </c>
+      <c r="H66" s="4"/>
+      <c r="I66" s="20"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="12">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B67" s="15"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="15"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="17">
+        <v>1</v>
+      </c>
+      <c r="H67" s="4"/>
+      <c r="I67" s="20"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="12">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B68" s="15"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="17">
+        <v>1</v>
+      </c>
+      <c r="H68" s="4"/>
+      <c r="I68" s="20"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="12">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B69" s="15"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="17">
+        <v>1</v>
+      </c>
+      <c r="H69" s="4"/>
+      <c r="I69" s="20"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="12">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B70" s="15"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="17">
+        <v>1</v>
+      </c>
+      <c r="H70" s="4"/>
+      <c r="I70" s="20"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="12">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B71" s="15"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="17">
+        <v>1</v>
+      </c>
+      <c r="H71" s="4"/>
+      <c r="I71" s="20"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="12">
+        <f t="shared" ref="A72:A117" si="1">+A71+1</f>
+        <v>66</v>
+      </c>
+      <c r="B72" s="15"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="17">
+        <v>1</v>
+      </c>
+      <c r="H72" s="4"/>
+      <c r="I72" s="20"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="12">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="B73" s="15"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="17">
+        <v>1</v>
+      </c>
+      <c r="H73" s="4"/>
+      <c r="I73" s="20"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="12">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="B74" s="15"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="17">
+        <v>1</v>
+      </c>
+      <c r="H74" s="4"/>
+      <c r="I74" s="20"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="12">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B75" s="15"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="17">
+        <v>1</v>
+      </c>
+      <c r="H75" s="4"/>
+      <c r="I75" s="20"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="12">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="B76" s="15"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="17">
+        <v>1</v>
+      </c>
+      <c r="H76" s="4"/>
+      <c r="I76" s="20"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="12">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="B77" s="15"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="17">
+        <v>1</v>
+      </c>
+      <c r="H77" s="4"/>
+      <c r="I77" s="20"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="12">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="B78" s="15"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="17">
+        <v>1</v>
+      </c>
+      <c r="H78" s="4"/>
+      <c r="I78" s="20"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="12">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="B79" s="15"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="17">
+        <v>1</v>
+      </c>
+      <c r="H79" s="4"/>
+      <c r="I79" s="20"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="12">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="B80" s="15"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="17">
+        <v>1</v>
+      </c>
+      <c r="H80" s="4"/>
+      <c r="I80" s="20"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="12">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="B81" s="15"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="17">
+        <v>1</v>
+      </c>
+      <c r="H81" s="4"/>
+      <c r="I81" s="20"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="12">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="B82" s="15"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="17">
+        <v>1</v>
+      </c>
+      <c r="H82" s="4"/>
+      <c r="I82" s="20"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="12">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="B83" s="15"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="17">
+        <v>1</v>
+      </c>
+      <c r="H83" s="4"/>
+      <c r="I83" s="20"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="12">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="B84" s="15"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="15"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="17">
+        <v>1</v>
+      </c>
+      <c r="H84" s="4"/>
+      <c r="I84" s="20"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="12">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="B85" s="15"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="16"/>
+      <c r="G85" s="17">
+        <v>1</v>
+      </c>
+      <c r="H85" s="4"/>
+      <c r="I85" s="20"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="12">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="B86" s="15"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="16"/>
+      <c r="G86" s="17">
+        <v>1</v>
+      </c>
+      <c r="H86" s="4"/>
+      <c r="I86" s="20"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="12">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="B87" s="15"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="17">
+        <v>1</v>
+      </c>
+      <c r="H87" s="4"/>
+      <c r="I87" s="20"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="12">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="B88" s="15"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="17">
+        <v>1</v>
+      </c>
+      <c r="H88" s="4"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="12">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="B89" s="15"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="17">
+        <v>1</v>
+      </c>
+      <c r="H89" s="4"/>
+      <c r="I89" s="20"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="12">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="B90" s="15"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="16"/>
+      <c r="G90" s="17">
+        <v>1</v>
+      </c>
+      <c r="H90" s="4"/>
+      <c r="I90" s="20"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="12">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="B91" s="15"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="17">
+        <v>1</v>
+      </c>
+      <c r="H91" s="4"/>
+      <c r="I91" s="20"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="12">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="B92" s="15"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="17">
+        <v>1</v>
+      </c>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="12">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="B93" s="15"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="17">
+        <v>1</v>
+      </c>
+      <c r="H93" s="4"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="12">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="B94" s="15"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="15"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="17">
+        <v>1</v>
+      </c>
+      <c r="H94" s="4"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="12">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="B95" s="15"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="15"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="17">
+        <v>1</v>
+      </c>
+      <c r="H95" s="4"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="12">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="B96" s="15"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="16"/>
+      <c r="G96" s="17">
+        <v>1</v>
+      </c>
+      <c r="H96" s="4"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="12">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="B97" s="15"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="16"/>
+      <c r="G97" s="17">
+        <v>1</v>
+      </c>
+      <c r="H97" s="4"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="12">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="B98" s="15"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="16"/>
+      <c r="G98" s="17">
+        <v>1</v>
+      </c>
+      <c r="H98" s="4"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="12">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="B99" s="15"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="15"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="17">
+        <v>1</v>
+      </c>
+      <c r="H99" s="4"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="12">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="B100" s="15"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="15"/>
+      <c r="F100" s="16"/>
+      <c r="G100" s="17">
+        <v>1</v>
+      </c>
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="12">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="B101" s="15"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="16"/>
+      <c r="G101" s="17">
+        <v>1</v>
+      </c>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="12">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="B102" s="15"/>
+      <c r="C102" s="13"/>
+      <c r="D102" s="14"/>
+      <c r="E102" s="15"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="17">
+        <v>1</v>
+      </c>
+      <c r="H102" s="4"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="12">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="B103" s="15"/>
+      <c r="C103" s="13"/>
+      <c r="D103" s="14"/>
+      <c r="E103" s="15"/>
+      <c r="F103" s="16"/>
+      <c r="G103" s="17">
+        <v>1</v>
+      </c>
+      <c r="H103" s="4"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="12">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="B104" s="15"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="22"/>
+      <c r="E104" s="15"/>
+      <c r="F104" s="16"/>
+      <c r="G104" s="17">
+        <v>1</v>
+      </c>
+      <c r="H104" s="4"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="12">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="B105" s="15"/>
+      <c r="C105" s="13"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="15"/>
+      <c r="F105" s="16"/>
+      <c r="G105" s="17">
+        <v>1</v>
+      </c>
+      <c r="H105" s="4"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="12">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="B106" s="15"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="15"/>
+      <c r="F106" s="16"/>
+      <c r="G106" s="17">
+        <v>1</v>
+      </c>
+      <c r="H106" s="4"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="12">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="B107" s="15"/>
+      <c r="C107" s="13"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="15"/>
+      <c r="F107" s="16"/>
+      <c r="G107" s="17">
+        <v>1</v>
+      </c>
+      <c r="H107" s="4"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="12">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="B108" s="15"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="14"/>
+      <c r="E108" s="15"/>
+      <c r="F108" s="16"/>
+      <c r="G108" s="17">
+        <v>1</v>
+      </c>
+      <c r="H108" s="4"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="12">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="B109" s="15"/>
+      <c r="C109" s="13"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="15"/>
+      <c r="F109" s="16"/>
+      <c r="G109" s="17">
+        <v>1</v>
+      </c>
+      <c r="H109" s="4"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="12">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="B110" s="15"/>
+      <c r="C110" s="13"/>
+      <c r="D110" s="14"/>
+      <c r="E110" s="15"/>
+      <c r="F110" s="16"/>
+      <c r="G110" s="17">
+        <v>1</v>
+      </c>
+      <c r="H110" s="4"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="12">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="B111" s="15"/>
+      <c r="C111" s="13"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="15"/>
+      <c r="F111" s="16"/>
+      <c r="G111" s="17">
+        <v>1</v>
+      </c>
+      <c r="H111" s="4"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="12">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="B112" s="15"/>
+      <c r="C112" s="13"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="15"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="17">
+        <v>1</v>
+      </c>
+      <c r="H112" s="4"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="12">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="B113" s="15"/>
+      <c r="C113" s="13"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="15"/>
+      <c r="F113" s="16"/>
+      <c r="G113" s="17">
+        <v>1</v>
+      </c>
+      <c r="H113" s="4"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="12">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="B114" s="15"/>
+      <c r="C114" s="13"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="15"/>
+      <c r="F114" s="16"/>
+      <c r="G114" s="17">
+        <v>1</v>
+      </c>
+      <c r="H114" s="4"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="12">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="B115" s="15"/>
+      <c r="C115" s="13"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="15"/>
+      <c r="F115" s="16"/>
+      <c r="G115" s="17">
+        <v>1</v>
+      </c>
+      <c r="H115" s="4"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="12">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="B116" s="15"/>
+      <c r="C116" s="13"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="15"/>
+      <c r="F116" s="16"/>
+      <c r="G116" s="17">
+        <v>1</v>
+      </c>
+      <c r="H116" s="4"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="12">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="B117" s="15"/>
+      <c r="C117" s="13"/>
+      <c r="D117" s="14"/>
+      <c r="E117" s="15"/>
+      <c r="F117" s="16"/>
+      <c r="G117" s="17">
+        <v>1</v>
+      </c>
+      <c r="H117" s="4"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:I11">
+    <sortCondition ref="C7:C11"/>
+    <sortCondition ref="D7:D11"/>
+  </sortState>
+  <mergeCells count="9">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="I4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283472" right="0.45" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2530064F-CE52-4801-872F-D1010C321307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1E0150-4209-4CEA-A080-32C4E9641A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2367" uniqueCount="1176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2372" uniqueCount="1178">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -3791,6 +3791,12 @@
   </si>
   <si>
     <t>NB(285/2026)</t>
+  </si>
+  <si>
+    <t>Maizi samira</t>
+  </si>
+  <si>
+    <t>cite 720 bt 15 n32</t>
   </si>
 </sst>
 </file>
@@ -26338,7 +26344,7 @@
       <c r="J3" s="25"/>
       <c r="K3" s="6">
         <f>SUMIF(F7:F364,"NB*",G7:G364)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -26378,7 +26384,7 @@
       <c r="J5" s="25"/>
       <c r="K5" s="8">
         <f>SUM(K2:K4)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -26570,16 +26576,30 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="16"/>
+      <c r="B12" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="13">
+        <v>2026143459</v>
+      </c>
+      <c r="E12" s="15">
+        <v>46267</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>791</v>
+      </c>
       <c r="G12" s="17">
         <v>1</v>
       </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="20"/>
+      <c r="H12" s="4" t="s">
+        <v>1176</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>1177</v>
+      </c>
       <c r="J12" s="20"/>
       <c r="K12" s="4"/>
     </row>

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1E0150-4209-4CEA-A080-32C4E9641A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08AEDDA0-1C8D-46C1-A227-3CA0EB943463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Janvier 2026 " sheetId="2" r:id="rId1"/>
@@ -21558,7 +21558,6 @@
       <c r="H28" s="4" t="s">
         <v>876</v>
       </c>
-      <c r="I28" s="20"/>
       <c r="J28" s="20"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21587,7 +21586,6 @@
       <c r="H29" s="18" t="s">
         <v>865</v>
       </c>
-      <c r="I29" s="20"/>
       <c r="J29" s="20"/>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21616,7 +21614,6 @@
       <c r="H30" s="18" t="s">
         <v>872</v>
       </c>
-      <c r="I30" s="20"/>
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Berrouaghia/Suivie pose Compteur 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08AEDDA0-1C8D-46C1-A227-3CA0EB943463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6D4570-63FA-4F13-8710-9EF8A344C44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21569,10 +21569,10 @@
         <v>19</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>284</v>
+        <v>18</v>
       </c>
       <c r="D29" s="13">
-        <v>2026003649</v>
+        <v>2026143455</v>
       </c>
       <c r="E29" s="15">
         <v>46226</v>
